--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="207">
   <si>
     <t xml:space="preserve">Acqlerate</t>
   </si>
@@ -496,7 +496,7 @@
     <t xml:space="preserve">Labor</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per person. Max Hrs = prorated standard capacity for that month. OT Hrs grays out for Exempt people — they don't earn OT.</t>
+    <t xml:space="preserve">One row per person. Max Hrs = prorated standard capacity for that month. OT Hrs grays out for Exempt people (don't earn OT) and Subs (typically T&amp;M, not tracked here).</t>
   </si>
   <si>
     <t xml:space="preserve">Employee
@@ -589,21 +589,42 @@
     <t xml:space="preserve">Sub</t>
   </si>
   <si>
-    <t xml:space="preserve">Monthly Rollup (auto) — Fringe &amp; OH applied here, once</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Unburdened
+    <t xml:space="preserve">Monthly Rollup (auto) — Prime gets Fringe/OH, Sub passes through at cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime
+Unburdened $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime
+Fringe $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime
+OH $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Fully
+Burdened $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub $
+(no burden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total
 Labor $</t>
   </si>
   <si>
-    <t xml:space="preserve">Fringe $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OH $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fully Burdened
-Labor $</t>
+    <t xml:space="preserve">G&amp;A $ on Labor
+(informational)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Labor $
++ G&amp;A (info)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard pulls Total Labor $ (col H) — G&amp;A is applied once, at Dashboard's Subtotal level, not twice.</t>
   </si>
   <si>
     <t xml:space="preserve">ODCs</t>
@@ -680,7 +701,7 @@
     <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,13 +793,21 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF085041"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,18 +822,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="FF0F6E56"/>
+        <bgColor rgb="FF01696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFAEEDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5EE"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF085041"/>
+        <bgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -818,6 +859,21 @@
       </left>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF0F172A"/>
       </right>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
@@ -853,7 +909,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="66">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -934,7 +990,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -954,8 +1014,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1030,8 +1098,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1042,7 +1122,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1054,11 +1142,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1071,7 +1183,28 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD85A30"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF3B6D11"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF888780"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1083,6 +1216,33 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF854F0B"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF085041"/>
+        <sz val="11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFAEEDA"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1100,15 +1260,15 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF3B6D11"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF01696F"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF888780"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFAEEDA"/>
+      <rgbColor rgb="FFE1F5EE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1119,10 +1279,10 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0F6E56"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -1133,15 +1293,15 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFEF9F27"/>
+      <rgbColor rgb="FFD85A30"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FFA6A6A6"/>
-      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF085041"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF0F172A"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF854F0B"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
@@ -1672,6 +1832,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFBFBFBF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B67"/>
@@ -2009,6 +2170,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
@@ -2128,6 +2290,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E17"/>
@@ -2281,10 +2444,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="21" t="n">
         <f aca="false">IFERROR(INDEX(E4:E13,COUNT(D4:D13)),0)</f>
         <v>2400000</v>
       </c>
@@ -2312,6 +2475,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF01696F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O34"/>
@@ -2341,145 +2505,149 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="21"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="9" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="9" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22" t="n">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23" t="n">
         <v>46023</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22" t="n">
+      <c r="B6" s="22"/>
+      <c r="C6" s="23" t="n">
         <v>46387</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="23" t="n">
+      <c r="B7" s="22"/>
+      <c r="C7" s="24" t="n">
         <f aca="false">DATEDIF(C5,C6,"m")+1</f>
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="24" t="n">
+      <c r="B8" s="22"/>
+      <c r="C8" s="25" t="n">
         <f aca="false">FundingMods!$B$15</f>
         <v>2400000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="20" t="n">
+      <c r="B9" s="22"/>
+      <c r="C9" s="26" t="n">
         <f aca="false">C8/C7</f>
         <v>200000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="23" t="n">
+      <c r="B12" s="22"/>
+      <c r="C12" s="24" t="n">
         <f aca="false">COUNT(D21:D32)</f>
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="20" t="n">
+      <c r="B13" s="22"/>
+      <c r="C13" s="26" t="n">
         <f aca="false">IF(C12=0,0,INDEX(L21:L32,C12))</f>
-        <v>156884.182120615</v>
+        <v>150000.704344615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="20" t="n">
+      <c r="B14" s="22"/>
+      <c r="C14" s="26" t="n">
         <f aca="false">C8-C13</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="21"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="10" t="n">
         <f aca="false">IFERROR(C13/C8,0)</f>
-        <v>0.0653684092169231</v>
+        <v>0.0625002934769231</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20" t="n">
+      <c r="B16" s="22"/>
+      <c r="C16" s="26" t="n">
         <f aca="true">IFERROR(AVERAGE(OFFSET(K21,MAX(C12-3,0),0,MIN(C12,3),1)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="23" t="str">
+      <c r="B17" s="22"/>
+      <c r="C17" s="24" t="str">
         <f aca="false">IFERROR(C14/C16,"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="23" t="str">
-        <f aca="false">IF(C12=0,"NO DATA YET",IF(C15&gt;(C12/C7)*1.1,"AT RISK — OVERRUNNING",IF(C15&lt;(C12/C7)*0.7,"AT RISK — UNDERRUNNING (option year risk)","ON TRACK")))</f>
-        <v>AT RISK — UNDERRUNNING (option year risk)</v>
-      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="28" t="str">
+        <f aca="false">IF(C12=0,"NO DATA YET",IF(C15&gt;(C12/C7)*1.1,"AT RISK — OVERRUNNING",IF(C15&lt;(C12/C7)*0.7,"AT RISK — UNDERRUNNING","ON TRACK")))</f>
+        <v>AT RISK — UNDERRUNNING</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
@@ -2529,10 +2697,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="30" t="n">
         <f aca="false">EDATE($C$5,A21-1)</f>
         <v>46023</v>
       </c>
@@ -2540,60 +2708,60 @@
         <f aca="false">$C$9*A21</f>
         <v>200000</v>
       </c>
-      <c r="D21" s="28" t="n">
-        <f aca="false">Labor!F25</f>
-        <v>38790.2116947115</v>
-      </c>
-      <c r="E21" s="28" t="n">
+      <c r="D21" s="31" t="n">
+        <f aca="false">Labor!H25</f>
+        <v>33046.3216947115</v>
+      </c>
+      <c r="E21" s="31" t="n">
         <f aca="false">IF(D21="","",ODCs!C27)</f>
         <v>14200</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="31" t="n">
         <f aca="false">IF(D21="","",Travel!C27)</f>
         <v>1090</v>
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">IF(D21="","",D21+E21+F21)</f>
-        <v>54080.2116947115</v>
-      </c>
-      <c r="H21" s="28" t="n">
+        <v>48336.3216947115</v>
+      </c>
+      <c r="H21" s="31" t="n">
         <f aca="false">IF(G21="","",G21*Rates!$B$5)</f>
-        <v>6489.62540336539</v>
+        <v>5800.35860336539</v>
       </c>
       <c r="I21" s="15" t="n">
         <f aca="false">IF(G21="","",G21+H21)</f>
-        <v>60569.8370980769</v>
-      </c>
-      <c r="J21" s="28" t="n">
+        <v>54136.6802980769</v>
+      </c>
+      <c r="J21" s="31" t="n">
         <f aca="false">IF(I21="","",I21*Rates!$B$11)</f>
-        <v>4239.88859686539</v>
+        <v>3789.56762086539</v>
       </c>
       <c r="K21" s="15" t="n">
         <f aca="false">IF(I21="","",I21+J21)</f>
-        <v>64809.7256949423</v>
+        <v>57926.2479189423</v>
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K21)=0,"",SUM($K$21:K21))</f>
-        <v>64809.7256949423</v>
-      </c>
-      <c r="M21" s="29" t="n">
+        <v>57926.2479189423</v>
+      </c>
+      <c r="M21" s="32" t="n">
         <f aca="false">IF(OR(L21="",C21=""),"",L21-C21)</f>
-        <v>-135190.274305058</v>
-      </c>
-      <c r="N21" s="30" t="n">
+        <v>-142073.752081058</v>
+      </c>
+      <c r="N21" s="33" t="n">
         <f aca="false">IF(OR(L21="",C21="",C21=0),"",M21/C21)</f>
-        <v>-0.675951371525288</v>
+        <v>-0.710368760405289</v>
       </c>
       <c r="O21" s="15" t="n">
         <f aca="false">IF(L21="","",$C$8-L21)</f>
-        <v>2335190.27430506</v>
+        <v>2342073.75208106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="n">
+      <c r="A22" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="35" t="n">
         <f aca="false">EDATE($C$5,A22-1)</f>
         <v>46054</v>
       </c>
@@ -2601,15 +2769,15 @@
         <f aca="false">$C$9*A22</f>
         <v>400000</v>
       </c>
-      <c r="D22" s="33" t="n">
-        <f aca="false">Labor!F26</f>
+      <c r="D22" s="36" t="n">
+        <f aca="false">Labor!H26</f>
         <v>28771.3216947115</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="36" t="n">
         <f aca="false">IF(D22="","",ODCs!C28)</f>
         <v>3100</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="36" t="n">
         <f aca="false">IF(D22="","",Travel!C28)</f>
         <v>0</v>
       </c>
@@ -2617,7 +2785,7 @@
         <f aca="false">IF(D22="","",D22+E22+F22)</f>
         <v>31871.3216947115</v>
       </c>
-      <c r="H22" s="33" t="n">
+      <c r="H22" s="36" t="n">
         <f aca="false">IF(G22="","",G22*Rates!$B$5)</f>
         <v>3824.55860336539</v>
       </c>
@@ -2625,7 +2793,7 @@
         <f aca="false">IF(G22="","",G22+H22)</f>
         <v>35695.8802980769</v>
       </c>
-      <c r="J22" s="33" t="n">
+      <c r="J22" s="36" t="n">
         <f aca="false">IF(I22="","",I22*Rates!$B$11)</f>
         <v>2498.71162086539</v>
       </c>
@@ -2635,26 +2803,26 @@
       </c>
       <c r="L22" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K22)=0,"",SUM($K$21:K22))</f>
-        <v>103004.317613885</v>
-      </c>
-      <c r="M22" s="34" t="n">
+        <v>96120.8398378846</v>
+      </c>
+      <c r="M22" s="37" t="n">
         <f aca="false">IF(OR(L22="",C22=""),"",L22-C22)</f>
-        <v>-296995.682386115</v>
-      </c>
-      <c r="N22" s="35" t="n">
+        <v>-303879.160162115</v>
+      </c>
+      <c r="N22" s="38" t="n">
         <f aca="false">IF(OR(L22="",C22="",C22=0),"",M22/C22)</f>
-        <v>-0.742489205965288</v>
+        <v>-0.759697900405288</v>
       </c>
       <c r="O22" s="19" t="n">
         <f aca="false">IF(L22="","",$C$8-L22)</f>
-        <v>2296995.68238612</v>
+        <v>2303879.16016212</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="n">
+      <c r="A23" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="30" t="n">
         <f aca="false">EDATE($C$5,A23-1)</f>
         <v>46082</v>
       </c>
@@ -2662,15 +2830,15 @@
         <f aca="false">$C$9*A23</f>
         <v>600000</v>
       </c>
-      <c r="D23" s="28" t="n">
-        <f aca="false">Labor!F27</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="28" t="n">
+      <c r="D23" s="31" t="n">
+        <f aca="false">Labor!H27</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="31" t="n">
         <f aca="false">IF(D23="","",ODCs!C29)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="31" t="n">
         <f aca="false">IF(D23="","",Travel!C29)</f>
         <v>1150</v>
       </c>
@@ -2678,7 +2846,7 @@
         <f aca="false">IF(D23="","",D23+E23+F23)</f>
         <v>1150</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="31" t="n">
         <f aca="false">IF(G23="","",G23*Rates!$B$5)</f>
         <v>138</v>
       </c>
@@ -2686,7 +2854,7 @@
         <f aca="false">IF(G23="","",G23+H23)</f>
         <v>1288</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="J23" s="31" t="n">
         <f aca="false">IF(I23="","",I23*Rates!$B$11)</f>
         <v>90.16</v>
       </c>
@@ -2696,26 +2864,26 @@
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K23)=0,"",SUM($K$21:K23))</f>
-        <v>104382.477613885</v>
-      </c>
-      <c r="M23" s="29" t="n">
+        <v>97498.9998378846</v>
+      </c>
+      <c r="M23" s="32" t="n">
         <f aca="false">IF(OR(L23="",C23=""),"",L23-C23)</f>
-        <v>-495617.522386115</v>
-      </c>
-      <c r="N23" s="30" t="n">
+        <v>-502501.000162115</v>
+      </c>
+      <c r="N23" s="33" t="n">
         <f aca="false">IF(OR(L23="",C23="",C23=0),"",M23/C23)</f>
-        <v>-0.826029203976859</v>
+        <v>-0.837501666936859</v>
       </c>
       <c r="O23" s="15" t="n">
         <f aca="false">IF(L23="","",$C$8-L23)</f>
-        <v>2295617.52238612</v>
+        <v>2302501.00016212</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="31" t="n">
+      <c r="A24" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="35" t="n">
         <f aca="false">EDATE($C$5,A24-1)</f>
         <v>46113</v>
       </c>
@@ -2723,15 +2891,15 @@
         <f aca="false">$C$9*A24</f>
         <v>800000</v>
       </c>
-      <c r="D24" s="33" t="n">
-        <f aca="false">Labor!F28</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="33" t="n">
+      <c r="D24" s="36" t="n">
+        <f aca="false">Labor!H28</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="36" t="n">
         <f aca="false">IF(D24="","",ODCs!C30)</f>
         <v>8600</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="36" t="n">
         <f aca="false">IF(D24="","",Travel!C30)</f>
         <v>0</v>
       </c>
@@ -2739,7 +2907,7 @@
         <f aca="false">IF(D24="","",D24+E24+F24)</f>
         <v>8600</v>
       </c>
-      <c r="H24" s="33" t="n">
+      <c r="H24" s="36" t="n">
         <f aca="false">IF(G24="","",G24*Rates!$B$5)</f>
         <v>1032</v>
       </c>
@@ -2747,7 +2915,7 @@
         <f aca="false">IF(G24="","",G24+H24)</f>
         <v>9632</v>
       </c>
-      <c r="J24" s="33" t="n">
+      <c r="J24" s="36" t="n">
         <f aca="false">IF(I24="","",I24*Rates!$B$11)</f>
         <v>674.24</v>
       </c>
@@ -2757,26 +2925,26 @@
       </c>
       <c r="L24" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K24)=0,"",SUM($K$21:K24))</f>
-        <v>114688.717613885</v>
-      </c>
-      <c r="M24" s="34" t="n">
+        <v>107805.239837885</v>
+      </c>
+      <c r="M24" s="37" t="n">
         <f aca="false">IF(OR(L24="",C24=""),"",L24-C24)</f>
-        <v>-685311.282386115</v>
-      </c>
-      <c r="N24" s="35" t="n">
+        <v>-692194.760162115</v>
+      </c>
+      <c r="N24" s="38" t="n">
         <f aca="false">IF(OR(L24="",C24="",C24=0),"",M24/C24)</f>
-        <v>-0.856639102982644</v>
+        <v>-0.865243450202644</v>
       </c>
       <c r="O24" s="19" t="n">
         <f aca="false">IF(L24="","",$C$8-L24)</f>
-        <v>2285311.28238612</v>
+        <v>2292194.76016212</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="30" t="n">
         <f aca="false">EDATE($C$5,A25-1)</f>
         <v>46143</v>
       </c>
@@ -2784,15 +2952,15 @@
         <f aca="false">$C$9*A25</f>
         <v>1000000</v>
       </c>
-      <c r="D25" s="28" t="n">
-        <f aca="false">Labor!F29</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="28" t="n">
+      <c r="D25" s="31" t="n">
+        <f aca="false">Labor!H29</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="31" t="n">
         <f aca="false">IF(D25="","",ODCs!C31)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="28" t="n">
+      <c r="F25" s="31" t="n">
         <f aca="false">IF(D25="","",Travel!C31)</f>
         <v>0</v>
       </c>
@@ -2800,7 +2968,7 @@
         <f aca="false">IF(D25="","",D25+E25+F25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="31" t="n">
         <f aca="false">IF(G25="","",G25*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -2808,7 +2976,7 @@
         <f aca="false">IF(G25="","",G25+H25)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="28" t="n">
+      <c r="J25" s="31" t="n">
         <f aca="false">IF(I25="","",I25*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -2818,26 +2986,26 @@
       </c>
       <c r="L25" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K25)=0,"",SUM($K$21:K25))</f>
-        <v>114688.717613885</v>
-      </c>
-      <c r="M25" s="29" t="n">
+        <v>107805.239837885</v>
+      </c>
+      <c r="M25" s="32" t="n">
         <f aca="false">IF(OR(L25="",C25=""),"",L25-C25)</f>
-        <v>-885311.282386115</v>
-      </c>
-      <c r="N25" s="30" t="n">
+        <v>-892194.760162115</v>
+      </c>
+      <c r="N25" s="33" t="n">
         <f aca="false">IF(OR(L25="",C25="",C25=0),"",M25/C25)</f>
-        <v>-0.885311282386116</v>
+        <v>-0.892194760162115</v>
       </c>
       <c r="O25" s="15" t="n">
         <f aca="false">IF(L25="","",$C$8-L25)</f>
-        <v>2285311.28238612</v>
+        <v>2292194.76016212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31" t="n">
+      <c r="A26" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="35" t="n">
         <f aca="false">EDATE($C$5,A26-1)</f>
         <v>46174</v>
       </c>
@@ -2845,15 +3013,15 @@
         <f aca="false">$C$9*A26</f>
         <v>1200000</v>
       </c>
-      <c r="D26" s="33" t="n">
-        <f aca="false">Labor!F30</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="33" t="n">
+      <c r="D26" s="36" t="n">
+        <f aca="false">Labor!H30</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="36" t="n">
         <f aca="false">IF(D26="","",ODCs!C32)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="36" t="n">
         <f aca="false">IF(D26="","",Travel!C32)</f>
         <v>0</v>
       </c>
@@ -2861,7 +3029,7 @@
         <f aca="false">IF(D26="","",D26+E26+F26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="33" t="n">
+      <c r="H26" s="36" t="n">
         <f aca="false">IF(G26="","",G26*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -2869,7 +3037,7 @@
         <f aca="false">IF(G26="","",G26+H26)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="33" t="n">
+      <c r="J26" s="36" t="n">
         <f aca="false">IF(I26="","",I26*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -2879,26 +3047,26 @@
       </c>
       <c r="L26" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K26)=0,"",SUM($K$21:K26))</f>
-        <v>114688.717613885</v>
-      </c>
-      <c r="M26" s="34" t="n">
+        <v>107805.239837885</v>
+      </c>
+      <c r="M26" s="37" t="n">
         <f aca="false">IF(OR(L26="",C26=""),"",L26-C26)</f>
-        <v>-1085311.28238612</v>
-      </c>
-      <c r="N26" s="35" t="n">
+        <v>-1092194.76016212</v>
+      </c>
+      <c r="N26" s="38" t="n">
         <f aca="false">IF(OR(L26="",C26="",C26=0),"",M26/C26)</f>
-        <v>-0.904426068655096</v>
+        <v>-0.910162300135096</v>
       </c>
       <c r="O26" s="19" t="n">
         <f aca="false">IF(L26="","",$C$8-L26)</f>
-        <v>2285311.28238612</v>
+        <v>2292194.76016212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="30" t="n">
         <f aca="false">EDATE($C$5,A27-1)</f>
         <v>46204</v>
       </c>
@@ -2906,15 +3074,15 @@
         <f aca="false">$C$9*A27</f>
         <v>1400000</v>
       </c>
-      <c r="D27" s="28" t="n">
-        <f aca="false">Labor!F31</f>
+      <c r="D27" s="31" t="n">
+        <f aca="false">Labor!H31</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="31" t="n">
         <f aca="false">IF(D27="","",ODCs!C33)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="F27" s="31" t="n">
         <f aca="false">IF(D27="","",Travel!C33)</f>
         <v>0</v>
       </c>
@@ -2922,7 +3090,7 @@
         <f aca="false">IF(D27="","",D27+E27+F27)</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="31" t="n">
         <f aca="false">IF(G27="","",G27*Rates!$B$5)</f>
         <v>1086.49038461538</v>
       </c>
@@ -2930,7 +3098,7 @@
         <f aca="false">IF(G27="","",G27+H27)</f>
         <v>10140.5769230769</v>
       </c>
-      <c r="J27" s="28" t="n">
+      <c r="J27" s="31" t="n">
         <f aca="false">IF(I27="","",I27*Rates!$B$11)</f>
         <v>709.840384615385</v>
       </c>
@@ -2940,26 +3108,26 @@
       </c>
       <c r="L27" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K27)=0,"",SUM($K$21:K27))</f>
-        <v>125539.134921577</v>
-      </c>
-      <c r="M27" s="29" t="n">
+        <v>118655.657145577</v>
+      </c>
+      <c r="M27" s="32" t="n">
         <f aca="false">IF(OR(L27="",C27=""),"",L27-C27)</f>
-        <v>-1274460.86507842</v>
-      </c>
-      <c r="N27" s="30" t="n">
+        <v>-1281344.34285442</v>
+      </c>
+      <c r="N27" s="33" t="n">
         <f aca="false">IF(OR(L27="",C27="",C27=0),"",M27/C27)</f>
-        <v>-0.910329189341731</v>
+        <v>-0.915245959181731</v>
       </c>
       <c r="O27" s="15" t="n">
         <f aca="false">IF(L27="","",$C$8-L27)</f>
-        <v>2274460.86507842</v>
+        <v>2281344.34285442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="35" t="n">
         <f aca="false">EDATE($C$5,A28-1)</f>
         <v>46235</v>
       </c>
@@ -2967,15 +3135,15 @@
         <f aca="false">$C$9*A28</f>
         <v>1600000</v>
       </c>
-      <c r="D28" s="33" t="n">
-        <f aca="false">Labor!F32</f>
+      <c r="D28" s="36" t="n">
+        <f aca="false">Labor!H32</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="36" t="n">
         <f aca="false">IF(D28="","",ODCs!C34)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="33" t="n">
+      <c r="F28" s="36" t="n">
         <f aca="false">IF(D28="","",Travel!C34)</f>
         <v>0</v>
       </c>
@@ -2983,7 +3151,7 @@
         <f aca="false">IF(D28="","",D28+E28+F28)</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="H28" s="33" t="n">
+      <c r="H28" s="36" t="n">
         <f aca="false">IF(G28="","",G28*Rates!$B$5)</f>
         <v>3138.68963942308</v>
       </c>
@@ -2991,7 +3159,7 @@
         <f aca="false">IF(G28="","",G28+H28)</f>
         <v>29294.4366346154</v>
       </c>
-      <c r="J28" s="33" t="n">
+      <c r="J28" s="36" t="n">
         <f aca="false">IF(I28="","",I28*Rates!$B$11)</f>
         <v>2050.61056442308</v>
       </c>
@@ -3001,26 +3169,26 @@
       </c>
       <c r="L28" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K28)=0,"",SUM($K$21:K28))</f>
-        <v>156884.182120615</v>
-      </c>
-      <c r="M28" s="34" t="n">
+        <v>150000.704344615</v>
+      </c>
+      <c r="M28" s="37" t="n">
         <f aca="false">IF(OR(L28="",C28=""),"",L28-C28)</f>
-        <v>-1443115.81787938</v>
-      </c>
-      <c r="N28" s="35" t="n">
+        <v>-1449999.29565538</v>
+      </c>
+      <c r="N28" s="38" t="n">
         <f aca="false">IF(OR(L28="",C28="",C28=0),"",M28/C28)</f>
-        <v>-0.901947386174615</v>
+        <v>-0.906249559784615</v>
       </c>
       <c r="O28" s="19" t="n">
         <f aca="false">IF(L28="","",$C$8-L28)</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="30" t="n">
         <f aca="false">EDATE($C$5,A29-1)</f>
         <v>46266</v>
       </c>
@@ -3028,15 +3196,15 @@
         <f aca="false">$C$9*A29</f>
         <v>1800000</v>
       </c>
-      <c r="D29" s="28" t="n">
-        <f aca="false">Labor!F33</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="28" t="n">
+      <c r="D29" s="31" t="n">
+        <f aca="false">Labor!H33</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="31" t="n">
         <f aca="false">IF(D29="","",ODCs!C35)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="F29" s="31" t="n">
         <f aca="false">IF(D29="","",Travel!C35)</f>
         <v>0</v>
       </c>
@@ -3044,7 +3212,7 @@
         <f aca="false">IF(D29="","",D29+E29+F29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="31" t="n">
         <f aca="false">IF(G29="","",G29*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3220,7 @@
         <f aca="false">IF(G29="","",G29+H29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="28" t="n">
+      <c r="J29" s="31" t="n">
         <f aca="false">IF(I29="","",I29*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -3062,26 +3230,26 @@
       </c>
       <c r="L29" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K29)=0,"",SUM($K$21:K29))</f>
-        <v>156884.182120615</v>
-      </c>
-      <c r="M29" s="29" t="n">
+        <v>150000.704344615</v>
+      </c>
+      <c r="M29" s="32" t="n">
         <f aca="false">IF(OR(L29="",C29=""),"",L29-C29)</f>
-        <v>-1643115.81787938</v>
-      </c>
-      <c r="N29" s="30" t="n">
+        <v>-1649999.29565538</v>
+      </c>
+      <c r="N29" s="33" t="n">
         <f aca="false">IF(OR(L29="",C29="",C29=0),"",M29/C29)</f>
-        <v>-0.912842121044103</v>
+        <v>-0.916666275364103</v>
       </c>
       <c r="O29" s="15" t="n">
         <f aca="false">IF(L29="","",$C$8-L29)</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="32" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">EDATE($C$5,A30-1)</f>
         <v>46296</v>
       </c>
@@ -3089,15 +3257,15 @@
         <f aca="false">$C$9*A30</f>
         <v>2000000</v>
       </c>
-      <c r="D30" s="33" t="n">
-        <f aca="false">Labor!F34</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="33" t="n">
+      <c r="D30" s="36" t="n">
+        <f aca="false">Labor!H34</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="36" t="n">
         <f aca="false">IF(D30="","",ODCs!C36)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="33" t="n">
+      <c r="F30" s="36" t="n">
         <f aca="false">IF(D30="","",Travel!C36)</f>
         <v>0</v>
       </c>
@@ -3105,7 +3273,7 @@
         <f aca="false">IF(D30="","",D30+E30+F30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="33" t="n">
+      <c r="H30" s="36" t="n">
         <f aca="false">IF(G30="","",G30*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -3113,7 +3281,7 @@
         <f aca="false">IF(G30="","",G30+H30)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="33" t="n">
+      <c r="J30" s="36" t="n">
         <f aca="false">IF(I30="","",I30*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -3123,26 +3291,26 @@
       </c>
       <c r="L30" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K30)=0,"",SUM($K$21:K30))</f>
-        <v>156884.182120615</v>
-      </c>
-      <c r="M30" s="34" t="n">
+        <v>150000.704344615</v>
+      </c>
+      <c r="M30" s="37" t="n">
         <f aca="false">IF(OR(L30="",C30=""),"",L30-C30)</f>
-        <v>-1843115.81787938</v>
-      </c>
-      <c r="N30" s="35" t="n">
+        <v>-1849999.29565538</v>
+      </c>
+      <c r="N30" s="38" t="n">
         <f aca="false">IF(OR(L30="",C30="",C30=0),"",M30/C30)</f>
-        <v>-0.921557908939692</v>
+        <v>-0.924999647827692</v>
       </c>
       <c r="O30" s="19" t="n">
         <f aca="false">IF(L30="","",$C$8-L30)</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="30" t="n">
         <f aca="false">EDATE($C$5,A31-1)</f>
         <v>46327</v>
       </c>
@@ -3150,15 +3318,15 @@
         <f aca="false">$C$9*A31</f>
         <v>2200000</v>
       </c>
-      <c r="D31" s="28" t="n">
-        <f aca="false">Labor!F35</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="28" t="n">
+      <c r="D31" s="31" t="n">
+        <f aca="false">Labor!H35</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="31" t="n">
         <f aca="false">IF(D31="","",ODCs!C37)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="28" t="n">
+      <c r="F31" s="31" t="n">
         <f aca="false">IF(D31="","",Travel!C37)</f>
         <v>0</v>
       </c>
@@ -3166,7 +3334,7 @@
         <f aca="false">IF(D31="","",D31+E31+F31)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="31" t="n">
         <f aca="false">IF(G31="","",G31*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -3174,7 +3342,7 @@
         <f aca="false">IF(G31="","",G31+H31)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J31" s="31" t="n">
         <f aca="false">IF(I31="","",I31*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -3184,26 +3352,26 @@
       </c>
       <c r="L31" s="15" t="n">
         <f aca="false">IF(SUM($K$21:K31)=0,"",SUM($K$21:K31))</f>
-        <v>156884.182120615</v>
-      </c>
-      <c r="M31" s="29" t="n">
+        <v>150000.704344615</v>
+      </c>
+      <c r="M31" s="32" t="n">
         <f aca="false">IF(OR(L31="",C31=""),"",L31-C31)</f>
-        <v>-2043115.81787938</v>
-      </c>
-      <c r="N31" s="30" t="n">
+        <v>-2049999.29565538</v>
+      </c>
+      <c r="N31" s="33" t="n">
         <f aca="false">IF(OR(L31="",C31="",C31=0),"",M31/C31)</f>
-        <v>-0.928689008126993</v>
+        <v>-0.931817861661539</v>
       </c>
       <c r="O31" s="15" t="n">
         <f aca="false">IF(L31="","",$C$8-L31)</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="35" t="n">
         <f aca="false">EDATE($C$5,A32-1)</f>
         <v>46357</v>
       </c>
@@ -3211,15 +3379,15 @@
         <f aca="false">$C$9*A32</f>
         <v>2400000</v>
       </c>
-      <c r="D32" s="33" t="n">
-        <f aca="false">Labor!F36</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="33" t="n">
+      <c r="D32" s="36" t="n">
+        <f aca="false">Labor!H36</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="36" t="n">
         <f aca="false">IF(D32="","",ODCs!C38)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="33" t="n">
+      <c r="F32" s="36" t="n">
         <f aca="false">IF(D32="","",Travel!C38)</f>
         <v>0</v>
       </c>
@@ -3227,7 +3395,7 @@
         <f aca="false">IF(D32="","",D32+E32+F32)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="33" t="n">
+      <c r="H32" s="36" t="n">
         <f aca="false">IF(G32="","",G32*Rates!$B$5)</f>
         <v>0</v>
       </c>
@@ -3235,7 +3403,7 @@
         <f aca="false">IF(G32="","",G32+H32)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="33" t="n">
+      <c r="J32" s="36" t="n">
         <f aca="false">IF(I32="","",I32*Rates!$B$11)</f>
         <v>0</v>
       </c>
@@ -3245,19 +3413,19 @@
       </c>
       <c r="L32" s="19" t="n">
         <f aca="false">IF(SUM($K$21:K32)=0,"",SUM($K$21:K32))</f>
-        <v>156884.182120615</v>
-      </c>
-      <c r="M32" s="34" t="n">
+        <v>150000.704344615</v>
+      </c>
+      <c r="M32" s="37" t="n">
         <f aca="false">IF(OR(L32="",C32=""),"",L32-C32)</f>
-        <v>-2243115.81787938</v>
-      </c>
-      <c r="N32" s="35" t="n">
+        <v>-2249999.29565538</v>
+      </c>
+      <c r="N32" s="38" t="n">
         <f aca="false">IF(OR(L32="",C32="",C32=0),"",M32/C32)</f>
-        <v>-0.934631590783077</v>
+        <v>-0.937499706523077</v>
       </c>
       <c r="O32" s="19" t="n">
         <f aca="false">IF(L32="","",$C$8-L32)</f>
-        <v>2243115.81787938</v>
+        <v>2249999.29565538</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3266,7 +3434,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
@@ -3281,7 +3449,19 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:G18"/>
   </mergeCells>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ISNUMBER(SEARCH("AT RISK",$C18))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>$C18="ON TRACK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>$C18="NO DATA YET"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3296,6 +3476,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P21"/>
@@ -3390,15 +3571,15 @@
       <c r="E5" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="F5" s="36"/>
+      <c r="F5" s="39"/>
       <c r="G5" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H5" s="37" t="n">
+      <c r="H5" s="40" t="n">
         <f aca="false">IF(A5="","",IF(D5="Exempt",IF(G5=0,"",E5/G5),F5))</f>
         <v>72.1153846153846</v>
       </c>
-      <c r="I5" s="26" t="str">
+      <c r="I5" s="29" t="str">
         <f aca="false">IF(A5="","",IF(D5="Non-Exempt",H5*1.5,"N/A"))</f>
         <v>N/A</v>
       </c>
@@ -3412,12 +3593,12 @@
       <c r="M5" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="38" t="n">
+      <c r="N5" s="41" t="n">
         <f aca="true">IF(A5="","",IFERROR(L5*MAX(0,DATEDIF(J5,IF(K5="",TODAY(),MIN(K5,TODAY())),"m")),0))</f>
         <v>8</v>
       </c>
-      <c r="O5" s="39"/>
-      <c r="P5" s="38" t="n">
+      <c r="O5" s="42"/>
+      <c r="P5" s="41" t="n">
         <f aca="false">IF(A5="","",M5+N5-O5)</f>
         <v>8</v>
       </c>
@@ -3438,15 +3619,15 @@
       <c r="E6" s="18" t="n">
         <v>165000</v>
       </c>
-      <c r="F6" s="40"/>
+      <c r="F6" s="43"/>
       <c r="G6" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H6" s="44" t="n">
         <f aca="false">IF(A6="","",IF(D6="Exempt",IF(G6=0,"",E6/G6),F6))</f>
         <v>79.3269230769231</v>
       </c>
-      <c r="I6" s="31" t="str">
+      <c r="I6" s="34" t="str">
         <f aca="false">IF(A6="","",IF(D6="Non-Exempt",H6*1.5,"N/A"))</f>
         <v>N/A</v>
       </c>
@@ -3460,12 +3641,12 @@
       <c r="M6" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="N6" s="42" t="n">
+      <c r="N6" s="45" t="n">
         <f aca="true">IF(A6="","",IFERROR(L6*MAX(0,DATEDIF(J6,IF(K6="",TODAY(),MIN(K6,TODAY())),"m")),0))</f>
         <v>56</v>
       </c>
-      <c r="O6" s="43"/>
-      <c r="P6" s="42" t="n">
+      <c r="O6" s="46"/>
+      <c r="P6" s="45" t="n">
         <f aca="false">IF(A6="","",M6+N6-O6)</f>
         <v>68</v>
       </c>
@@ -3484,17 +3665,17 @@
         <v>148</v>
       </c>
       <c r="E7" s="14"/>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="39" t="n">
         <v>28.5</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="40" t="n">
         <f aca="false">IF(A7="","",IF(D7="Exempt",IF(G7=0,"",E7/G7),F7))</f>
         <v>28.5</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="40" t="n">
         <f aca="false">IF(A7="","",IF(D7="Non-Exempt",H7*1.5,"N/A"))</f>
         <v>42.75</v>
       </c>
@@ -3508,12 +3689,12 @@
       <c r="M7" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="38" t="n">
+      <c r="N7" s="41" t="n">
         <f aca="true">IF(A7="","",IFERROR(L7*MAX(0,DATEDIF(J7,IF(K7="",TODAY(),MIN(K7,TODAY())),"m")),0))</f>
         <v>46.69</v>
       </c>
-      <c r="O7" s="39"/>
-      <c r="P7" s="38" t="n">
+      <c r="O7" s="42"/>
+      <c r="P7" s="41" t="n">
         <f aca="false">IF(A7="","",M7+N7-O7)</f>
         <v>51.69</v>
       </c>
@@ -3524,15 +3705,15 @@
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="18"/>
-      <c r="F8" s="40"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H8" s="41" t="str">
+      <c r="H8" s="44" t="str">
         <f aca="false">IF(A8="","",IF(D8="Exempt",IF(G8=0,"",E8/G8),F8))</f>
         <v/>
       </c>
-      <c r="I8" s="31" t="str">
+      <c r="I8" s="34" t="str">
         <f aca="false">IF(A8="","",IF(D8="Non-Exempt",H8*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3540,12 +3721,12 @@
       <c r="K8" s="17"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
-      <c r="N8" s="42" t="str">
+      <c r="N8" s="45" t="str">
         <f aca="true">IF(A8="","",IFERROR(L8*MAX(0,DATEDIF(J8,IF(K8="",TODAY(),MIN(K8,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="42" t="str">
+      <c r="O8" s="46"/>
+      <c r="P8" s="45" t="str">
         <f aca="false">IF(A8="","",M8+N8-O8)</f>
         <v/>
       </c>
@@ -3556,15 +3737,15 @@
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="36"/>
+      <c r="F9" s="39"/>
       <c r="G9" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H9" s="37" t="str">
+      <c r="H9" s="40" t="str">
         <f aca="false">IF(A9="","",IF(D9="Exempt",IF(G9=0,"",E9/G9),F9))</f>
         <v/>
       </c>
-      <c r="I9" s="26" t="str">
+      <c r="I9" s="29" t="str">
         <f aca="false">IF(A9="","",IF(D9="Non-Exempt",H9*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3572,12 +3753,12 @@
       <c r="K9" s="13"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
-      <c r="N9" s="38" t="str">
+      <c r="N9" s="41" t="str">
         <f aca="true">IF(A9="","",IFERROR(L9*MAX(0,DATEDIF(J9,IF(K9="",TODAY(),MIN(K9,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O9" s="39"/>
-      <c r="P9" s="38" t="str">
+      <c r="O9" s="42"/>
+      <c r="P9" s="41" t="str">
         <f aca="false">IF(A9="","",M9+N9-O9)</f>
         <v/>
       </c>
@@ -3588,15 +3769,15 @@
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="18"/>
-      <c r="F10" s="40"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H10" s="41" t="str">
+      <c r="H10" s="44" t="str">
         <f aca="false">IF(A10="","",IF(D10="Exempt",IF(G10=0,"",E10/G10),F10))</f>
         <v/>
       </c>
-      <c r="I10" s="31" t="str">
+      <c r="I10" s="34" t="str">
         <f aca="false">IF(A10="","",IF(D10="Non-Exempt",H10*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3604,12 +3785,12 @@
       <c r="K10" s="17"/>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
-      <c r="N10" s="42" t="str">
+      <c r="N10" s="45" t="str">
         <f aca="true">IF(A10="","",IFERROR(L10*MAX(0,DATEDIF(J10,IF(K10="",TODAY(),MIN(K10,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O10" s="43"/>
-      <c r="P10" s="42" t="str">
+      <c r="O10" s="46"/>
+      <c r="P10" s="45" t="str">
         <f aca="false">IF(A10="","",M10+N10-O10)</f>
         <v/>
       </c>
@@ -3620,15 +3801,15 @@
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
       <c r="E11" s="14"/>
-      <c r="F11" s="36"/>
+      <c r="F11" s="39"/>
       <c r="G11" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H11" s="37" t="str">
+      <c r="H11" s="40" t="str">
         <f aca="false">IF(A11="","",IF(D11="Exempt",IF(G11=0,"",E11/G11),F11))</f>
         <v/>
       </c>
-      <c r="I11" s="26" t="str">
+      <c r="I11" s="29" t="str">
         <f aca="false">IF(A11="","",IF(D11="Non-Exempt",H11*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3636,12 +3817,12 @@
       <c r="K11" s="13"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
-      <c r="N11" s="38" t="str">
+      <c r="N11" s="41" t="str">
         <f aca="true">IF(A11="","",IFERROR(L11*MAX(0,DATEDIF(J11,IF(K11="",TODAY(),MIN(K11,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O11" s="39"/>
-      <c r="P11" s="38" t="str">
+      <c r="O11" s="42"/>
+      <c r="P11" s="41" t="str">
         <f aca="false">IF(A11="","",M11+N11-O11)</f>
         <v/>
       </c>
@@ -3652,15 +3833,15 @@
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
       <c r="E12" s="18"/>
-      <c r="F12" s="40"/>
+      <c r="F12" s="43"/>
       <c r="G12" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H12" s="41" t="str">
+      <c r="H12" s="44" t="str">
         <f aca="false">IF(A12="","",IF(D12="Exempt",IF(G12=0,"",E12/G12),F12))</f>
         <v/>
       </c>
-      <c r="I12" s="31" t="str">
+      <c r="I12" s="34" t="str">
         <f aca="false">IF(A12="","",IF(D12="Non-Exempt",H12*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3668,12 +3849,12 @@
       <c r="K12" s="17"/>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
-      <c r="N12" s="42" t="str">
+      <c r="N12" s="45" t="str">
         <f aca="true">IF(A12="","",IFERROR(L12*MAX(0,DATEDIF(J12,IF(K12="",TODAY(),MIN(K12,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="42" t="str">
+      <c r="O12" s="46"/>
+      <c r="P12" s="45" t="str">
         <f aca="false">IF(A12="","",M12+N12-O12)</f>
         <v/>
       </c>
@@ -3684,15 +3865,15 @@
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="39"/>
       <c r="G13" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H13" s="37" t="str">
+      <c r="H13" s="40" t="str">
         <f aca="false">IF(A13="","",IF(D13="Exempt",IF(G13=0,"",E13/G13),F13))</f>
         <v/>
       </c>
-      <c r="I13" s="26" t="str">
+      <c r="I13" s="29" t="str">
         <f aca="false">IF(A13="","",IF(D13="Non-Exempt",H13*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3700,12 +3881,12 @@
       <c r="K13" s="13"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
-      <c r="N13" s="38" t="str">
+      <c r="N13" s="41" t="str">
         <f aca="true">IF(A13="","",IFERROR(L13*MAX(0,DATEDIF(J13,IF(K13="",TODAY(),MIN(K13,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O13" s="39"/>
-      <c r="P13" s="38" t="str">
+      <c r="O13" s="42"/>
+      <c r="P13" s="41" t="str">
         <f aca="false">IF(A13="","",M13+N13-O13)</f>
         <v/>
       </c>
@@ -3716,15 +3897,15 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="18"/>
-      <c r="F14" s="40"/>
+      <c r="F14" s="43"/>
       <c r="G14" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H14" s="41" t="str">
+      <c r="H14" s="44" t="str">
         <f aca="false">IF(A14="","",IF(D14="Exempt",IF(G14=0,"",E14/G14),F14))</f>
         <v/>
       </c>
-      <c r="I14" s="31" t="str">
+      <c r="I14" s="34" t="str">
         <f aca="false">IF(A14="","",IF(D14="Non-Exempt",H14*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3732,12 +3913,12 @@
       <c r="K14" s="17"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
-      <c r="N14" s="42" t="str">
+      <c r="N14" s="45" t="str">
         <f aca="true">IF(A14="","",IFERROR(L14*MAX(0,DATEDIF(J14,IF(K14="",TODAY(),MIN(K14,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O14" s="43"/>
-      <c r="P14" s="42" t="str">
+      <c r="O14" s="46"/>
+      <c r="P14" s="45" t="str">
         <f aca="false">IF(A14="","",M14+N14-O14)</f>
         <v/>
       </c>
@@ -3748,15 +3929,15 @@
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="14"/>
-      <c r="F15" s="36"/>
+      <c r="F15" s="39"/>
       <c r="G15" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H15" s="37" t="str">
+      <c r="H15" s="40" t="str">
         <f aca="false">IF(A15="","",IF(D15="Exempt",IF(G15=0,"",E15/G15),F15))</f>
         <v/>
       </c>
-      <c r="I15" s="26" t="str">
+      <c r="I15" s="29" t="str">
         <f aca="false">IF(A15="","",IF(D15="Non-Exempt",H15*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3764,12 +3945,12 @@
       <c r="K15" s="13"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
-      <c r="N15" s="38" t="str">
+      <c r="N15" s="41" t="str">
         <f aca="true">IF(A15="","",IFERROR(L15*MAX(0,DATEDIF(J15,IF(K15="",TODAY(),MIN(K15,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O15" s="39"/>
-      <c r="P15" s="38" t="str">
+      <c r="O15" s="42"/>
+      <c r="P15" s="41" t="str">
         <f aca="false">IF(A15="","",M15+N15-O15)</f>
         <v/>
       </c>
@@ -3780,15 +3961,15 @@
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="18"/>
-      <c r="F16" s="40"/>
+      <c r="F16" s="43"/>
       <c r="G16" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H16" s="41" t="str">
+      <c r="H16" s="44" t="str">
         <f aca="false">IF(A16="","",IF(D16="Exempt",IF(G16=0,"",E16/G16),F16))</f>
         <v/>
       </c>
-      <c r="I16" s="31" t="str">
+      <c r="I16" s="34" t="str">
         <f aca="false">IF(A16="","",IF(D16="Non-Exempt",H16*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3796,12 +3977,12 @@
       <c r="K16" s="17"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
-      <c r="N16" s="42" t="str">
+      <c r="N16" s="45" t="str">
         <f aca="true">IF(A16="","",IFERROR(L16*MAX(0,DATEDIF(J16,IF(K16="",TODAY(),MIN(K16,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O16" s="43"/>
-      <c r="P16" s="42" t="str">
+      <c r="O16" s="46"/>
+      <c r="P16" s="45" t="str">
         <f aca="false">IF(A16="","",M16+N16-O16)</f>
         <v/>
       </c>
@@ -3812,15 +3993,15 @@
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="36"/>
+      <c r="F17" s="39"/>
       <c r="G17" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H17" s="37" t="str">
+      <c r="H17" s="40" t="str">
         <f aca="false">IF(A17="","",IF(D17="Exempt",IF(G17=0,"",E17/G17),F17))</f>
         <v/>
       </c>
-      <c r="I17" s="26" t="str">
+      <c r="I17" s="29" t="str">
         <f aca="false">IF(A17="","",IF(D17="Non-Exempt",H17*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3828,12 +4009,12 @@
       <c r="K17" s="13"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
-      <c r="N17" s="38" t="str">
+      <c r="N17" s="41" t="str">
         <f aca="true">IF(A17="","",IFERROR(L17*MAX(0,DATEDIF(J17,IF(K17="",TODAY(),MIN(K17,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O17" s="39"/>
-      <c r="P17" s="38" t="str">
+      <c r="O17" s="42"/>
+      <c r="P17" s="41" t="str">
         <f aca="false">IF(A17="","",M17+N17-O17)</f>
         <v/>
       </c>
@@ -3844,15 +4025,15 @@
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="40"/>
+      <c r="F18" s="43"/>
       <c r="G18" s="16" t="n">
         <v>2080</v>
       </c>
-      <c r="H18" s="41" t="str">
+      <c r="H18" s="44" t="str">
         <f aca="false">IF(A18="","",IF(D18="Exempt",IF(G18=0,"",E18/G18),F18))</f>
         <v/>
       </c>
-      <c r="I18" s="31" t="str">
+      <c r="I18" s="34" t="str">
         <f aca="false">IF(A18="","",IF(D18="Non-Exempt",H18*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3860,12 +4041,12 @@
       <c r="K18" s="17"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-      <c r="N18" s="42" t="str">
+      <c r="N18" s="45" t="str">
         <f aca="true">IF(A18="","",IFERROR(L18*MAX(0,DATEDIF(J18,IF(K18="",TODAY(),MIN(K18,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O18" s="43"/>
-      <c r="P18" s="42" t="str">
+      <c r="O18" s="46"/>
+      <c r="P18" s="45" t="str">
         <f aca="false">IF(A18="","",M18+N18-O18)</f>
         <v/>
       </c>
@@ -3876,15 +4057,15 @@
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="14"/>
-      <c r="F19" s="36"/>
+      <c r="F19" s="39"/>
       <c r="G19" s="12" t="n">
         <v>2080</v>
       </c>
-      <c r="H19" s="37" t="str">
+      <c r="H19" s="40" t="str">
         <f aca="false">IF(A19="","",IF(D19="Exempt",IF(G19=0,"",E19/G19),F19))</f>
         <v/>
       </c>
-      <c r="I19" s="26" t="str">
+      <c r="I19" s="29" t="str">
         <f aca="false">IF(A19="","",IF(D19="Non-Exempt",H19*1.5,"N/A"))</f>
         <v/>
       </c>
@@ -3892,12 +4073,12 @@
       <c r="K19" s="13"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
-      <c r="N19" s="38" t="str">
+      <c r="N19" s="41" t="str">
         <f aca="true">IF(A19="","",IFERROR(L19*MAX(0,DATEDIF(J19,IF(K19="",TODAY(),MIN(K19,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O19" s="39"/>
-      <c r="P19" s="38" t="str">
+      <c r="O19" s="42"/>
+      <c r="P19" s="41" t="str">
         <f aca="false">IF(A19="","",M19+N19-O19)</f>
         <v/>
       </c>
@@ -3928,9 +4109,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BF38"/>
+  <dimension ref="A1:BF40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -3993,116 +4175,116 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44" t="s">
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44" t="s">
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44" t="s">
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44" t="s">
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44" t="s">
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44" t="s">
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44" t="s">
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="44" t="s">
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44" t="s">
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="AR4" s="44"/>
-      <c r="AS4" s="44"/>
-      <c r="AT4" s="44"/>
-      <c r="AU4" s="44" t="s">
+      <c r="AR4" s="49"/>
+      <c r="AS4" s="49"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="49" t="s">
         <v>165</v>
       </c>
-      <c r="AV4" s="44"/>
-      <c r="AW4" s="44"/>
-      <c r="AX4" s="44"/>
-      <c r="AY4" s="44" t="s">
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="AZ4" s="44"/>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44"/>
-      <c r="BC4" s="11" t="s">
+      <c r="AZ4" s="49"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="BD4" s="11" t="s">
+      <c r="BD4" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="BE4" s="11" t="s">
+      <c r="BE4" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="BF4" s="11" t="s">
+      <c r="BF4" s="47" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="48"/>
       <c r="G5" s="11" t="s">
         <v>171</v>
       </c>
@@ -4112,7 +4294,7 @@
       <c r="I5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="K5" s="11" t="s">
@@ -4124,7 +4306,7 @@
       <c r="M5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="O5" s="11" t="s">
@@ -4136,7 +4318,7 @@
       <c r="Q5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="R5" s="11" t="s">
+      <c r="R5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="S5" s="11" t="s">
@@ -4148,7 +4330,7 @@
       <c r="U5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="V5" s="11" t="s">
+      <c r="V5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="W5" s="11" t="s">
@@ -4160,7 +4342,7 @@
       <c r="Y5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="Z5" s="11" t="s">
+      <c r="Z5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AA5" s="11" t="s">
@@ -4172,7 +4354,7 @@
       <c r="AC5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AD5" s="11" t="s">
+      <c r="AD5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AE5" s="11" t="s">
@@ -4184,7 +4366,7 @@
       <c r="AG5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AH5" s="11" t="s">
+      <c r="AH5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AI5" s="11" t="s">
@@ -4196,7 +4378,7 @@
       <c r="AK5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AL5" s="11" t="s">
+      <c r="AL5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AM5" s="11" t="s">
@@ -4208,7 +4390,7 @@
       <c r="AO5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AP5" s="11" t="s">
+      <c r="AP5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AQ5" s="11" t="s">
@@ -4220,7 +4402,7 @@
       <c r="AS5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AT5" s="11" t="s">
+      <c r="AT5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AU5" s="11" t="s">
@@ -4232,7 +4414,7 @@
       <c r="AW5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="AX5" s="11" t="s">
+      <c r="AX5" s="50" t="s">
         <v>174</v>
       </c>
       <c r="AY5" s="11" t="s">
@@ -4244,166 +4426,166 @@
       <c r="BA5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="BB5" s="11" t="s">
+      <c r="BB5" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="BC5" s="11"/>
-      <c r="BD5" s="11"/>
-      <c r="BE5" s="11"/>
-      <c r="BF5" s="11"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>123456</v>
       </c>
-      <c r="B6" s="45" t="str">
+      <c r="B6" s="51" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A6,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>John Smith</v>
       </c>
-      <c r="C6" s="45" t="str">
+      <c r="C6" s="51" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Engineer 4</v>
       </c>
-      <c r="D6" s="46" t="n">
+      <c r="D6" s="52" t="n">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>72.1153846153846</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="F6" s="45" t="str">
+      <c r="F6" s="53" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Exempt</v>
       </c>
-      <c r="G6" s="47" t="n">
+      <c r="G6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="15" t="n">
-        <f aca="false">IF(A6="","",H6*$D6+IF($F6="Exempt",0,I6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="47" t="n">
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="55" t="n">
+        <f aca="false">IF(A6="","",H6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,I6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="15" t="n">
-        <f aca="false">IF(A6="","",L6*$D6+IF($F6="Exempt",0,M6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="47" t="n">
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="55" t="n">
+        <f aca="false">IF(A6="","",L6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,M6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="15" t="n">
-        <f aca="false">IF(A6="","",P6*$D6+IF($F6="Exempt",0,Q6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="47" t="n">
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="55" t="n">
+        <f aca="false">IF(A6="","",P6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,Q6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="15" t="n">
-        <f aca="false">IF(A6="","",T6*$D6+IF($F6="Exempt",0,U6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="W6" s="47" t="n">
+      <c r="T6" s="42"/>
+      <c r="U6" s="42"/>
+      <c r="V6" s="55" t="n">
+        <f aca="false">IF(A6="","",T6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,U6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="39"/>
-      <c r="Z6" s="15" t="n">
-        <f aca="false">IF(A6="","",X6*$D6+IF($F6="Exempt",0,Y6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AA6" s="47" t="n">
+      <c r="X6" s="42"/>
+      <c r="Y6" s="42"/>
+      <c r="Z6" s="55" t="n">
+        <f aca="false">IF(A6="","",X6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,Y6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="15" t="n">
-        <f aca="false">IF(A6="","",AB6*$D6+IF($F6="Exempt",0,AC6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AE6" s="47" t="n">
+      <c r="AB6" s="42"/>
+      <c r="AC6" s="42"/>
+      <c r="AD6" s="55" t="n">
+        <f aca="false">IF(A6="","",AB6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AC6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>123.010752688172</v>
       </c>
-      <c r="AF6" s="39" t="n">
+      <c r="AF6" s="42" t="n">
         <v>60</v>
       </c>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="15" t="n">
-        <f aca="false">IF(A6="","",AF6*$D6+IF($F6="Exempt",0,AG6*$D6*1.5))</f>
+      <c r="AG6" s="42"/>
+      <c r="AH6" s="55" t="n">
+        <f aca="false">IF(A6="","",AF6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AG6*$D6*1.5))</f>
         <v>4326.92307692308</v>
       </c>
-      <c r="AI6" s="47" t="n">
+      <c r="AI6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ6" s="39" t="n">
+      <c r="AJ6" s="42" t="n">
         <v>173.33</v>
       </c>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="15" t="n">
-        <f aca="false">IF(A6="","",AJ6*$D6+IF($F6="Exempt",0,AK6*$D6*1.5))</f>
+      <c r="AK6" s="42"/>
+      <c r="AL6" s="55" t="n">
+        <f aca="false">IF(A6="","",AJ6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AK6*$D6*1.5))</f>
         <v>12499.7596153846</v>
       </c>
-      <c r="AM6" s="47" t="n">
+      <c r="AM6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="15" t="n">
-        <f aca="false">IF(A6="","",AN6*$D6+IF($F6="Exempt",0,AO6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="47" t="n">
+      <c r="AN6" s="42"/>
+      <c r="AO6" s="42"/>
+      <c r="AP6" s="55" t="n">
+        <f aca="false">IF(A6="","",AN6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AO6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="15" t="n">
-        <f aca="false">IF(A6="","",AR6*$D6+IF($F6="Exempt",0,AS6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AU6" s="47" t="n">
+      <c r="AR6" s="42"/>
+      <c r="AS6" s="42"/>
+      <c r="AT6" s="55" t="n">
+        <f aca="false">IF(A6="","",AR6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AS6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV6" s="39"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="15" t="n">
-        <f aca="false">IF(A6="","",AV6*$D6+IF($F6="Exempt",0,AW6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AY6" s="47" t="n">
+      <c r="AV6" s="42"/>
+      <c r="AW6" s="42"/>
+      <c r="AX6" s="55" t="n">
+        <f aca="false">IF(A6="","",AV6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AW6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="54" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ6" s="39"/>
-      <c r="BA6" s="39"/>
-      <c r="BB6" s="15" t="n">
-        <f aca="false">IF(A6="","",AZ6*$D6+IF($F6="Exempt",0,BA6*$D6*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="BC6" s="38" t="n">
+      <c r="AZ6" s="42"/>
+      <c r="BA6" s="42"/>
+      <c r="BB6" s="55" t="n">
+        <f aca="false">IF(A6="","",AZ6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,BA6*$D6*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="BC6" s="41" t="n">
         <f aca="false">IF(A6="","",SUM(G6,K6,O6,S6,W6,AA6,AE6,AI6,AM6,AQ6,AU6,AY6))</f>
         <v>989.677419354839</v>
       </c>
-      <c r="BD6" s="38" t="n">
+      <c r="BD6" s="41" t="n">
         <f aca="false">IF(A6="","",SUM(H6,I6,L6,M6,P6,Q6,T6,U6,X6,Y6,AB6,AC6,AF6,AG6,AJ6,AK6,AN6,AO6,AR6,AS6,AV6,AW6,AZ6,BA6))</f>
         <v>233.33</v>
       </c>
@@ -4420,154 +4602,154 @@
       <c r="A7" s="16" t="n">
         <v>123457</v>
       </c>
-      <c r="B7" s="48" t="str">
+      <c r="B7" s="56" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A7,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>Maria Alvarez</v>
       </c>
-      <c r="C7" s="48" t="str">
+      <c r="C7" s="56" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Program Manager</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="57" t="n">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>79.3269230769231</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="F7" s="48" t="str">
+      <c r="F7" s="58" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Exempt</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="46" t="n">
         <v>173.33</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="19" t="n">
-        <f aca="false">IF(A7="","",H7*$D7+IF($F7="Exempt",0,I7*$D7*1.5))</f>
+      <c r="I7" s="46"/>
+      <c r="J7" s="60" t="n">
+        <f aca="false">IF(A7="","",H7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,I7*$D7*1.5))</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="K7" s="50" t="n">
+      <c r="K7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="L7" s="43" t="n">
+      <c r="L7" s="46" t="n">
         <v>173.33</v>
       </c>
-      <c r="M7" s="43"/>
-      <c r="N7" s="19" t="n">
-        <f aca="false">IF(A7="","",L7*$D7+IF($F7="Exempt",0,M7*$D7*1.5))</f>
+      <c r="M7" s="46"/>
+      <c r="N7" s="60" t="n">
+        <f aca="false">IF(A7="","",L7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,M7*$D7*1.5))</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="O7" s="50" t="n">
+      <c r="O7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="19" t="n">
-        <f aca="false">IF(A7="","",P7*$D7+IF($F7="Exempt",0,Q7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="50" t="n">
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="60" t="n">
+        <f aca="false">IF(A7="","",P7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,Q7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="19" t="n">
-        <f aca="false">IF(A7="","",T7*$D7+IF($F7="Exempt",0,U7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="W7" s="50" t="n">
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="60" t="n">
+        <f aca="false">IF(A7="","",T7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,U7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="19" t="n">
-        <f aca="false">IF(A7="","",X7*$D7+IF($F7="Exempt",0,Y7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AA7" s="50" t="n">
+      <c r="X7" s="46"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="60" t="n">
+        <f aca="false">IF(A7="","",X7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,Y7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="43"/>
-      <c r="AD7" s="19" t="n">
-        <f aca="false">IF(A7="","",AB7*$D7+IF($F7="Exempt",0,AC7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="50" t="n">
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="46"/>
+      <c r="AD7" s="60" t="n">
+        <f aca="false">IF(A7="","",AB7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AC7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AF7" s="43"/>
-      <c r="AG7" s="43"/>
-      <c r="AH7" s="19" t="n">
-        <f aca="false">IF(A7="","",AF7*$D7+IF($F7="Exempt",0,AG7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="50" t="n">
+      <c r="AF7" s="46"/>
+      <c r="AG7" s="46"/>
+      <c r="AH7" s="60" t="n">
+        <f aca="false">IF(A7="","",AF7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AG7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="19" t="n">
-        <f aca="false">IF(A7="","",AJ7*$D7+IF($F7="Exempt",0,AK7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AM7" s="50" t="n">
+      <c r="AJ7" s="46"/>
+      <c r="AK7" s="46"/>
+      <c r="AL7" s="60" t="n">
+        <f aca="false">IF(A7="","",AJ7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AK7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN7" s="43"/>
-      <c r="AO7" s="43"/>
-      <c r="AP7" s="19" t="n">
-        <f aca="false">IF(A7="","",AN7*$D7+IF($F7="Exempt",0,AO7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="50" t="n">
+      <c r="AN7" s="46"/>
+      <c r="AO7" s="46"/>
+      <c r="AP7" s="60" t="n">
+        <f aca="false">IF(A7="","",AN7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AO7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR7" s="43"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="19" t="n">
-        <f aca="false">IF(A7="","",AR7*$D7+IF($F7="Exempt",0,AS7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AU7" s="50" t="n">
+      <c r="AR7" s="46"/>
+      <c r="AS7" s="46"/>
+      <c r="AT7" s="60" t="n">
+        <f aca="false">IF(A7="","",AR7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AS7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV7" s="43"/>
-      <c r="AW7" s="43"/>
-      <c r="AX7" s="19" t="n">
-        <f aca="false">IF(A7="","",AV7*$D7+IF($F7="Exempt",0,AW7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AY7" s="50" t="n">
+      <c r="AV7" s="46"/>
+      <c r="AW7" s="46"/>
+      <c r="AX7" s="60" t="n">
+        <f aca="false">IF(A7="","",AV7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AW7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="59" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ7" s="43"/>
-      <c r="BA7" s="43"/>
-      <c r="BB7" s="19" t="n">
-        <f aca="false">IF(A7="","",AZ7*$D7+IF($F7="Exempt",0,BA7*$D7*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="BC7" s="42" t="n">
+      <c r="AZ7" s="46"/>
+      <c r="BA7" s="46"/>
+      <c r="BB7" s="60" t="n">
+        <f aca="false">IF(A7="","",AZ7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,BA7*$D7*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="BC7" s="45" t="n">
         <f aca="false">IF(A7="","",SUM(G7,K7,O7,S7,W7,AA7,AE7,AI7,AM7,AQ7,AU7,AY7))</f>
         <v>2080</v>
       </c>
-      <c r="BD7" s="42" t="n">
+      <c r="BD7" s="45" t="n">
         <f aca="false">IF(A7="","",SUM(H7,I7,L7,M7,P7,Q7,T7,U7,X7,Y7,AB7,AC7,AF7,AG7,AJ7,AK7,AN7,AO7,AR7,AS7,AV7,AW7,AZ7,BA7))</f>
         <v>346.66</v>
       </c>
@@ -4584,154 +4766,154 @@
       <c r="A8" s="12" t="n">
         <v>123458</v>
       </c>
-      <c r="B8" s="45" t="str">
+      <c r="B8" s="51" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A8,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>Dave Chen</v>
       </c>
-      <c r="C8" s="45" t="str">
+      <c r="C8" s="51" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Admin Support</v>
       </c>
-      <c r="D8" s="46" t="n">
+      <c r="D8" s="52" t="n">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>28.5</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="45" t="str">
+      <c r="F8" s="53" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Non-Exempt</v>
       </c>
-      <c r="G8" s="47" t="n">
+      <c r="G8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="42" t="n">
         <v>150</v>
       </c>
-      <c r="I8" s="39" t="n">
+      <c r="I8" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="J8" s="15" t="n">
-        <f aca="false">IF(A8="","",H8*$D8+IF($F8="Exempt",0,I8*$D8*1.5))</f>
-        <v>4788</v>
-      </c>
-      <c r="K8" s="47" t="n">
+      <c r="J8" s="55" t="n">
+        <f aca="false">IF(A8="","",H8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,I8*$D8*1.5))</f>
+        <v>4275</v>
+      </c>
+      <c r="K8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="15" t="n">
-        <f aca="false">IF(A8="","",L8*$D8+IF($F8="Exempt",0,M8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="47" t="n">
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="55" t="n">
+        <f aca="false">IF(A8="","",L8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,M8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="15" t="n">
-        <f aca="false">IF(A8="","",P8*$D8+IF($F8="Exempt",0,Q8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="47" t="n">
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="55" t="n">
+        <f aca="false">IF(A8="","",P8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,Q8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="T8" s="39"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="15" t="n">
-        <f aca="false">IF(A8="","",T8*$D8+IF($F8="Exempt",0,U8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="W8" s="47" t="n">
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="55" t="n">
+        <f aca="false">IF(A8="","",T8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,U8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="X8" s="39"/>
-      <c r="Y8" s="39"/>
-      <c r="Z8" s="15" t="n">
-        <f aca="false">IF(A8="","",X8*$D8+IF($F8="Exempt",0,Y8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AA8" s="47" t="n">
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="55" t="n">
+        <f aca="false">IF(A8="","",X8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,Y8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AA8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AB8" s="39"/>
-      <c r="AC8" s="39"/>
-      <c r="AD8" s="15" t="n">
-        <f aca="false">IF(A8="","",AB8*$D8+IF($F8="Exempt",0,AC8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AE8" s="47" t="n">
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="42"/>
+      <c r="AD8" s="55" t="n">
+        <f aca="false">IF(A8="","",AB8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AC8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AF8" s="39"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="15" t="n">
-        <f aca="false">IF(A8="","",AF8*$D8+IF($F8="Exempt",0,AG8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="47" t="n">
+      <c r="AF8" s="42"/>
+      <c r="AG8" s="42"/>
+      <c r="AH8" s="55" t="n">
+        <f aca="false">IF(A8="","",AF8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AG8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ8" s="39"/>
-      <c r="AK8" s="39"/>
-      <c r="AL8" s="15" t="n">
-        <f aca="false">IF(A8="","",AJ8*$D8+IF($F8="Exempt",0,AK8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="47" t="n">
+      <c r="AJ8" s="42"/>
+      <c r="AK8" s="42"/>
+      <c r="AL8" s="55" t="n">
+        <f aca="false">IF(A8="","",AJ8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AK8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN8" s="39"/>
-      <c r="AO8" s="39"/>
-      <c r="AP8" s="15" t="n">
-        <f aca="false">IF(A8="","",AN8*$D8+IF($F8="Exempt",0,AO8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="47" t="n">
+      <c r="AN8" s="42"/>
+      <c r="AO8" s="42"/>
+      <c r="AP8" s="55" t="n">
+        <f aca="false">IF(A8="","",AN8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AO8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR8" s="39"/>
-      <c r="AS8" s="39"/>
-      <c r="AT8" s="15" t="n">
-        <f aca="false">IF(A8="","",AR8*$D8+IF($F8="Exempt",0,AS8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AU8" s="47" t="n">
+      <c r="AR8" s="42"/>
+      <c r="AS8" s="42"/>
+      <c r="AT8" s="55" t="n">
+        <f aca="false">IF(A8="","",AR8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AS8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV8" s="39"/>
-      <c r="AW8" s="39"/>
-      <c r="AX8" s="15" t="n">
-        <f aca="false">IF(A8="","",AV8*$D8+IF($F8="Exempt",0,AW8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="AY8" s="47" t="n">
+      <c r="AV8" s="42"/>
+      <c r="AW8" s="42"/>
+      <c r="AX8" s="55" t="n">
+        <f aca="false">IF(A8="","",AV8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AW8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="54" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ8" s="39"/>
-      <c r="BA8" s="39"/>
-      <c r="BB8" s="15" t="n">
-        <f aca="false">IF(A8="","",AZ8*$D8+IF($F8="Exempt",0,BA8*$D8*1.5))</f>
-        <v>0</v>
-      </c>
-      <c r="BC8" s="38" t="n">
+      <c r="AZ8" s="42"/>
+      <c r="BA8" s="42"/>
+      <c r="BB8" s="55" t="n">
+        <f aca="false">IF(A8="","",AZ8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,BA8*$D8*1.5))</f>
+        <v>0</v>
+      </c>
+      <c r="BC8" s="41" t="n">
         <f aca="false">IF(A8="","",SUM(G8,K8,O8,S8,W8,AA8,AE8,AI8,AM8,AQ8,AU8,AY8))</f>
         <v>2080</v>
       </c>
-      <c r="BD8" s="38" t="n">
+      <c r="BD8" s="41" t="n">
         <f aca="false">IF(A8="","",SUM(H8,I8,L8,M8,P8,Q8,T8,U8,X8,Y8,AB8,AC8,AF8,AG8,AJ8,AK8,AN8,AO8,AR8,AS8,AV8,AW8,AZ8,BA8))</f>
         <v>162</v>
       </c>
@@ -4741,153 +4923,153 @@
       </c>
       <c r="BF8" s="15" t="n">
         <f aca="false">IF(A8="","",SUM(J8,N8,R8,V8,Z8,AD8,AH8,AL8,AP8,AT8,AX8,BB8))</f>
-        <v>4788</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16"/>
-      <c r="B9" s="48" t="str">
+      <c r="B9" s="56" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A9,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C9" s="48" t="str">
+      <c r="C9" s="56" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D9" s="49" t="str">
+      <c r="D9" s="57" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E9" s="16"/>
-      <c r="F9" s="48" t="str">
+      <c r="F9" s="58" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G9" s="50" t="str">
+      <c r="G9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="19" t="str">
-        <f aca="false">IF(A9="","",H9*$D9+IF($F9="Exempt",0,I9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="K9" s="50" t="str">
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="60" t="str">
+        <f aca="false">IF(A9="","",H9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,I9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="K9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="19" t="str">
-        <f aca="false">IF(A9="","",L9*$D9+IF($F9="Exempt",0,M9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="O9" s="50" t="str">
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="60" t="str">
+        <f aca="false">IF(A9="","",L9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,M9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="O9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="19" t="str">
-        <f aca="false">IF(A9="","",P9*$D9+IF($F9="Exempt",0,Q9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="S9" s="50" t="str">
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="60" t="str">
+        <f aca="false">IF(A9="","",P9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,Q9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="S9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="19" t="str">
-        <f aca="false">IF(A9="","",T9*$D9+IF($F9="Exempt",0,U9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="W9" s="50" t="str">
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="60" t="str">
+        <f aca="false">IF(A9="","",T9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,U9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="W9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="19" t="str">
-        <f aca="false">IF(A9="","",X9*$D9+IF($F9="Exempt",0,Y9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA9" s="50" t="str">
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="60" t="str">
+        <f aca="false">IF(A9="","",X9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,Y9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="19" t="str">
-        <f aca="false">IF(A9="","",AB9*$D9+IF($F9="Exempt",0,AC9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="50" t="str">
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="60" t="str">
+        <f aca="false">IF(A9="","",AB9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AC9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="19" t="str">
-        <f aca="false">IF(A9="","",AF9*$D9+IF($F9="Exempt",0,AG9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI9" s="50" t="str">
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="60" t="str">
+        <f aca="false">IF(A9="","",AF9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AG9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="19" t="str">
-        <f aca="false">IF(A9="","",AJ9*$D9+IF($F9="Exempt",0,AK9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM9" s="50" t="str">
+      <c r="AJ9" s="46"/>
+      <c r="AK9" s="46"/>
+      <c r="AL9" s="60" t="str">
+        <f aca="false">IF(A9="","",AJ9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AK9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN9" s="43"/>
-      <c r="AO9" s="43"/>
-      <c r="AP9" s="19" t="str">
-        <f aca="false">IF(A9="","",AN9*$D9+IF($F9="Exempt",0,AO9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="50" t="str">
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="60" t="str">
+        <f aca="false">IF(A9="","",AN9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AO9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR9" s="43"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="19" t="str">
-        <f aca="false">IF(A9="","",AR9*$D9+IF($F9="Exempt",0,AS9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU9" s="50" t="str">
+      <c r="AR9" s="46"/>
+      <c r="AS9" s="46"/>
+      <c r="AT9" s="60" t="str">
+        <f aca="false">IF(A9="","",AR9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AS9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV9" s="43"/>
-      <c r="AW9" s="43"/>
-      <c r="AX9" s="19" t="str">
-        <f aca="false">IF(A9="","",AV9*$D9+IF($F9="Exempt",0,AW9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY9" s="50" t="str">
+      <c r="AV9" s="46"/>
+      <c r="AW9" s="46"/>
+      <c r="AX9" s="60" t="str">
+        <f aca="false">IF(A9="","",AV9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AW9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY9" s="59" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="43"/>
-      <c r="BB9" s="19" t="str">
-        <f aca="false">IF(A9="","",AZ9*$D9+IF($F9="Exempt",0,BA9*$D9*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC9" s="42" t="str">
+      <c r="AZ9" s="46"/>
+      <c r="BA9" s="46"/>
+      <c r="BB9" s="60" t="str">
+        <f aca="false">IF(A9="","",AZ9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,BA9*$D9*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC9" s="45" t="str">
         <f aca="false">IF(A9="","",SUM(G9,K9,O9,S9,W9,AA9,AE9,AI9,AM9,AQ9,AU9,AY9))</f>
         <v/>
       </c>
-      <c r="BD9" s="42" t="str">
+      <c r="BD9" s="45" t="str">
         <f aca="false">IF(A9="","",SUM(H9,I9,L9,M9,P9,Q9,T9,U9,X9,Y9,AB9,AC9,AF9,AG9,AJ9,AK9,AN9,AO9,AR9,AS9,AV9,AW9,AZ9,BA9))</f>
         <v/>
       </c>
@@ -4902,148 +5084,148 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12"/>
-      <c r="B10" s="45" t="str">
+      <c r="B10" s="51" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A10,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C10" s="45" t="str">
+      <c r="C10" s="51" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D10" s="46" t="str">
+      <c r="D10" s="52" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E10" s="12"/>
-      <c r="F10" s="45" t="str">
+      <c r="F10" s="53" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G10" s="47" t="str">
+      <c r="G10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="15" t="str">
-        <f aca="false">IF(A10="","",H10*$D10+IF($F10="Exempt",0,I10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="K10" s="47" t="str">
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="55" t="str">
+        <f aca="false">IF(A10="","",H10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,I10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="K10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="15" t="str">
-        <f aca="false">IF(A10="","",L10*$D10+IF($F10="Exempt",0,M10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="O10" s="47" t="str">
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="55" t="str">
+        <f aca="false">IF(A10="","",L10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,M10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="O10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="15" t="str">
-        <f aca="false">IF(A10="","",P10*$D10+IF($F10="Exempt",0,Q10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="S10" s="47" t="str">
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="55" t="str">
+        <f aca="false">IF(A10="","",P10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,Q10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="S10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T10" s="39"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="15" t="str">
-        <f aca="false">IF(A10="","",T10*$D10+IF($F10="Exempt",0,U10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="W10" s="47" t="str">
+      <c r="T10" s="42"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="55" t="str">
+        <f aca="false">IF(A10="","",T10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,U10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="W10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
-      <c r="Z10" s="15" t="str">
-        <f aca="false">IF(A10="","",X10*$D10+IF($F10="Exempt",0,Y10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA10" s="47" t="str">
+      <c r="X10" s="42"/>
+      <c r="Y10" s="42"/>
+      <c r="Z10" s="55" t="str">
+        <f aca="false">IF(A10="","",X10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,Y10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB10" s="39"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="15" t="str">
-        <f aca="false">IF(A10="","",AB10*$D10+IF($F10="Exempt",0,AC10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE10" s="47" t="str">
+      <c r="AB10" s="42"/>
+      <c r="AC10" s="42"/>
+      <c r="AD10" s="55" t="str">
+        <f aca="false">IF(A10="","",AB10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AC10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="15" t="str">
-        <f aca="false">IF(A10="","",AF10*$D10+IF($F10="Exempt",0,AG10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI10" s="47" t="str">
+      <c r="AF10" s="42"/>
+      <c r="AG10" s="42"/>
+      <c r="AH10" s="55" t="str">
+        <f aca="false">IF(A10="","",AF10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AG10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="39"/>
-      <c r="AL10" s="15" t="str">
-        <f aca="false">IF(A10="","",AJ10*$D10+IF($F10="Exempt",0,AK10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM10" s="47" t="str">
+      <c r="AJ10" s="42"/>
+      <c r="AK10" s="42"/>
+      <c r="AL10" s="55" t="str">
+        <f aca="false">IF(A10="","",AJ10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AK10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN10" s="39"/>
-      <c r="AO10" s="39"/>
-      <c r="AP10" s="15" t="str">
-        <f aca="false">IF(A10="","",AN10*$D10+IF($F10="Exempt",0,AO10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ10" s="47" t="str">
+      <c r="AN10" s="42"/>
+      <c r="AO10" s="42"/>
+      <c r="AP10" s="55" t="str">
+        <f aca="false">IF(A10="","",AN10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AO10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR10" s="39"/>
-      <c r="AS10" s="39"/>
-      <c r="AT10" s="15" t="str">
-        <f aca="false">IF(A10="","",AR10*$D10+IF($F10="Exempt",0,AS10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU10" s="47" t="str">
+      <c r="AR10" s="42"/>
+      <c r="AS10" s="42"/>
+      <c r="AT10" s="55" t="str">
+        <f aca="false">IF(A10="","",AR10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AS10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV10" s="39"/>
-      <c r="AW10" s="39"/>
-      <c r="AX10" s="15" t="str">
-        <f aca="false">IF(A10="","",AV10*$D10+IF($F10="Exempt",0,AW10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY10" s="47" t="str">
+      <c r="AV10" s="42"/>
+      <c r="AW10" s="42"/>
+      <c r="AX10" s="55" t="str">
+        <f aca="false">IF(A10="","",AV10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AW10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY10" s="54" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ10" s="39"/>
-      <c r="BA10" s="39"/>
-      <c r="BB10" s="15" t="str">
-        <f aca="false">IF(A10="","",AZ10*$D10+IF($F10="Exempt",0,BA10*$D10*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC10" s="38" t="str">
+      <c r="AZ10" s="42"/>
+      <c r="BA10" s="42"/>
+      <c r="BB10" s="55" t="str">
+        <f aca="false">IF(A10="","",AZ10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,BA10*$D10*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC10" s="41" t="str">
         <f aca="false">IF(A10="","",SUM(G10,K10,O10,S10,W10,AA10,AE10,AI10,AM10,AQ10,AU10,AY10))</f>
         <v/>
       </c>
-      <c r="BD10" s="38" t="str">
+      <c r="BD10" s="41" t="str">
         <f aca="false">IF(A10="","",SUM(H10,I10,L10,M10,P10,Q10,T10,U10,X10,Y10,AB10,AC10,AF10,AG10,AJ10,AK10,AN10,AO10,AR10,AS10,AV10,AW10,AZ10,BA10))</f>
         <v/>
       </c>
@@ -5058,148 +5240,148 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16"/>
-      <c r="B11" s="48" t="str">
+      <c r="B11" s="56" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A11,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C11" s="48" t="str">
+      <c r="C11" s="56" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D11" s="49" t="str">
+      <c r="D11" s="57" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E11" s="16"/>
-      <c r="F11" s="48" t="str">
+      <c r="F11" s="58" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G11" s="50" t="str">
+      <c r="G11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="19" t="str">
-        <f aca="false">IF(A11="","",H11*$D11+IF($F11="Exempt",0,I11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="K11" s="50" t="str">
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="60" t="str">
+        <f aca="false">IF(A11="","",H11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,I11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="K11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="19" t="str">
-        <f aca="false">IF(A11="","",L11*$D11+IF($F11="Exempt",0,M11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="O11" s="50" t="str">
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="60" t="str">
+        <f aca="false">IF(A11="","",L11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,M11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="O11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="19" t="str">
-        <f aca="false">IF(A11="","",P11*$D11+IF($F11="Exempt",0,Q11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="S11" s="50" t="str">
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="60" t="str">
+        <f aca="false">IF(A11="","",P11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,Q11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="S11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="19" t="str">
-        <f aca="false">IF(A11="","",T11*$D11+IF($F11="Exempt",0,U11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="W11" s="50" t="str">
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="60" t="str">
+        <f aca="false">IF(A11="","",T11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,U11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="W11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="19" t="str">
-        <f aca="false">IF(A11="","",X11*$D11+IF($F11="Exempt",0,Y11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA11" s="50" t="str">
+      <c r="X11" s="46"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="60" t="str">
+        <f aca="false">IF(A11="","",X11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,Y11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="19" t="str">
-        <f aca="false">IF(A11="","",AB11*$D11+IF($F11="Exempt",0,AC11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE11" s="50" t="str">
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="60" t="str">
+        <f aca="false">IF(A11="","",AB11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AC11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="19" t="str">
-        <f aca="false">IF(A11="","",AF11*$D11+IF($F11="Exempt",0,AG11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI11" s="50" t="str">
+      <c r="AF11" s="46"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="60" t="str">
+        <f aca="false">IF(A11="","",AF11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AG11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="19" t="str">
-        <f aca="false">IF(A11="","",AJ11*$D11+IF($F11="Exempt",0,AK11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM11" s="50" t="str">
+      <c r="AJ11" s="46"/>
+      <c r="AK11" s="46"/>
+      <c r="AL11" s="60" t="str">
+        <f aca="false">IF(A11="","",AJ11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AK11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN11" s="43"/>
-      <c r="AO11" s="43"/>
-      <c r="AP11" s="19" t="str">
-        <f aca="false">IF(A11="","",AN11*$D11+IF($F11="Exempt",0,AO11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ11" s="50" t="str">
+      <c r="AN11" s="46"/>
+      <c r="AO11" s="46"/>
+      <c r="AP11" s="60" t="str">
+        <f aca="false">IF(A11="","",AN11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AO11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR11" s="43"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="19" t="str">
-        <f aca="false">IF(A11="","",AR11*$D11+IF($F11="Exempt",0,AS11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU11" s="50" t="str">
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="46"/>
+      <c r="AT11" s="60" t="str">
+        <f aca="false">IF(A11="","",AR11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AS11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV11" s="43"/>
-      <c r="AW11" s="43"/>
-      <c r="AX11" s="19" t="str">
-        <f aca="false">IF(A11="","",AV11*$D11+IF($F11="Exempt",0,AW11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY11" s="50" t="str">
+      <c r="AV11" s="46"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="60" t="str">
+        <f aca="false">IF(A11="","",AV11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AW11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY11" s="59" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="43"/>
-      <c r="BB11" s="19" t="str">
-        <f aca="false">IF(A11="","",AZ11*$D11+IF($F11="Exempt",0,BA11*$D11*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC11" s="42" t="str">
+      <c r="AZ11" s="46"/>
+      <c r="BA11" s="46"/>
+      <c r="BB11" s="60" t="str">
+        <f aca="false">IF(A11="","",AZ11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,BA11*$D11*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC11" s="45" t="str">
         <f aca="false">IF(A11="","",SUM(G11,K11,O11,S11,W11,AA11,AE11,AI11,AM11,AQ11,AU11,AY11))</f>
         <v/>
       </c>
-      <c r="BD11" s="42" t="str">
+      <c r="BD11" s="45" t="str">
         <f aca="false">IF(A11="","",SUM(H11,I11,L11,M11,P11,Q11,T11,U11,X11,Y11,AB11,AC11,AF11,AG11,AJ11,AK11,AN11,AO11,AR11,AS11,AV11,AW11,AZ11,BA11))</f>
         <v/>
       </c>
@@ -5214,148 +5396,148 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12"/>
-      <c r="B12" s="45" t="str">
+      <c r="B12" s="51" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A12,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C12" s="45" t="str">
+      <c r="C12" s="51" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D12" s="46" t="str">
+      <c r="D12" s="52" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E12" s="12"/>
-      <c r="F12" s="45" t="str">
+      <c r="F12" s="53" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G12" s="47" t="str">
+      <c r="G12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="15" t="str">
-        <f aca="false">IF(A12="","",H12*$D12+IF($F12="Exempt",0,I12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="K12" s="47" t="str">
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="55" t="str">
+        <f aca="false">IF(A12="","",H12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,I12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="K12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="15" t="str">
-        <f aca="false">IF(A12="","",L12*$D12+IF($F12="Exempt",0,M12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="O12" s="47" t="str">
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="55" t="str">
+        <f aca="false">IF(A12="","",L12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,M12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="O12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="15" t="str">
-        <f aca="false">IF(A12="","",P12*$D12+IF($F12="Exempt",0,Q12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="S12" s="47" t="str">
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="55" t="str">
+        <f aca="false">IF(A12="","",P12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,Q12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="S12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="15" t="str">
-        <f aca="false">IF(A12="","",T12*$D12+IF($F12="Exempt",0,U12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="W12" s="47" t="str">
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="55" t="str">
+        <f aca="false">IF(A12="","",T12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,U12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="W12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="15" t="str">
-        <f aca="false">IF(A12="","",X12*$D12+IF($F12="Exempt",0,Y12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA12" s="47" t="str">
+      <c r="X12" s="42"/>
+      <c r="Y12" s="42"/>
+      <c r="Z12" s="55" t="str">
+        <f aca="false">IF(A12="","",X12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,Y12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="15" t="str">
-        <f aca="false">IF(A12="","",AB12*$D12+IF($F12="Exempt",0,AC12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE12" s="47" t="str">
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="55" t="str">
+        <f aca="false">IF(A12="","",AB12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AC12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="15" t="str">
-        <f aca="false">IF(A12="","",AF12*$D12+IF($F12="Exempt",0,AG12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI12" s="47" t="str">
+      <c r="AF12" s="42"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="55" t="str">
+        <f aca="false">IF(A12="","",AF12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AG12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="15" t="str">
-        <f aca="false">IF(A12="","",AJ12*$D12+IF($F12="Exempt",0,AK12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM12" s="47" t="str">
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="55" t="str">
+        <f aca="false">IF(A12="","",AJ12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AK12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="15" t="str">
-        <f aca="false">IF(A12="","",AN12*$D12+IF($F12="Exempt",0,AO12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ12" s="47" t="str">
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
+      <c r="AP12" s="55" t="str">
+        <f aca="false">IF(A12="","",AN12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AO12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="15" t="str">
-        <f aca="false">IF(A12="","",AR12*$D12+IF($F12="Exempt",0,AS12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU12" s="47" t="str">
+      <c r="AR12" s="42"/>
+      <c r="AS12" s="42"/>
+      <c r="AT12" s="55" t="str">
+        <f aca="false">IF(A12="","",AR12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AS12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV12" s="39"/>
-      <c r="AW12" s="39"/>
-      <c r="AX12" s="15" t="str">
-        <f aca="false">IF(A12="","",AV12*$D12+IF($F12="Exempt",0,AW12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY12" s="47" t="str">
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="55" t="str">
+        <f aca="false">IF(A12="","",AV12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AW12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY12" s="54" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ12" s="39"/>
-      <c r="BA12" s="39"/>
-      <c r="BB12" s="15" t="str">
-        <f aca="false">IF(A12="","",AZ12*$D12+IF($F12="Exempt",0,BA12*$D12*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC12" s="38" t="str">
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
+      <c r="BB12" s="55" t="str">
+        <f aca="false">IF(A12="","",AZ12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,BA12*$D12*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC12" s="41" t="str">
         <f aca="false">IF(A12="","",SUM(G12,K12,O12,S12,W12,AA12,AE12,AI12,AM12,AQ12,AU12,AY12))</f>
         <v/>
       </c>
-      <c r="BD12" s="38" t="str">
+      <c r="BD12" s="41" t="str">
         <f aca="false">IF(A12="","",SUM(H12,I12,L12,M12,P12,Q12,T12,U12,X12,Y12,AB12,AC12,AF12,AG12,AJ12,AK12,AN12,AO12,AR12,AS12,AV12,AW12,AZ12,BA12))</f>
         <v/>
       </c>
@@ -5370,148 +5552,148 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16"/>
-      <c r="B13" s="48" t="str">
+      <c r="B13" s="56" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A13,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C13" s="48" t="str">
+      <c r="C13" s="56" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D13" s="49" t="str">
+      <c r="D13" s="57" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E13" s="16"/>
-      <c r="F13" s="48" t="str">
+      <c r="F13" s="58" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G13" s="50" t="str">
+      <c r="G13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="19" t="str">
-        <f aca="false">IF(A13="","",H13*$D13+IF($F13="Exempt",0,I13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="K13" s="50" t="str">
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="60" t="str">
+        <f aca="false">IF(A13="","",H13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,I13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="K13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="19" t="str">
-        <f aca="false">IF(A13="","",L13*$D13+IF($F13="Exempt",0,M13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="O13" s="50" t="str">
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="60" t="str">
+        <f aca="false">IF(A13="","",L13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,M13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="O13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="19" t="str">
-        <f aca="false">IF(A13="","",P13*$D13+IF($F13="Exempt",0,Q13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="S13" s="50" t="str">
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="60" t="str">
+        <f aca="false">IF(A13="","",P13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,Q13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="S13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="19" t="str">
-        <f aca="false">IF(A13="","",T13*$D13+IF($F13="Exempt",0,U13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="W13" s="50" t="str">
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="60" t="str">
+        <f aca="false">IF(A13="","",T13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,U13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="W13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="19" t="str">
-        <f aca="false">IF(A13="","",X13*$D13+IF($F13="Exempt",0,Y13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA13" s="50" t="str">
+      <c r="X13" s="46"/>
+      <c r="Y13" s="46"/>
+      <c r="Z13" s="60" t="str">
+        <f aca="false">IF(A13="","",X13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,Y13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="19" t="str">
-        <f aca="false">IF(A13="","",AB13*$D13+IF($F13="Exempt",0,AC13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE13" s="50" t="str">
+      <c r="AB13" s="46"/>
+      <c r="AC13" s="46"/>
+      <c r="AD13" s="60" t="str">
+        <f aca="false">IF(A13="","",AB13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AC13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF13" s="43"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="19" t="str">
-        <f aca="false">IF(A13="","",AF13*$D13+IF($F13="Exempt",0,AG13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI13" s="50" t="str">
+      <c r="AF13" s="46"/>
+      <c r="AG13" s="46"/>
+      <c r="AH13" s="60" t="str">
+        <f aca="false">IF(A13="","",AF13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AG13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
-      <c r="AL13" s="19" t="str">
-        <f aca="false">IF(A13="","",AJ13*$D13+IF($F13="Exempt",0,AK13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM13" s="50" t="str">
+      <c r="AJ13" s="46"/>
+      <c r="AK13" s="46"/>
+      <c r="AL13" s="60" t="str">
+        <f aca="false">IF(A13="","",AJ13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AK13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN13" s="43"/>
-      <c r="AO13" s="43"/>
-      <c r="AP13" s="19" t="str">
-        <f aca="false">IF(A13="","",AN13*$D13+IF($F13="Exempt",0,AO13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ13" s="50" t="str">
+      <c r="AN13" s="46"/>
+      <c r="AO13" s="46"/>
+      <c r="AP13" s="60" t="str">
+        <f aca="false">IF(A13="","",AN13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AO13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR13" s="43"/>
-      <c r="AS13" s="43"/>
-      <c r="AT13" s="19" t="str">
-        <f aca="false">IF(A13="","",AR13*$D13+IF($F13="Exempt",0,AS13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU13" s="50" t="str">
+      <c r="AR13" s="46"/>
+      <c r="AS13" s="46"/>
+      <c r="AT13" s="60" t="str">
+        <f aca="false">IF(A13="","",AR13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AS13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV13" s="43"/>
-      <c r="AW13" s="43"/>
-      <c r="AX13" s="19" t="str">
-        <f aca="false">IF(A13="","",AV13*$D13+IF($F13="Exempt",0,AW13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY13" s="50" t="str">
+      <c r="AV13" s="46"/>
+      <c r="AW13" s="46"/>
+      <c r="AX13" s="60" t="str">
+        <f aca="false">IF(A13="","",AV13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AW13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY13" s="59" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ13" s="43"/>
-      <c r="BA13" s="43"/>
-      <c r="BB13" s="19" t="str">
-        <f aca="false">IF(A13="","",AZ13*$D13+IF($F13="Exempt",0,BA13*$D13*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC13" s="42" t="str">
+      <c r="AZ13" s="46"/>
+      <c r="BA13" s="46"/>
+      <c r="BB13" s="60" t="str">
+        <f aca="false">IF(A13="","",AZ13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,BA13*$D13*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC13" s="45" t="str">
         <f aca="false">IF(A13="","",SUM(G13,K13,O13,S13,W13,AA13,AE13,AI13,AM13,AQ13,AU13,AY13))</f>
         <v/>
       </c>
-      <c r="BD13" s="42" t="str">
+      <c r="BD13" s="45" t="str">
         <f aca="false">IF(A13="","",SUM(H13,I13,L13,M13,P13,Q13,T13,U13,X13,Y13,AB13,AC13,AF13,AG13,AJ13,AK13,AN13,AO13,AR13,AS13,AV13,AW13,AZ13,BA13))</f>
         <v/>
       </c>
@@ -5526,148 +5708,148 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12"/>
-      <c r="B14" s="45" t="str">
+      <c r="B14" s="51" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A14,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C14" s="45" t="str">
+      <c r="C14" s="51" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D14" s="46" t="str">
+      <c r="D14" s="52" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="45" t="str">
+      <c r="F14" s="53" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G14" s="47" t="str">
+      <c r="G14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="15" t="str">
-        <f aca="false">IF(A14="","",H14*$D14+IF($F14="Exempt",0,I14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="K14" s="47" t="str">
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="55" t="str">
+        <f aca="false">IF(A14="","",H14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,I14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="K14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="15" t="str">
-        <f aca="false">IF(A14="","",L14*$D14+IF($F14="Exempt",0,M14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="O14" s="47" t="str">
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="55" t="str">
+        <f aca="false">IF(A14="","",L14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,M14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="O14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="15" t="str">
-        <f aca="false">IF(A14="","",P14*$D14+IF($F14="Exempt",0,Q14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="S14" s="47" t="str">
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="55" t="str">
+        <f aca="false">IF(A14="","",P14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,Q14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="S14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="15" t="str">
-        <f aca="false">IF(A14="","",T14*$D14+IF($F14="Exempt",0,U14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="W14" s="47" t="str">
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="55" t="str">
+        <f aca="false">IF(A14="","",T14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,U14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="W14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="15" t="str">
-        <f aca="false">IF(A14="","",X14*$D14+IF($F14="Exempt",0,Y14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA14" s="47" t="str">
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="55" t="str">
+        <f aca="false">IF(A14="","",X14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,Y14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="15" t="str">
-        <f aca="false">IF(A14="","",AB14*$D14+IF($F14="Exempt",0,AC14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE14" s="47" t="str">
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="55" t="str">
+        <f aca="false">IF(A14="","",AB14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AC14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF14" s="39"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="15" t="str">
-        <f aca="false">IF(A14="","",AF14*$D14+IF($F14="Exempt",0,AG14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI14" s="47" t="str">
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
+      <c r="AH14" s="55" t="str">
+        <f aca="false">IF(A14="","",AF14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AG14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="39"/>
-      <c r="AK14" s="39"/>
-      <c r="AL14" s="15" t="str">
-        <f aca="false">IF(A14="","",AJ14*$D14+IF($F14="Exempt",0,AK14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM14" s="47" t="str">
+      <c r="AJ14" s="42"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="55" t="str">
+        <f aca="false">IF(A14="","",AJ14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AK14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN14" s="39"/>
-      <c r="AO14" s="39"/>
-      <c r="AP14" s="15" t="str">
-        <f aca="false">IF(A14="","",AN14*$D14+IF($F14="Exempt",0,AO14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ14" s="47" t="str">
+      <c r="AN14" s="42"/>
+      <c r="AO14" s="42"/>
+      <c r="AP14" s="55" t="str">
+        <f aca="false">IF(A14="","",AN14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AO14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR14" s="39"/>
-      <c r="AS14" s="39"/>
-      <c r="AT14" s="15" t="str">
-        <f aca="false">IF(A14="","",AR14*$D14+IF($F14="Exempt",0,AS14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU14" s="47" t="str">
+      <c r="AR14" s="42"/>
+      <c r="AS14" s="42"/>
+      <c r="AT14" s="55" t="str">
+        <f aca="false">IF(A14="","",AR14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AS14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV14" s="39"/>
-      <c r="AW14" s="39"/>
-      <c r="AX14" s="15" t="str">
-        <f aca="false">IF(A14="","",AV14*$D14+IF($F14="Exempt",0,AW14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY14" s="47" t="str">
+      <c r="AV14" s="42"/>
+      <c r="AW14" s="42"/>
+      <c r="AX14" s="55" t="str">
+        <f aca="false">IF(A14="","",AV14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AW14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY14" s="54" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ14" s="39"/>
-      <c r="BA14" s="39"/>
-      <c r="BB14" s="15" t="str">
-        <f aca="false">IF(A14="","",AZ14*$D14+IF($F14="Exempt",0,BA14*$D14*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC14" s="38" t="str">
+      <c r="AZ14" s="42"/>
+      <c r="BA14" s="42"/>
+      <c r="BB14" s="55" t="str">
+        <f aca="false">IF(A14="","",AZ14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,BA14*$D14*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC14" s="41" t="str">
         <f aca="false">IF(A14="","",SUM(G14,K14,O14,S14,W14,AA14,AE14,AI14,AM14,AQ14,AU14,AY14))</f>
         <v/>
       </c>
-      <c r="BD14" s="38" t="str">
+      <c r="BD14" s="41" t="str">
         <f aca="false">IF(A14="","",SUM(H14,I14,L14,M14,P14,Q14,T14,U14,X14,Y14,AB14,AC14,AF14,AG14,AJ14,AK14,AN14,AO14,AR14,AS14,AV14,AW14,AZ14,BA14))</f>
         <v/>
       </c>
@@ -5682,148 +5864,148 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16"/>
-      <c r="B15" s="48" t="str">
+      <c r="B15" s="56" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A15,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C15" s="48" t="str">
+      <c r="C15" s="56" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D15" s="49" t="str">
+      <c r="D15" s="57" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E15" s="16"/>
-      <c r="F15" s="48" t="str">
+      <c r="F15" s="58" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G15" s="50" t="str">
+      <c r="G15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="19" t="str">
-        <f aca="false">IF(A15="","",H15*$D15+IF($F15="Exempt",0,I15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="K15" s="50" t="str">
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="60" t="str">
+        <f aca="false">IF(A15="","",H15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,I15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="K15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="19" t="str">
-        <f aca="false">IF(A15="","",L15*$D15+IF($F15="Exempt",0,M15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="O15" s="50" t="str">
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="60" t="str">
+        <f aca="false">IF(A15="","",L15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,M15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="O15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="19" t="str">
-        <f aca="false">IF(A15="","",P15*$D15+IF($F15="Exempt",0,Q15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="S15" s="50" t="str">
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="60" t="str">
+        <f aca="false">IF(A15="","",P15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,Q15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="S15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="19" t="str">
-        <f aca="false">IF(A15="","",T15*$D15+IF($F15="Exempt",0,U15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="W15" s="50" t="str">
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="60" t="str">
+        <f aca="false">IF(A15="","",T15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,U15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="W15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="19" t="str">
-        <f aca="false">IF(A15="","",X15*$D15+IF($F15="Exempt",0,Y15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA15" s="50" t="str">
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="60" t="str">
+        <f aca="false">IF(A15="","",X15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,Y15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="19" t="str">
-        <f aca="false">IF(A15="","",AB15*$D15+IF($F15="Exempt",0,AC15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE15" s="50" t="str">
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="60" t="str">
+        <f aca="false">IF(A15="","",AB15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AC15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="19" t="str">
-        <f aca="false">IF(A15="","",AF15*$D15+IF($F15="Exempt",0,AG15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI15" s="50" t="str">
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="60" t="str">
+        <f aca="false">IF(A15="","",AF15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AG15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="19" t="str">
-        <f aca="false">IF(A15="","",AJ15*$D15+IF($F15="Exempt",0,AK15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM15" s="50" t="str">
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="60" t="str">
+        <f aca="false">IF(A15="","",AJ15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AK15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="19" t="str">
-        <f aca="false">IF(A15="","",AN15*$D15+IF($F15="Exempt",0,AO15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ15" s="50" t="str">
+      <c r="AN15" s="46"/>
+      <c r="AO15" s="46"/>
+      <c r="AP15" s="60" t="str">
+        <f aca="false">IF(A15="","",AN15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AO15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="19" t="str">
-        <f aca="false">IF(A15="","",AR15*$D15+IF($F15="Exempt",0,AS15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU15" s="50" t="str">
+      <c r="AR15" s="46"/>
+      <c r="AS15" s="46"/>
+      <c r="AT15" s="60" t="str">
+        <f aca="false">IF(A15="","",AR15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AS15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV15" s="43"/>
-      <c r="AW15" s="43"/>
-      <c r="AX15" s="19" t="str">
-        <f aca="false">IF(A15="","",AV15*$D15+IF($F15="Exempt",0,AW15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY15" s="50" t="str">
+      <c r="AV15" s="46"/>
+      <c r="AW15" s="46"/>
+      <c r="AX15" s="60" t="str">
+        <f aca="false">IF(A15="","",AV15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AW15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY15" s="59" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ15" s="43"/>
-      <c r="BA15" s="43"/>
-      <c r="BB15" s="19" t="str">
-        <f aca="false">IF(A15="","",AZ15*$D15+IF($F15="Exempt",0,BA15*$D15*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC15" s="42" t="str">
+      <c r="AZ15" s="46"/>
+      <c r="BA15" s="46"/>
+      <c r="BB15" s="60" t="str">
+        <f aca="false">IF(A15="","",AZ15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,BA15*$D15*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC15" s="45" t="str">
         <f aca="false">IF(A15="","",SUM(G15,K15,O15,S15,W15,AA15,AE15,AI15,AM15,AQ15,AU15,AY15))</f>
         <v/>
       </c>
-      <c r="BD15" s="42" t="str">
+      <c r="BD15" s="45" t="str">
         <f aca="false">IF(A15="","",SUM(H15,I15,L15,M15,P15,Q15,T15,U15,X15,Y15,AB15,AC15,AF15,AG15,AJ15,AK15,AN15,AO15,AR15,AS15,AV15,AW15,AZ15,BA15))</f>
         <v/>
       </c>
@@ -5838,148 +6020,148 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
-      <c r="B16" s="45" t="str">
+      <c r="B16" s="51" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A16,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C16" s="45" t="str">
+      <c r="C16" s="51" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D16" s="46" t="str">
+      <c r="D16" s="52" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E16" s="12"/>
-      <c r="F16" s="45" t="str">
+      <c r="F16" s="53" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G16" s="47" t="str">
+      <c r="G16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="15" t="str">
-        <f aca="false">IF(A16="","",H16*$D16+IF($F16="Exempt",0,I16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="K16" s="47" t="str">
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="55" t="str">
+        <f aca="false">IF(A16="","",H16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,I16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="K16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="15" t="str">
-        <f aca="false">IF(A16="","",L16*$D16+IF($F16="Exempt",0,M16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="O16" s="47" t="str">
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="55" t="str">
+        <f aca="false">IF(A16="","",L16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,M16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="O16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="15" t="str">
-        <f aca="false">IF(A16="","",P16*$D16+IF($F16="Exempt",0,Q16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="S16" s="47" t="str">
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="55" t="str">
+        <f aca="false">IF(A16="","",P16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,Q16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="S16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T16" s="39"/>
-      <c r="U16" s="39"/>
-      <c r="V16" s="15" t="str">
-        <f aca="false">IF(A16="","",T16*$D16+IF($F16="Exempt",0,U16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="W16" s="47" t="str">
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="55" t="str">
+        <f aca="false">IF(A16="","",T16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,U16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="W16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X16" s="39"/>
-      <c r="Y16" s="39"/>
-      <c r="Z16" s="15" t="str">
-        <f aca="false">IF(A16="","",X16*$D16+IF($F16="Exempt",0,Y16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA16" s="47" t="str">
+      <c r="X16" s="42"/>
+      <c r="Y16" s="42"/>
+      <c r="Z16" s="55" t="str">
+        <f aca="false">IF(A16="","",X16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,Y16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB16" s="39"/>
-      <c r="AC16" s="39"/>
-      <c r="AD16" s="15" t="str">
-        <f aca="false">IF(A16="","",AB16*$D16+IF($F16="Exempt",0,AC16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE16" s="47" t="str">
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="42"/>
+      <c r="AD16" s="55" t="str">
+        <f aca="false">IF(A16="","",AB16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AC16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF16" s="39"/>
-      <c r="AG16" s="39"/>
-      <c r="AH16" s="15" t="str">
-        <f aca="false">IF(A16="","",AF16*$D16+IF($F16="Exempt",0,AG16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI16" s="47" t="str">
+      <c r="AF16" s="42"/>
+      <c r="AG16" s="42"/>
+      <c r="AH16" s="55" t="str">
+        <f aca="false">IF(A16="","",AF16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AG16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="15" t="str">
-        <f aca="false">IF(A16="","",AJ16*$D16+IF($F16="Exempt",0,AK16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM16" s="47" t="str">
+      <c r="AJ16" s="42"/>
+      <c r="AK16" s="42"/>
+      <c r="AL16" s="55" t="str">
+        <f aca="false">IF(A16="","",AJ16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AK16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN16" s="39"/>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="15" t="str">
-        <f aca="false">IF(A16="","",AN16*$D16+IF($F16="Exempt",0,AO16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ16" s="47" t="str">
+      <c r="AN16" s="42"/>
+      <c r="AO16" s="42"/>
+      <c r="AP16" s="55" t="str">
+        <f aca="false">IF(A16="","",AN16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AO16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR16" s="39"/>
-      <c r="AS16" s="39"/>
-      <c r="AT16" s="15" t="str">
-        <f aca="false">IF(A16="","",AR16*$D16+IF($F16="Exempt",0,AS16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU16" s="47" t="str">
+      <c r="AR16" s="42"/>
+      <c r="AS16" s="42"/>
+      <c r="AT16" s="55" t="str">
+        <f aca="false">IF(A16="","",AR16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AS16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV16" s="39"/>
-      <c r="AW16" s="39"/>
-      <c r="AX16" s="15" t="str">
-        <f aca="false">IF(A16="","",AV16*$D16+IF($F16="Exempt",0,AW16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY16" s="47" t="str">
+      <c r="AV16" s="42"/>
+      <c r="AW16" s="42"/>
+      <c r="AX16" s="55" t="str">
+        <f aca="false">IF(A16="","",AV16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AW16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY16" s="54" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ16" s="39"/>
-      <c r="BA16" s="39"/>
-      <c r="BB16" s="15" t="str">
-        <f aca="false">IF(A16="","",AZ16*$D16+IF($F16="Exempt",0,BA16*$D16*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC16" s="38" t="str">
+      <c r="AZ16" s="42"/>
+      <c r="BA16" s="42"/>
+      <c r="BB16" s="55" t="str">
+        <f aca="false">IF(A16="","",AZ16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,BA16*$D16*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC16" s="41" t="str">
         <f aca="false">IF(A16="","",SUM(G16,K16,O16,S16,W16,AA16,AE16,AI16,AM16,AQ16,AU16,AY16))</f>
         <v/>
       </c>
-      <c r="BD16" s="38" t="str">
+      <c r="BD16" s="41" t="str">
         <f aca="false">IF(A16="","",SUM(H16,I16,L16,M16,P16,Q16,T16,U16,X16,Y16,AB16,AC16,AF16,AG16,AJ16,AK16,AN16,AO16,AR16,AS16,AV16,AW16,AZ16,BA16))</f>
         <v/>
       </c>
@@ -5994,148 +6176,148 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="16"/>
-      <c r="B17" s="48" t="str">
+      <c r="B17" s="56" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A17,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C17" s="48" t="str">
+      <c r="C17" s="56" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D17" s="49" t="str">
+      <c r="D17" s="57" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E17" s="16"/>
-      <c r="F17" s="48" t="str">
+      <c r="F17" s="58" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G17" s="50" t="str">
+      <c r="G17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="19" t="str">
-        <f aca="false">IF(A17="","",H17*$D17+IF($F17="Exempt",0,I17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="K17" s="50" t="str">
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="60" t="str">
+        <f aca="false">IF(A17="","",H17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,I17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="K17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="19" t="str">
-        <f aca="false">IF(A17="","",L17*$D17+IF($F17="Exempt",0,M17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="O17" s="50" t="str">
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="60" t="str">
+        <f aca="false">IF(A17="","",L17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,M17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="O17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="19" t="str">
-        <f aca="false">IF(A17="","",P17*$D17+IF($F17="Exempt",0,Q17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="S17" s="50" t="str">
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="60" t="str">
+        <f aca="false">IF(A17="","",P17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,Q17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="S17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="19" t="str">
-        <f aca="false">IF(A17="","",T17*$D17+IF($F17="Exempt",0,U17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="W17" s="50" t="str">
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="60" t="str">
+        <f aca="false">IF(A17="","",T17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,U17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="W17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="19" t="str">
-        <f aca="false">IF(A17="","",X17*$D17+IF($F17="Exempt",0,Y17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA17" s="50" t="str">
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="60" t="str">
+        <f aca="false">IF(A17="","",X17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,Y17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="19" t="str">
-        <f aca="false">IF(A17="","",AB17*$D17+IF($F17="Exempt",0,AC17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE17" s="50" t="str">
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="60" t="str">
+        <f aca="false">IF(A17="","",AB17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AC17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="43"/>
-      <c r="AH17" s="19" t="str">
-        <f aca="false">IF(A17="","",AF17*$D17+IF($F17="Exempt",0,AG17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI17" s="50" t="str">
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="60" t="str">
+        <f aca="false">IF(A17="","",AF17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AG17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ17" s="43"/>
-      <c r="AK17" s="43"/>
-      <c r="AL17" s="19" t="str">
-        <f aca="false">IF(A17="","",AJ17*$D17+IF($F17="Exempt",0,AK17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM17" s="50" t="str">
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="60" t="str">
+        <f aca="false">IF(A17="","",AJ17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AK17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN17" s="43"/>
-      <c r="AO17" s="43"/>
-      <c r="AP17" s="19" t="str">
-        <f aca="false">IF(A17="","",AN17*$D17+IF($F17="Exempt",0,AO17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ17" s="50" t="str">
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="46"/>
+      <c r="AP17" s="60" t="str">
+        <f aca="false">IF(A17="","",AN17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AO17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR17" s="43"/>
-      <c r="AS17" s="43"/>
-      <c r="AT17" s="19" t="str">
-        <f aca="false">IF(A17="","",AR17*$D17+IF($F17="Exempt",0,AS17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU17" s="50" t="str">
+      <c r="AR17" s="46"/>
+      <c r="AS17" s="46"/>
+      <c r="AT17" s="60" t="str">
+        <f aca="false">IF(A17="","",AR17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AS17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV17" s="43"/>
-      <c r="AW17" s="43"/>
-      <c r="AX17" s="19" t="str">
-        <f aca="false">IF(A17="","",AV17*$D17+IF($F17="Exempt",0,AW17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY17" s="50" t="str">
+      <c r="AV17" s="46"/>
+      <c r="AW17" s="46"/>
+      <c r="AX17" s="60" t="str">
+        <f aca="false">IF(A17="","",AV17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AW17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY17" s="59" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ17" s="43"/>
-      <c r="BA17" s="43"/>
-      <c r="BB17" s="19" t="str">
-        <f aca="false">IF(A17="","",AZ17*$D17+IF($F17="Exempt",0,BA17*$D17*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC17" s="42" t="str">
+      <c r="AZ17" s="46"/>
+      <c r="BA17" s="46"/>
+      <c r="BB17" s="60" t="str">
+        <f aca="false">IF(A17="","",AZ17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,BA17*$D17*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC17" s="45" t="str">
         <f aca="false">IF(A17="","",SUM(G17,K17,O17,S17,W17,AA17,AE17,AI17,AM17,AQ17,AU17,AY17))</f>
         <v/>
       </c>
-      <c r="BD17" s="42" t="str">
+      <c r="BD17" s="45" t="str">
         <f aca="false">IF(A17="","",SUM(H17,I17,L17,M17,P17,Q17,T17,U17,X17,Y17,AB17,AC17,AF17,AG17,AJ17,AK17,AN17,AO17,AR17,AS17,AV17,AW17,AZ17,BA17))</f>
         <v/>
       </c>
@@ -6150,148 +6332,148 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12"/>
-      <c r="B18" s="45" t="str">
+      <c r="B18" s="51" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A18,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C18" s="45" t="str">
+      <c r="C18" s="51" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D18" s="46" t="str">
+      <c r="D18" s="52" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="45" t="str">
+      <c r="F18" s="53" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G18" s="47" t="str">
+      <c r="G18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="15" t="str">
-        <f aca="false">IF(A18="","",H18*$D18+IF($F18="Exempt",0,I18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="K18" s="47" t="str">
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="55" t="str">
+        <f aca="false">IF(A18="","",H18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,I18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="K18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L18" s="39"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="15" t="str">
-        <f aca="false">IF(A18="","",L18*$D18+IF($F18="Exempt",0,M18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="O18" s="47" t="str">
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="55" t="str">
+        <f aca="false">IF(A18="","",L18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,M18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="O18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="15" t="str">
-        <f aca="false">IF(A18="","",P18*$D18+IF($F18="Exempt",0,Q18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="S18" s="47" t="str">
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="55" t="str">
+        <f aca="false">IF(A18="","",P18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,Q18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="S18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T18" s="39"/>
-      <c r="U18" s="39"/>
-      <c r="V18" s="15" t="str">
-        <f aca="false">IF(A18="","",T18*$D18+IF($F18="Exempt",0,U18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="W18" s="47" t="str">
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="55" t="str">
+        <f aca="false">IF(A18="","",T18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,U18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="W18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="39"/>
-      <c r="Z18" s="15" t="str">
-        <f aca="false">IF(A18="","",X18*$D18+IF($F18="Exempt",0,Y18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA18" s="47" t="str">
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="55" t="str">
+        <f aca="false">IF(A18="","",X18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,Y18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB18" s="39"/>
-      <c r="AC18" s="39"/>
-      <c r="AD18" s="15" t="str">
-        <f aca="false">IF(A18="","",AB18*$D18+IF($F18="Exempt",0,AC18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE18" s="47" t="str">
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="55" t="str">
+        <f aca="false">IF(A18="","",AB18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AC18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF18" s="39"/>
-      <c r="AG18" s="39"/>
-      <c r="AH18" s="15" t="str">
-        <f aca="false">IF(A18="","",AF18*$D18+IF($F18="Exempt",0,AG18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI18" s="47" t="str">
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="55" t="str">
+        <f aca="false">IF(A18="","",AF18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AG18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ18" s="39"/>
-      <c r="AK18" s="39"/>
-      <c r="AL18" s="15" t="str">
-        <f aca="false">IF(A18="","",AJ18*$D18+IF($F18="Exempt",0,AK18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM18" s="47" t="str">
+      <c r="AJ18" s="42"/>
+      <c r="AK18" s="42"/>
+      <c r="AL18" s="55" t="str">
+        <f aca="false">IF(A18="","",AJ18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AK18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN18" s="39"/>
-      <c r="AO18" s="39"/>
-      <c r="AP18" s="15" t="str">
-        <f aca="false">IF(A18="","",AN18*$D18+IF($F18="Exempt",0,AO18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ18" s="47" t="str">
+      <c r="AN18" s="42"/>
+      <c r="AO18" s="42"/>
+      <c r="AP18" s="55" t="str">
+        <f aca="false">IF(A18="","",AN18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AO18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR18" s="39"/>
-      <c r="AS18" s="39"/>
-      <c r="AT18" s="15" t="str">
-        <f aca="false">IF(A18="","",AR18*$D18+IF($F18="Exempt",0,AS18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU18" s="47" t="str">
+      <c r="AR18" s="42"/>
+      <c r="AS18" s="42"/>
+      <c r="AT18" s="55" t="str">
+        <f aca="false">IF(A18="","",AR18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AS18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV18" s="39"/>
-      <c r="AW18" s="39"/>
-      <c r="AX18" s="15" t="str">
-        <f aca="false">IF(A18="","",AV18*$D18+IF($F18="Exempt",0,AW18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY18" s="47" t="str">
+      <c r="AV18" s="42"/>
+      <c r="AW18" s="42"/>
+      <c r="AX18" s="55" t="str">
+        <f aca="false">IF(A18="","",AV18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AW18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY18" s="54" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ18" s="39"/>
-      <c r="BA18" s="39"/>
-      <c r="BB18" s="15" t="str">
-        <f aca="false">IF(A18="","",AZ18*$D18+IF($F18="Exempt",0,BA18*$D18*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC18" s="38" t="str">
+      <c r="AZ18" s="42"/>
+      <c r="BA18" s="42"/>
+      <c r="BB18" s="55" t="str">
+        <f aca="false">IF(A18="","",AZ18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,BA18*$D18*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC18" s="41" t="str">
         <f aca="false">IF(A18="","",SUM(G18,K18,O18,S18,W18,AA18,AE18,AI18,AM18,AQ18,AU18,AY18))</f>
         <v/>
       </c>
-      <c r="BD18" s="38" t="str">
+      <c r="BD18" s="41" t="str">
         <f aca="false">IF(A18="","",SUM(H18,I18,L18,M18,P18,Q18,T18,U18,X18,Y18,AB18,AC18,AF18,AG18,AJ18,AK18,AN18,AO18,AR18,AS18,AV18,AW18,AZ18,BA18))</f>
         <v/>
       </c>
@@ -6306,148 +6488,148 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16"/>
-      <c r="B19" s="48" t="str">
+      <c r="B19" s="56" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A19,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C19" s="48" t="str">
+      <c r="C19" s="56" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D19" s="49" t="str">
+      <c r="D19" s="57" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E19" s="16"/>
-      <c r="F19" s="48" t="str">
+      <c r="F19" s="58" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G19" s="50" t="str">
+      <c r="G19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="19" t="str">
-        <f aca="false">IF(A19="","",H19*$D19+IF($F19="Exempt",0,I19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="K19" s="50" t="str">
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="60" t="str">
+        <f aca="false">IF(A19="","",H19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,I19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="K19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="19" t="str">
-        <f aca="false">IF(A19="","",L19*$D19+IF($F19="Exempt",0,M19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="O19" s="50" t="str">
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="60" t="str">
+        <f aca="false">IF(A19="","",L19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,M19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="O19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="19" t="str">
-        <f aca="false">IF(A19="","",P19*$D19+IF($F19="Exempt",0,Q19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="S19" s="50" t="str">
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="60" t="str">
+        <f aca="false">IF(A19="","",P19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,Q19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="S19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="19" t="str">
-        <f aca="false">IF(A19="","",T19*$D19+IF($F19="Exempt",0,U19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="W19" s="50" t="str">
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="60" t="str">
+        <f aca="false">IF(A19="","",T19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,U19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="W19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="19" t="str">
-        <f aca="false">IF(A19="","",X19*$D19+IF($F19="Exempt",0,Y19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA19" s="50" t="str">
+      <c r="X19" s="46"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="60" t="str">
+        <f aca="false">IF(A19="","",X19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,Y19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="19" t="str">
-        <f aca="false">IF(A19="","",AB19*$D19+IF($F19="Exempt",0,AC19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE19" s="50" t="str">
+      <c r="AB19" s="46"/>
+      <c r="AC19" s="46"/>
+      <c r="AD19" s="60" t="str">
+        <f aca="false">IF(A19="","",AB19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AC19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF19" s="43"/>
-      <c r="AG19" s="43"/>
-      <c r="AH19" s="19" t="str">
-        <f aca="false">IF(A19="","",AF19*$D19+IF($F19="Exempt",0,AG19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI19" s="50" t="str">
+      <c r="AF19" s="46"/>
+      <c r="AG19" s="46"/>
+      <c r="AH19" s="60" t="str">
+        <f aca="false">IF(A19="","",AF19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AG19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ19" s="43"/>
-      <c r="AK19" s="43"/>
-      <c r="AL19" s="19" t="str">
-        <f aca="false">IF(A19="","",AJ19*$D19+IF($F19="Exempt",0,AK19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM19" s="50" t="str">
+      <c r="AJ19" s="46"/>
+      <c r="AK19" s="46"/>
+      <c r="AL19" s="60" t="str">
+        <f aca="false">IF(A19="","",AJ19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AK19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN19" s="43"/>
-      <c r="AO19" s="43"/>
-      <c r="AP19" s="19" t="str">
-        <f aca="false">IF(A19="","",AN19*$D19+IF($F19="Exempt",0,AO19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ19" s="50" t="str">
+      <c r="AN19" s="46"/>
+      <c r="AO19" s="46"/>
+      <c r="AP19" s="60" t="str">
+        <f aca="false">IF(A19="","",AN19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AO19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="19" t="str">
-        <f aca="false">IF(A19="","",AR19*$D19+IF($F19="Exempt",0,AS19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU19" s="50" t="str">
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46"/>
+      <c r="AT19" s="60" t="str">
+        <f aca="false">IF(A19="","",AR19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AS19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV19" s="43"/>
-      <c r="AW19" s="43"/>
-      <c r="AX19" s="19" t="str">
-        <f aca="false">IF(A19="","",AV19*$D19+IF($F19="Exempt",0,AW19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY19" s="50" t="str">
+      <c r="AV19" s="46"/>
+      <c r="AW19" s="46"/>
+      <c r="AX19" s="60" t="str">
+        <f aca="false">IF(A19="","",AV19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AW19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY19" s="59" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ19" s="43"/>
-      <c r="BA19" s="43"/>
-      <c r="BB19" s="19" t="str">
-        <f aca="false">IF(A19="","",AZ19*$D19+IF($F19="Exempt",0,BA19*$D19*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC19" s="42" t="str">
+      <c r="AZ19" s="46"/>
+      <c r="BA19" s="46"/>
+      <c r="BB19" s="60" t="str">
+        <f aca="false">IF(A19="","",AZ19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,BA19*$D19*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC19" s="45" t="str">
         <f aca="false">IF(A19="","",SUM(G19,K19,O19,S19,W19,AA19,AE19,AI19,AM19,AQ19,AU19,AY19))</f>
         <v/>
       </c>
-      <c r="BD19" s="42" t="str">
+      <c r="BD19" s="45" t="str">
         <f aca="false">IF(A19="","",SUM(H19,I19,L19,M19,P19,Q19,T19,U19,X19,Y19,AB19,AC19,AF19,AG19,AJ19,AK19,AN19,AO19,AR19,AS19,AV19,AW19,AZ19,BA19))</f>
         <v/>
       </c>
@@ -6462,148 +6644,148 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
-      <c r="B20" s="45" t="str">
+      <c r="B20" s="51" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A20,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C20" s="45" t="str">
+      <c r="C20" s="51" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D20" s="46" t="str">
+      <c r="D20" s="52" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="45" t="str">
+      <c r="F20" s="53" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G20" s="47" t="str">
+      <c r="G20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="15" t="str">
-        <f aca="false">IF(A20="","",H20*$D20+IF($F20="Exempt",0,I20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="K20" s="47" t="str">
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="55" t="str">
+        <f aca="false">IF(A20="","",H20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,I20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="K20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="15" t="str">
-        <f aca="false">IF(A20="","",L20*$D20+IF($F20="Exempt",0,M20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="O20" s="47" t="str">
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="55" t="str">
+        <f aca="false">IF(A20="","",L20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,M20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="O20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="15" t="str">
-        <f aca="false">IF(A20="","",P20*$D20+IF($F20="Exempt",0,Q20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="S20" s="47" t="str">
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="55" t="str">
+        <f aca="false">IF(A20="","",P20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,Q20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="S20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T20" s="39"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="15" t="str">
-        <f aca="false">IF(A20="","",T20*$D20+IF($F20="Exempt",0,U20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="W20" s="47" t="str">
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="55" t="str">
+        <f aca="false">IF(A20="","",T20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,U20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="W20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="15" t="str">
-        <f aca="false">IF(A20="","",X20*$D20+IF($F20="Exempt",0,Y20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AA20" s="47" t="str">
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="55" t="str">
+        <f aca="false">IF(A20="","",X20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,Y20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AA20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB20" s="39"/>
-      <c r="AC20" s="39"/>
-      <c r="AD20" s="15" t="str">
-        <f aca="false">IF(A20="","",AB20*$D20+IF($F20="Exempt",0,AC20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AE20" s="47" t="str">
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="55" t="str">
+        <f aca="false">IF(A20="","",AB20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AC20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF20" s="39"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="15" t="str">
-        <f aca="false">IF(A20="","",AF20*$D20+IF($F20="Exempt",0,AG20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AI20" s="47" t="str">
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="42"/>
+      <c r="AH20" s="55" t="str">
+        <f aca="false">IF(A20="","",AF20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AG20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AI20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="39"/>
-      <c r="AL20" s="15" t="str">
-        <f aca="false">IF(A20="","",AJ20*$D20+IF($F20="Exempt",0,AK20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AM20" s="47" t="str">
+      <c r="AJ20" s="42"/>
+      <c r="AK20" s="42"/>
+      <c r="AL20" s="55" t="str">
+        <f aca="false">IF(A20="","",AJ20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AK20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AM20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN20" s="39"/>
-      <c r="AO20" s="39"/>
-      <c r="AP20" s="15" t="str">
-        <f aca="false">IF(A20="","",AN20*$D20+IF($F20="Exempt",0,AO20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AQ20" s="47" t="str">
+      <c r="AN20" s="42"/>
+      <c r="AO20" s="42"/>
+      <c r="AP20" s="55" t="str">
+        <f aca="false">IF(A20="","",AN20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AO20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AQ20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR20" s="39"/>
-      <c r="AS20" s="39"/>
-      <c r="AT20" s="15" t="str">
-        <f aca="false">IF(A20="","",AR20*$D20+IF($F20="Exempt",0,AS20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AU20" s="47" t="str">
+      <c r="AR20" s="42"/>
+      <c r="AS20" s="42"/>
+      <c r="AT20" s="55" t="str">
+        <f aca="false">IF(A20="","",AR20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AS20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AU20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV20" s="39"/>
-      <c r="AW20" s="39"/>
-      <c r="AX20" s="15" t="str">
-        <f aca="false">IF(A20="","",AV20*$D20+IF($F20="Exempt",0,AW20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="AY20" s="47" t="str">
+      <c r="AV20" s="42"/>
+      <c r="AW20" s="42"/>
+      <c r="AX20" s="55" t="str">
+        <f aca="false">IF(A20="","",AV20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AW20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="AY20" s="54" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ20" s="39"/>
-      <c r="BA20" s="39"/>
-      <c r="BB20" s="15" t="str">
-        <f aca="false">IF(A20="","",AZ20*$D20+IF($F20="Exempt",0,BA20*$D20*1.5))</f>
-        <v/>
-      </c>
-      <c r="BC20" s="38" t="str">
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="55" t="str">
+        <f aca="false">IF(A20="","",AZ20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,BA20*$D20*1.5))</f>
+        <v/>
+      </c>
+      <c r="BC20" s="41" t="str">
         <f aca="false">IF(A20="","",SUM(G20,K20,O20,S20,W20,AA20,AE20,AI20,AM20,AQ20,AU20,AY20))</f>
         <v/>
       </c>
-      <c r="BD20" s="38" t="str">
+      <c r="BD20" s="41" t="str">
         <f aca="false">IF(A20="","",SUM(H20,I20,L20,M20,P20,Q20,T20,U20,X20,Y20,AB20,AC20,AF20,AG20,AJ20,AK20,AN20,AO20,AR20,AS20,AV20,AW20,AZ20,BA20))</f>
         <v/>
       </c>
@@ -6617,11 +6799,11 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="27" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
         <v>108</v>
       </c>
@@ -6640,49 +6822,77 @@
       <c r="F24" s="11" t="s">
         <v>181</v>
       </c>
+      <c r="G24" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="n">
+      <c r="A25" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A25-1)</f>
         <v>46023</v>
       </c>
       <c r="C25" s="15" t="n">
-        <f aca="false">SUM(J$6:J$20)</f>
-        <v>18537.7355769231</v>
-      </c>
-      <c r="D25" s="28" t="n">
+        <f aca="false">SUMIFS(J$6:J$20,$E$6:$E$20,"Prime")</f>
+        <v>13749.7355769231</v>
+      </c>
+      <c r="D25" s="31" t="n">
         <f aca="false">C25*Rates!$B$3</f>
-        <v>6488.20745192308</v>
-      </c>
-      <c r="E25" s="28" t="n">
+        <v>4812.40745192308</v>
+      </c>
+      <c r="E25" s="31" t="n">
         <f aca="false">(C25+D25)*Rates!$B$4</f>
-        <v>13764.2686658654</v>
+        <v>10209.1786658654</v>
       </c>
       <c r="F25" s="15" t="n">
         <f aca="false">C25+D25+E25</f>
-        <v>38790.2116947115</v>
+        <v>28771.3216947115</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <f aca="false">SUMIFS(J$6:J$20,$E$6:$E$20,"Sub")</f>
+        <v>4275</v>
+      </c>
+      <c r="H25" s="61" t="n">
+        <f aca="false">F25+G25</f>
+        <v>33046.3216947115</v>
+      </c>
+      <c r="I25" s="62" t="n">
+        <f aca="false">H25*Rates!$B$5</f>
+        <v>3965.55860336539</v>
+      </c>
+      <c r="J25" s="63" t="n">
+        <f aca="false">H25+I25</f>
+        <v>37011.8802980769</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="31" t="n">
+      <c r="A26" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A26-1)</f>
         <v>46054</v>
       </c>
       <c r="C26" s="19" t="n">
-        <f aca="false">SUM(N$6:N$20)</f>
+        <f aca="false">SUMIFS(N$6:N$20,$E$6:$E$20,"Prime")</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="36" t="n">
         <f aca="false">C26*Rates!$B$3</f>
         <v>4812.40745192308</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="36" t="n">
         <f aca="false">(C26+D26)*Rates!$B$4</f>
         <v>10209.1786658654</v>
       </c>
@@ -6690,24 +6900,40 @@
         <f aca="false">C26+D26+E26</f>
         <v>28771.3216947115</v>
       </c>
+      <c r="G26" s="19" t="n">
+        <f aca="false">SUMIFS(N$6:N$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="61" t="n">
+        <f aca="false">F26+G26</f>
+        <v>28771.3216947115</v>
+      </c>
+      <c r="I26" s="62" t="n">
+        <f aca="false">H26*Rates!$B$5</f>
+        <v>3452.55860336539</v>
+      </c>
+      <c r="J26" s="63" t="n">
+        <f aca="false">H26+I26</f>
+        <v>32223.8802980769</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46082</v>
       </c>
       <c r="C27" s="15" t="n">
-        <f aca="false">SUM(R$6:R$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="28" t="n">
+        <f aca="false">SUMIFS(R$6:R$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="31" t="n">
         <f aca="false">C27*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="31" t="n">
         <f aca="false">(C27+D27)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6715,24 +6941,40 @@
         <f aca="false">C27+D27+E27</f>
         <v>0</v>
       </c>
+      <c r="G27" s="15" t="n">
+        <f aca="false">SUMIFS(R$6:R$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="61" t="n">
+        <f aca="false">F27+G27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="62" t="n">
+        <f aca="false">H27*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="63" t="n">
+        <f aca="false">H27+I27</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46113</v>
       </c>
       <c r="C28" s="19" t="n">
-        <f aca="false">SUM(V$6:V$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="33" t="n">
+        <f aca="false">SUMIFS(V$6:V$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="36" t="n">
         <f aca="false">C28*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="36" t="n">
         <f aca="false">(C28+D28)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6740,24 +6982,40 @@
         <f aca="false">C28+D28+E28</f>
         <v>0</v>
       </c>
+      <c r="G28" s="19" t="n">
+        <f aca="false">SUMIFS(V$6:V$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="61" t="n">
+        <f aca="false">F28+G28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="62" t="n">
+        <f aca="false">H28*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="63" t="n">
+        <f aca="false">H28+I28</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46143</v>
       </c>
       <c r="C29" s="15" t="n">
-        <f aca="false">SUM(Z$6:Z$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="28" t="n">
+        <f aca="false">SUMIFS(Z$6:Z$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="31" t="n">
         <f aca="false">C29*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E29" s="28" t="n">
+      <c r="E29" s="31" t="n">
         <f aca="false">(C29+D29)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6765,24 +7023,40 @@
         <f aca="false">C29+D29+E29</f>
         <v>0</v>
       </c>
+      <c r="G29" s="15" t="n">
+        <f aca="false">SUMIFS(Z$6:Z$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="61" t="n">
+        <f aca="false">F29+G29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="62" t="n">
+        <f aca="false">H29*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="63" t="n">
+        <f aca="false">H29+I29</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="32" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46174</v>
       </c>
       <c r="C30" s="19" t="n">
-        <f aca="false">SUM(AD$6:AD$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="33" t="n">
+        <f aca="false">SUMIFS(AD$6:AD$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="36" t="n">
         <f aca="false">C30*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E30" s="33" t="n">
+      <c r="E30" s="36" t="n">
         <f aca="false">(C30+D30)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6790,24 +7064,40 @@
         <f aca="false">C30+D30+E30</f>
         <v>0</v>
       </c>
+      <c r="G30" s="19" t="n">
+        <f aca="false">SUMIFS(AD$6:AD$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="61" t="n">
+        <f aca="false">F30+G30</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="62" t="n">
+        <f aca="false">H30*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="63" t="n">
+        <f aca="false">H30+I30</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46204</v>
       </c>
       <c r="C31" s="15" t="n">
-        <f aca="false">SUM(AH$6:AH$20)</f>
+        <f aca="false">SUMIFS(AH$6:AH$20,$E$6:$E$20,"Prime")</f>
         <v>4326.92307692308</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="31" t="n">
         <f aca="false">C31*Rates!$B$3</f>
         <v>1514.42307692308</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E31" s="31" t="n">
         <f aca="false">(C31+D31)*Rates!$B$4</f>
         <v>3212.74038461539</v>
       </c>
@@ -6815,24 +7105,40 @@
         <f aca="false">C31+D31+E31</f>
         <v>9054.08653846154</v>
       </c>
+      <c r="G31" s="15" t="n">
+        <f aca="false">SUMIFS(AH$6:AH$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="61" t="n">
+        <f aca="false">F31+G31</f>
+        <v>9054.08653846154</v>
+      </c>
+      <c r="I31" s="62" t="n">
+        <f aca="false">H31*Rates!$B$5</f>
+        <v>1086.49038461538</v>
+      </c>
+      <c r="J31" s="63" t="n">
+        <f aca="false">H31+I31</f>
+        <v>10140.5769230769</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46235</v>
       </c>
       <c r="C32" s="19" t="n">
-        <f aca="false">SUM(AL$6:AL$20)</f>
+        <f aca="false">SUMIFS(AL$6:AL$20,$E$6:$E$20,"Prime")</f>
         <v>12499.7596153846</v>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="36" t="n">
         <f aca="false">C32*Rates!$B$3</f>
         <v>4374.91586538462</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="36" t="n">
         <f aca="false">(C32+D32)*Rates!$B$4</f>
         <v>9281.07151442308</v>
       </c>
@@ -6840,24 +7146,40 @@
         <f aca="false">C32+D32+E32</f>
         <v>26155.7469951923</v>
       </c>
+      <c r="G32" s="19" t="n">
+        <f aca="false">SUMIFS(AL$6:AL$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="61" t="n">
+        <f aca="false">F32+G32</f>
+        <v>26155.7469951923</v>
+      </c>
+      <c r="I32" s="62" t="n">
+        <f aca="false">H32*Rates!$B$5</f>
+        <v>3138.68963942308</v>
+      </c>
+      <c r="J32" s="63" t="n">
+        <f aca="false">H32+I32</f>
+        <v>29294.4366346154</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46266</v>
       </c>
       <c r="C33" s="15" t="n">
-        <f aca="false">SUM(AP$6:AP$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="28" t="n">
+        <f aca="false">SUMIFS(AP$6:AP$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="31" t="n">
         <f aca="false">C33*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E33" s="31" t="n">
         <f aca="false">(C33+D33)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6865,24 +7187,40 @@
         <f aca="false">C33+D33+E33</f>
         <v>0</v>
       </c>
+      <c r="G33" s="15" t="n">
+        <f aca="false">SUMIFS(AP$6:AP$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="61" t="n">
+        <f aca="false">F33+G33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="62" t="n">
+        <f aca="false">H33*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="63" t="n">
+        <f aca="false">H33+I33</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="n">
+      <c r="A34" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46296</v>
       </c>
       <c r="C34" s="19" t="n">
-        <f aca="false">SUM(AT$6:AT$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="33" t="n">
+        <f aca="false">SUMIFS(AT$6:AT$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="36" t="n">
         <f aca="false">C34*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="36" t="n">
         <f aca="false">(C34+D34)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6890,24 +7228,40 @@
         <f aca="false">C34+D34+E34</f>
         <v>0</v>
       </c>
+      <c r="G34" s="19" t="n">
+        <f aca="false">SUMIFS(AT$6:AT$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="61" t="n">
+        <f aca="false">F34+G34</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="62" t="n">
+        <f aca="false">H34*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="63" t="n">
+        <f aca="false">H34+I34</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="27" t="n">
+      <c r="B35" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46327</v>
       </c>
       <c r="C35" s="15" t="n">
-        <f aca="false">SUM(AX$6:AX$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="28" t="n">
+        <f aca="false">SUMIFS(AX$6:AX$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="31" t="n">
         <f aca="false">C35*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E35" s="28" t="n">
+      <c r="E35" s="31" t="n">
         <f aca="false">(C35+D35)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6915,24 +7269,40 @@
         <f aca="false">C35+D35+E35</f>
         <v>0</v>
       </c>
+      <c r="G35" s="15" t="n">
+        <f aca="false">SUMIFS(AX$6:AX$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="61" t="n">
+        <f aca="false">F35+G35</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="62" t="n">
+        <f aca="false">H35*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="63" t="n">
+        <f aca="false">H35+I35</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="31" t="n">
+      <c r="A36" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46357</v>
       </c>
       <c r="C36" s="19" t="n">
-        <f aca="false">SUM(BB$6:BB$20)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="33" t="n">
+        <f aca="false">SUMIFS(BB$6:BB$20,$E$6:$E$20,"Prime")</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="36" t="n">
         <f aca="false">C36*Rates!$B$3</f>
         <v>0</v>
       </c>
-      <c r="E36" s="33" t="n">
+      <c r="E36" s="36" t="n">
         <f aca="false">(C36+D36)*Rates!$B$4</f>
         <v>0</v>
       </c>
@@ -6940,9 +7310,30 @@
         <f aca="false">C36+D36+E36</f>
         <v>0</v>
       </c>
+      <c r="G36" s="19" t="n">
+        <f aca="false">SUMIFS(BB$6:BB$20,$E$6:$E$20,"Sub")</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="61" t="n">
+        <f aca="false">F36+G36</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="62" t="n">
+        <f aca="false">H36*Rates!$B$5</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="63" t="n">
+        <f aca="false">H36+I36</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6972,63 +7363,84 @@
     <mergeCell ref="BF4:BF5"/>
   </mergeCells>
   <conditionalFormatting sqref="I6:I20">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M20">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6:Q20">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U6:U20">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y6:Y20">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC6:AC20">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG6:AG20">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK6:AK20">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO6:AO20">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS6:AS20">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW6:AW20">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$F6="Exempt"</formula>
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA6:BA20">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($F6="Exempt",$E6="Sub")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E20">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>$E6="Sub"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>$E6="Prime"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:F20">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>$E6="Sub"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F20">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$F6="Exempt"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>$F6="Non-Exempt"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -7051,6 +7463,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E40"/>
@@ -7065,32 +7478,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>183</v>
+      <c r="A3" s="27" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="44" t="s">
-        <v>185</v>
+      <c r="E4" s="64" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7098,10 +7511,10 @@
         <v>46036</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>1</v>
@@ -7115,10 +7528,10 @@
         <v>46056</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>2</v>
@@ -7132,10 +7545,10 @@
         <v>46132</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>4</v>
@@ -7250,35 +7663,38 @@
       <c r="E22" s="18"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="51" t="n">
+      <c r="A23" s="65"/>
+      <c r="B23" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="21" t="n">
         <f aca="false">SUM(E5:E22)</f>
         <v>25900</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="s">
-        <v>192</v>
+      <c r="A25" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="44" t="s">
-        <v>193</v>
+      <c r="C26" s="64" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46023</v>
       </c>
@@ -7288,10 +7704,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46054</v>
       </c>
@@ -7301,10 +7717,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46082</v>
       </c>
@@ -7314,10 +7730,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="32" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46113</v>
       </c>
@@ -7327,10 +7743,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46143</v>
       </c>
@@ -7340,10 +7756,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46174</v>
       </c>
@@ -7353,10 +7769,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46204</v>
       </c>
@@ -7366,10 +7782,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="n">
+      <c r="A34" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46235</v>
       </c>
@@ -7379,10 +7795,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="27" t="n">
+      <c r="B35" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46266</v>
       </c>
@@ -7392,10 +7808,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="31" t="n">
+      <c r="A36" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46296</v>
       </c>
@@ -7405,10 +7821,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="26" t="n">
+      <c r="A37" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B37" s="27" t="n">
+      <c r="B37" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A37-1)</f>
         <v>46327</v>
       </c>
@@ -7418,10 +7834,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="n">
+      <c r="A38" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B38" s="32" t="n">
+      <c r="B38" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A38-1)</f>
         <v>46357</v>
       </c>
@@ -7450,6 +7866,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF0F6E56"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E40"/>
@@ -7464,32 +7881,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>183</v>
+      <c r="A3" s="27" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="44" t="s">
-        <v>185</v>
+      <c r="E4" s="64" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7497,10 +7914,10 @@
         <v>46042</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>1</v>
@@ -7514,10 +7931,10 @@
         <v>46042</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>1</v>
@@ -7531,10 +7948,10 @@
         <v>46091</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>3</v>
@@ -7649,35 +8066,38 @@
       <c r="E22" s="18"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="E23" s="51" t="n">
+      <c r="A23" s="65"/>
+      <c r="B23" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="21" t="n">
         <f aca="false">SUM(E5:E22)</f>
         <v>2240</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="s">
-        <v>192</v>
+      <c r="A25" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="44" t="s">
+      <c r="A26" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="B26" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="44" t="s">
-        <v>201</v>
+      <c r="C26" s="64" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="26" t="n">
+      <c r="A27" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46023</v>
       </c>
@@ -7687,10 +8107,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="31" t="n">
+      <c r="A28" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="32" t="n">
+      <c r="B28" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46054</v>
       </c>
@@ -7700,10 +8120,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="26" t="n">
+      <c r="A29" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46082</v>
       </c>
@@ -7713,10 +8133,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="31" t="n">
+      <c r="A30" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="32" t="n">
+      <c r="B30" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46113</v>
       </c>
@@ -7726,10 +8146,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="26" t="n">
+      <c r="A31" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46143</v>
       </c>
@@ -7739,10 +8159,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="31" t="n">
+      <c r="A32" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46174</v>
       </c>
@@ -7752,10 +8172,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="26" t="n">
+      <c r="A33" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46204</v>
       </c>
@@ -7765,10 +8185,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="n">
+      <c r="A34" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46235</v>
       </c>
@@ -7778,10 +8198,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="26" t="n">
+      <c r="A35" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="27" t="n">
+      <c r="B35" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46266</v>
       </c>
@@ -7791,10 +8211,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="31" t="n">
+      <c r="A36" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46296</v>
       </c>
@@ -7804,10 +8224,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="26" t="n">
+      <c r="A37" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B37" s="27" t="n">
+      <c r="B37" s="30" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A37-1)</f>
         <v>46327</v>
       </c>
@@ -7817,10 +8237,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="31" t="n">
+      <c r="A38" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B38" s="32" t="n">
+      <c r="B38" s="35" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A38-1)</f>
         <v>46357</v>
       </c>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="227">
   <si>
     <t xml:space="preserve">Acqlerate</t>
   </si>
@@ -59,13 +59,22 @@
     <t xml:space="preserve">1. Rates — your negotiated Fringe, Overhead, G&amp;A, and Fee rates. Everything else depends on these.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. FundingMods — log your original award and every funding modification since. This is what sets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   your current TOA (Total Obligated Amount) — it is NOT a single static number anymore, it's the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   running total of your funding log, which is how it actually works on a real contract.</t>
+    <t xml:space="preserve">2. FundingMods — log your original award and every funding modification since, split across</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Labor / Travel / ODC CLINs (leave a CLIN blank if a mod doesn't touch it). Tag a Project if</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   you run more than one under this contract — leave it blank if you don't. Your current TOA is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   NOT a single static number, it's the running total of this log, same as on a real contract. The</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   CLIN Funding Status table at the bottom shows spend against each CLIN's ceiling separately —</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   a CLIN can run out even when the contract overall still has funding left.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Dashboard — enter Program Name, Contract #, and Period of Performance dates near the top.</t>
@@ -209,6 +218,12 @@
     <t xml:space="preserve">Acqlerate  ·  acqlerate.com</t>
   </si>
   <si>
+    <t xml:space="preserve">INDIRECT RATES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied in sequence: Fringe -&gt; Overhead -&gt; G&amp;A. These drive every burdened cost figure on this sheet and on Labor.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fringe Rate (%)</t>
   </si>
   <si>
@@ -227,42 +242,48 @@
     <t xml:space="preserve">Applied to Total Cost Input (fully burdened labor + ODCs + Travel). Covers company-wide G&amp;A: executive, finance, HR, business development.</t>
   </si>
   <si>
+    <t xml:space="preserve">FEE STRUCTURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick Fixed or Award from the dropdown — the Applicable Fee Rate below switches automatically.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fee Type in Use</t>
   </si>
   <si>
     <t xml:space="preserve">Fixed</t>
   </si>
   <si>
-    <t xml:space="preserve">Type exactly "Fixed" or "Award" (case-sensitive) to switch which fee rate below is used.</t>
+    <t xml:space="preserve">Fixed = flat % of Total Cost (CPFF). Award = pool rate, actual earned fee depends on your award fee score.</t>
   </si>
   <si>
     <t xml:space="preserve">Fixed Fee Rate (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Used if Fee Type = "Fixed". A flat % of Total Cost that doesn't vary with performance (CPFF).</t>
+    <t xml:space="preserve">Used if Fee Type = Fixed. A flat % of Total Cost that doesn't vary with performance.</t>
   </si>
   <si>
     <t xml:space="preserve">Target Award Fee Rate (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Used if Fee Type = "Award". This is the MAX pool rate — actual earned fee depends on your award fee score (see the CPAF lesson). This tracker assumes 100% earned for planning; adjust down if you have a current-period score.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applicable Fee Rate (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Picked automatically from the Fee Type cell above. This is what the Dashboard tab actually uses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fee base note:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This tracker applies fee to Total Cost (burdened labor + ODCs + Travel + G&amp;A). Some contracts exclude ODCs, travel, or facilities capital cost of money from the fee base — check your specific contract's fee clause (FAR 52.216 series) before relying on this for real billing.</t>
+    <t xml:space="preserve">Used if Fee Type = Award. This is the MAX pool rate (see the CPAF lesson). This tracker assumes 100% earned for planning; adjust down if you have a current-period score.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicable Fee Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is what the Dashboard tab actually uses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee base note: this tracker applies fee to Total Cost (burdened labor + ODCs + Travel + G&amp;A). Some contracts exclude ODCs, travel, or facilities capital cost of money from the fee base — check your specific contract's fee clause (FAR 52.216 series) before relying on this for real billing.</t>
   </si>
   <si>
     <t xml:space="preserve">Funding Modification Log</t>
   </si>
   <si>
+    <t xml:space="preserve">One row per modification. Split the mod's dollars across the CLIN(s) it actually funds — leave a CLIN blank if the mod doesn't touch it. Project is optional: tag it if you run more than one project/task order under this contract, leave blank for contract-wide.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mod #</t>
   </si>
   <si>
@@ -272,10 +293,40 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Funding Added / (Removed) $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative TOA $</t>
+    <t xml:space="preserve">Project
+(optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor CLIN
+$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel CLIN
+$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODC CLIN
+$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mod Total
+$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Labor
+TOA $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Travel
+TOA $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. ODC
+TOA $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Total
+TOA $</t>
   </si>
   <si>
     <t xml:space="preserve">P00000 (Award)</t>
@@ -290,10 +341,37 @@
     <t xml:space="preserve">Incremental funding — added scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Current TOA (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cumulative total as of the last modification entered above.</t>
+    <t xml:space="preserve">CLIN Funding Status (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative
+TOA $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent to
+Date $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining
+$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
     <t xml:space="preserve">Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
@@ -493,9 +571,6 @@
     <t xml:space="preserve">Non-Exempt</t>
   </si>
   <si>
-    <t xml:space="preserve">Labor</t>
-  </si>
-  <si>
     <t xml:space="preserve">One row per person. Max Hrs = prorated standard capacity for that month. OT Hrs grays out for Exempt people (don't earn OT) and Subs (typically T&amp;M, not tracked here).</t>
   </si>
   <si>
@@ -661,9 +736,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total ODCs $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travel</t>
   </si>
   <si>
     <t xml:space="preserve">Airfare</t>
@@ -701,7 +773,7 @@
     <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,6 +834,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF085041"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
@@ -769,8 +849,17 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF085041"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF085041"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -785,15 +874,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF008000"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF085041"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -807,7 +895,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,26 +910,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE1F5EE"/>
+        <bgColor rgb="FFE6F1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF0F6E56"/>
         <bgColor rgb="FF01696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFAEEDA"/>
+        <fgColor rgb="FF085041"/>
+        <bgColor rgb="FF0F6E56"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE1F5EE"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF1EFE8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF085041"/>
-        <bgColor rgb="FF0F6E56"/>
+        <fgColor rgb="FFE6F1FB"/>
+        <bgColor rgb="FFEEEDFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAEEDA"/>
+        <bgColor rgb="FFF1EFE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEDFE"/>
+        <bgColor rgb="FFE6F1FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1EFE8"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -909,7 +1021,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -938,35 +1050,67 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -974,27 +1118,79 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1002,71 +1198,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1074,103 +1254,143 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1272,7 +1492,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFEEEDFE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1282,9 +1502,9 @@
       <rgbColor rgb="FF0F6E56"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFE6F1FB"/>
+      <rgbColor rgb="FFF1EFE8"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1835,7 +2055,7 @@
     <tabColor rgb="FFBFBFBF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
@@ -1938,25 +2158,25 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>18</v>
+      <c r="A23" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2006,48 +2226,48 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
+      <c r="A36" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>31</v>
+      <c r="A37" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="A39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4"/>
+      <c r="A41" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>35</v>
+      <c r="A42" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="A44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2062,25 +2282,25 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
+      <c r="A49" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="A51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="5" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2090,25 +2310,25 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
+      <c r="A54" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>46</v>
+      <c r="A55" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>48</v>
-      </c>
+      <c r="A57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="5" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2128,31 +2348,46 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
+      <c r="A62" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>53</v>
+      <c r="A63" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2173,109 +2408,196 @@
     <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="7" t="n">
+      <c r="C6" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="10" t="n">
         <v>0.55</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="7" t="n">
+      <c r="C7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="7" t="n">
+      <c r="C8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="10" t="n">
         <v>0.07</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="7" t="n">
+      <c r="C14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="10" t="n">
-        <f aca="false">IF(B7="Fixed",B8,IF(B7="Award",B9,NA()))</f>
+      <c r="C15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14" t="n">
+        <f aca="false">IF(B13="Fixed",B14,IF(B13="Award",B15,NA()))</f>
         <v>0.07</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>76</v>
-      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A19:F19"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13" type="list">
+      <formula1>"Fixed,Award"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2293,174 +2615,508 @@
     <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="L1" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+    </row>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <v>46023</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="14" t="n">
+      <c r="C5" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="23" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H5" s="24" t="n">
+        <f aca="false">IF(A5="","",SUM(E5:G5))</f>
         <v>2000000</v>
       </c>
-      <c r="E4" s="15" t="n">
-        <f aca="false">IF(D4="","",D4)</f>
+      <c r="I5" s="25" t="n">
+        <f aca="false">IF(A5="","",SUM($E$5:E5))</f>
+        <v>1400000</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <f aca="false">IF(A5="","",SUM($F$5:F5))</f>
+        <v>300000</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <f aca="false">IF(A5="","",SUM($G$5:G5))</f>
+        <v>300000</v>
+      </c>
+      <c r="L5" s="26" t="n">
+        <f aca="false">IF(A5="","",I5+J5+K5)</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="17" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="28" t="n">
         <v>46143</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="C6" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="29"/>
+      <c r="E6" s="30" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <f aca="false">IF(A6="","",SUM(E6:G6))</f>
         <v>400000</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <f aca="false">IF(D5="","",SUM($D$4:D5))</f>
+      <c r="I6" s="32" t="n">
+        <f aca="false">IF(A6="","",SUM($E$5:E6))</f>
+        <v>1700000</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <f aca="false">IF(A6="","",SUM($F$5:F6))</f>
+        <v>350000</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <f aca="false">IF(A6="","",SUM($G$5:G6))</f>
+        <v>350000</v>
+      </c>
+      <c r="L6" s="33" t="n">
+        <f aca="false">IF(A6="","",I6+J6+K6)</f>
         <v>2400000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15" t="str">
-        <f aca="false">IF(D6="","",SUM($D$4:D6))</f>
-        <v/>
-      </c>
-    </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19" t="str">
-        <f aca="false">IF(D7="","",SUM($D$4:D7))</f>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24" t="str">
+        <f aca="false">IF(A7="","",SUM(E7:G7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="25" t="str">
+        <f aca="false">IF(A7="","",SUM($E$5:E7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="25" t="str">
+        <f aca="false">IF(A7="","",SUM($F$5:F7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="25" t="str">
+        <f aca="false">IF(A7="","",SUM($G$5:G7))</f>
+        <v/>
+      </c>
+      <c r="L7" s="26" t="str">
+        <f aca="false">IF(A7="","",I7+J7+K7)</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15" t="str">
-        <f aca="false">IF(D8="","",SUM($D$4:D8))</f>
+      <c r="A8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31" t="str">
+        <f aca="false">IF(A8="","",SUM(E8:G8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="32" t="str">
+        <f aca="false">IF(A8="","",SUM($E$5:E8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="32" t="str">
+        <f aca="false">IF(A8="","",SUM($F$5:F8))</f>
+        <v/>
+      </c>
+      <c r="K8" s="32" t="str">
+        <f aca="false">IF(A8="","",SUM($G$5:G8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="33" t="str">
+        <f aca="false">IF(A8="","",I8+J8+K8)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19" t="str">
-        <f aca="false">IF(D9="","",SUM($D$4:D9))</f>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24" t="str">
+        <f aca="false">IF(A9="","",SUM(E9:G9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="25" t="str">
+        <f aca="false">IF(A9="","",SUM($E$5:E9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="25" t="str">
+        <f aca="false">IF(A9="","",SUM($F$5:F9))</f>
+        <v/>
+      </c>
+      <c r="K9" s="25" t="str">
+        <f aca="false">IF(A9="","",SUM($G$5:G9))</f>
+        <v/>
+      </c>
+      <c r="L9" s="26" t="str">
+        <f aca="false">IF(A9="","",I9+J9+K9)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="15" t="str">
-        <f aca="false">IF(D10="","",SUM($D$4:D10))</f>
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31" t="str">
+        <f aca="false">IF(A10="","",SUM(E10:G10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="32" t="str">
+        <f aca="false">IF(A10="","",SUM($E$5:E10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="32" t="str">
+        <f aca="false">IF(A10="","",SUM($F$5:F10))</f>
+        <v/>
+      </c>
+      <c r="K10" s="32" t="str">
+        <f aca="false">IF(A10="","",SUM($G$5:G10))</f>
+        <v/>
+      </c>
+      <c r="L10" s="33" t="str">
+        <f aca="false">IF(A10="","",I10+J10+K10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19" t="str">
-        <f aca="false">IF(D11="","",SUM($D$4:D11))</f>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24" t="str">
+        <f aca="false">IF(A11="","",SUM(E11:G11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="25" t="str">
+        <f aca="false">IF(A11="","",SUM($E$5:E11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="25" t="str">
+        <f aca="false">IF(A11="","",SUM($F$5:F11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="25" t="str">
+        <f aca="false">IF(A11="","",SUM($G$5:G11))</f>
+        <v/>
+      </c>
+      <c r="L11" s="26" t="str">
+        <f aca="false">IF(A11="","",I11+J11+K11)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="15" t="str">
-        <f aca="false">IF(D12="","",SUM($D$4:D12))</f>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31" t="str">
+        <f aca="false">IF(A12="","",SUM(E12:G12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="32" t="str">
+        <f aca="false">IF(A12="","",SUM($E$5:E12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="32" t="str">
+        <f aca="false">IF(A12="","",SUM($F$5:F12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="32" t="str">
+        <f aca="false">IF(A12="","",SUM($G$5:G12))</f>
+        <v/>
+      </c>
+      <c r="L12" s="33" t="str">
+        <f aca="false">IF(A12="","",I12+J12+K12)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19" t="str">
-        <f aca="false">IF(D13="","",SUM($D$4:D13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="21" t="n">
-        <f aca="false">IFERROR(INDEX(E4:E13,COUNT(D4:D13)),0)</f>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="24" t="str">
+        <f aca="false">IF(A13="","",SUM(E13:G13))</f>
+        <v/>
+      </c>
+      <c r="I13" s="25" t="str">
+        <f aca="false">IF(A13="","",SUM($E$5:E13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="str">
+        <f aca="false">IF(A13="","",SUM($F$5:F13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="25" t="str">
+        <f aca="false">IF(A13="","",SUM($G$5:G13))</f>
+        <v/>
+      </c>
+      <c r="L13" s="26" t="str">
+        <f aca="false">IF(A13="","",I13+J13+K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31" t="str">
+        <f aca="false">IF(A14="","",SUM(E14:G14))</f>
+        <v/>
+      </c>
+      <c r="I14" s="32" t="str">
+        <f aca="false">IF(A14="","",SUM($E$5:E14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="32" t="str">
+        <f aca="false">IF(A14="","",SUM($F$5:F14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="32" t="str">
+        <f aca="false">IF(A14="","",SUM($G$5:G14))</f>
+        <v/>
+      </c>
+      <c r="L14" s="33" t="str">
+        <f aca="false">IF(A14="","",I14+J14+K14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <f aca="false">IFERROR(INDEX($I$5:$I$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>1700000</v>
+      </c>
+      <c r="C19" s="35" t="n">
+        <f aca="false">SUM(Dashboard!$D$21:$D$32)</f>
+        <v>97027.4769230769</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <f aca="false">B19-C19</f>
+        <v>1602972.52307692</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <f aca="false">IFERROR(C19/B19,0)</f>
+        <v>0.0570749864253394</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="32" t="n">
+        <f aca="false">IFERROR(INDEX($J$5:$J$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>350000</v>
+      </c>
+      <c r="C20" s="38" t="n">
+        <f aca="false">SUM(Dashboard!$F$21:$F$32)</f>
+        <v>2240</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <f aca="false">B20-C20</f>
+        <v>347760</v>
+      </c>
+      <c r="E20" s="39" t="n">
+        <f aca="false">IFERROR(C20/B20,0)</f>
+        <v>0.0064</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <f aca="false">IFERROR(INDEX($K$5:$K$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>350000</v>
+      </c>
+      <c r="C21" s="35" t="n">
+        <f aca="false">SUM(Dashboard!$E$21:$E$32)</f>
+        <v>25900</v>
+      </c>
+      <c r="D21" s="25" t="n">
+        <f aca="false">B21-C21</f>
+        <v>324100</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <f aca="false">IFERROR(C21/B21,0)</f>
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="41" t="n">
+        <f aca="false">SUM(B19:B21)</f>
         <v>2400000</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>89</v>
+      <c r="C22" s="41" t="n">
+        <f aca="false">SUM(C19:C21)</f>
+        <v>125167.476923077</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <f aca="false">SUM(D19:D21)</f>
+        <v>2274832.52307692</v>
+      </c>
+      <c r="E22" s="42" t="n">
+        <f aca="false">IFERROR(C22/B22,0)</f>
+        <v>0.0521531153846154</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2498,939 +3154,939 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="9" t="s">
-        <v>92</v>
+      <c r="A3" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="9" t="s">
-        <v>94</v>
+      <c r="A4" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23" t="n">
+      <c r="A5" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="45" t="n">
         <v>46023</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23" t="n">
+      <c r="A6" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="43"/>
+      <c r="C6" s="45" t="n">
         <v>46387</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="24" t="n">
+      <c r="A7" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="46" t="n">
         <f aca="false">DATEDIF(C5,C6,"m")+1</f>
         <v>12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="25" t="n">
-        <f aca="false">FundingMods!$B$15</f>
+      <c r="A8" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="43"/>
+      <c r="C8" s="47" t="n">
+        <f aca="false">FundingMods!$B$22</f>
         <v>2400000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="26" t="n">
+      <c r="A9" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="48" t="n">
         <f aca="false">C8/C7</f>
         <v>200000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
-        <v>100</v>
+      <c r="A11" s="34" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="24" t="n">
+      <c r="A12" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="43"/>
+      <c r="C12" s="46" t="n">
         <f aca="false">COUNT(D21:D32)</f>
         <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="26" t="n">
+      <c r="A13" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="43"/>
+      <c r="C13" s="48" t="n">
         <f aca="false">IF(C12=0,0,INDEX(L21:L32,C12))</f>
         <v>150000.704344615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="26" t="n">
+      <c r="A14" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="48" t="n">
         <f aca="false">C8-C13</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="10" t="n">
+      <c r="A15" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="49" t="n">
         <f aca="false">IFERROR(C13/C8,0)</f>
         <v>0.0625002934769231</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="26" t="n">
+      <c r="A16" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="48" t="n">
         <f aca="true">IFERROR(AVERAGE(OFFSET(K21,MAX(C12-3,0),0,MIN(C12,3),1)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="24" t="str">
+      <c r="A17" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="43"/>
+      <c r="C17" s="46" t="str">
         <f aca="false">IFERROR(C14/C16,"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="28" t="str">
+      <c r="A18" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="43"/>
+      <c r="C18" s="50" t="str">
         <f aca="false">IF(C12=0,"NO DATA YET",IF(C15&gt;(C12/C7)*1.1,"AT RISK — OVERRUNNING",IF(C15&lt;(C12/C7)*0.7,"AT RISK — UNDERRUNNING","ON TRACK")))</f>
         <v>AT RISK — UNDERRUNNING</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="M20" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="O20" s="11" t="s">
-        <v>122</v>
+      <c r="A20" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="n">
+      <c r="A21" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="52" t="n">
         <f aca="false">EDATE($C$5,A21-1)</f>
         <v>46023</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="25" t="n">
         <f aca="false">$C$9*A21</f>
         <v>200000</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="35" t="n">
         <f aca="false">Labor!H25</f>
         <v>33046.3216947115</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="35" t="n">
         <f aca="false">IF(D21="","",ODCs!C27)</f>
         <v>14200</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F21" s="35" t="n">
         <f aca="false">IF(D21="","",Travel!C27)</f>
         <v>1090</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="25" t="n">
         <f aca="false">IF(D21="","",D21+E21+F21)</f>
         <v>48336.3216947115</v>
       </c>
-      <c r="H21" s="31" t="n">
-        <f aca="false">IF(G21="","",G21*Rates!$B$5)</f>
+      <c r="H21" s="35" t="n">
+        <f aca="false">IF(G21="","",G21*Rates!$B$8)</f>
         <v>5800.35860336539</v>
       </c>
-      <c r="I21" s="15" t="n">
+      <c r="I21" s="25" t="n">
         <f aca="false">IF(G21="","",G21+H21)</f>
         <v>54136.6802980769</v>
       </c>
-      <c r="J21" s="31" t="n">
-        <f aca="false">IF(I21="","",I21*Rates!$B$11)</f>
+      <c r="J21" s="35" t="n">
+        <f aca="false">IF(I21="","",I21*Rates!$C$17)</f>
         <v>3789.56762086539</v>
       </c>
-      <c r="K21" s="15" t="n">
+      <c r="K21" s="25" t="n">
         <f aca="false">IF(I21="","",I21+J21)</f>
         <v>57926.2479189423</v>
       </c>
-      <c r="L21" s="15" t="n">
+      <c r="L21" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K21)=0,"",SUM($K$21:K21))</f>
         <v>57926.2479189423</v>
       </c>
-      <c r="M21" s="32" t="n">
+      <c r="M21" s="53" t="n">
         <f aca="false">IF(OR(L21="",C21=""),"",L21-C21)</f>
         <v>-142073.752081058</v>
       </c>
-      <c r="N21" s="33" t="n">
+      <c r="N21" s="36" t="n">
         <f aca="false">IF(OR(L21="",C21="",C21=0),"",M21/C21)</f>
         <v>-0.710368760405289</v>
       </c>
-      <c r="O21" s="15" t="n">
+      <c r="O21" s="25" t="n">
         <f aca="false">IF(L21="","",$C$8-L21)</f>
         <v>2342073.75208106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="55" t="n">
         <f aca="false">EDATE($C$5,A22-1)</f>
         <v>46054</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="32" t="n">
         <f aca="false">$C$9*A22</f>
         <v>400000</v>
       </c>
-      <c r="D22" s="36" t="n">
+      <c r="D22" s="38" t="n">
         <f aca="false">Labor!H26</f>
         <v>28771.3216947115</v>
       </c>
-      <c r="E22" s="36" t="n">
+      <c r="E22" s="38" t="n">
         <f aca="false">IF(D22="","",ODCs!C28)</f>
         <v>3100</v>
       </c>
-      <c r="F22" s="36" t="n">
+      <c r="F22" s="38" t="n">
         <f aca="false">IF(D22="","",Travel!C28)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="32" t="n">
         <f aca="false">IF(D22="","",D22+E22+F22)</f>
         <v>31871.3216947115</v>
       </c>
-      <c r="H22" s="36" t="n">
-        <f aca="false">IF(G22="","",G22*Rates!$B$5)</f>
+      <c r="H22" s="38" t="n">
+        <f aca="false">IF(G22="","",G22*Rates!$B$8)</f>
         <v>3824.55860336539</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="I22" s="32" t="n">
         <f aca="false">IF(G22="","",G22+H22)</f>
         <v>35695.8802980769</v>
       </c>
-      <c r="J22" s="36" t="n">
-        <f aca="false">IF(I22="","",I22*Rates!$B$11)</f>
+      <c r="J22" s="38" t="n">
+        <f aca="false">IF(I22="","",I22*Rates!$C$17)</f>
         <v>2498.71162086539</v>
       </c>
-      <c r="K22" s="19" t="n">
+      <c r="K22" s="32" t="n">
         <f aca="false">IF(I22="","",I22+J22)</f>
         <v>38194.5919189423</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K22)=0,"",SUM($K$21:K22))</f>
         <v>96120.8398378846</v>
       </c>
-      <c r="M22" s="37" t="n">
+      <c r="M22" s="56" t="n">
         <f aca="false">IF(OR(L22="",C22=""),"",L22-C22)</f>
         <v>-303879.160162115</v>
       </c>
-      <c r="N22" s="38" t="n">
+      <c r="N22" s="39" t="n">
         <f aca="false">IF(OR(L22="",C22="",C22=0),"",M22/C22)</f>
         <v>-0.759697900405288</v>
       </c>
-      <c r="O22" s="19" t="n">
+      <c r="O22" s="32" t="n">
         <f aca="false">IF(L22="","",$C$8-L22)</f>
         <v>2303879.16016212</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="n">
+      <c r="A23" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="52" t="n">
         <f aca="false">EDATE($C$5,A23-1)</f>
         <v>46082</v>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="25" t="n">
         <f aca="false">$C$9*A23</f>
         <v>600000</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="35" t="n">
         <f aca="false">Labor!H27</f>
         <v>0</v>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="35" t="n">
         <f aca="false">IF(D23="","",ODCs!C29)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="31" t="n">
+      <c r="F23" s="35" t="n">
         <f aca="false">IF(D23="","",Travel!C29)</f>
         <v>1150</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="25" t="n">
         <f aca="false">IF(D23="","",D23+E23+F23)</f>
         <v>1150</v>
       </c>
-      <c r="H23" s="31" t="n">
-        <f aca="false">IF(G23="","",G23*Rates!$B$5)</f>
+      <c r="H23" s="35" t="n">
+        <f aca="false">IF(G23="","",G23*Rates!$B$8)</f>
         <v>138</v>
       </c>
-      <c r="I23" s="15" t="n">
+      <c r="I23" s="25" t="n">
         <f aca="false">IF(G23="","",G23+H23)</f>
         <v>1288</v>
       </c>
-      <c r="J23" s="31" t="n">
-        <f aca="false">IF(I23="","",I23*Rates!$B$11)</f>
+      <c r="J23" s="35" t="n">
+        <f aca="false">IF(I23="","",I23*Rates!$C$17)</f>
         <v>90.16</v>
       </c>
-      <c r="K23" s="15" t="n">
+      <c r="K23" s="25" t="n">
         <f aca="false">IF(I23="","",I23+J23)</f>
         <v>1378.16</v>
       </c>
-      <c r="L23" s="15" t="n">
+      <c r="L23" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K23)=0,"",SUM($K$21:K23))</f>
         <v>97498.9998378846</v>
       </c>
-      <c r="M23" s="32" t="n">
+      <c r="M23" s="53" t="n">
         <f aca="false">IF(OR(L23="",C23=""),"",L23-C23)</f>
         <v>-502501.000162115</v>
       </c>
-      <c r="N23" s="33" t="n">
+      <c r="N23" s="36" t="n">
         <f aca="false">IF(OR(L23="",C23="",C23=0),"",M23/C23)</f>
         <v>-0.837501666936859</v>
       </c>
-      <c r="O23" s="15" t="n">
+      <c r="O23" s="25" t="n">
         <f aca="false">IF(L23="","",$C$8-L23)</f>
         <v>2302501.00016212</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="55" t="n">
         <f aca="false">EDATE($C$5,A24-1)</f>
         <v>46113</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="32" t="n">
         <f aca="false">$C$9*A24</f>
         <v>800000</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="38" t="n">
         <f aca="false">Labor!H28</f>
         <v>0</v>
       </c>
-      <c r="E24" s="36" t="n">
+      <c r="E24" s="38" t="n">
         <f aca="false">IF(D24="","",ODCs!C30)</f>
         <v>8600</v>
       </c>
-      <c r="F24" s="36" t="n">
+      <c r="F24" s="38" t="n">
         <f aca="false">IF(D24="","",Travel!C30)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="32" t="n">
         <f aca="false">IF(D24="","",D24+E24+F24)</f>
         <v>8600</v>
       </c>
-      <c r="H24" s="36" t="n">
-        <f aca="false">IF(G24="","",G24*Rates!$B$5)</f>
+      <c r="H24" s="38" t="n">
+        <f aca="false">IF(G24="","",G24*Rates!$B$8)</f>
         <v>1032</v>
       </c>
-      <c r="I24" s="19" t="n">
+      <c r="I24" s="32" t="n">
         <f aca="false">IF(G24="","",G24+H24)</f>
         <v>9632</v>
       </c>
-      <c r="J24" s="36" t="n">
-        <f aca="false">IF(I24="","",I24*Rates!$B$11)</f>
+      <c r="J24" s="38" t="n">
+        <f aca="false">IF(I24="","",I24*Rates!$C$17)</f>
         <v>674.24</v>
       </c>
-      <c r="K24" s="19" t="n">
+      <c r="K24" s="32" t="n">
         <f aca="false">IF(I24="","",I24+J24)</f>
         <v>10306.24</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="L24" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K24)=0,"",SUM($K$21:K24))</f>
         <v>107805.239837885</v>
       </c>
-      <c r="M24" s="37" t="n">
+      <c r="M24" s="56" t="n">
         <f aca="false">IF(OR(L24="",C24=""),"",L24-C24)</f>
         <v>-692194.760162115</v>
       </c>
-      <c r="N24" s="38" t="n">
+      <c r="N24" s="39" t="n">
         <f aca="false">IF(OR(L24="",C24="",C24=0),"",M24/C24)</f>
         <v>-0.865243450202644</v>
       </c>
-      <c r="O24" s="19" t="n">
+      <c r="O24" s="32" t="n">
         <f aca="false">IF(L24="","",$C$8-L24)</f>
         <v>2292194.76016212</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="52" t="n">
         <f aca="false">EDATE($C$5,A25-1)</f>
         <v>46143</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="25" t="n">
         <f aca="false">$C$9*A25</f>
         <v>1000000</v>
       </c>
-      <c r="D25" s="31" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">Labor!H29</f>
         <v>0</v>
       </c>
-      <c r="E25" s="31" t="n">
+      <c r="E25" s="35" t="n">
         <f aca="false">IF(D25="","",ODCs!C31)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="31" t="n">
+      <c r="F25" s="35" t="n">
         <f aca="false">IF(D25="","",Travel!C31)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="25" t="n">
         <f aca="false">IF(D25="","",D25+E25+F25)</f>
         <v>0</v>
       </c>
-      <c r="H25" s="31" t="n">
-        <f aca="false">IF(G25="","",G25*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="15" t="n">
+      <c r="H25" s="35" t="n">
+        <f aca="false">IF(G25="","",G25*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="25" t="n">
         <f aca="false">IF(G25="","",G25+H25)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="31" t="n">
-        <f aca="false">IF(I25="","",I25*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="15" t="n">
+      <c r="J25" s="35" t="n">
+        <f aca="false">IF(I25="","",I25*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="25" t="n">
         <f aca="false">IF(I25="","",I25+J25)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="15" t="n">
+      <c r="L25" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K25)=0,"",SUM($K$21:K25))</f>
         <v>107805.239837885</v>
       </c>
-      <c r="M25" s="32" t="n">
+      <c r="M25" s="53" t="n">
         <f aca="false">IF(OR(L25="",C25=""),"",L25-C25)</f>
         <v>-892194.760162115</v>
       </c>
-      <c r="N25" s="33" t="n">
+      <c r="N25" s="36" t="n">
         <f aca="false">IF(OR(L25="",C25="",C25=0),"",M25/C25)</f>
         <v>-0.892194760162115</v>
       </c>
-      <c r="O25" s="15" t="n">
+      <c r="O25" s="25" t="n">
         <f aca="false">IF(L25="","",$C$8-L25)</f>
         <v>2292194.76016212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="55" t="n">
         <f aca="false">EDATE($C$5,A26-1)</f>
         <v>46174</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">$C$9*A26</f>
         <v>1200000</v>
       </c>
-      <c r="D26" s="36" t="n">
+      <c r="D26" s="38" t="n">
         <f aca="false">Labor!H30</f>
         <v>0</v>
       </c>
-      <c r="E26" s="36" t="n">
+      <c r="E26" s="38" t="n">
         <f aca="false">IF(D26="","",ODCs!C32)</f>
         <v>0</v>
       </c>
-      <c r="F26" s="36" t="n">
+      <c r="F26" s="38" t="n">
         <f aca="false">IF(D26="","",Travel!C32)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="32" t="n">
         <f aca="false">IF(D26="","",D26+E26+F26)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="36" t="n">
-        <f aca="false">IF(G26="","",G26*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="19" t="n">
+      <c r="H26" s="38" t="n">
+        <f aca="false">IF(G26="","",G26*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="32" t="n">
         <f aca="false">IF(G26="","",G26+H26)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="36" t="n">
-        <f aca="false">IF(I26="","",I26*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="19" t="n">
+      <c r="J26" s="38" t="n">
+        <f aca="false">IF(I26="","",I26*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="32" t="n">
         <f aca="false">IF(I26="","",I26+J26)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K26)=0,"",SUM($K$21:K26))</f>
         <v>107805.239837885</v>
       </c>
-      <c r="M26" s="37" t="n">
+      <c r="M26" s="56" t="n">
         <f aca="false">IF(OR(L26="",C26=""),"",L26-C26)</f>
         <v>-1092194.76016212</v>
       </c>
-      <c r="N26" s="38" t="n">
+      <c r="N26" s="39" t="n">
         <f aca="false">IF(OR(L26="",C26="",C26=0),"",M26/C26)</f>
         <v>-0.910162300135096</v>
       </c>
-      <c r="O26" s="19" t="n">
+      <c r="O26" s="32" t="n">
         <f aca="false">IF(L26="","",$C$8-L26)</f>
         <v>2292194.76016212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">EDATE($C$5,A27-1)</f>
         <v>46204</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">$C$9*A27</f>
         <v>1400000</v>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="35" t="n">
         <f aca="false">Labor!H31</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="E27" s="31" t="n">
+      <c r="E27" s="35" t="n">
         <f aca="false">IF(D27="","",ODCs!C33)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="31" t="n">
+      <c r="F27" s="35" t="n">
         <f aca="false">IF(D27="","",Travel!C33)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="25" t="n">
         <f aca="false">IF(D27="","",D27+E27+F27)</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="H27" s="31" t="n">
-        <f aca="false">IF(G27="","",G27*Rates!$B$5)</f>
+      <c r="H27" s="35" t="n">
+        <f aca="false">IF(G27="","",G27*Rates!$B$8)</f>
         <v>1086.49038461538</v>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I27" s="25" t="n">
         <f aca="false">IF(G27="","",G27+H27)</f>
         <v>10140.5769230769</v>
       </c>
-      <c r="J27" s="31" t="n">
-        <f aca="false">IF(I27="","",I27*Rates!$B$11)</f>
+      <c r="J27" s="35" t="n">
+        <f aca="false">IF(I27="","",I27*Rates!$C$17)</f>
         <v>709.840384615385</v>
       </c>
-      <c r="K27" s="15" t="n">
+      <c r="K27" s="25" t="n">
         <f aca="false">IF(I27="","",I27+J27)</f>
         <v>10850.4173076923</v>
       </c>
-      <c r="L27" s="15" t="n">
+      <c r="L27" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K27)=0,"",SUM($K$21:K27))</f>
         <v>118655.657145577</v>
       </c>
-      <c r="M27" s="32" t="n">
+      <c r="M27" s="53" t="n">
         <f aca="false">IF(OR(L27="",C27=""),"",L27-C27)</f>
         <v>-1281344.34285442</v>
       </c>
-      <c r="N27" s="33" t="n">
+      <c r="N27" s="36" t="n">
         <f aca="false">IF(OR(L27="",C27="",C27=0),"",M27/C27)</f>
         <v>-0.915245959181731</v>
       </c>
-      <c r="O27" s="15" t="n">
+      <c r="O27" s="25" t="n">
         <f aca="false">IF(L27="","",$C$8-L27)</f>
         <v>2281344.34285442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="55" t="n">
         <f aca="false">EDATE($C$5,A28-1)</f>
         <v>46235</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">$C$9*A28</f>
         <v>1600000</v>
       </c>
-      <c r="D28" s="36" t="n">
+      <c r="D28" s="38" t="n">
         <f aca="false">Labor!H32</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="E28" s="36" t="n">
+      <c r="E28" s="38" t="n">
         <f aca="false">IF(D28="","",ODCs!C34)</f>
         <v>0</v>
       </c>
-      <c r="F28" s="36" t="n">
+      <c r="F28" s="38" t="n">
         <f aca="false">IF(D28="","",Travel!C34)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="32" t="n">
         <f aca="false">IF(D28="","",D28+E28+F28)</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="H28" s="36" t="n">
-        <f aca="false">IF(G28="","",G28*Rates!$B$5)</f>
+      <c r="H28" s="38" t="n">
+        <f aca="false">IF(G28="","",G28*Rates!$B$8)</f>
         <v>3138.68963942308</v>
       </c>
-      <c r="I28" s="19" t="n">
+      <c r="I28" s="32" t="n">
         <f aca="false">IF(G28="","",G28+H28)</f>
         <v>29294.4366346154</v>
       </c>
-      <c r="J28" s="36" t="n">
-        <f aca="false">IF(I28="","",I28*Rates!$B$11)</f>
+      <c r="J28" s="38" t="n">
+        <f aca="false">IF(I28="","",I28*Rates!$C$17)</f>
         <v>2050.61056442308</v>
       </c>
-      <c r="K28" s="19" t="n">
+      <c r="K28" s="32" t="n">
         <f aca="false">IF(I28="","",I28+J28)</f>
         <v>31345.0471990385</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="L28" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K28)=0,"",SUM($K$21:K28))</f>
         <v>150000.704344615</v>
       </c>
-      <c r="M28" s="37" t="n">
+      <c r="M28" s="56" t="n">
         <f aca="false">IF(OR(L28="",C28=""),"",L28-C28)</f>
         <v>-1449999.29565538</v>
       </c>
-      <c r="N28" s="38" t="n">
+      <c r="N28" s="39" t="n">
         <f aca="false">IF(OR(L28="",C28="",C28=0),"",M28/C28)</f>
         <v>-0.906249559784615</v>
       </c>
-      <c r="O28" s="19" t="n">
+      <c r="O28" s="32" t="n">
         <f aca="false">IF(L28="","",$C$8-L28)</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">EDATE($C$5,A29-1)</f>
         <v>46266</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="25" t="n">
         <f aca="false">$C$9*A29</f>
         <v>1800000</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="35" t="n">
         <f aca="false">Labor!H33</f>
         <v>0</v>
       </c>
-      <c r="E29" s="31" t="n">
+      <c r="E29" s="35" t="n">
         <f aca="false">IF(D29="","",ODCs!C35)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="31" t="n">
+      <c r="F29" s="35" t="n">
         <f aca="false">IF(D29="","",Travel!C35)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="25" t="n">
         <f aca="false">IF(D29="","",D29+E29+F29)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="31" t="n">
-        <f aca="false">IF(G29="","",G29*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="15" t="n">
+      <c r="H29" s="35" t="n">
+        <f aca="false">IF(G29="","",G29*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="25" t="n">
         <f aca="false">IF(G29="","",G29+H29)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="31" t="n">
-        <f aca="false">IF(I29="","",I29*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="15" t="n">
+      <c r="J29" s="35" t="n">
+        <f aca="false">IF(I29="","",I29*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="25" t="n">
         <f aca="false">IF(I29="","",I29+J29)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="15" t="n">
+      <c r="L29" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K29)=0,"",SUM($K$21:K29))</f>
         <v>150000.704344615</v>
       </c>
-      <c r="M29" s="32" t="n">
+      <c r="M29" s="53" t="n">
         <f aca="false">IF(OR(L29="",C29=""),"",L29-C29)</f>
         <v>-1649999.29565538</v>
       </c>
-      <c r="N29" s="33" t="n">
+      <c r="N29" s="36" t="n">
         <f aca="false">IF(OR(L29="",C29="",C29=0),"",M29/C29)</f>
         <v>-0.916666275364103</v>
       </c>
-      <c r="O29" s="15" t="n">
+      <c r="O29" s="25" t="n">
         <f aca="false">IF(L29="","",$C$8-L29)</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="55" t="n">
         <f aca="false">EDATE($C$5,A30-1)</f>
         <v>46296</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="32" t="n">
         <f aca="false">$C$9*A30</f>
         <v>2000000</v>
       </c>
-      <c r="D30" s="36" t="n">
+      <c r="D30" s="38" t="n">
         <f aca="false">Labor!H34</f>
         <v>0</v>
       </c>
-      <c r="E30" s="36" t="n">
+      <c r="E30" s="38" t="n">
         <f aca="false">IF(D30="","",ODCs!C36)</f>
         <v>0</v>
       </c>
-      <c r="F30" s="36" t="n">
+      <c r="F30" s="38" t="n">
         <f aca="false">IF(D30="","",Travel!C36)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="32" t="n">
         <f aca="false">IF(D30="","",D30+E30+F30)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="36" t="n">
-        <f aca="false">IF(G30="","",G30*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="19" t="n">
+      <c r="H30" s="38" t="n">
+        <f aca="false">IF(G30="","",G30*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="32" t="n">
         <f aca="false">IF(G30="","",G30+H30)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="36" t="n">
-        <f aca="false">IF(I30="","",I30*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="19" t="n">
+      <c r="J30" s="38" t="n">
+        <f aca="false">IF(I30="","",I30*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="32" t="n">
         <f aca="false">IF(I30="","",I30+J30)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="19" t="n">
+      <c r="L30" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K30)=0,"",SUM($K$21:K30))</f>
         <v>150000.704344615</v>
       </c>
-      <c r="M30" s="37" t="n">
+      <c r="M30" s="56" t="n">
         <f aca="false">IF(OR(L30="",C30=""),"",L30-C30)</f>
         <v>-1849999.29565538</v>
       </c>
-      <c r="N30" s="38" t="n">
+      <c r="N30" s="39" t="n">
         <f aca="false">IF(OR(L30="",C30="",C30=0),"",M30/C30)</f>
         <v>-0.924999647827692</v>
       </c>
-      <c r="O30" s="19" t="n">
+      <c r="O30" s="32" t="n">
         <f aca="false">IF(L30="","",$C$8-L30)</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="52" t="n">
         <f aca="false">EDATE($C$5,A31-1)</f>
         <v>46327</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="25" t="n">
         <f aca="false">$C$9*A31</f>
         <v>2200000</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="35" t="n">
         <f aca="false">Labor!H35</f>
         <v>0</v>
       </c>
-      <c r="E31" s="31" t="n">
+      <c r="E31" s="35" t="n">
         <f aca="false">IF(D31="","",ODCs!C37)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="31" t="n">
+      <c r="F31" s="35" t="n">
         <f aca="false">IF(D31="","",Travel!C37)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="25" t="n">
         <f aca="false">IF(D31="","",D31+E31+F31)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="31" t="n">
-        <f aca="false">IF(G31="","",G31*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="15" t="n">
+      <c r="H31" s="35" t="n">
+        <f aca="false">IF(G31="","",G31*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="25" t="n">
         <f aca="false">IF(G31="","",G31+H31)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="31" t="n">
-        <f aca="false">IF(I31="","",I31*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="15" t="n">
+      <c r="J31" s="35" t="n">
+        <f aca="false">IF(I31="","",I31*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="25" t="n">
         <f aca="false">IF(I31="","",I31+J31)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="15" t="n">
+      <c r="L31" s="25" t="n">
         <f aca="false">IF(SUM($K$21:K31)=0,"",SUM($K$21:K31))</f>
         <v>150000.704344615</v>
       </c>
-      <c r="M31" s="32" t="n">
+      <c r="M31" s="53" t="n">
         <f aca="false">IF(OR(L31="",C31=""),"",L31-C31)</f>
         <v>-2049999.29565538</v>
       </c>
-      <c r="N31" s="33" t="n">
+      <c r="N31" s="36" t="n">
         <f aca="false">IF(OR(L31="",C31="",C31=0),"",M31/C31)</f>
         <v>-0.931817861661539</v>
       </c>
-      <c r="O31" s="15" t="n">
+      <c r="O31" s="25" t="n">
         <f aca="false">IF(L31="","",$C$8-L31)</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="55" t="n">
         <f aca="false">EDATE($C$5,A32-1)</f>
         <v>46357</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="32" t="n">
         <f aca="false">$C$9*A32</f>
         <v>2400000</v>
       </c>
-      <c r="D32" s="36" t="n">
+      <c r="D32" s="38" t="n">
         <f aca="false">Labor!H36</f>
         <v>0</v>
       </c>
-      <c r="E32" s="36" t="n">
+      <c r="E32" s="38" t="n">
         <f aca="false">IF(D32="","",ODCs!C38)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="36" t="n">
+      <c r="F32" s="38" t="n">
         <f aca="false">IF(D32="","",Travel!C38)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="32" t="n">
         <f aca="false">IF(D32="","",D32+E32+F32)</f>
         <v>0</v>
       </c>
-      <c r="H32" s="36" t="n">
-        <f aca="false">IF(G32="","",G32*Rates!$B$5)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="19" t="n">
+      <c r="H32" s="38" t="n">
+        <f aca="false">IF(G32="","",G32*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="32" t="n">
         <f aca="false">IF(G32="","",G32+H32)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="36" t="n">
-        <f aca="false">IF(I32="","",I32*Rates!$B$11)</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="19" t="n">
+      <c r="J32" s="38" t="n">
+        <f aca="false">IF(I32="","",I32*Rates!$C$17)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="32" t="n">
         <f aca="false">IF(I32="","",I32+J32)</f>
         <v>0</v>
       </c>
-      <c r="L32" s="19" t="n">
+      <c r="L32" s="32" t="n">
         <f aca="false">IF(SUM($K$21:K32)=0,"",SUM($K$21:K32))</f>
         <v>150000.704344615</v>
       </c>
-      <c r="M32" s="37" t="n">
+      <c r="M32" s="56" t="n">
         <f aca="false">IF(OR(L32="",C32=""),"",L32-C32)</f>
         <v>-2249999.29565538</v>
       </c>
-      <c r="N32" s="38" t="n">
+      <c r="N32" s="39" t="n">
         <f aca="false">IF(OR(L32="",C32="",C32=0),"",M32/C32)</f>
         <v>-0.937499706523077</v>
       </c>
-      <c r="O32" s="19" t="n">
+      <c r="O32" s="32" t="n">
         <f aca="false">IF(L32="","",$C$8-L32)</f>
         <v>2249999.29565538</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3483,7 +4139,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="11"/>
@@ -3494,598 +4151,598 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>140</v>
+      <c r="A4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="20" t="n">
         <v>123456</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="14" t="n">
+      <c r="B5" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="23" t="n">
         <v>150000</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="12" t="n">
+      <c r="F5" s="57"/>
+      <c r="G5" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H5" s="40" t="n">
+      <c r="H5" s="58" t="n">
         <f aca="false">IF(A5="","",IF(D5="Exempt",IF(G5=0,"",E5/G5),F5))</f>
         <v>72.1153846153846</v>
       </c>
-      <c r="I5" s="29" t="str">
+      <c r="I5" s="51" t="str">
         <f aca="false">IF(A5="","",IF(D5="Non-Exempt",H5*1.5,"N/A"))</f>
         <v>N/A</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="21" t="n">
         <v>46213</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="12" t="n">
+      <c r="K5" s="21"/>
+      <c r="L5" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="41" t="n">
+      <c r="M5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="59" t="n">
         <f aca="true">IF(A5="","",IFERROR(L5*MAX(0,DATEDIF(J5,IF(K5="",TODAY(),MIN(K5,TODAY())),"m")),0))</f>
         <v>8</v>
       </c>
-      <c r="O5" s="42"/>
-      <c r="P5" s="41" t="n">
+      <c r="O5" s="60"/>
+      <c r="P5" s="59" t="n">
         <f aca="false">IF(A5="","",M5+N5-O5)</f>
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="27" t="n">
         <v>123457</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="B6" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="30" t="n">
         <v>165000</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="16" t="n">
+      <c r="F6" s="61"/>
+      <c r="G6" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H6" s="44" t="n">
+      <c r="H6" s="62" t="n">
         <f aca="false">IF(A6="","",IF(D6="Exempt",IF(G6=0,"",E6/G6),F6))</f>
         <v>79.3269230769231</v>
       </c>
-      <c r="I6" s="34" t="str">
+      <c r="I6" s="54" t="str">
         <f aca="false">IF(A6="","",IF(D6="Non-Exempt",H6*1.5,"N/A"))</f>
         <v>N/A</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="28" t="n">
         <v>46023</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="16" t="n">
+      <c r="K6" s="28"/>
+      <c r="L6" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="M6" s="16" t="n">
+      <c r="M6" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="N6" s="45" t="n">
+      <c r="N6" s="63" t="n">
         <f aca="true">IF(A6="","",IFERROR(L6*MAX(0,DATEDIF(J6,IF(K6="",TODAY(),MIN(K6,TODAY())),"m")),0))</f>
         <v>56</v>
       </c>
-      <c r="O6" s="46"/>
-      <c r="P6" s="45" t="n">
+      <c r="O6" s="64"/>
+      <c r="P6" s="63" t="n">
         <f aca="false">IF(A6="","",M6+N6-O6)</f>
         <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="20" t="n">
         <v>123458</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="39" t="n">
+      <c r="B7" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="57" t="n">
         <v>28.5</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H7" s="40" t="n">
+      <c r="H7" s="58" t="n">
         <f aca="false">IF(A7="","",IF(D7="Exempt",IF(G7=0,"",E7/G7),F7))</f>
         <v>28.5</v>
       </c>
-      <c r="I7" s="40" t="n">
+      <c r="I7" s="58" t="n">
         <f aca="false">IF(A7="","",IF(D7="Non-Exempt",H7*1.5,"N/A"))</f>
         <v>42.75</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="21" t="n">
         <v>46023</v>
       </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="12" t="n">
+      <c r="K7" s="21"/>
+      <c r="L7" s="20" t="n">
         <v>6.67</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="41" t="n">
+      <c r="N7" s="59" t="n">
         <f aca="true">IF(A7="","",IFERROR(L7*MAX(0,DATEDIF(J7,IF(K7="",TODAY(),MIN(K7,TODAY())),"m")),0))</f>
         <v>46.69</v>
       </c>
-      <c r="O7" s="42"/>
-      <c r="P7" s="41" t="n">
+      <c r="O7" s="60"/>
+      <c r="P7" s="59" t="n">
         <f aca="false">IF(A7="","",M7+N7-O7)</f>
         <v>51.69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="16" t="n">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H8" s="44" t="str">
+      <c r="H8" s="62" t="str">
         <f aca="false">IF(A8="","",IF(D8="Exempt",IF(G8=0,"",E8/G8),F8))</f>
         <v/>
       </c>
-      <c r="I8" s="34" t="str">
+      <c r="I8" s="54" t="str">
         <f aca="false">IF(A8="","",IF(D8="Non-Exempt",H8*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="45" t="str">
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="63" t="str">
         <f aca="true">IF(A8="","",IFERROR(L8*MAX(0,DATEDIF(J8,IF(K8="",TODAY(),MIN(K8,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="45" t="str">
+      <c r="O8" s="64"/>
+      <c r="P8" s="63" t="str">
         <f aca="false">IF(A8="","",M8+N8-O8)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="12" t="n">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H9" s="40" t="str">
+      <c r="H9" s="58" t="str">
         <f aca="false">IF(A9="","",IF(D9="Exempt",IF(G9=0,"",E9/G9),F9))</f>
         <v/>
       </c>
-      <c r="I9" s="29" t="str">
+      <c r="I9" s="51" t="str">
         <f aca="false">IF(A9="","",IF(D9="Non-Exempt",H9*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="41" t="str">
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="59" t="str">
         <f aca="true">IF(A9="","",IFERROR(L9*MAX(0,DATEDIF(J9,IF(K9="",TODAY(),MIN(K9,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O9" s="42"/>
-      <c r="P9" s="41" t="str">
+      <c r="O9" s="60"/>
+      <c r="P9" s="59" t="str">
         <f aca="false">IF(A9="","",M9+N9-O9)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="16" t="n">
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H10" s="44" t="str">
+      <c r="H10" s="62" t="str">
         <f aca="false">IF(A10="","",IF(D10="Exempt",IF(G10=0,"",E10/G10),F10))</f>
         <v/>
       </c>
-      <c r="I10" s="34" t="str">
+      <c r="I10" s="54" t="str">
         <f aca="false">IF(A10="","",IF(D10="Non-Exempt",H10*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="45" t="str">
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="63" t="str">
         <f aca="true">IF(A10="","",IFERROR(L10*MAX(0,DATEDIF(J10,IF(K10="",TODAY(),MIN(K10,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O10" s="46"/>
-      <c r="P10" s="45" t="str">
+      <c r="O10" s="64"/>
+      <c r="P10" s="63" t="str">
         <f aca="false">IF(A10="","",M10+N10-O10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="12" t="n">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H11" s="40" t="str">
+      <c r="H11" s="58" t="str">
         <f aca="false">IF(A11="","",IF(D11="Exempt",IF(G11=0,"",E11/G11),F11))</f>
         <v/>
       </c>
-      <c r="I11" s="29" t="str">
+      <c r="I11" s="51" t="str">
         <f aca="false">IF(A11="","",IF(D11="Non-Exempt",H11*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="41" t="str">
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="59" t="str">
         <f aca="true">IF(A11="","",IFERROR(L11*MAX(0,DATEDIF(J11,IF(K11="",TODAY(),MIN(K11,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O11" s="42"/>
-      <c r="P11" s="41" t="str">
+      <c r="O11" s="60"/>
+      <c r="P11" s="59" t="str">
         <f aca="false">IF(A11="","",M11+N11-O11)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="16" t="n">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H12" s="44" t="str">
+      <c r="H12" s="62" t="str">
         <f aca="false">IF(A12="","",IF(D12="Exempt",IF(G12=0,"",E12/G12),F12))</f>
         <v/>
       </c>
-      <c r="I12" s="34" t="str">
+      <c r="I12" s="54" t="str">
         <f aca="false">IF(A12="","",IF(D12="Non-Exempt",H12*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="45" t="str">
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="63" t="str">
         <f aca="true">IF(A12="","",IFERROR(L12*MAX(0,DATEDIF(J12,IF(K12="",TODAY(),MIN(K12,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O12" s="46"/>
-      <c r="P12" s="45" t="str">
+      <c r="O12" s="64"/>
+      <c r="P12" s="63" t="str">
         <f aca="false">IF(A12="","",M12+N12-O12)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="12" t="n">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H13" s="40" t="str">
+      <c r="H13" s="58" t="str">
         <f aca="false">IF(A13="","",IF(D13="Exempt",IF(G13=0,"",E13/G13),F13))</f>
         <v/>
       </c>
-      <c r="I13" s="29" t="str">
+      <c r="I13" s="51" t="str">
         <f aca="false">IF(A13="","",IF(D13="Non-Exempt",H13*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="41" t="str">
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="59" t="str">
         <f aca="true">IF(A13="","",IFERROR(L13*MAX(0,DATEDIF(J13,IF(K13="",TODAY(),MIN(K13,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O13" s="42"/>
-      <c r="P13" s="41" t="str">
+      <c r="O13" s="60"/>
+      <c r="P13" s="59" t="str">
         <f aca="false">IF(A13="","",M13+N13-O13)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="16" t="n">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H14" s="44" t="str">
+      <c r="H14" s="62" t="str">
         <f aca="false">IF(A14="","",IF(D14="Exempt",IF(G14=0,"",E14/G14),F14))</f>
         <v/>
       </c>
-      <c r="I14" s="34" t="str">
+      <c r="I14" s="54" t="str">
         <f aca="false">IF(A14="","",IF(D14="Non-Exempt",H14*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="45" t="str">
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="63" t="str">
         <f aca="true">IF(A14="","",IFERROR(L14*MAX(0,DATEDIF(J14,IF(K14="",TODAY(),MIN(K14,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O14" s="46"/>
-      <c r="P14" s="45" t="str">
+      <c r="O14" s="64"/>
+      <c r="P14" s="63" t="str">
         <f aca="false">IF(A14="","",M14+N14-O14)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="12" t="n">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H15" s="40" t="str">
+      <c r="H15" s="58" t="str">
         <f aca="false">IF(A15="","",IF(D15="Exempt",IF(G15=0,"",E15/G15),F15))</f>
         <v/>
       </c>
-      <c r="I15" s="29" t="str">
+      <c r="I15" s="51" t="str">
         <f aca="false">IF(A15="","",IF(D15="Non-Exempt",H15*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="41" t="str">
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="59" t="str">
         <f aca="true">IF(A15="","",IFERROR(L15*MAX(0,DATEDIF(J15,IF(K15="",TODAY(),MIN(K15,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O15" s="42"/>
-      <c r="P15" s="41" t="str">
+      <c r="O15" s="60"/>
+      <c r="P15" s="59" t="str">
         <f aca="false">IF(A15="","",M15+N15-O15)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="16" t="n">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H16" s="44" t="str">
+      <c r="H16" s="62" t="str">
         <f aca="false">IF(A16="","",IF(D16="Exempt",IF(G16=0,"",E16/G16),F16))</f>
         <v/>
       </c>
-      <c r="I16" s="34" t="str">
+      <c r="I16" s="54" t="str">
         <f aca="false">IF(A16="","",IF(D16="Non-Exempt",H16*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="45" t="str">
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="63" t="str">
         <f aca="true">IF(A16="","",IFERROR(L16*MAX(0,DATEDIF(J16,IF(K16="",TODAY(),MIN(K16,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O16" s="46"/>
-      <c r="P16" s="45" t="str">
+      <c r="O16" s="64"/>
+      <c r="P16" s="63" t="str">
         <f aca="false">IF(A16="","",M16+N16-O16)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="12" t="n">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H17" s="40" t="str">
+      <c r="H17" s="58" t="str">
         <f aca="false">IF(A17="","",IF(D17="Exempt",IF(G17=0,"",E17/G17),F17))</f>
         <v/>
       </c>
-      <c r="I17" s="29" t="str">
+      <c r="I17" s="51" t="str">
         <f aca="false">IF(A17="","",IF(D17="Non-Exempt",H17*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="41" t="str">
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="59" t="str">
         <f aca="true">IF(A17="","",IFERROR(L17*MAX(0,DATEDIF(J17,IF(K17="",TODAY(),MIN(K17,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O17" s="42"/>
-      <c r="P17" s="41" t="str">
+      <c r="O17" s="60"/>
+      <c r="P17" s="59" t="str">
         <f aca="false">IF(A17="","",M17+N17-O17)</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="16" t="n">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="27" t="n">
         <v>2080</v>
       </c>
-      <c r="H18" s="44" t="str">
+      <c r="H18" s="62" t="str">
         <f aca="false">IF(A18="","",IF(D18="Exempt",IF(G18=0,"",E18/G18),F18))</f>
         <v/>
       </c>
-      <c r="I18" s="34" t="str">
+      <c r="I18" s="54" t="str">
         <f aca="false">IF(A18="","",IF(D18="Non-Exempt",H18*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="45" t="str">
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="63" t="str">
         <f aca="true">IF(A18="","",IFERROR(L18*MAX(0,DATEDIF(J18,IF(K18="",TODAY(),MIN(K18,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O18" s="46"/>
-      <c r="P18" s="45" t="str">
+      <c r="O18" s="64"/>
+      <c r="P18" s="63" t="str">
         <f aca="false">IF(A18="","",M18+N18-O18)</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="12" t="n">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="20" t="n">
         <v>2080</v>
       </c>
-      <c r="H19" s="40" t="str">
+      <c r="H19" s="58" t="str">
         <f aca="false">IF(A19="","",IF(D19="Exempt",IF(G19=0,"",E19/G19),F19))</f>
         <v/>
       </c>
-      <c r="I19" s="29" t="str">
+      <c r="I19" s="51" t="str">
         <f aca="false">IF(A19="","",IF(D19="Non-Exempt",H19*1.5,"N/A"))</f>
         <v/>
       </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="41" t="str">
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="59" t="str">
         <f aca="true">IF(A19="","",IFERROR(L19*MAX(0,DATEDIF(J19,IF(K19="",TODAY(),MIN(K19,TODAY())),"m")),0))</f>
         <v/>
       </c>
-      <c r="O19" s="42"/>
-      <c r="P19" s="41" t="str">
+      <c r="O19" s="60"/>
+      <c r="P19" s="59" t="str">
         <f aca="false">IF(A19="","",M19+N19-O19)</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4116,11 +4773,11 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
@@ -4156,3185 +4813,3184 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="51" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="55" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="57" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="54" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="57" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="BF1" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="49"/>
-      <c r="AA4" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="49"/>
-      <c r="AE4" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="AF4" s="49"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
-      <c r="AL4" s="49"/>
-      <c r="AM4" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="AN4" s="49"/>
-      <c r="AO4" s="49"/>
-      <c r="AP4" s="49"/>
-      <c r="AQ4" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="AR4" s="49"/>
-      <c r="AS4" s="49"/>
-      <c r="AT4" s="49"/>
-      <c r="AU4" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="AV4" s="49"/>
-      <c r="AW4" s="49"/>
-      <c r="AX4" s="49"/>
-      <c r="AY4" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="AZ4" s="49"/>
-      <c r="BA4" s="49"/>
-      <c r="BB4" s="49"/>
-      <c r="BC4" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="BD4" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="BE4" s="47" t="s">
-        <v>169</v>
-      </c>
-      <c r="BF4" s="47" t="s">
-        <v>170</v>
+      <c r="A4" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="66" t="s">
+        <v>176</v>
+      </c>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="66" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66" t="s">
+        <v>178</v>
+      </c>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="T4" s="66"/>
+      <c r="U4" s="66"/>
+      <c r="V4" s="66"/>
+      <c r="W4" s="66" t="s">
+        <v>180</v>
+      </c>
+      <c r="X4" s="66"/>
+      <c r="Y4" s="66"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="66"/>
+      <c r="AI4" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="AJ4" s="66"/>
+      <c r="AK4" s="66"/>
+      <c r="AL4" s="66"/>
+      <c r="AM4" s="66" t="s">
+        <v>184</v>
+      </c>
+      <c r="AN4" s="66"/>
+      <c r="AO4" s="66"/>
+      <c r="AP4" s="66"/>
+      <c r="AQ4" s="66" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR4" s="66"/>
+      <c r="AS4" s="66"/>
+      <c r="AT4" s="66"/>
+      <c r="AU4" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="AV4" s="66"/>
+      <c r="AW4" s="66"/>
+      <c r="AX4" s="66"/>
+      <c r="AY4" s="66" t="s">
+        <v>187</v>
+      </c>
+      <c r="AZ4" s="66"/>
+      <c r="BA4" s="66"/>
+      <c r="BB4" s="66"/>
+      <c r="BC4" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="BD4" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="BE4" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="BF4" s="19" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="N5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="R5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="V5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="W5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="X5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AD5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AH5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AI5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AJ5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AL5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AM5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AN5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AP5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AR5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AS5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AT5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AU5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AV5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="AW5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="AX5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY5" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="AZ5" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="BA5" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="BB5" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="W5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="X5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AH5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AJ5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AK5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AL5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AM5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AN5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AP5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AQ5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AR5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AS5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AT5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AU5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AV5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="AW5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="AX5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="AY5" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="AZ5" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="BA5" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="BB5" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="BC5" s="19"/>
+      <c r="BD5" s="19"/>
+      <c r="BE5" s="19"/>
+      <c r="BF5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="20" t="n">
         <v>123456</v>
       </c>
-      <c r="B6" s="51" t="str">
+      <c r="B6" s="67" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A6,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>John Smith</v>
       </c>
-      <c r="C6" s="51" t="str">
+      <c r="C6" s="67" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Engineer 4</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="68" t="n">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>72.1153846153846</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="F6" s="53" t="str">
+      <c r="E6" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F6" s="69" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Exempt</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="70" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="55" t="n">
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="72" t="n">
         <f aca="false">IF(A6="","",H6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,I6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="54" t="n">
+      <c r="K6" s="70" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="55" t="n">
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="72" t="n">
         <f aca="false">IF(A6="","",L6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,M6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="O6" s="54" t="n">
+      <c r="O6" s="70" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="55" t="n">
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="72" t="n">
         <f aca="false">IF(A6="","",P6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,Q6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="S6" s="54" t="n">
+      <c r="S6" s="73" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="55" t="n">
+      <c r="T6" s="74"/>
+      <c r="U6" s="74"/>
+      <c r="V6" s="75" t="n">
         <f aca="false">IF(A6="","",T6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,U6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="W6" s="54" t="n">
+      <c r="W6" s="73" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
-      <c r="Z6" s="55" t="n">
+      <c r="X6" s="74"/>
+      <c r="Y6" s="74"/>
+      <c r="Z6" s="75" t="n">
         <f aca="false">IF(A6="","",X6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,Y6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="54" t="n">
+      <c r="AA6" s="73" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>0</v>
       </c>
-      <c r="AB6" s="42"/>
-      <c r="AC6" s="42"/>
-      <c r="AD6" s="55" t="n">
+      <c r="AB6" s="74"/>
+      <c r="AC6" s="74"/>
+      <c r="AD6" s="75" t="n">
         <f aca="false">IF(A6="","",AB6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AC6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="54" t="n">
+      <c r="AE6" s="76" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>123.010752688172</v>
       </c>
-      <c r="AF6" s="42" t="n">
+      <c r="AF6" s="77" t="n">
         <v>60</v>
       </c>
-      <c r="AG6" s="42"/>
-      <c r="AH6" s="55" t="n">
+      <c r="AG6" s="77"/>
+      <c r="AH6" s="78" t="n">
         <f aca="false">IF(A6="","",AF6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AG6*$D6*1.5))</f>
         <v>4326.92307692308</v>
       </c>
-      <c r="AI6" s="54" t="n">
+      <c r="AI6" s="76" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ6" s="42" t="n">
+      <c r="AJ6" s="77" t="n">
         <v>173.33</v>
       </c>
-      <c r="AK6" s="42"/>
-      <c r="AL6" s="55" t="n">
+      <c r="AK6" s="77"/>
+      <c r="AL6" s="78" t="n">
         <f aca="false">IF(A6="","",AJ6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AK6*$D6*1.5))</f>
         <v>12499.7596153846</v>
       </c>
-      <c r="AM6" s="54" t="n">
+      <c r="AM6" s="76" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN6" s="42"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="55" t="n">
+      <c r="AN6" s="77"/>
+      <c r="AO6" s="77"/>
+      <c r="AP6" s="78" t="n">
         <f aca="false">IF(A6="","",AN6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AO6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="54" t="n">
+      <c r="AQ6" s="79" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR6" s="42"/>
-      <c r="AS6" s="42"/>
-      <c r="AT6" s="55" t="n">
+      <c r="AR6" s="80"/>
+      <c r="AS6" s="80"/>
+      <c r="AT6" s="81" t="n">
         <f aca="false">IF(A6="","",AR6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AS6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AU6" s="54" t="n">
+      <c r="AU6" s="79" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV6" s="42"/>
-      <c r="AW6" s="42"/>
-      <c r="AX6" s="55" t="n">
+      <c r="AV6" s="80"/>
+      <c r="AW6" s="80"/>
+      <c r="AX6" s="81" t="n">
         <f aca="false">IF(A6="","",AV6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,AW6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="54" t="n">
+      <c r="AY6" s="79" t="n">
         <f aca="false">IFERROR(IF(A6="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A6,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A6,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A6,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ6" s="42"/>
-      <c r="BA6" s="42"/>
-      <c r="BB6" s="55" t="n">
+      <c r="AZ6" s="80"/>
+      <c r="BA6" s="80"/>
+      <c r="BB6" s="81" t="n">
         <f aca="false">IF(A6="","",AZ6*$D6+IF(OR($F6="Exempt",$E6="Sub"),0,BA6*$D6*1.5))</f>
         <v>0</v>
       </c>
-      <c r="BC6" s="41" t="n">
+      <c r="BC6" s="82" t="n">
         <f aca="false">IF(A6="","",SUM(G6,K6,O6,S6,W6,AA6,AE6,AI6,AM6,AQ6,AU6,AY6))</f>
         <v>989.677419354839</v>
       </c>
-      <c r="BD6" s="41" t="n">
+      <c r="BD6" s="82" t="n">
         <f aca="false">IF(A6="","",SUM(H6,I6,L6,M6,P6,Q6,T6,U6,X6,Y6,AB6,AC6,AF6,AG6,AJ6,AK6,AN6,AO6,AR6,AS6,AV6,AW6,AZ6,BA6))</f>
         <v>233.33</v>
       </c>
-      <c r="BE6" s="15" t="n">
+      <c r="BE6" s="83" t="n">
         <f aca="false">IF(A6="","",BC6*$D6)</f>
         <v>71370.9677419355</v>
       </c>
-      <c r="BF6" s="15" t="n">
+      <c r="BF6" s="83" t="n">
         <f aca="false">IF(A6="","",SUM(J6,N6,R6,V6,Z6,AD6,AH6,AL6,AP6,AT6,AX6,BB6))</f>
         <v>16826.6826923077</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="27" t="n">
         <v>123457</v>
       </c>
-      <c r="B7" s="56" t="str">
+      <c r="B7" s="84" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A7,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>Maria Alvarez</v>
       </c>
-      <c r="C7" s="56" t="str">
+      <c r="C7" s="84" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Program Manager</v>
       </c>
-      <c r="D7" s="57" t="n">
+      <c r="D7" s="85" t="n">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>79.3269230769231</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="58" t="str">
+      <c r="E7" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="86" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Exempt</v>
       </c>
-      <c r="G7" s="59" t="n">
+      <c r="G7" s="70" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="H7" s="46" t="n">
+      <c r="H7" s="71" t="n">
         <v>173.33</v>
       </c>
-      <c r="I7" s="46"/>
-      <c r="J7" s="60" t="n">
+      <c r="I7" s="71"/>
+      <c r="J7" s="72" t="n">
         <f aca="false">IF(A7="","",H7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,I7*$D7*1.5))</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="K7" s="59" t="n">
+      <c r="K7" s="70" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="L7" s="46" t="n">
+      <c r="L7" s="71" t="n">
         <v>173.33</v>
       </c>
-      <c r="M7" s="46"/>
-      <c r="N7" s="60" t="n">
+      <c r="M7" s="71"/>
+      <c r="N7" s="72" t="n">
         <f aca="false">IF(A7="","",L7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,M7*$D7*1.5))</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="O7" s="59" t="n">
+      <c r="O7" s="70" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="60" t="n">
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="72" t="n">
         <f aca="false">IF(A7="","",P7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,Q7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="S7" s="59" t="n">
+      <c r="S7" s="73" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="60" t="n">
+      <c r="T7" s="74"/>
+      <c r="U7" s="74"/>
+      <c r="V7" s="75" t="n">
         <f aca="false">IF(A7="","",T7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,U7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="W7" s="59" t="n">
+      <c r="W7" s="73" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="60" t="n">
+      <c r="X7" s="74"/>
+      <c r="Y7" s="74"/>
+      <c r="Z7" s="75" t="n">
         <f aca="false">IF(A7="","",X7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,Y7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="59" t="n">
+      <c r="AA7" s="73" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="60" t="n">
+      <c r="AB7" s="74"/>
+      <c r="AC7" s="74"/>
+      <c r="AD7" s="75" t="n">
         <f aca="false">IF(A7="","",AB7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AC7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="59" t="n">
+      <c r="AE7" s="76" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="46"/>
-      <c r="AH7" s="60" t="n">
+      <c r="AF7" s="77"/>
+      <c r="AG7" s="77"/>
+      <c r="AH7" s="78" t="n">
         <f aca="false">IF(A7="","",AF7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AG7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AI7" s="59" t="n">
+      <c r="AI7" s="76" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ7" s="46"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="60" t="n">
+      <c r="AJ7" s="77"/>
+      <c r="AK7" s="77"/>
+      <c r="AL7" s="78" t="n">
         <f aca="false">IF(A7="","",AJ7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AK7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="59" t="n">
+      <c r="AM7" s="76" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN7" s="46"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="60" t="n">
+      <c r="AN7" s="77"/>
+      <c r="AO7" s="77"/>
+      <c r="AP7" s="78" t="n">
         <f aca="false">IF(A7="","",AN7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AO7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="59" t="n">
+      <c r="AQ7" s="79" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR7" s="46"/>
-      <c r="AS7" s="46"/>
-      <c r="AT7" s="60" t="n">
+      <c r="AR7" s="80"/>
+      <c r="AS7" s="80"/>
+      <c r="AT7" s="81" t="n">
         <f aca="false">IF(A7="","",AR7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AS7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AU7" s="59" t="n">
+      <c r="AU7" s="79" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV7" s="46"/>
-      <c r="AW7" s="46"/>
-      <c r="AX7" s="60" t="n">
+      <c r="AV7" s="80"/>
+      <c r="AW7" s="80"/>
+      <c r="AX7" s="81" t="n">
         <f aca="false">IF(A7="","",AV7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,AW7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AY7" s="59" t="n">
+      <c r="AY7" s="79" t="n">
         <f aca="false">IFERROR(IF(A7="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A7,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A7,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A7,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ7" s="46"/>
-      <c r="BA7" s="46"/>
-      <c r="BB7" s="60" t="n">
+      <c r="AZ7" s="80"/>
+      <c r="BA7" s="80"/>
+      <c r="BB7" s="81" t="n">
         <f aca="false">IF(A7="","",AZ7*$D7+IF(OR($F7="Exempt",$E7="Sub"),0,BA7*$D7*1.5))</f>
         <v>0</v>
       </c>
-      <c r="BC7" s="45" t="n">
+      <c r="BC7" s="82" t="n">
         <f aca="false">IF(A7="","",SUM(G7,K7,O7,S7,W7,AA7,AE7,AI7,AM7,AQ7,AU7,AY7))</f>
         <v>2080</v>
       </c>
-      <c r="BD7" s="45" t="n">
+      <c r="BD7" s="82" t="n">
         <f aca="false">IF(A7="","",SUM(H7,I7,L7,M7,P7,Q7,T7,U7,X7,Y7,AB7,AC7,AF7,AG7,AJ7,AK7,AN7,AO7,AR7,AS7,AV7,AW7,AZ7,BA7))</f>
         <v>346.66</v>
       </c>
-      <c r="BE7" s="19" t="n">
+      <c r="BE7" s="83" t="n">
         <f aca="false">IF(A7="","",BC7*$D7)</f>
         <v>165000</v>
       </c>
-      <c r="BF7" s="19" t="n">
+      <c r="BF7" s="83" t="n">
         <f aca="false">IF(A7="","",SUM(J7,N7,R7,V7,Z7,AD7,AH7,AL7,AP7,AT7,AX7,BB7))</f>
         <v>27499.4711538462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="20" t="n">
         <v>123458</v>
       </c>
-      <c r="B8" s="51" t="str">
+      <c r="B8" s="67" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A8,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v>Dave Chen</v>
       </c>
-      <c r="C8" s="51" t="str">
+      <c r="C8" s="67" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Admin Support</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="68" t="n">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>28.5</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="53" t="str">
+      <c r="E8" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F8" s="69" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
         <v>Non-Exempt</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="70" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="71" t="n">
         <v>150</v>
       </c>
-      <c r="I8" s="42" t="n">
+      <c r="I8" s="71" t="n">
         <v>12</v>
       </c>
-      <c r="J8" s="55" t="n">
+      <c r="J8" s="72" t="n">
         <f aca="false">IF(A8="","",H8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,I8*$D8*1.5))</f>
         <v>4275</v>
       </c>
-      <c r="K8" s="54" t="n">
+      <c r="K8" s="70" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="55" t="n">
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="72" t="n">
         <f aca="false">IF(A8="","",L8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,M8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="O8" s="54" t="n">
+      <c r="O8" s="70" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="55" t="n">
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="72" t="n">
         <f aca="false">IF(A8="","",P8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,Q8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="S8" s="54" t="n">
+      <c r="S8" s="73" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="55" t="n">
+      <c r="T8" s="74"/>
+      <c r="U8" s="74"/>
+      <c r="V8" s="75" t="n">
         <f aca="false">IF(A8="","",T8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,U8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="W8" s="54" t="n">
+      <c r="W8" s="73" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="42"/>
-      <c r="Z8" s="55" t="n">
+      <c r="X8" s="74"/>
+      <c r="Y8" s="74"/>
+      <c r="Z8" s="75" t="n">
         <f aca="false">IF(A8="","",X8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,Y8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AA8" s="54" t="n">
+      <c r="AA8" s="73" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="42"/>
-      <c r="AD8" s="55" t="n">
+      <c r="AB8" s="74"/>
+      <c r="AC8" s="74"/>
+      <c r="AD8" s="75" t="n">
         <f aca="false">IF(A8="","",AB8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AC8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="54" t="n">
+      <c r="AE8" s="76" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="42"/>
-      <c r="AH8" s="55" t="n">
+      <c r="AF8" s="77"/>
+      <c r="AG8" s="77"/>
+      <c r="AH8" s="78" t="n">
         <f aca="false">IF(A8="","",AF8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AG8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AI8" s="54" t="n">
+      <c r="AI8" s="76" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AJ8" s="42"/>
-      <c r="AK8" s="42"/>
-      <c r="AL8" s="55" t="n">
+      <c r="AJ8" s="77"/>
+      <c r="AK8" s="77"/>
+      <c r="AL8" s="78" t="n">
         <f aca="false">IF(A8="","",AJ8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AK8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AM8" s="54" t="n">
+      <c r="AM8" s="76" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AN8" s="42"/>
-      <c r="AO8" s="42"/>
-      <c r="AP8" s="55" t="n">
+      <c r="AN8" s="77"/>
+      <c r="AO8" s="77"/>
+      <c r="AP8" s="78" t="n">
         <f aca="false">IF(A8="","",AN8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AO8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AQ8" s="54" t="n">
+      <c r="AQ8" s="79" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AR8" s="42"/>
-      <c r="AS8" s="42"/>
-      <c r="AT8" s="55" t="n">
+      <c r="AR8" s="80"/>
+      <c r="AS8" s="80"/>
+      <c r="AT8" s="81" t="n">
         <f aca="false">IF(A8="","",AR8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AS8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AU8" s="54" t="n">
+      <c r="AU8" s="79" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AV8" s="42"/>
-      <c r="AW8" s="42"/>
-      <c r="AX8" s="55" t="n">
+      <c r="AV8" s="80"/>
+      <c r="AW8" s="80"/>
+      <c r="AX8" s="81" t="n">
         <f aca="false">IF(A8="","",AV8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,AW8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="AY8" s="54" t="n">
+      <c r="AY8" s="79" t="n">
         <f aca="false">IFERROR(IF(A8="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A8,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A8,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A8,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v>173.333333333333</v>
       </c>
-      <c r="AZ8" s="42"/>
-      <c r="BA8" s="42"/>
-      <c r="BB8" s="55" t="n">
+      <c r="AZ8" s="80"/>
+      <c r="BA8" s="80"/>
+      <c r="BB8" s="81" t="n">
         <f aca="false">IF(A8="","",AZ8*$D8+IF(OR($F8="Exempt",$E8="Sub"),0,BA8*$D8*1.5))</f>
         <v>0</v>
       </c>
-      <c r="BC8" s="41" t="n">
+      <c r="BC8" s="82" t="n">
         <f aca="false">IF(A8="","",SUM(G8,K8,O8,S8,W8,AA8,AE8,AI8,AM8,AQ8,AU8,AY8))</f>
         <v>2080</v>
       </c>
-      <c r="BD8" s="41" t="n">
+      <c r="BD8" s="82" t="n">
         <f aca="false">IF(A8="","",SUM(H8,I8,L8,M8,P8,Q8,T8,U8,X8,Y8,AB8,AC8,AF8,AG8,AJ8,AK8,AN8,AO8,AR8,AS8,AV8,AW8,AZ8,BA8))</f>
         <v>162</v>
       </c>
-      <c r="BE8" s="15" t="n">
+      <c r="BE8" s="83" t="n">
         <f aca="false">IF(A8="","",BC8*$D8)</f>
         <v>59280</v>
       </c>
-      <c r="BF8" s="15" t="n">
+      <c r="BF8" s="83" t="n">
         <f aca="false">IF(A8="","",SUM(J8,N8,R8,V8,Z8,AD8,AH8,AL8,AP8,AT8,AX8,BB8))</f>
         <v>4275</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16"/>
-      <c r="B9" s="56" t="str">
+      <c r="A9" s="27"/>
+      <c r="B9" s="84" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A9,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C9" s="56" t="str">
+      <c r="C9" s="84" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D9" s="57" t="str">
+      <c r="D9" s="85" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="58" t="str">
+      <c r="E9" s="27"/>
+      <c r="F9" s="86" t="str">
         <f aca="false">IF(A9="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A9,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G9" s="59" t="str">
+      <c r="G9" s="70" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="60" t="str">
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="72" t="str">
         <f aca="false">IF(A9="","",H9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,I9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="K9" s="59" t="str">
+      <c r="K9" s="70" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="60" t="str">
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="72" t="str">
         <f aca="false">IF(A9="","",L9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,M9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="O9" s="59" t="str">
+      <c r="O9" s="70" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="60" t="str">
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="72" t="str">
         <f aca="false">IF(A9="","",P9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,Q9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="S9" s="59" t="str">
+      <c r="S9" s="73" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="60" t="str">
+      <c r="T9" s="74"/>
+      <c r="U9" s="74"/>
+      <c r="V9" s="75" t="str">
         <f aca="false">IF(A9="","",T9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,U9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="W9" s="59" t="str">
+      <c r="W9" s="73" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="60" t="str">
+      <c r="X9" s="74"/>
+      <c r="Y9" s="74"/>
+      <c r="Z9" s="75" t="str">
         <f aca="false">IF(A9="","",X9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,Y9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AA9" s="59" t="str">
+      <c r="AA9" s="73" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB9" s="46"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="60" t="str">
+      <c r="AB9" s="74"/>
+      <c r="AC9" s="74"/>
+      <c r="AD9" s="75" t="str">
         <f aca="false">IF(A9="","",AB9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AC9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AE9" s="59" t="str">
+      <c r="AE9" s="76" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF9" s="46"/>
-      <c r="AG9" s="46"/>
-      <c r="AH9" s="60" t="str">
+      <c r="AF9" s="77"/>
+      <c r="AG9" s="77"/>
+      <c r="AH9" s="78" t="str">
         <f aca="false">IF(A9="","",AF9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AG9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AI9" s="59" t="str">
+      <c r="AI9" s="76" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ9" s="46"/>
-      <c r="AK9" s="46"/>
-      <c r="AL9" s="60" t="str">
+      <c r="AJ9" s="77"/>
+      <c r="AK9" s="77"/>
+      <c r="AL9" s="78" t="str">
         <f aca="false">IF(A9="","",AJ9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AK9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AM9" s="59" t="str">
+      <c r="AM9" s="76" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN9" s="46"/>
-      <c r="AO9" s="46"/>
-      <c r="AP9" s="60" t="str">
+      <c r="AN9" s="77"/>
+      <c r="AO9" s="77"/>
+      <c r="AP9" s="78" t="str">
         <f aca="false">IF(A9="","",AN9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AO9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AQ9" s="59" t="str">
+      <c r="AQ9" s="79" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR9" s="46"/>
-      <c r="AS9" s="46"/>
-      <c r="AT9" s="60" t="str">
+      <c r="AR9" s="80"/>
+      <c r="AS9" s="80"/>
+      <c r="AT9" s="81" t="str">
         <f aca="false">IF(A9="","",AR9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AS9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AU9" s="59" t="str">
+      <c r="AU9" s="79" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV9" s="46"/>
-      <c r="AW9" s="46"/>
-      <c r="AX9" s="60" t="str">
+      <c r="AV9" s="80"/>
+      <c r="AW9" s="80"/>
+      <c r="AX9" s="81" t="str">
         <f aca="false">IF(A9="","",AV9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,AW9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="AY9" s="59" t="str">
+      <c r="AY9" s="79" t="str">
         <f aca="false">IFERROR(IF(A9="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A9,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A9,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A9,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ9" s="46"/>
-      <c r="BA9" s="46"/>
-      <c r="BB9" s="60" t="str">
+      <c r="AZ9" s="80"/>
+      <c r="BA9" s="80"/>
+      <c r="BB9" s="81" t="str">
         <f aca="false">IF(A9="","",AZ9*$D9+IF(OR($F9="Exempt",$E9="Sub"),0,BA9*$D9*1.5))</f>
         <v/>
       </c>
-      <c r="BC9" s="45" t="str">
+      <c r="BC9" s="82" t="str">
         <f aca="false">IF(A9="","",SUM(G9,K9,O9,S9,W9,AA9,AE9,AI9,AM9,AQ9,AU9,AY9))</f>
         <v/>
       </c>
-      <c r="BD9" s="45" t="str">
+      <c r="BD9" s="82" t="str">
         <f aca="false">IF(A9="","",SUM(H9,I9,L9,M9,P9,Q9,T9,U9,X9,Y9,AB9,AC9,AF9,AG9,AJ9,AK9,AN9,AO9,AR9,AS9,AV9,AW9,AZ9,BA9))</f>
         <v/>
       </c>
-      <c r="BE9" s="19" t="str">
+      <c r="BE9" s="83" t="str">
         <f aca="false">IF(A9="","",BC9*$D9)</f>
         <v/>
       </c>
-      <c r="BF9" s="19" t="str">
+      <c r="BF9" s="83" t="str">
         <f aca="false">IF(A9="","",SUM(J9,N9,R9,V9,Z9,AD9,AH9,AL9,AP9,AT9,AX9,BB9))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12"/>
-      <c r="B10" s="51" t="str">
+      <c r="A10" s="20"/>
+      <c r="B10" s="67" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A10,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C10" s="51" t="str">
+      <c r="C10" s="67" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D10" s="52" t="str">
+      <c r="D10" s="68" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="53" t="str">
+      <c r="E10" s="20"/>
+      <c r="F10" s="69" t="str">
         <f aca="false">IF(A10="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A10,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G10" s="54" t="str">
+      <c r="G10" s="70" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="55" t="str">
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72" t="str">
         <f aca="false">IF(A10="","",H10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,I10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="K10" s="54" t="str">
+      <c r="K10" s="70" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="55" t="str">
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="72" t="str">
         <f aca="false">IF(A10="","",L10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,M10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="O10" s="54" t="str">
+      <c r="O10" s="70" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="55" t="str">
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="72" t="str">
         <f aca="false">IF(A10="","",P10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,Q10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="S10" s="54" t="str">
+      <c r="S10" s="73" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="55" t="str">
+      <c r="T10" s="74"/>
+      <c r="U10" s="74"/>
+      <c r="V10" s="75" t="str">
         <f aca="false">IF(A10="","",T10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,U10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="W10" s="54" t="str">
+      <c r="W10" s="73" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X10" s="42"/>
-      <c r="Y10" s="42"/>
-      <c r="Z10" s="55" t="str">
+      <c r="X10" s="74"/>
+      <c r="Y10" s="74"/>
+      <c r="Z10" s="75" t="str">
         <f aca="false">IF(A10="","",X10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,Y10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AA10" s="54" t="str">
+      <c r="AA10" s="73" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB10" s="42"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="55" t="str">
+      <c r="AB10" s="74"/>
+      <c r="AC10" s="74"/>
+      <c r="AD10" s="75" t="str">
         <f aca="false">IF(A10="","",AB10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AC10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AE10" s="54" t="str">
+      <c r="AE10" s="76" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF10" s="42"/>
-      <c r="AG10" s="42"/>
-      <c r="AH10" s="55" t="str">
+      <c r="AF10" s="77"/>
+      <c r="AG10" s="77"/>
+      <c r="AH10" s="78" t="str">
         <f aca="false">IF(A10="","",AF10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AG10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AI10" s="54" t="str">
+      <c r="AI10" s="76" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ10" s="42"/>
-      <c r="AK10" s="42"/>
-      <c r="AL10" s="55" t="str">
+      <c r="AJ10" s="77"/>
+      <c r="AK10" s="77"/>
+      <c r="AL10" s="78" t="str">
         <f aca="false">IF(A10="","",AJ10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AK10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AM10" s="54" t="str">
+      <c r="AM10" s="76" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN10" s="42"/>
-      <c r="AO10" s="42"/>
-      <c r="AP10" s="55" t="str">
+      <c r="AN10" s="77"/>
+      <c r="AO10" s="77"/>
+      <c r="AP10" s="78" t="str">
         <f aca="false">IF(A10="","",AN10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AO10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AQ10" s="54" t="str">
+      <c r="AQ10" s="79" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR10" s="42"/>
-      <c r="AS10" s="42"/>
-      <c r="AT10" s="55" t="str">
+      <c r="AR10" s="80"/>
+      <c r="AS10" s="80"/>
+      <c r="AT10" s="81" t="str">
         <f aca="false">IF(A10="","",AR10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AS10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AU10" s="54" t="str">
+      <c r="AU10" s="79" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV10" s="42"/>
-      <c r="AW10" s="42"/>
-      <c r="AX10" s="55" t="str">
+      <c r="AV10" s="80"/>
+      <c r="AW10" s="80"/>
+      <c r="AX10" s="81" t="str">
         <f aca="false">IF(A10="","",AV10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,AW10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="AY10" s="54" t="str">
+      <c r="AY10" s="79" t="str">
         <f aca="false">IFERROR(IF(A10="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A10,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A10,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A10,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ10" s="42"/>
-      <c r="BA10" s="42"/>
-      <c r="BB10" s="55" t="str">
+      <c r="AZ10" s="80"/>
+      <c r="BA10" s="80"/>
+      <c r="BB10" s="81" t="str">
         <f aca="false">IF(A10="","",AZ10*$D10+IF(OR($F10="Exempt",$E10="Sub"),0,BA10*$D10*1.5))</f>
         <v/>
       </c>
-      <c r="BC10" s="41" t="str">
+      <c r="BC10" s="82" t="str">
         <f aca="false">IF(A10="","",SUM(G10,K10,O10,S10,W10,AA10,AE10,AI10,AM10,AQ10,AU10,AY10))</f>
         <v/>
       </c>
-      <c r="BD10" s="41" t="str">
+      <c r="BD10" s="82" t="str">
         <f aca="false">IF(A10="","",SUM(H10,I10,L10,M10,P10,Q10,T10,U10,X10,Y10,AB10,AC10,AF10,AG10,AJ10,AK10,AN10,AO10,AR10,AS10,AV10,AW10,AZ10,BA10))</f>
         <v/>
       </c>
-      <c r="BE10" s="15" t="str">
+      <c r="BE10" s="83" t="str">
         <f aca="false">IF(A10="","",BC10*$D10)</f>
         <v/>
       </c>
-      <c r="BF10" s="15" t="str">
+      <c r="BF10" s="83" t="str">
         <f aca="false">IF(A10="","",SUM(J10,N10,R10,V10,Z10,AD10,AH10,AL10,AP10,AT10,AX10,BB10))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16"/>
-      <c r="B11" s="56" t="str">
+      <c r="A11" s="27"/>
+      <c r="B11" s="84" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A11,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C11" s="56" t="str">
+      <c r="C11" s="84" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D11" s="57" t="str">
+      <c r="D11" s="85" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="58" t="str">
+      <c r="E11" s="27"/>
+      <c r="F11" s="86" t="str">
         <f aca="false">IF(A11="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A11,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G11" s="59" t="str">
+      <c r="G11" s="70" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="60" t="str">
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="72" t="str">
         <f aca="false">IF(A11="","",H11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,I11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="K11" s="59" t="str">
+      <c r="K11" s="70" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="60" t="str">
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="72" t="str">
         <f aca="false">IF(A11="","",L11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,M11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="O11" s="59" t="str">
+      <c r="O11" s="70" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P11" s="46"/>
-      <c r="Q11" s="46"/>
-      <c r="R11" s="60" t="str">
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="72" t="str">
         <f aca="false">IF(A11="","",P11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,Q11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="S11" s="59" t="str">
+      <c r="S11" s="73" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="60" t="str">
+      <c r="T11" s="74"/>
+      <c r="U11" s="74"/>
+      <c r="V11" s="75" t="str">
         <f aca="false">IF(A11="","",T11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,U11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="W11" s="59" t="str">
+      <c r="W11" s="73" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46"/>
-      <c r="Z11" s="60" t="str">
+      <c r="X11" s="74"/>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="75" t="str">
         <f aca="false">IF(A11="","",X11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,Y11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AA11" s="59" t="str">
+      <c r="AA11" s="73" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="46"/>
-      <c r="AD11" s="60" t="str">
+      <c r="AB11" s="74"/>
+      <c r="AC11" s="74"/>
+      <c r="AD11" s="75" t="str">
         <f aca="false">IF(A11="","",AB11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AC11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AE11" s="59" t="str">
+      <c r="AE11" s="76" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF11" s="46"/>
-      <c r="AG11" s="46"/>
-      <c r="AH11" s="60" t="str">
+      <c r="AF11" s="77"/>
+      <c r="AG11" s="77"/>
+      <c r="AH11" s="78" t="str">
         <f aca="false">IF(A11="","",AF11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AG11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AI11" s="59" t="str">
+      <c r="AI11" s="76" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ11" s="46"/>
-      <c r="AK11" s="46"/>
-      <c r="AL11" s="60" t="str">
+      <c r="AJ11" s="77"/>
+      <c r="AK11" s="77"/>
+      <c r="AL11" s="78" t="str">
         <f aca="false">IF(A11="","",AJ11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AK11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AM11" s="59" t="str">
+      <c r="AM11" s="76" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN11" s="46"/>
-      <c r="AO11" s="46"/>
-      <c r="AP11" s="60" t="str">
+      <c r="AN11" s="77"/>
+      <c r="AO11" s="77"/>
+      <c r="AP11" s="78" t="str">
         <f aca="false">IF(A11="","",AN11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AO11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AQ11" s="59" t="str">
+      <c r="AQ11" s="79" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR11" s="46"/>
-      <c r="AS11" s="46"/>
-      <c r="AT11" s="60" t="str">
+      <c r="AR11" s="80"/>
+      <c r="AS11" s="80"/>
+      <c r="AT11" s="81" t="str">
         <f aca="false">IF(A11="","",AR11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AS11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AU11" s="59" t="str">
+      <c r="AU11" s="79" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV11" s="46"/>
-      <c r="AW11" s="46"/>
-      <c r="AX11" s="60" t="str">
+      <c r="AV11" s="80"/>
+      <c r="AW11" s="80"/>
+      <c r="AX11" s="81" t="str">
         <f aca="false">IF(A11="","",AV11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,AW11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="AY11" s="59" t="str">
+      <c r="AY11" s="79" t="str">
         <f aca="false">IFERROR(IF(A11="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A11,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A11,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A11,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ11" s="46"/>
-      <c r="BA11" s="46"/>
-      <c r="BB11" s="60" t="str">
+      <c r="AZ11" s="80"/>
+      <c r="BA11" s="80"/>
+      <c r="BB11" s="81" t="str">
         <f aca="false">IF(A11="","",AZ11*$D11+IF(OR($F11="Exempt",$E11="Sub"),0,BA11*$D11*1.5))</f>
         <v/>
       </c>
-      <c r="BC11" s="45" t="str">
+      <c r="BC11" s="82" t="str">
         <f aca="false">IF(A11="","",SUM(G11,K11,O11,S11,W11,AA11,AE11,AI11,AM11,AQ11,AU11,AY11))</f>
         <v/>
       </c>
-      <c r="BD11" s="45" t="str">
+      <c r="BD11" s="82" t="str">
         <f aca="false">IF(A11="","",SUM(H11,I11,L11,M11,P11,Q11,T11,U11,X11,Y11,AB11,AC11,AF11,AG11,AJ11,AK11,AN11,AO11,AR11,AS11,AV11,AW11,AZ11,BA11))</f>
         <v/>
       </c>
-      <c r="BE11" s="19" t="str">
+      <c r="BE11" s="83" t="str">
         <f aca="false">IF(A11="","",BC11*$D11)</f>
         <v/>
       </c>
-      <c r="BF11" s="19" t="str">
+      <c r="BF11" s="83" t="str">
         <f aca="false">IF(A11="","",SUM(J11,N11,R11,V11,Z11,AD11,AH11,AL11,AP11,AT11,AX11,BB11))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12"/>
-      <c r="B12" s="51" t="str">
+      <c r="A12" s="20"/>
+      <c r="B12" s="67" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A12,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C12" s="51" t="str">
+      <c r="C12" s="67" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D12" s="52" t="str">
+      <c r="D12" s="68" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="53" t="str">
+      <c r="E12" s="20"/>
+      <c r="F12" s="69" t="str">
         <f aca="false">IF(A12="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A12,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G12" s="54" t="str">
+      <c r="G12" s="70" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="55" t="str">
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="72" t="str">
         <f aca="false">IF(A12="","",H12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,I12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="K12" s="54" t="str">
+      <c r="K12" s="70" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="55" t="str">
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="72" t="str">
         <f aca="false">IF(A12="","",L12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,M12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="O12" s="54" t="str">
+      <c r="O12" s="70" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="55" t="str">
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="72" t="str">
         <f aca="false">IF(A12="","",P12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,Q12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="S12" s="54" t="str">
+      <c r="S12" s="73" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="55" t="str">
+      <c r="T12" s="74"/>
+      <c r="U12" s="74"/>
+      <c r="V12" s="75" t="str">
         <f aca="false">IF(A12="","",T12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,U12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="W12" s="54" t="str">
+      <c r="W12" s="73" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X12" s="42"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="55" t="str">
+      <c r="X12" s="74"/>
+      <c r="Y12" s="74"/>
+      <c r="Z12" s="75" t="str">
         <f aca="false">IF(A12="","",X12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,Y12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AA12" s="54" t="str">
+      <c r="AA12" s="73" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB12" s="42"/>
-      <c r="AC12" s="42"/>
-      <c r="AD12" s="55" t="str">
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="74"/>
+      <c r="AD12" s="75" t="str">
         <f aca="false">IF(A12="","",AB12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AC12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AE12" s="54" t="str">
+      <c r="AE12" s="76" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF12" s="42"/>
-      <c r="AG12" s="42"/>
-      <c r="AH12" s="55" t="str">
+      <c r="AF12" s="77"/>
+      <c r="AG12" s="77"/>
+      <c r="AH12" s="78" t="str">
         <f aca="false">IF(A12="","",AF12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AG12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AI12" s="54" t="str">
+      <c r="AI12" s="76" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="55" t="str">
+      <c r="AJ12" s="77"/>
+      <c r="AK12" s="77"/>
+      <c r="AL12" s="78" t="str">
         <f aca="false">IF(A12="","",AJ12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AK12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AM12" s="54" t="str">
+      <c r="AM12" s="76" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
-      <c r="AP12" s="55" t="str">
+      <c r="AN12" s="77"/>
+      <c r="AO12" s="77"/>
+      <c r="AP12" s="78" t="str">
         <f aca="false">IF(A12="","",AN12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AO12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AQ12" s="54" t="str">
+      <c r="AQ12" s="79" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR12" s="42"/>
-      <c r="AS12" s="42"/>
-      <c r="AT12" s="55" t="str">
+      <c r="AR12" s="80"/>
+      <c r="AS12" s="80"/>
+      <c r="AT12" s="81" t="str">
         <f aca="false">IF(A12="","",AR12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AS12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AU12" s="54" t="str">
+      <c r="AU12" s="79" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="55" t="str">
+      <c r="AV12" s="80"/>
+      <c r="AW12" s="80"/>
+      <c r="AX12" s="81" t="str">
         <f aca="false">IF(A12="","",AV12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,AW12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="AY12" s="54" t="str">
+      <c r="AY12" s="79" t="str">
         <f aca="false">IFERROR(IF(A12="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A12,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A12,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A12,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
-      <c r="BB12" s="55" t="str">
+      <c r="AZ12" s="80"/>
+      <c r="BA12" s="80"/>
+      <c r="BB12" s="81" t="str">
         <f aca="false">IF(A12="","",AZ12*$D12+IF(OR($F12="Exempt",$E12="Sub"),0,BA12*$D12*1.5))</f>
         <v/>
       </c>
-      <c r="BC12" s="41" t="str">
+      <c r="BC12" s="82" t="str">
         <f aca="false">IF(A12="","",SUM(G12,K12,O12,S12,W12,AA12,AE12,AI12,AM12,AQ12,AU12,AY12))</f>
         <v/>
       </c>
-      <c r="BD12" s="41" t="str">
+      <c r="BD12" s="82" t="str">
         <f aca="false">IF(A12="","",SUM(H12,I12,L12,M12,P12,Q12,T12,U12,X12,Y12,AB12,AC12,AF12,AG12,AJ12,AK12,AN12,AO12,AR12,AS12,AV12,AW12,AZ12,BA12))</f>
         <v/>
       </c>
-      <c r="BE12" s="15" t="str">
+      <c r="BE12" s="83" t="str">
         <f aca="false">IF(A12="","",BC12*$D12)</f>
         <v/>
       </c>
-      <c r="BF12" s="15" t="str">
+      <c r="BF12" s="83" t="str">
         <f aca="false">IF(A12="","",SUM(J12,N12,R12,V12,Z12,AD12,AH12,AL12,AP12,AT12,AX12,BB12))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16"/>
-      <c r="B13" s="56" t="str">
+      <c r="A13" s="27"/>
+      <c r="B13" s="84" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A13,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C13" s="56" t="str">
+      <c r="C13" s="84" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D13" s="57" t="str">
+      <c r="D13" s="85" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="58" t="str">
+      <c r="E13" s="27"/>
+      <c r="F13" s="86" t="str">
         <f aca="false">IF(A13="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A13,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G13" s="59" t="str">
+      <c r="G13" s="70" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="60" t="str">
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72" t="str">
         <f aca="false">IF(A13="","",H13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,I13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="K13" s="59" t="str">
+      <c r="K13" s="70" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="60" t="str">
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="72" t="str">
         <f aca="false">IF(A13="","",L13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,M13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="O13" s="59" t="str">
+      <c r="O13" s="70" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="60" t="str">
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="72" t="str">
         <f aca="false">IF(A13="","",P13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,Q13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="S13" s="59" t="str">
+      <c r="S13" s="73" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="60" t="str">
+      <c r="T13" s="74"/>
+      <c r="U13" s="74"/>
+      <c r="V13" s="75" t="str">
         <f aca="false">IF(A13="","",T13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,U13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="W13" s="59" t="str">
+      <c r="W13" s="73" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="46"/>
-      <c r="Z13" s="60" t="str">
+      <c r="X13" s="74"/>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="75" t="str">
         <f aca="false">IF(A13="","",X13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,Y13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AA13" s="59" t="str">
+      <c r="AA13" s="73" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB13" s="46"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="60" t="str">
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="75" t="str">
         <f aca="false">IF(A13="","",AB13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AC13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AE13" s="59" t="str">
+      <c r="AE13" s="76" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="46"/>
-      <c r="AH13" s="60" t="str">
+      <c r="AF13" s="77"/>
+      <c r="AG13" s="77"/>
+      <c r="AH13" s="78" t="str">
         <f aca="false">IF(A13="","",AF13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AG13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AI13" s="59" t="str">
+      <c r="AI13" s="76" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ13" s="46"/>
-      <c r="AK13" s="46"/>
-      <c r="AL13" s="60" t="str">
+      <c r="AJ13" s="77"/>
+      <c r="AK13" s="77"/>
+      <c r="AL13" s="78" t="str">
         <f aca="false">IF(A13="","",AJ13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AK13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AM13" s="59" t="str">
+      <c r="AM13" s="76" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN13" s="46"/>
-      <c r="AO13" s="46"/>
-      <c r="AP13" s="60" t="str">
+      <c r="AN13" s="77"/>
+      <c r="AO13" s="77"/>
+      <c r="AP13" s="78" t="str">
         <f aca="false">IF(A13="","",AN13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AO13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AQ13" s="59" t="str">
+      <c r="AQ13" s="79" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR13" s="46"/>
-      <c r="AS13" s="46"/>
-      <c r="AT13" s="60" t="str">
+      <c r="AR13" s="80"/>
+      <c r="AS13" s="80"/>
+      <c r="AT13" s="81" t="str">
         <f aca="false">IF(A13="","",AR13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AS13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AU13" s="59" t="str">
+      <c r="AU13" s="79" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV13" s="46"/>
-      <c r="AW13" s="46"/>
-      <c r="AX13" s="60" t="str">
+      <c r="AV13" s="80"/>
+      <c r="AW13" s="80"/>
+      <c r="AX13" s="81" t="str">
         <f aca="false">IF(A13="","",AV13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,AW13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="AY13" s="59" t="str">
+      <c r="AY13" s="79" t="str">
         <f aca="false">IFERROR(IF(A13="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A13,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A13,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A13,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ13" s="46"/>
-      <c r="BA13" s="46"/>
-      <c r="BB13" s="60" t="str">
+      <c r="AZ13" s="80"/>
+      <c r="BA13" s="80"/>
+      <c r="BB13" s="81" t="str">
         <f aca="false">IF(A13="","",AZ13*$D13+IF(OR($F13="Exempt",$E13="Sub"),0,BA13*$D13*1.5))</f>
         <v/>
       </c>
-      <c r="BC13" s="45" t="str">
+      <c r="BC13" s="82" t="str">
         <f aca="false">IF(A13="","",SUM(G13,K13,O13,S13,W13,AA13,AE13,AI13,AM13,AQ13,AU13,AY13))</f>
         <v/>
       </c>
-      <c r="BD13" s="45" t="str">
+      <c r="BD13" s="82" t="str">
         <f aca="false">IF(A13="","",SUM(H13,I13,L13,M13,P13,Q13,T13,U13,X13,Y13,AB13,AC13,AF13,AG13,AJ13,AK13,AN13,AO13,AR13,AS13,AV13,AW13,AZ13,BA13))</f>
         <v/>
       </c>
-      <c r="BE13" s="19" t="str">
+      <c r="BE13" s="83" t="str">
         <f aca="false">IF(A13="","",BC13*$D13)</f>
         <v/>
       </c>
-      <c r="BF13" s="19" t="str">
+      <c r="BF13" s="83" t="str">
         <f aca="false">IF(A13="","",SUM(J13,N13,R13,V13,Z13,AD13,AH13,AL13,AP13,AT13,AX13,BB13))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12"/>
-      <c r="B14" s="51" t="str">
+      <c r="A14" s="20"/>
+      <c r="B14" s="67" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A14,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C14" s="51" t="str">
+      <c r="C14" s="67" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D14" s="52" t="str">
+      <c r="D14" s="68" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="53" t="str">
+      <c r="E14" s="20"/>
+      <c r="F14" s="69" t="str">
         <f aca="false">IF(A14="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A14,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G14" s="54" t="str">
+      <c r="G14" s="70" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="55" t="str">
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="72" t="str">
         <f aca="false">IF(A14="","",H14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,I14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="K14" s="54" t="str">
+      <c r="K14" s="70" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="55" t="str">
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="72" t="str">
         <f aca="false">IF(A14="","",L14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,M14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="O14" s="54" t="str">
+      <c r="O14" s="70" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="55" t="str">
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="72" t="str">
         <f aca="false">IF(A14="","",P14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,Q14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="S14" s="54" t="str">
+      <c r="S14" s="73" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="55" t="str">
+      <c r="T14" s="74"/>
+      <c r="U14" s="74"/>
+      <c r="V14" s="75" t="str">
         <f aca="false">IF(A14="","",T14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,U14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="W14" s="54" t="str">
+      <c r="W14" s="73" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="42"/>
-      <c r="Z14" s="55" t="str">
+      <c r="X14" s="74"/>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="75" t="str">
         <f aca="false">IF(A14="","",X14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,Y14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AA14" s="54" t="str">
+      <c r="AA14" s="73" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB14" s="42"/>
-      <c r="AC14" s="42"/>
-      <c r="AD14" s="55" t="str">
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="74"/>
+      <c r="AD14" s="75" t="str">
         <f aca="false">IF(A14="","",AB14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AC14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AE14" s="54" t="str">
+      <c r="AE14" s="76" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF14" s="42"/>
-      <c r="AG14" s="42"/>
-      <c r="AH14" s="55" t="str">
+      <c r="AF14" s="77"/>
+      <c r="AG14" s="77"/>
+      <c r="AH14" s="78" t="str">
         <f aca="false">IF(A14="","",AF14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AG14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AI14" s="54" t="str">
+      <c r="AI14" s="76" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ14" s="42"/>
-      <c r="AK14" s="42"/>
-      <c r="AL14" s="55" t="str">
+      <c r="AJ14" s="77"/>
+      <c r="AK14" s="77"/>
+      <c r="AL14" s="78" t="str">
         <f aca="false">IF(A14="","",AJ14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AK14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AM14" s="54" t="str">
+      <c r="AM14" s="76" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN14" s="42"/>
-      <c r="AO14" s="42"/>
-      <c r="AP14" s="55" t="str">
+      <c r="AN14" s="77"/>
+      <c r="AO14" s="77"/>
+      <c r="AP14" s="78" t="str">
         <f aca="false">IF(A14="","",AN14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AO14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AQ14" s="54" t="str">
+      <c r="AQ14" s="79" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR14" s="42"/>
-      <c r="AS14" s="42"/>
-      <c r="AT14" s="55" t="str">
+      <c r="AR14" s="80"/>
+      <c r="AS14" s="80"/>
+      <c r="AT14" s="81" t="str">
         <f aca="false">IF(A14="","",AR14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AS14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AU14" s="54" t="str">
+      <c r="AU14" s="79" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV14" s="42"/>
-      <c r="AW14" s="42"/>
-      <c r="AX14" s="55" t="str">
+      <c r="AV14" s="80"/>
+      <c r="AW14" s="80"/>
+      <c r="AX14" s="81" t="str">
         <f aca="false">IF(A14="","",AV14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,AW14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="AY14" s="54" t="str">
+      <c r="AY14" s="79" t="str">
         <f aca="false">IFERROR(IF(A14="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A14,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A14,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A14,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ14" s="42"/>
-      <c r="BA14" s="42"/>
-      <c r="BB14" s="55" t="str">
+      <c r="AZ14" s="80"/>
+      <c r="BA14" s="80"/>
+      <c r="BB14" s="81" t="str">
         <f aca="false">IF(A14="","",AZ14*$D14+IF(OR($F14="Exempt",$E14="Sub"),0,BA14*$D14*1.5))</f>
         <v/>
       </c>
-      <c r="BC14" s="41" t="str">
+      <c r="BC14" s="82" t="str">
         <f aca="false">IF(A14="","",SUM(G14,K14,O14,S14,W14,AA14,AE14,AI14,AM14,AQ14,AU14,AY14))</f>
         <v/>
       </c>
-      <c r="BD14" s="41" t="str">
+      <c r="BD14" s="82" t="str">
         <f aca="false">IF(A14="","",SUM(H14,I14,L14,M14,P14,Q14,T14,U14,X14,Y14,AB14,AC14,AF14,AG14,AJ14,AK14,AN14,AO14,AR14,AS14,AV14,AW14,AZ14,BA14))</f>
         <v/>
       </c>
-      <c r="BE14" s="15" t="str">
+      <c r="BE14" s="83" t="str">
         <f aca="false">IF(A14="","",BC14*$D14)</f>
         <v/>
       </c>
-      <c r="BF14" s="15" t="str">
+      <c r="BF14" s="83" t="str">
         <f aca="false">IF(A14="","",SUM(J14,N14,R14,V14,Z14,AD14,AH14,AL14,AP14,AT14,AX14,BB14))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16"/>
-      <c r="B15" s="56" t="str">
+      <c r="A15" s="27"/>
+      <c r="B15" s="84" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A15,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C15" s="56" t="str">
+      <c r="C15" s="84" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D15" s="57" t="str">
+      <c r="D15" s="85" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="58" t="str">
+      <c r="E15" s="27"/>
+      <c r="F15" s="86" t="str">
         <f aca="false">IF(A15="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A15,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G15" s="59" t="str">
+      <c r="G15" s="70" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="60" t="str">
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="72" t="str">
         <f aca="false">IF(A15="","",H15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,I15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="K15" s="59" t="str">
+      <c r="K15" s="70" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="60" t="str">
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="72" t="str">
         <f aca="false">IF(A15="","",L15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,M15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="O15" s="59" t="str">
+      <c r="O15" s="70" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="60" t="str">
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="72" t="str">
         <f aca="false">IF(A15="","",P15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,Q15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="S15" s="59" t="str">
+      <c r="S15" s="73" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="60" t="str">
+      <c r="T15" s="74"/>
+      <c r="U15" s="74"/>
+      <c r="V15" s="75" t="str">
         <f aca="false">IF(A15="","",T15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,U15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="W15" s="59" t="str">
+      <c r="W15" s="73" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46"/>
-      <c r="Z15" s="60" t="str">
+      <c r="X15" s="74"/>
+      <c r="Y15" s="74"/>
+      <c r="Z15" s="75" t="str">
         <f aca="false">IF(A15="","",X15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,Y15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AA15" s="59" t="str">
+      <c r="AA15" s="73" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="60" t="str">
+      <c r="AB15" s="74"/>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="75" t="str">
         <f aca="false">IF(A15="","",AB15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AC15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AE15" s="59" t="str">
+      <c r="AE15" s="76" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="60" t="str">
+      <c r="AF15" s="77"/>
+      <c r="AG15" s="77"/>
+      <c r="AH15" s="78" t="str">
         <f aca="false">IF(A15="","",AF15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AG15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AI15" s="59" t="str">
+      <c r="AI15" s="76" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="46"/>
-      <c r="AL15" s="60" t="str">
+      <c r="AJ15" s="77"/>
+      <c r="AK15" s="77"/>
+      <c r="AL15" s="78" t="str">
         <f aca="false">IF(A15="","",AJ15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AK15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AM15" s="59" t="str">
+      <c r="AM15" s="76" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN15" s="46"/>
-      <c r="AO15" s="46"/>
-      <c r="AP15" s="60" t="str">
+      <c r="AN15" s="77"/>
+      <c r="AO15" s="77"/>
+      <c r="AP15" s="78" t="str">
         <f aca="false">IF(A15="","",AN15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AO15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AQ15" s="59" t="str">
+      <c r="AQ15" s="79" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR15" s="46"/>
-      <c r="AS15" s="46"/>
-      <c r="AT15" s="60" t="str">
+      <c r="AR15" s="80"/>
+      <c r="AS15" s="80"/>
+      <c r="AT15" s="81" t="str">
         <f aca="false">IF(A15="","",AR15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AS15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AU15" s="59" t="str">
+      <c r="AU15" s="79" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV15" s="46"/>
-      <c r="AW15" s="46"/>
-      <c r="AX15" s="60" t="str">
+      <c r="AV15" s="80"/>
+      <c r="AW15" s="80"/>
+      <c r="AX15" s="81" t="str">
         <f aca="false">IF(A15="","",AV15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,AW15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="AY15" s="59" t="str">
+      <c r="AY15" s="79" t="str">
         <f aca="false">IFERROR(IF(A15="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A15,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A15,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A15,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ15" s="46"/>
-      <c r="BA15" s="46"/>
-      <c r="BB15" s="60" t="str">
+      <c r="AZ15" s="80"/>
+      <c r="BA15" s="80"/>
+      <c r="BB15" s="81" t="str">
         <f aca="false">IF(A15="","",AZ15*$D15+IF(OR($F15="Exempt",$E15="Sub"),0,BA15*$D15*1.5))</f>
         <v/>
       </c>
-      <c r="BC15" s="45" t="str">
+      <c r="BC15" s="82" t="str">
         <f aca="false">IF(A15="","",SUM(G15,K15,O15,S15,W15,AA15,AE15,AI15,AM15,AQ15,AU15,AY15))</f>
         <v/>
       </c>
-      <c r="BD15" s="45" t="str">
+      <c r="BD15" s="82" t="str">
         <f aca="false">IF(A15="","",SUM(H15,I15,L15,M15,P15,Q15,T15,U15,X15,Y15,AB15,AC15,AF15,AG15,AJ15,AK15,AN15,AO15,AR15,AS15,AV15,AW15,AZ15,BA15))</f>
         <v/>
       </c>
-      <c r="BE15" s="19" t="str">
+      <c r="BE15" s="83" t="str">
         <f aca="false">IF(A15="","",BC15*$D15)</f>
         <v/>
       </c>
-      <c r="BF15" s="19" t="str">
+      <c r="BF15" s="83" t="str">
         <f aca="false">IF(A15="","",SUM(J15,N15,R15,V15,Z15,AD15,AH15,AL15,AP15,AT15,AX15,BB15))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12"/>
-      <c r="B16" s="51" t="str">
+      <c r="A16" s="20"/>
+      <c r="B16" s="67" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A16,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C16" s="51" t="str">
+      <c r="C16" s="67" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D16" s="52" t="str">
+      <c r="D16" s="68" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="53" t="str">
+      <c r="E16" s="20"/>
+      <c r="F16" s="69" t="str">
         <f aca="false">IF(A16="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A16,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G16" s="54" t="str">
+      <c r="G16" s="70" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="55" t="str">
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="72" t="str">
         <f aca="false">IF(A16="","",H16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,I16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="K16" s="54" t="str">
+      <c r="K16" s="70" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="55" t="str">
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="72" t="str">
         <f aca="false">IF(A16="","",L16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,M16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="O16" s="54" t="str">
+      <c r="O16" s="70" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="55" t="str">
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72" t="str">
         <f aca="false">IF(A16="","",P16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,Q16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="S16" s="54" t="str">
+      <c r="S16" s="73" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T16" s="42"/>
-      <c r="U16" s="42"/>
-      <c r="V16" s="55" t="str">
+      <c r="T16" s="74"/>
+      <c r="U16" s="74"/>
+      <c r="V16" s="75" t="str">
         <f aca="false">IF(A16="","",T16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,U16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="W16" s="54" t="str">
+      <c r="W16" s="73" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X16" s="42"/>
-      <c r="Y16" s="42"/>
-      <c r="Z16" s="55" t="str">
+      <c r="X16" s="74"/>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="75" t="str">
         <f aca="false">IF(A16="","",X16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,Y16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AA16" s="54" t="str">
+      <c r="AA16" s="73" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB16" s="42"/>
-      <c r="AC16" s="42"/>
-      <c r="AD16" s="55" t="str">
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="75" t="str">
         <f aca="false">IF(A16="","",AB16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AC16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AE16" s="54" t="str">
+      <c r="AE16" s="76" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF16" s="42"/>
-      <c r="AG16" s="42"/>
-      <c r="AH16" s="55" t="str">
+      <c r="AF16" s="77"/>
+      <c r="AG16" s="77"/>
+      <c r="AH16" s="78" t="str">
         <f aca="false">IF(A16="","",AF16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AG16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AI16" s="54" t="str">
+      <c r="AI16" s="76" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ16" s="42"/>
-      <c r="AK16" s="42"/>
-      <c r="AL16" s="55" t="str">
+      <c r="AJ16" s="77"/>
+      <c r="AK16" s="77"/>
+      <c r="AL16" s="78" t="str">
         <f aca="false">IF(A16="","",AJ16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AK16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AM16" s="54" t="str">
+      <c r="AM16" s="76" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN16" s="42"/>
-      <c r="AO16" s="42"/>
-      <c r="AP16" s="55" t="str">
+      <c r="AN16" s="77"/>
+      <c r="AO16" s="77"/>
+      <c r="AP16" s="78" t="str">
         <f aca="false">IF(A16="","",AN16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AO16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AQ16" s="54" t="str">
+      <c r="AQ16" s="79" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR16" s="42"/>
-      <c r="AS16" s="42"/>
-      <c r="AT16" s="55" t="str">
+      <c r="AR16" s="80"/>
+      <c r="AS16" s="80"/>
+      <c r="AT16" s="81" t="str">
         <f aca="false">IF(A16="","",AR16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AS16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AU16" s="54" t="str">
+      <c r="AU16" s="79" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV16" s="42"/>
-      <c r="AW16" s="42"/>
-      <c r="AX16" s="55" t="str">
+      <c r="AV16" s="80"/>
+      <c r="AW16" s="80"/>
+      <c r="AX16" s="81" t="str">
         <f aca="false">IF(A16="","",AV16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,AW16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="AY16" s="54" t="str">
+      <c r="AY16" s="79" t="str">
         <f aca="false">IFERROR(IF(A16="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A16,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A16,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A16,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ16" s="42"/>
-      <c r="BA16" s="42"/>
-      <c r="BB16" s="55" t="str">
+      <c r="AZ16" s="80"/>
+      <c r="BA16" s="80"/>
+      <c r="BB16" s="81" t="str">
         <f aca="false">IF(A16="","",AZ16*$D16+IF(OR($F16="Exempt",$E16="Sub"),0,BA16*$D16*1.5))</f>
         <v/>
       </c>
-      <c r="BC16" s="41" t="str">
+      <c r="BC16" s="82" t="str">
         <f aca="false">IF(A16="","",SUM(G16,K16,O16,S16,W16,AA16,AE16,AI16,AM16,AQ16,AU16,AY16))</f>
         <v/>
       </c>
-      <c r="BD16" s="41" t="str">
+      <c r="BD16" s="82" t="str">
         <f aca="false">IF(A16="","",SUM(H16,I16,L16,M16,P16,Q16,T16,U16,X16,Y16,AB16,AC16,AF16,AG16,AJ16,AK16,AN16,AO16,AR16,AS16,AV16,AW16,AZ16,BA16))</f>
         <v/>
       </c>
-      <c r="BE16" s="15" t="str">
+      <c r="BE16" s="83" t="str">
         <f aca="false">IF(A16="","",BC16*$D16)</f>
         <v/>
       </c>
-      <c r="BF16" s="15" t="str">
+      <c r="BF16" s="83" t="str">
         <f aca="false">IF(A16="","",SUM(J16,N16,R16,V16,Z16,AD16,AH16,AL16,AP16,AT16,AX16,BB16))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16"/>
-      <c r="B17" s="56" t="str">
+      <c r="A17" s="27"/>
+      <c r="B17" s="84" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A17,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C17" s="56" t="str">
+      <c r="C17" s="84" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D17" s="57" t="str">
+      <c r="D17" s="85" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="58" t="str">
+      <c r="E17" s="27"/>
+      <c r="F17" s="86" t="str">
         <f aca="false">IF(A17="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A17,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G17" s="59" t="str">
+      <c r="G17" s="70" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="60" t="str">
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72" t="str">
         <f aca="false">IF(A17="","",H17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,I17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="K17" s="59" t="str">
+      <c r="K17" s="70" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="60" t="str">
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="72" t="str">
         <f aca="false">IF(A17="","",L17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,M17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="O17" s="59" t="str">
+      <c r="O17" s="70" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="46"/>
-      <c r="R17" s="60" t="str">
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72" t="str">
         <f aca="false">IF(A17="","",P17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,Q17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="S17" s="59" t="str">
+      <c r="S17" s="73" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="60" t="str">
+      <c r="T17" s="74"/>
+      <c r="U17" s="74"/>
+      <c r="V17" s="75" t="str">
         <f aca="false">IF(A17="","",T17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,U17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="W17" s="59" t="str">
+      <c r="W17" s="73" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="60" t="str">
+      <c r="X17" s="74"/>
+      <c r="Y17" s="74"/>
+      <c r="Z17" s="75" t="str">
         <f aca="false">IF(A17="","",X17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,Y17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AA17" s="59" t="str">
+      <c r="AA17" s="73" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="60" t="str">
+      <c r="AB17" s="74"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="75" t="str">
         <f aca="false">IF(A17="","",AB17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AC17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AE17" s="59" t="str">
+      <c r="AE17" s="76" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AH17" s="60" t="str">
+      <c r="AF17" s="77"/>
+      <c r="AG17" s="77"/>
+      <c r="AH17" s="78" t="str">
         <f aca="false">IF(A17="","",AF17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AG17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AI17" s="59" t="str">
+      <c r="AI17" s="76" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ17" s="46"/>
-      <c r="AK17" s="46"/>
-      <c r="AL17" s="60" t="str">
+      <c r="AJ17" s="77"/>
+      <c r="AK17" s="77"/>
+      <c r="AL17" s="78" t="str">
         <f aca="false">IF(A17="","",AJ17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AK17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AM17" s="59" t="str">
+      <c r="AM17" s="76" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN17" s="46"/>
-      <c r="AO17" s="46"/>
-      <c r="AP17" s="60" t="str">
+      <c r="AN17" s="77"/>
+      <c r="AO17" s="77"/>
+      <c r="AP17" s="78" t="str">
         <f aca="false">IF(A17="","",AN17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AO17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AQ17" s="59" t="str">
+      <c r="AQ17" s="79" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR17" s="46"/>
-      <c r="AS17" s="46"/>
-      <c r="AT17" s="60" t="str">
+      <c r="AR17" s="80"/>
+      <c r="AS17" s="80"/>
+      <c r="AT17" s="81" t="str">
         <f aca="false">IF(A17="","",AR17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AS17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AU17" s="59" t="str">
+      <c r="AU17" s="79" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV17" s="46"/>
-      <c r="AW17" s="46"/>
-      <c r="AX17" s="60" t="str">
+      <c r="AV17" s="80"/>
+      <c r="AW17" s="80"/>
+      <c r="AX17" s="81" t="str">
         <f aca="false">IF(A17="","",AV17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,AW17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="AY17" s="59" t="str">
+      <c r="AY17" s="79" t="str">
         <f aca="false">IFERROR(IF(A17="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A17,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A17,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A17,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ17" s="46"/>
-      <c r="BA17" s="46"/>
-      <c r="BB17" s="60" t="str">
+      <c r="AZ17" s="80"/>
+      <c r="BA17" s="80"/>
+      <c r="BB17" s="81" t="str">
         <f aca="false">IF(A17="","",AZ17*$D17+IF(OR($F17="Exempt",$E17="Sub"),0,BA17*$D17*1.5))</f>
         <v/>
       </c>
-      <c r="BC17" s="45" t="str">
+      <c r="BC17" s="82" t="str">
         <f aca="false">IF(A17="","",SUM(G17,K17,O17,S17,W17,AA17,AE17,AI17,AM17,AQ17,AU17,AY17))</f>
         <v/>
       </c>
-      <c r="BD17" s="45" t="str">
+      <c r="BD17" s="82" t="str">
         <f aca="false">IF(A17="","",SUM(H17,I17,L17,M17,P17,Q17,T17,U17,X17,Y17,AB17,AC17,AF17,AG17,AJ17,AK17,AN17,AO17,AR17,AS17,AV17,AW17,AZ17,BA17))</f>
         <v/>
       </c>
-      <c r="BE17" s="19" t="str">
+      <c r="BE17" s="83" t="str">
         <f aca="false">IF(A17="","",BC17*$D17)</f>
         <v/>
       </c>
-      <c r="BF17" s="19" t="str">
+      <c r="BF17" s="83" t="str">
         <f aca="false">IF(A17="","",SUM(J17,N17,R17,V17,Z17,AD17,AH17,AL17,AP17,AT17,AX17,BB17))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12"/>
-      <c r="B18" s="51" t="str">
+      <c r="A18" s="20"/>
+      <c r="B18" s="67" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A18,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C18" s="51" t="str">
+      <c r="C18" s="67" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D18" s="52" t="str">
+      <c r="D18" s="68" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="53" t="str">
+      <c r="E18" s="20"/>
+      <c r="F18" s="69" t="str">
         <f aca="false">IF(A18="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A18,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G18" s="54" t="str">
+      <c r="G18" s="70" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="55" t="str">
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="72" t="str">
         <f aca="false">IF(A18="","",H18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,I18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="K18" s="54" t="str">
+      <c r="K18" s="70" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="55" t="str">
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="72" t="str">
         <f aca="false">IF(A18="","",L18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,M18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="O18" s="54" t="str">
+      <c r="O18" s="70" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="55" t="str">
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="72" t="str">
         <f aca="false">IF(A18="","",P18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,Q18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="S18" s="54" t="str">
+      <c r="S18" s="73" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="55" t="str">
+      <c r="T18" s="74"/>
+      <c r="U18" s="74"/>
+      <c r="V18" s="75" t="str">
         <f aca="false">IF(A18="","",T18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,U18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="W18" s="54" t="str">
+      <c r="W18" s="73" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X18" s="42"/>
-      <c r="Y18" s="42"/>
-      <c r="Z18" s="55" t="str">
+      <c r="X18" s="74"/>
+      <c r="Y18" s="74"/>
+      <c r="Z18" s="75" t="str">
         <f aca="false">IF(A18="","",X18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,Y18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AA18" s="54" t="str">
+      <c r="AA18" s="73" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB18" s="42"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="55" t="str">
+      <c r="AB18" s="74"/>
+      <c r="AC18" s="74"/>
+      <c r="AD18" s="75" t="str">
         <f aca="false">IF(A18="","",AB18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AC18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AE18" s="54" t="str">
+      <c r="AE18" s="76" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF18" s="42"/>
-      <c r="AG18" s="42"/>
-      <c r="AH18" s="55" t="str">
+      <c r="AF18" s="77"/>
+      <c r="AG18" s="77"/>
+      <c r="AH18" s="78" t="str">
         <f aca="false">IF(A18="","",AF18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AG18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AI18" s="54" t="str">
+      <c r="AI18" s="76" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ18" s="42"/>
-      <c r="AK18" s="42"/>
-      <c r="AL18" s="55" t="str">
+      <c r="AJ18" s="77"/>
+      <c r="AK18" s="77"/>
+      <c r="AL18" s="78" t="str">
         <f aca="false">IF(A18="","",AJ18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AK18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AM18" s="54" t="str">
+      <c r="AM18" s="76" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN18" s="42"/>
-      <c r="AO18" s="42"/>
-      <c r="AP18" s="55" t="str">
+      <c r="AN18" s="77"/>
+      <c r="AO18" s="77"/>
+      <c r="AP18" s="78" t="str">
         <f aca="false">IF(A18="","",AN18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AO18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AQ18" s="54" t="str">
+      <c r="AQ18" s="79" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR18" s="42"/>
-      <c r="AS18" s="42"/>
-      <c r="AT18" s="55" t="str">
+      <c r="AR18" s="80"/>
+      <c r="AS18" s="80"/>
+      <c r="AT18" s="81" t="str">
         <f aca="false">IF(A18="","",AR18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AS18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AU18" s="54" t="str">
+      <c r="AU18" s="79" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV18" s="42"/>
-      <c r="AW18" s="42"/>
-      <c r="AX18" s="55" t="str">
+      <c r="AV18" s="80"/>
+      <c r="AW18" s="80"/>
+      <c r="AX18" s="81" t="str">
         <f aca="false">IF(A18="","",AV18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,AW18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="AY18" s="54" t="str">
+      <c r="AY18" s="79" t="str">
         <f aca="false">IFERROR(IF(A18="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A18,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A18,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A18,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ18" s="42"/>
-      <c r="BA18" s="42"/>
-      <c r="BB18" s="55" t="str">
+      <c r="AZ18" s="80"/>
+      <c r="BA18" s="80"/>
+      <c r="BB18" s="81" t="str">
         <f aca="false">IF(A18="","",AZ18*$D18+IF(OR($F18="Exempt",$E18="Sub"),0,BA18*$D18*1.5))</f>
         <v/>
       </c>
-      <c r="BC18" s="41" t="str">
+      <c r="BC18" s="82" t="str">
         <f aca="false">IF(A18="","",SUM(G18,K18,O18,S18,W18,AA18,AE18,AI18,AM18,AQ18,AU18,AY18))</f>
         <v/>
       </c>
-      <c r="BD18" s="41" t="str">
+      <c r="BD18" s="82" t="str">
         <f aca="false">IF(A18="","",SUM(H18,I18,L18,M18,P18,Q18,T18,U18,X18,Y18,AB18,AC18,AF18,AG18,AJ18,AK18,AN18,AO18,AR18,AS18,AV18,AW18,AZ18,BA18))</f>
         <v/>
       </c>
-      <c r="BE18" s="15" t="str">
+      <c r="BE18" s="83" t="str">
         <f aca="false">IF(A18="","",BC18*$D18)</f>
         <v/>
       </c>
-      <c r="BF18" s="15" t="str">
+      <c r="BF18" s="83" t="str">
         <f aca="false">IF(A18="","",SUM(J18,N18,R18,V18,Z18,AD18,AH18,AL18,AP18,AT18,AX18,BB18))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16"/>
-      <c r="B19" s="56" t="str">
+      <c r="A19" s="27"/>
+      <c r="B19" s="84" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A19,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C19" s="56" t="str">
+      <c r="C19" s="84" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D19" s="57" t="str">
+      <c r="D19" s="85" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="58" t="str">
+      <c r="E19" s="27"/>
+      <c r="F19" s="86" t="str">
         <f aca="false">IF(A19="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A19,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G19" s="59" t="str">
+      <c r="G19" s="70" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="60" t="str">
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="72" t="str">
         <f aca="false">IF(A19="","",H19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,I19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="K19" s="59" t="str">
+      <c r="K19" s="70" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="60" t="str">
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="72" t="str">
         <f aca="false">IF(A19="","",L19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,M19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="O19" s="59" t="str">
+      <c r="O19" s="70" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="60" t="str">
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="72" t="str">
         <f aca="false">IF(A19="","",P19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,Q19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="S19" s="59" t="str">
+      <c r="S19" s="73" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="60" t="str">
+      <c r="T19" s="74"/>
+      <c r="U19" s="74"/>
+      <c r="V19" s="75" t="str">
         <f aca="false">IF(A19="","",T19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,U19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="W19" s="59" t="str">
+      <c r="W19" s="73" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="46"/>
-      <c r="Z19" s="60" t="str">
+      <c r="X19" s="74"/>
+      <c r="Y19" s="74"/>
+      <c r="Z19" s="75" t="str">
         <f aca="false">IF(A19="","",X19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,Y19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AA19" s="59" t="str">
+      <c r="AA19" s="73" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB19" s="46"/>
-      <c r="AC19" s="46"/>
-      <c r="AD19" s="60" t="str">
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="75" t="str">
         <f aca="false">IF(A19="","",AB19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AC19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AE19" s="59" t="str">
+      <c r="AE19" s="76" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF19" s="46"/>
-      <c r="AG19" s="46"/>
-      <c r="AH19" s="60" t="str">
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="77"/>
+      <c r="AH19" s="78" t="str">
         <f aca="false">IF(A19="","",AF19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AG19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AI19" s="59" t="str">
+      <c r="AI19" s="76" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ19" s="46"/>
-      <c r="AK19" s="46"/>
-      <c r="AL19" s="60" t="str">
+      <c r="AJ19" s="77"/>
+      <c r="AK19" s="77"/>
+      <c r="AL19" s="78" t="str">
         <f aca="false">IF(A19="","",AJ19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AK19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AM19" s="59" t="str">
+      <c r="AM19" s="76" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN19" s="46"/>
-      <c r="AO19" s="46"/>
-      <c r="AP19" s="60" t="str">
+      <c r="AN19" s="77"/>
+      <c r="AO19" s="77"/>
+      <c r="AP19" s="78" t="str">
         <f aca="false">IF(A19="","",AN19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AO19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AQ19" s="59" t="str">
+      <c r="AQ19" s="79" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR19" s="46"/>
-      <c r="AS19" s="46"/>
-      <c r="AT19" s="60" t="str">
+      <c r="AR19" s="80"/>
+      <c r="AS19" s="80"/>
+      <c r="AT19" s="81" t="str">
         <f aca="false">IF(A19="","",AR19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AS19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AU19" s="59" t="str">
+      <c r="AU19" s="79" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV19" s="46"/>
-      <c r="AW19" s="46"/>
-      <c r="AX19" s="60" t="str">
+      <c r="AV19" s="80"/>
+      <c r="AW19" s="80"/>
+      <c r="AX19" s="81" t="str">
         <f aca="false">IF(A19="","",AV19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,AW19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="AY19" s="59" t="str">
+      <c r="AY19" s="79" t="str">
         <f aca="false">IFERROR(IF(A19="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A19,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A19,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A19,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ19" s="46"/>
-      <c r="BA19" s="46"/>
-      <c r="BB19" s="60" t="str">
+      <c r="AZ19" s="80"/>
+      <c r="BA19" s="80"/>
+      <c r="BB19" s="81" t="str">
         <f aca="false">IF(A19="","",AZ19*$D19+IF(OR($F19="Exempt",$E19="Sub"),0,BA19*$D19*1.5))</f>
         <v/>
       </c>
-      <c r="BC19" s="45" t="str">
+      <c r="BC19" s="82" t="str">
         <f aca="false">IF(A19="","",SUM(G19,K19,O19,S19,W19,AA19,AE19,AI19,AM19,AQ19,AU19,AY19))</f>
         <v/>
       </c>
-      <c r="BD19" s="45" t="str">
+      <c r="BD19" s="82" t="str">
         <f aca="false">IF(A19="","",SUM(H19,I19,L19,M19,P19,Q19,T19,U19,X19,Y19,AB19,AC19,AF19,AG19,AJ19,AK19,AN19,AO19,AR19,AS19,AV19,AW19,AZ19,BA19))</f>
         <v/>
       </c>
-      <c r="BE19" s="19" t="str">
+      <c r="BE19" s="83" t="str">
         <f aca="false">IF(A19="","",BC19*$D19)</f>
         <v/>
       </c>
-      <c r="BF19" s="19" t="str">
+      <c r="BF19" s="83" t="str">
         <f aca="false">IF(A19="","",SUM(J19,N19,R19,V19,Z19,AD19,AH19,AL19,AP19,AT19,AX19,BB19))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12"/>
-      <c r="B20" s="51" t="str">
+      <c r="A20" s="20"/>
+      <c r="B20" s="67" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$B$5:$B$19,MATCH($A20,Personnel!$A$5:$A$19,0)),"-- not found --"))</f>
         <v/>
       </c>
-      <c r="C20" s="51" t="str">
+      <c r="C20" s="67" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$C$5:$C$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="D20" s="52" t="str">
+      <c r="D20" s="68" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$H$5:$H$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="53" t="str">
+      <c r="E20" s="20"/>
+      <c r="F20" s="69" t="str">
         <f aca="false">IF(A20="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A20,Personnel!$A$5:$A$19,0)),""))</f>
         <v/>
       </c>
-      <c r="G20" s="54" t="str">
+      <c r="G20" s="70" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,0),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,0),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,0)),MONTH(EDATE(Dashboard!$C$5,0)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,0),0))))),"")</f>
         <v/>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="55" t="str">
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="72" t="str">
         <f aca="false">IF(A20="","",H20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,I20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="K20" s="54" t="str">
+      <c r="K20" s="70" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,1),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,1),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,1)),MONTH(EDATE(Dashboard!$C$5,1)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,1),0))))),"")</f>
         <v/>
       </c>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="55" t="str">
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="72" t="str">
         <f aca="false">IF(A20="","",L20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,M20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="O20" s="54" t="str">
+      <c r="O20" s="70" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,2),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,2),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,2)),MONTH(EDATE(Dashboard!$C$5,2)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,2),0))))),"")</f>
         <v/>
       </c>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="55" t="str">
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72" t="str">
         <f aca="false">IF(A20="","",P20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,Q20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="S20" s="54" t="str">
+      <c r="S20" s="73" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,3),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,3),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,3)),MONTH(EDATE(Dashboard!$C$5,3)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,3),0))))),"")</f>
         <v/>
       </c>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="55" t="str">
+      <c r="T20" s="74"/>
+      <c r="U20" s="74"/>
+      <c r="V20" s="75" t="str">
         <f aca="false">IF(A20="","",T20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,U20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="W20" s="54" t="str">
+      <c r="W20" s="73" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,4),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,4),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,4)),MONTH(EDATE(Dashboard!$C$5,4)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,4),0))))),"")</f>
         <v/>
       </c>
-      <c r="X20" s="42"/>
-      <c r="Y20" s="42"/>
-      <c r="Z20" s="55" t="str">
+      <c r="X20" s="74"/>
+      <c r="Y20" s="74"/>
+      <c r="Z20" s="75" t="str">
         <f aca="false">IF(A20="","",X20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,Y20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AA20" s="54" t="str">
+      <c r="AA20" s="73" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,5),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,5),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,5)),MONTH(EDATE(Dashboard!$C$5,5)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,5),0))))),"")</f>
         <v/>
       </c>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="55" t="str">
+      <c r="AB20" s="74"/>
+      <c r="AC20" s="74"/>
+      <c r="AD20" s="75" t="str">
         <f aca="false">IF(A20="","",AB20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AC20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AE20" s="54" t="str">
+      <c r="AE20" s="76" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,6),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,6),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,6)),MONTH(EDATE(Dashboard!$C$5,6)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,6),0))))),"")</f>
         <v/>
       </c>
-      <c r="AF20" s="42"/>
-      <c r="AG20" s="42"/>
-      <c r="AH20" s="55" t="str">
+      <c r="AF20" s="77"/>
+      <c r="AG20" s="77"/>
+      <c r="AH20" s="78" t="str">
         <f aca="false">IF(A20="","",AF20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AG20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AI20" s="54" t="str">
+      <c r="AI20" s="76" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,7),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,7),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,7)),MONTH(EDATE(Dashboard!$C$5,7)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,7),0))))),"")</f>
         <v/>
       </c>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="42"/>
-      <c r="AL20" s="55" t="str">
+      <c r="AJ20" s="77"/>
+      <c r="AK20" s="77"/>
+      <c r="AL20" s="78" t="str">
         <f aca="false">IF(A20="","",AJ20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AK20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AM20" s="54" t="str">
+      <c r="AM20" s="76" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,8),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,8),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,8)),MONTH(EDATE(Dashboard!$C$5,8)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,8),0))))),"")</f>
         <v/>
       </c>
-      <c r="AN20" s="42"/>
-      <c r="AO20" s="42"/>
-      <c r="AP20" s="55" t="str">
+      <c r="AN20" s="77"/>
+      <c r="AO20" s="77"/>
+      <c r="AP20" s="78" t="str">
         <f aca="false">IF(A20="","",AN20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AO20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AQ20" s="54" t="str">
+      <c r="AQ20" s="79" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,9),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,9),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,9)),MONTH(EDATE(Dashboard!$C$5,9)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,9),0))))),"")</f>
         <v/>
       </c>
-      <c r="AR20" s="42"/>
-      <c r="AS20" s="42"/>
-      <c r="AT20" s="55" t="str">
+      <c r="AR20" s="80"/>
+      <c r="AS20" s="80"/>
+      <c r="AT20" s="81" t="str">
         <f aca="false">IF(A20="","",AR20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AS20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AU20" s="54" t="str">
+      <c r="AU20" s="79" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,10),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,10),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,10)),MONTH(EDATE(Dashboard!$C$5,10)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,10),0))))),"")</f>
         <v/>
       </c>
-      <c r="AV20" s="42"/>
-      <c r="AW20" s="42"/>
-      <c r="AX20" s="55" t="str">
+      <c r="AV20" s="80"/>
+      <c r="AW20" s="80"/>
+      <c r="AX20" s="81" t="str">
         <f aca="false">IF(A20="","",AV20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,AW20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="AY20" s="54" t="str">
+      <c r="AY20" s="79" t="str">
         <f aca="false">IFERROR(IF(A20="","",MAX(0,(INDEX(Personnel!$G$5:$G$19,MATCH($A20,Personnel!$A$5:$A$19,0))/12)*((MIN(EOMONTH(EDATE(Dashboard!$C$5,11),0),IF(INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))="",EOMONTH(EDATE(Dashboard!$C$5,11),0),INDEX(Personnel!$K$5:$K$19,MATCH($A20,Personnel!$A$5:$A$19,0))))-MAX(DATE(YEAR(EDATE(Dashboard!$C$5,11)),MONTH(EDATE(Dashboard!$C$5,11)),1),INDEX(Personnel!$J$5:$J$19,MATCH($A20,Personnel!$A$5:$A$19,0)))+1)/DAY(EOMONTH(EDATE(Dashboard!$C$5,11),0))))),"")</f>
         <v/>
       </c>
-      <c r="AZ20" s="42"/>
-      <c r="BA20" s="42"/>
-      <c r="BB20" s="55" t="str">
+      <c r="AZ20" s="80"/>
+      <c r="BA20" s="80"/>
+      <c r="BB20" s="81" t="str">
         <f aca="false">IF(A20="","",AZ20*$D20+IF(OR($F20="Exempt",$E20="Sub"),0,BA20*$D20*1.5))</f>
         <v/>
       </c>
-      <c r="BC20" s="41" t="str">
+      <c r="BC20" s="82" t="str">
         <f aca="false">IF(A20="","",SUM(G20,K20,O20,S20,W20,AA20,AE20,AI20,AM20,AQ20,AU20,AY20))</f>
         <v/>
       </c>
-      <c r="BD20" s="41" t="str">
+      <c r="BD20" s="82" t="str">
         <f aca="false">IF(A20="","",SUM(H20,I20,L20,M20,P20,Q20,T20,U20,X20,Y20,AB20,AC20,AF20,AG20,AJ20,AK20,AN20,AO20,AR20,AS20,AV20,AW20,AZ20,BA20))</f>
         <v/>
       </c>
-      <c r="BE20" s="15" t="str">
+      <c r="BE20" s="83" t="str">
         <f aca="false">IF(A20="","",BC20*$D20)</f>
         <v/>
       </c>
-      <c r="BF20" s="15" t="str">
+      <c r="BF20" s="83" t="str">
         <f aca="false">IF(A20="","",SUM(J20,N20,R20,V20,Z20,AD20,AH20,AL20,AP20,AT20,AX20,BB20))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>177</v>
+      <c r="A23" s="34" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="H24" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="47" t="s">
-        <v>185</v>
+      <c r="A24" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29" t="n">
+      <c r="A25" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A25-1)</f>
         <v>46023</v>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="25" t="n">
         <f aca="false">SUMIFS(J$6:J$20,$E$6:$E$20,"Prime")</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="D25" s="31" t="n">
-        <f aca="false">C25*Rates!$B$3</f>
+      <c r="D25" s="35" t="n">
+        <f aca="false">C25*Rates!$B$6</f>
         <v>4812.40745192308</v>
       </c>
-      <c r="E25" s="31" t="n">
-        <f aca="false">(C25+D25)*Rates!$B$4</f>
+      <c r="E25" s="35" t="n">
+        <f aca="false">(C25+D25)*Rates!$B$7</f>
         <v>10209.1786658654</v>
       </c>
-      <c r="F25" s="15" t="n">
+      <c r="F25" s="25" t="n">
         <f aca="false">C25+D25+E25</f>
         <v>28771.3216947115</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="25" t="n">
         <f aca="false">SUMIFS(J$6:J$20,$E$6:$E$20,"Sub")</f>
         <v>4275</v>
       </c>
-      <c r="H25" s="61" t="n">
+      <c r="H25" s="41" t="n">
         <f aca="false">F25+G25</f>
         <v>33046.3216947115</v>
       </c>
-      <c r="I25" s="62" t="n">
-        <f aca="false">H25*Rates!$B$5</f>
+      <c r="I25" s="87" t="n">
+        <f aca="false">H25*Rates!$B$8</f>
         <v>3965.55860336539</v>
       </c>
-      <c r="J25" s="63" t="n">
+      <c r="J25" s="88" t="n">
         <f aca="false">H25+I25</f>
         <v>37011.8802980769</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A26-1)</f>
         <v>46054</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">SUMIFS(N$6:N$20,$E$6:$E$20,"Prime")</f>
         <v>13749.7355769231</v>
       </c>
-      <c r="D26" s="36" t="n">
-        <f aca="false">C26*Rates!$B$3</f>
+      <c r="D26" s="38" t="n">
+        <f aca="false">C26*Rates!$B$6</f>
         <v>4812.40745192308</v>
       </c>
-      <c r="E26" s="36" t="n">
-        <f aca="false">(C26+D26)*Rates!$B$4</f>
+      <c r="E26" s="38" t="n">
+        <f aca="false">(C26+D26)*Rates!$B$7</f>
         <v>10209.1786658654</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="32" t="n">
         <f aca="false">C26+D26+E26</f>
         <v>28771.3216947115</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="32" t="n">
         <f aca="false">SUMIFS(N$6:N$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H26" s="61" t="n">
+      <c r="H26" s="41" t="n">
         <f aca="false">F26+G26</f>
         <v>28771.3216947115</v>
       </c>
-      <c r="I26" s="62" t="n">
-        <f aca="false">H26*Rates!$B$5</f>
+      <c r="I26" s="87" t="n">
+        <f aca="false">H26*Rates!$B$8</f>
         <v>3452.55860336539</v>
       </c>
-      <c r="J26" s="63" t="n">
+      <c r="J26" s="88" t="n">
         <f aca="false">H26+I26</f>
         <v>32223.8802980769</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46082</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">SUMIFS(R$6:R$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="31" t="n">
-        <f aca="false">C27*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="31" t="n">
-        <f aca="false">(C27+D27)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="15" t="n">
+      <c r="D27" s="35" t="n">
+        <f aca="false">C27*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="35" t="n">
+        <f aca="false">(C27+D27)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="25" t="n">
         <f aca="false">C27+D27+E27</f>
         <v>0</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="25" t="n">
         <f aca="false">SUMIFS(R$6:R$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="61" t="n">
+      <c r="H27" s="41" t="n">
         <f aca="false">F27+G27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="62" t="n">
-        <f aca="false">H27*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="63" t="n">
+      <c r="I27" s="87" t="n">
+        <f aca="false">H27*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="88" t="n">
         <f aca="false">H27+I27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46113</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">SUMIFS(V$6:V$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D28" s="36" t="n">
-        <f aca="false">C28*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="36" t="n">
-        <f aca="false">(C28+D28)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="19" t="n">
+      <c r="D28" s="38" t="n">
+        <f aca="false">C28*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <f aca="false">(C28+D28)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="32" t="n">
         <f aca="false">C28+D28+E28</f>
         <v>0</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="32" t="n">
         <f aca="false">SUMIFS(V$6:V$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="61" t="n">
+      <c r="H28" s="41" t="n">
         <f aca="false">F28+G28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="62" t="n">
-        <f aca="false">H28*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="63" t="n">
+      <c r="I28" s="87" t="n">
+        <f aca="false">H28*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="88" t="n">
         <f aca="false">H28+I28</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46143</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="25" t="n">
         <f aca="false">SUMIFS(Z$6:Z$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D29" s="31" t="n">
-        <f aca="false">C29*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="31" t="n">
-        <f aca="false">(C29+D29)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="15" t="n">
+      <c r="D29" s="35" t="n">
+        <f aca="false">C29*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="35" t="n">
+        <f aca="false">(C29+D29)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="25" t="n">
         <f aca="false">C29+D29+E29</f>
         <v>0</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="25" t="n">
         <f aca="false">SUMIFS(Z$6:Z$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H29" s="61" t="n">
+      <c r="H29" s="41" t="n">
         <f aca="false">F29+G29</f>
         <v>0</v>
       </c>
-      <c r="I29" s="62" t="n">
-        <f aca="false">H29*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="63" t="n">
+      <c r="I29" s="87" t="n">
+        <f aca="false">H29*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="88" t="n">
         <f aca="false">H29+I29</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46174</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="32" t="n">
         <f aca="false">SUMIFS(AD$6:AD$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D30" s="36" t="n">
-        <f aca="false">C30*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="36" t="n">
-        <f aca="false">(C30+D30)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="19" t="n">
+      <c r="D30" s="38" t="n">
+        <f aca="false">C30*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <f aca="false">(C30+D30)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="32" t="n">
         <f aca="false">C30+D30+E30</f>
         <v>0</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="32" t="n">
         <f aca="false">SUMIFS(AD$6:AD$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H30" s="61" t="n">
+      <c r="H30" s="41" t="n">
         <f aca="false">F30+G30</f>
         <v>0</v>
       </c>
-      <c r="I30" s="62" t="n">
-        <f aca="false">H30*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="63" t="n">
+      <c r="I30" s="87" t="n">
+        <f aca="false">H30*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="88" t="n">
         <f aca="false">H30+I30</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46204</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="25" t="n">
         <f aca="false">SUMIFS(AH$6:AH$20,$E$6:$E$20,"Prime")</f>
         <v>4326.92307692308</v>
       </c>
-      <c r="D31" s="31" t="n">
-        <f aca="false">C31*Rates!$B$3</f>
+      <c r="D31" s="35" t="n">
+        <f aca="false">C31*Rates!$B$6</f>
         <v>1514.42307692308</v>
       </c>
-      <c r="E31" s="31" t="n">
-        <f aca="false">(C31+D31)*Rates!$B$4</f>
+      <c r="E31" s="35" t="n">
+        <f aca="false">(C31+D31)*Rates!$B$7</f>
         <v>3212.74038461539</v>
       </c>
-      <c r="F31" s="15" t="n">
+      <c r="F31" s="25" t="n">
         <f aca="false">C31+D31+E31</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="25" t="n">
         <f aca="false">SUMIFS(AH$6:AH$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="61" t="n">
+      <c r="H31" s="41" t="n">
         <f aca="false">F31+G31</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="I31" s="62" t="n">
-        <f aca="false">H31*Rates!$B$5</f>
+      <c r="I31" s="87" t="n">
+        <f aca="false">H31*Rates!$B$8</f>
         <v>1086.49038461538</v>
       </c>
-      <c r="J31" s="63" t="n">
+      <c r="J31" s="88" t="n">
         <f aca="false">H31+I31</f>
         <v>10140.5769230769</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46235</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="32" t="n">
         <f aca="false">SUMIFS(AL$6:AL$20,$E$6:$E$20,"Prime")</f>
         <v>12499.7596153846</v>
       </c>
-      <c r="D32" s="36" t="n">
-        <f aca="false">C32*Rates!$B$3</f>
+      <c r="D32" s="38" t="n">
+        <f aca="false">C32*Rates!$B$6</f>
         <v>4374.91586538462</v>
       </c>
-      <c r="E32" s="36" t="n">
-        <f aca="false">(C32+D32)*Rates!$B$4</f>
+      <c r="E32" s="38" t="n">
+        <f aca="false">(C32+D32)*Rates!$B$7</f>
         <v>9281.07151442308</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="32" t="n">
         <f aca="false">C32+D32+E32</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="32" t="n">
         <f aca="false">SUMIFS(AL$6:AL$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H32" s="61" t="n">
+      <c r="H32" s="41" t="n">
         <f aca="false">F32+G32</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="I32" s="62" t="n">
-        <f aca="false">H32*Rates!$B$5</f>
+      <c r="I32" s="87" t="n">
+        <f aca="false">H32*Rates!$B$8</f>
         <v>3138.68963942308</v>
       </c>
-      <c r="J32" s="63" t="n">
+      <c r="J32" s="88" t="n">
         <f aca="false">H32+I32</f>
         <v>29294.4366346154</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46266</v>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C33" s="25" t="n">
         <f aca="false">SUMIFS(AP$6:AP$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="31" t="n">
-        <f aca="false">C33*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="31" t="n">
-        <f aca="false">(C33+D33)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="15" t="n">
+      <c r="D33" s="35" t="n">
+        <f aca="false">C33*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="35" t="n">
+        <f aca="false">(C33+D33)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="25" t="n">
         <f aca="false">C33+D33+E33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="25" t="n">
         <f aca="false">SUMIFS(AP$6:AP$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H33" s="61" t="n">
+      <c r="H33" s="41" t="n">
         <f aca="false">F33+G33</f>
         <v>0</v>
       </c>
-      <c r="I33" s="62" t="n">
-        <f aca="false">H33*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="63" t="n">
+      <c r="I33" s="87" t="n">
+        <f aca="false">H33*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="88" t="n">
         <f aca="false">H33+I33</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="B34" s="35" t="n">
+      <c r="B34" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46296</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="32" t="n">
         <f aca="false">SUMIFS(AT$6:AT$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D34" s="36" t="n">
-        <f aca="false">C34*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="36" t="n">
-        <f aca="false">(C34+D34)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="19" t="n">
+      <c r="D34" s="38" t="n">
+        <f aca="false">C34*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="38" t="n">
+        <f aca="false">(C34+D34)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="32" t="n">
         <f aca="false">C34+D34+E34</f>
         <v>0</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="32" t="n">
         <f aca="false">SUMIFS(AT$6:AT$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H34" s="61" t="n">
+      <c r="H34" s="41" t="n">
         <f aca="false">F34+G34</f>
         <v>0</v>
       </c>
-      <c r="I34" s="62" t="n">
-        <f aca="false">H34*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="63" t="n">
+      <c r="I34" s="87" t="n">
+        <f aca="false">H34*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="88" t="n">
         <f aca="false">H34+I34</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46327</v>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="25" t="n">
         <f aca="false">SUMIFS(AX$6:AX$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D35" s="31" t="n">
-        <f aca="false">C35*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="31" t="n">
-        <f aca="false">(C35+D35)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="15" t="n">
+      <c r="D35" s="35" t="n">
+        <f aca="false">C35*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="35" t="n">
+        <f aca="false">(C35+D35)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="25" t="n">
         <f aca="false">C35+D35+E35</f>
         <v>0</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="25" t="n">
         <f aca="false">SUMIFS(AX$6:AX$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H35" s="61" t="n">
+      <c r="H35" s="41" t="n">
         <f aca="false">F35+G35</f>
         <v>0</v>
       </c>
-      <c r="I35" s="62" t="n">
-        <f aca="false">H35*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="63" t="n">
+      <c r="I35" s="87" t="n">
+        <f aca="false">H35*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="88" t="n">
         <f aca="false">H35+I35</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46357</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="32" t="n">
         <f aca="false">SUMIFS(BB$6:BB$20,$E$6:$E$20,"Prime")</f>
         <v>0</v>
       </c>
-      <c r="D36" s="36" t="n">
-        <f aca="false">C36*Rates!$B$3</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="36" t="n">
-        <f aca="false">(C36+D36)*Rates!$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="19" t="n">
+      <c r="D36" s="38" t="n">
+        <f aca="false">C36*Rates!$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="38" t="n">
+        <f aca="false">(C36+D36)*Rates!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="32" t="n">
         <f aca="false">C36+D36+E36</f>
         <v>0</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="32" t="n">
         <f aca="false">SUMIFS(BB$6:BB$20,$E$6:$E$20,"Sub")</f>
         <v>0</v>
       </c>
-      <c r="H36" s="61" t="n">
+      <c r="H36" s="41" t="n">
         <f aca="false">F36+G36</f>
         <v>0</v>
       </c>
-      <c r="I36" s="62" t="n">
-        <f aca="false">H36*Rates!$B$5</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="63" t="n">
+      <c r="I36" s="87" t="n">
+        <f aca="false">H36*Rates!$B$8</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="88" t="n">
         <f aca="false">H36+I36</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -7470,385 +8126,385 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>188</v>
+      <c r="A3" s="34" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>190</v>
+      <c r="A4" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="21" t="n">
         <v>46036</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="B5" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="23" t="n">
         <v>14200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="28" t="n">
         <v>46056</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="D6" s="16" t="n">
+      <c r="B6" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="30" t="n">
         <v>3100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="21" t="n">
         <v>46132</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="B7" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="23" t="n">
         <v>8600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="30"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="30"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="30"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="65"/>
-      <c r="B23" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="21" t="n">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="92" t="n">
         <f aca="false">SUM(E5:E22)</f>
         <v>25900</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>197</v>
+      <c r="A25" s="34" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>198</v>
+      <c r="A26" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="89" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46023</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A27)</f>
         <v>14200</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46054</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A28)</f>
         <v>3100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46082</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46113</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A30)</f>
         <v>8600</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46143</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46174</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46204</v>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C33" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="35" t="n">
+      <c r="B34" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46235</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46266</v>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46296</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A37-1)</f>
         <v>46327</v>
       </c>
-      <c r="C37" s="15" t="n">
+      <c r="C37" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A37)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A38-1)</f>
         <v>46357</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -7873,385 +8529,385 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>188</v>
+      <c r="A3" s="34" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="64" t="s">
-        <v>190</v>
+      <c r="A4" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="21" t="n">
         <v>46042</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" s="12" t="n">
+      <c r="B5" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="23" t="n">
         <v>480</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="28" t="n">
         <v>46042</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="16" t="n">
+      <c r="B6" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="30" t="n">
         <v>610</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="21" t="n">
         <v>46091</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="12" t="n">
+      <c r="B7" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="23" t="n">
         <v>1150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="18"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="18"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="14"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="18"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="18"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="30"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="30"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="30"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="14"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="30"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="23"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="30"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="65"/>
-      <c r="B23" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="21" t="n">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="92" t="n">
         <f aca="false">SUM(E5:E22)</f>
         <v>2240</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>197</v>
+      <c r="A25" s="34" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="64" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>206</v>
+      <c r="A26" s="89" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="89" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
         <v>46023</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A27)</f>
         <v>1090</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
         <v>46054</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="n">
+      <c r="A29" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
         <v>46082</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A29)</f>
         <v>1150</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="34" t="n">
+      <c r="A30" s="54" t="n">
         <v>4</v>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
         <v>46113</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A30)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="29" t="n">
+      <c r="A31" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
         <v>46143</v>
       </c>
-      <c r="C31" s="15" t="n">
+      <c r="C31" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A31)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="34" t="n">
+      <c r="A32" s="54" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
         <v>46174</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A32)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="29" t="n">
+      <c r="A33" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
         <v>46204</v>
       </c>
-      <c r="C33" s="15" t="n">
+      <c r="C33" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="34" t="n">
+      <c r="A34" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="B34" s="35" t="n">
+      <c r="B34" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
         <v>46235</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="29" t="n">
+      <c r="A35" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
         <v>46266</v>
       </c>
-      <c r="C35" s="15" t="n">
+      <c r="C35" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="34" t="n">
+      <c r="A36" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
         <v>46296</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A36)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="52" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A37-1)</f>
         <v>46327</v>
       </c>
-      <c r="C37" s="15" t="n">
+      <c r="C37" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A37)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="34" t="n">
+      <c r="A38" s="54" t="n">
         <v>12</v>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="55" t="n">
         <f aca="false">EDATE(Dashboard!$C$5,A38-1)</f>
         <v>46357</v>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Labor" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="ODCs" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Travel" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="M&amp;E" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="ROM Calculator" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="286">
   <si>
     <t xml:space="preserve">Acqlerate</t>
   </si>
@@ -125,22 +127,52 @@
     <t xml:space="preserve">6. ODCs — log each purchase as a line item (date, category, description, month #, amount). The</t>
   </si>
   <si>
-    <t xml:space="preserve">   Monthly Rollup section at the bottom totals them automatically by month.</t>
+    <t xml:space="preserve">   Monthly Rollup section at the bottom totals them automatically by month. Use this for general</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   other direct costs — software, shipping, supplies — not equipment or materials.</t>
   </si>
   <si>
     <t xml:space="preserve">7. Travel — same idea as ODCs: log each trip/expense as a line item, it rolls up by month.</t>
   </si>
   <si>
+    <t xml:space="preserve">8. M&amp;E — same pattern again, kept separate from ODCs because Materials &amp; Equipment is usually its</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   own CLIN on a real contract, not lumped in with general ODCs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The Dashboard tab does the rest automatically:</t>
   </si>
   <si>
-    <t xml:space="preserve">Labor + ODCs + Travel → Subtotal → + G&amp;A → Total Cost → + Fee → Total Billed for the month. That</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolls into cumulative spend, variance against your straight-line plan, a 3-month rolling burn rate,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a projected fund-exhaustion date, and a plain-language status flag.</t>
+    <t xml:space="preserve">Labor + ODCs + M&amp;E + Travel → Subtotal → + G&amp;A → Total Cost → + Fee → Total Billed for the month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That rolls into cumulative spend, variance against your straight-line plan, a 3-month rolling burn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rate, a projected fund-exhaustion date, and a plain-language status flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One more tab, separate from all of the above — ROM Calculator:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This one doesn't log anything or touch your totals. It's a standalone what-if: type in a role,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salary or hourly rate, a start and end date, and pick from four common location/allowance adders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(COLA, LQA, Relocation, Other — edit any of them). It runs the same Fringe/OH/G&amp;A/Fee buildup as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the rest of the workbook and gives you a single fully burdened number, plus a copy-paste sentence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">you can drop straight into an email — built for exactly the moment a CO or COR asks "what would</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it cost to add this person" and you need a defensible answer in the next five minutes.</t>
   </si>
   <si>
     <t xml:space="preserve">One thing to know about "Planned Cumulative $":</t>
@@ -239,7 +271,7 @@
     <t xml:space="preserve">G&amp;A Rate (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Applied to Total Cost Input (fully burdened labor + ODCs + Travel). Covers company-wide G&amp;A: executive, finance, HR, business development.</t>
+    <t xml:space="preserve">Applied to Total Cost Input (fully burdened labor + ODCs + Travel + M&amp;E). Covers company-wide G&amp;A: executive, finance, HR, business development.</t>
   </si>
   <si>
     <t xml:space="preserve">FEE STRUCTURE</t>
@@ -275,7 +307,7 @@
     <t xml:space="preserve">This is what the Dashboard tab actually uses.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fee base note: this tracker applies fee to Total Cost (burdened labor + ODCs + Travel + G&amp;A). Some contracts exclude ODCs, travel, or facilities capital cost of money from the fee base — check your specific contract's fee clause (FAR 52.216 series) before relying on this for real billing.</t>
+    <t xml:space="preserve">Fee base note: this tracker applies fee to Total Cost (burdened labor + ODCs + Travel + M&amp;E + G&amp;A). Some contracts exclude ODCs, travel, M&amp;E, or facilities capital cost of money from the fee base — check your specific contract's fee clause (FAR 52.216 series) before relying on this for real billing.</t>
   </si>
   <si>
     <t xml:space="preserve">Funding Modification Log</t>
@@ -309,6 +341,10 @@
 $</t>
   </si>
   <si>
+    <t xml:space="preserve">M&amp;E CLIN
+$</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mod Total
 $</t>
   </si>
@@ -325,6 +361,10 @@
 TOA $</t>
   </si>
   <si>
+    <t xml:space="preserve">Cum. M&amp;E
+TOA $</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cum. Total
 TOA $</t>
   </si>
@@ -371,6 +411,9 @@
     <t xml:space="preserve">ODC</t>
   </si>
   <si>
+    <t xml:space="preserve">M&amp;E</t>
+  </si>
+  <si>
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
@@ -447,11 +490,14 @@
     <t xml:space="preserve">ODCs $</t>
   </si>
   <si>
+    <t xml:space="preserve">M&amp;E $</t>
+  </si>
+  <si>
     <t xml:space="preserve">Travel $</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal
-(L+O+T)</t>
+(L+O+M+T)</t>
   </si>
   <si>
     <t xml:space="preserve">G&amp;A $</t>
@@ -714,56 +760,191 @@
     <t xml:space="preserve">Amount $</t>
   </si>
   <si>
+    <t xml:space="preserve">Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual license renewal — 3 seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliverable courier — CDRL package</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumables — lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOG TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Rollup (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total ODCs $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airfare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM — kickoff meeting, NAS Norfolk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lodging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM — kickoff meeting, 3 nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airfare + Per Diem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Engineer — site visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Travel $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materials &amp; Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replacement network switches (5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test bench calibration</t>
+  </si>
+  <si>
     <t xml:space="preserve">Materials</t>
   </si>
   <si>
-    <t xml:space="preserve">Replacement network switches (5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test bench calibration</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spare parts kit</t>
   </si>
   <si>
-    <t xml:space="preserve">LOG TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly Rollup (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total ODCs $</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM — kickoff meeting, NAS Norfolk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lodging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM — kickoff meeting, 3 nights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airfare + Per Diem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Engineer — site visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Travel $</t>
+    <t xml:space="preserve">Total Materials &amp; Equipment $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROM Calculator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quick answer for "what would it cost to add or change this person?" — a standalone what-if, separate from your actual Labor log. Doesn't affect Dashboard totals or Labor actuals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCENARIO INPUTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill in the role and dates — everything below calculates automatically from your Rates tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role / LCAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Salary (Exempt only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Hourly Rate (Non-Exempt only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Annual Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defaults to your PoP End on Dashboard — type over it for a custom end date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE LABOR COST (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-line day proration over the period — a ROM approximation, not a payroll calendar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-Time Rate $/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days in Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated Hours in Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Labor $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fringe $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Fully Burdened Labor $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCATION / ALLOWANCE ADDERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common OCONUS adders — edit the label or amount, or leave a row blank to skip it. Annual amounts prorate over the period above; one-time amounts don't.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost for Period $ (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLA (Cost of Living Allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual $ (prorate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LQA (Living Quarters Allowance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-Time $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Adders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROM ESTIMATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same buildup as Dashboard: Labor + Adders -&gt; Subtotal -&gt; + G&amp;A -&gt; Total Cost -&gt; + Fee -&gt; fully burdened total.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal (Labor + Adders) $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Cost $</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL ROM ESTIMATE (fully burdened)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy the line above straight into an email — everything in it flows from your Rates tab, so it stays consistent with how you bill.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
@@ -772,8 +953,9 @@
     <numFmt numFmtId="169" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,6 +1076,47 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF7A5AF8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF085041"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF085041"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1021,7 +1244,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="108">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1391,6 +1614,66 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1509,7 +1792,7 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF7A5AF8"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
@@ -1558,6 +1841,49 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="380520" cy="380520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>247320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="247320" cy="247320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1874,6 +2200,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>247320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="247320" cy="247320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -2055,7 +2424,7 @@
     <tabColor rgb="FFBFBFBF"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
@@ -2241,48 +2610,48 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4"/>
+      <c r="A39" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>34</v>
+      <c r="A40" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="A42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4"/>
+      <c r="A44" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
+      <c r="A45" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2297,63 +2666,63 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
+      <c r="A52" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>47</v>
-      </c>
+      <c r="A55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
-        <v>49</v>
+      <c r="A58" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="5" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2363,25 +2732,25 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4"/>
+      <c r="A65" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>56</v>
+      <c r="A66" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="A68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2390,7 +2759,542 @@
         <v>60</v>
       </c>
     </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF7A5AF8"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="94" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="96" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="97"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="95"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="94" t="n">
+        <v>2080</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="98" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="99" t="n">
+        <f aca="false">Dashboard!$C$6</f>
+        <v>46387</v>
+      </c>
+      <c r="C14" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="93" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" s="93"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="101" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="58" t="n">
+        <f aca="false">IF(B9="Exempt",IF(B12=0,"",B10/B12),B11)</f>
+        <v>72.1153846153846</v>
+      </c>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="101" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20" s="102" t="n">
+        <f aca="false">IF(OR(B13="",B14=""),"",B14-B13+1)</f>
+        <v>122</v>
+      </c>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="95"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="101" t="s">
+        <v>263</v>
+      </c>
+      <c r="B21" s="59" t="n">
+        <f aca="false">IF(B20="","",B12*B20/365)</f>
+        <v>695.232876712329</v>
+      </c>
+      <c r="C21" s="95"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="101" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="25" t="n">
+        <f aca="false">IF(OR(B21="",B19=""),"",B21*B19)</f>
+        <v>50136.9863013699</v>
+      </c>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="101" t="s">
+        <v>265</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <f aca="false">IF(B22="","",B22*Rates!$B$6)</f>
+        <v>17547.9452054795</v>
+      </c>
+      <c r="C23" s="95"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="101" t="s">
+        <v>266</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <f aca="false">IF(B22="","",(B22+B23)*Rates!$B$7)</f>
+        <v>37226.7123287671</v>
+      </c>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+    </row>
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" s="103" t="n">
+        <f aca="false">IF(B22="","",B22+B23+B24)</f>
+        <v>104911.643835616</v>
+      </c>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="93" t="s">
+        <v>268</v>
+      </c>
+      <c r="B27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D31" s="25" t="n">
+        <f aca="false">IF(C31="","",IF(B31="One-Time $",C31,C31*B20/365))</f>
+        <v>2673.97260273973</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <f aca="false">IF(C32="","",IF(B32="One-Time $",C32,C32*B20/365))</f>
+        <v>8021.91780821918</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D33" s="25" t="n">
+        <f aca="false">IF(C33="","",IF(B33="One-Time $",C33,C33*B20/365))</f>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="32" t="str">
+        <f aca="false">IF(C34="","",IF(B34="One-Time $",C34,C34*B20/365))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="B35" s="104"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="41" t="n">
+        <f aca="false">SUM(D31:D34)</f>
+        <v>25695.8904109589</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="93" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="93"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="101" t="s">
+        <v>282</v>
+      </c>
+      <c r="B40" s="25" t="n">
+        <f aca="false">IF(B25="","",B25+D35)</f>
+        <v>130607.534246575</v>
+      </c>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="101" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="25" t="n">
+        <f aca="false">IF(B40="","",B40*Rates!$B$8)</f>
+        <v>15672.904109589</v>
+      </c>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="101" t="s">
+        <v>283</v>
+      </c>
+      <c r="B42" s="25" t="n">
+        <f aca="false">IF(B40="","",B40+B41)</f>
+        <v>146280.438356164</v>
+      </c>
+      <c r="C42" s="95"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="95"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="101" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="25" t="n">
+        <f aca="false">IF(B42="","",B42*Rates!$C$17)</f>
+        <v>10239.6306849315</v>
+      </c>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="B44" s="106" t="n">
+        <f aca="false">IF(B42="","",B42+B43)</f>
+        <v>156520.069041096</v>
+      </c>
+      <c r="C44" s="104"/>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+    </row>
+    <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="107" t="str">
+        <f aca="false">"For "&amp;B8&amp;" from "&amp;TEXT(B13,"mm/dd/yyyy")&amp;" to "&amp;TEXT(B14,"mm/dd/yyyy")&amp;" ("&amp;B20&amp;" days): "&amp;TEXT(B44,"$#,##0")&amp;" fully burdened, ROM estimate."</f>
+        <v>For Engineer 4 from 09/01/2026 to 12/31/2026 (122 days): $156,520 fully burdened, ROM estimate.</v>
+      </c>
+      <c r="B46" s="107"/>
+      <c r="C46" s="107"/>
+      <c r="D46" s="107"/>
+      <c r="E46" s="107"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A47:E47"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B9" type="list">
+      <formula1>"Exempt,Non-Exempt"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B31" type="list">
+      <formula1>"One-Time $,Annual $ (prorate)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B32" type="list">
+      <formula1>"One-Time $,Annual $ (prorate)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B33" type="list">
+      <formula1>"One-Time $,Annual $ (prorate)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B34" type="list">
+      <formula1>"One-Time $,Annual $ (prorate)"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2420,15 +3324,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2438,7 +3342,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2448,13 +3352,13 @@
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>0.35</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -2462,13 +3366,13 @@
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B7" s="10" t="n">
         <v>0.55</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -2476,13 +3380,13 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>0.12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -2490,7 +3394,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2500,7 +3404,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2510,13 +3414,13 @@
     </row>
     <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -2524,13 +3428,13 @@
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.07</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -2538,13 +3442,13 @@
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
@@ -2552,7 +3456,7 @@
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="n">
@@ -2561,13 +3465,13 @@
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F17" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -2615,28 +3519,28 @@
     <tabColor rgb="FFEF9F27"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>62</v>
+        <v>93</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -2649,125 +3553,147 @@
       <c r="J3" s="16"/>
       <c r="K3" s="16"/>
       <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>93</v>
+        <v>101</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B5" s="21" t="n">
         <v>46023</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="23" t="n">
-        <v>1400000</v>
+        <v>1300000</v>
       </c>
       <c r="F5" s="23" t="n">
         <v>300000</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H5" s="24" t="n">
-        <f aca="false">IF(A5="","",SUM(E5:G5))</f>
+        <v>250000</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I5" s="24" t="n">
+        <f aca="false">IF(A5="","",SUM(E5:H5))</f>
         <v>2000000</v>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="J5" s="25" t="n">
         <f aca="false">IF(A5="","",SUM($E$5:E5))</f>
-        <v>1400000</v>
-      </c>
-      <c r="J5" s="25" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="K5" s="25" t="n">
         <f aca="false">IF(A5="","",SUM($F$5:F5))</f>
         <v>300000</v>
       </c>
-      <c r="K5" s="25" t="n">
+      <c r="L5" s="25" t="n">
         <f aca="false">IF(A5="","",SUM($G$5:G5))</f>
-        <v>300000</v>
-      </c>
-      <c r="L5" s="26" t="n">
-        <f aca="false">IF(A5="","",I5+J5+K5)</f>
+        <v>250000</v>
+      </c>
+      <c r="M5" s="25" t="n">
+        <f aca="false">IF(A5="","",SUM($H$5:H5))</f>
+        <v>150000</v>
+      </c>
+      <c r="N5" s="26" t="n">
+        <f aca="false">IF(A5="","",J5+K5+L5+M5)</f>
         <v>2000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>46143</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6" s="30" t="n">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="F6" s="30" t="n">
         <v>50000</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="31" t="n">
-        <f aca="false">IF(A6="","",SUM(E6:G6))</f>
-        <v>400000</v>
-      </c>
-      <c r="I6" s="32" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <f aca="false">IF(A6="","",SUM(E6:H6))</f>
+        <v>350000</v>
+      </c>
+      <c r="J6" s="32" t="n">
         <f aca="false">IF(A6="","",SUM($E$5:E6))</f>
-        <v>1700000</v>
-      </c>
-      <c r="J6" s="32" t="n">
+        <v>1550000</v>
+      </c>
+      <c r="K6" s="32" t="n">
         <f aca="false">IF(A6="","",SUM($F$5:F6))</f>
         <v>350000</v>
       </c>
-      <c r="K6" s="32" t="n">
+      <c r="L6" s="32" t="n">
         <f aca="false">IF(A6="","",SUM($G$5:G6))</f>
-        <v>350000</v>
-      </c>
-      <c r="L6" s="33" t="n">
-        <f aca="false">IF(A6="","",I6+J6+K6)</f>
-        <v>2400000</v>
+        <v>280000</v>
+      </c>
+      <c r="M6" s="32" t="n">
+        <f aca="false">IF(A6="","",SUM($H$5:H6))</f>
+        <v>170000</v>
+      </c>
+      <c r="N6" s="33" t="n">
+        <f aca="false">IF(A6="","",J6+K6+L6+M6)</f>
+        <v>2350000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2778,24 +3704,29 @@
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
-      <c r="H7" s="24" t="str">
-        <f aca="false">IF(A7="","",SUM(E7:G7))</f>
-        <v/>
-      </c>
-      <c r="I7" s="25" t="str">
+      <c r="H7" s="23"/>
+      <c r="I7" s="24" t="str">
+        <f aca="false">IF(A7="","",SUM(E7:H7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="25" t="str">
         <f aca="false">IF(A7="","",SUM($E$5:E7))</f>
         <v/>
       </c>
-      <c r="J7" s="25" t="str">
+      <c r="K7" s="25" t="str">
         <f aca="false">IF(A7="","",SUM($F$5:F7))</f>
         <v/>
       </c>
-      <c r="K7" s="25" t="str">
+      <c r="L7" s="25" t="str">
         <f aca="false">IF(A7="","",SUM($G$5:G7))</f>
         <v/>
       </c>
-      <c r="L7" s="26" t="str">
-        <f aca="false">IF(A7="","",I7+J7+K7)</f>
+      <c r="M7" s="25" t="str">
+        <f aca="false">IF(A7="","",SUM($H$5:H7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="26" t="str">
+        <f aca="false">IF(A7="","",J7+K7+L7+M7)</f>
         <v/>
       </c>
     </row>
@@ -2807,24 +3738,29 @@
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
       <c r="G8" s="30"/>
-      <c r="H8" s="31" t="str">
-        <f aca="false">IF(A8="","",SUM(E8:G8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="32" t="str">
+      <c r="H8" s="30"/>
+      <c r="I8" s="31" t="str">
+        <f aca="false">IF(A8="","",SUM(E8:H8))</f>
+        <v/>
+      </c>
+      <c r="J8" s="32" t="str">
         <f aca="false">IF(A8="","",SUM($E$5:E8))</f>
         <v/>
       </c>
-      <c r="J8" s="32" t="str">
+      <c r="K8" s="32" t="str">
         <f aca="false">IF(A8="","",SUM($F$5:F8))</f>
         <v/>
       </c>
-      <c r="K8" s="32" t="str">
+      <c r="L8" s="32" t="str">
         <f aca="false">IF(A8="","",SUM($G$5:G8))</f>
         <v/>
       </c>
-      <c r="L8" s="33" t="str">
-        <f aca="false">IF(A8="","",I8+J8+K8)</f>
+      <c r="M8" s="32" t="str">
+        <f aca="false">IF(A8="","",SUM($H$5:H8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="33" t="str">
+        <f aca="false">IF(A8="","",J8+K8+L8+M8)</f>
         <v/>
       </c>
     </row>
@@ -2836,24 +3772,29 @@
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
-      <c r="H9" s="24" t="str">
-        <f aca="false">IF(A9="","",SUM(E9:G9))</f>
-        <v/>
-      </c>
-      <c r="I9" s="25" t="str">
+      <c r="H9" s="23"/>
+      <c r="I9" s="24" t="str">
+        <f aca="false">IF(A9="","",SUM(E9:H9))</f>
+        <v/>
+      </c>
+      <c r="J9" s="25" t="str">
         <f aca="false">IF(A9="","",SUM($E$5:E9))</f>
         <v/>
       </c>
-      <c r="J9" s="25" t="str">
+      <c r="K9" s="25" t="str">
         <f aca="false">IF(A9="","",SUM($F$5:F9))</f>
         <v/>
       </c>
-      <c r="K9" s="25" t="str">
+      <c r="L9" s="25" t="str">
         <f aca="false">IF(A9="","",SUM($G$5:G9))</f>
         <v/>
       </c>
-      <c r="L9" s="26" t="str">
-        <f aca="false">IF(A9="","",I9+J9+K9)</f>
+      <c r="M9" s="25" t="str">
+        <f aca="false">IF(A9="","",SUM($H$5:H9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="26" t="str">
+        <f aca="false">IF(A9="","",J9+K9+L9+M9)</f>
         <v/>
       </c>
     </row>
@@ -2865,24 +3806,29 @@
       <c r="E10" s="30"/>
       <c r="F10" s="30"/>
       <c r="G10" s="30"/>
-      <c r="H10" s="31" t="str">
-        <f aca="false">IF(A10="","",SUM(E10:G10))</f>
-        <v/>
-      </c>
-      <c r="I10" s="32" t="str">
+      <c r="H10" s="30"/>
+      <c r="I10" s="31" t="str">
+        <f aca="false">IF(A10="","",SUM(E10:H10))</f>
+        <v/>
+      </c>
+      <c r="J10" s="32" t="str">
         <f aca="false">IF(A10="","",SUM($E$5:E10))</f>
         <v/>
       </c>
-      <c r="J10" s="32" t="str">
+      <c r="K10" s="32" t="str">
         <f aca="false">IF(A10="","",SUM($F$5:F10))</f>
         <v/>
       </c>
-      <c r="K10" s="32" t="str">
+      <c r="L10" s="32" t="str">
         <f aca="false">IF(A10="","",SUM($G$5:G10))</f>
         <v/>
       </c>
-      <c r="L10" s="33" t="str">
-        <f aca="false">IF(A10="","",I10+J10+K10)</f>
+      <c r="M10" s="32" t="str">
+        <f aca="false">IF(A10="","",SUM($H$5:H10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="33" t="str">
+        <f aca="false">IF(A10="","",J10+K10+L10+M10)</f>
         <v/>
       </c>
     </row>
@@ -2894,24 +3840,29 @@
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
-      <c r="H11" s="24" t="str">
-        <f aca="false">IF(A11="","",SUM(E11:G11))</f>
-        <v/>
-      </c>
-      <c r="I11" s="25" t="str">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24" t="str">
+        <f aca="false">IF(A11="","",SUM(E11:H11))</f>
+        <v/>
+      </c>
+      <c r="J11" s="25" t="str">
         <f aca="false">IF(A11="","",SUM($E$5:E11))</f>
         <v/>
       </c>
-      <c r="J11" s="25" t="str">
+      <c r="K11" s="25" t="str">
         <f aca="false">IF(A11="","",SUM($F$5:F11))</f>
         <v/>
       </c>
-      <c r="K11" s="25" t="str">
+      <c r="L11" s="25" t="str">
         <f aca="false">IF(A11="","",SUM($G$5:G11))</f>
         <v/>
       </c>
-      <c r="L11" s="26" t="str">
-        <f aca="false">IF(A11="","",I11+J11+K11)</f>
+      <c r="M11" s="25" t="str">
+        <f aca="false">IF(A11="","",SUM($H$5:H11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="26" t="str">
+        <f aca="false">IF(A11="","",J11+K11+L11+M11)</f>
         <v/>
       </c>
     </row>
@@ -2923,24 +3874,29 @@
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
-      <c r="H12" s="31" t="str">
-        <f aca="false">IF(A12="","",SUM(E12:G12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="32" t="str">
+      <c r="H12" s="30"/>
+      <c r="I12" s="31" t="str">
+        <f aca="false">IF(A12="","",SUM(E12:H12))</f>
+        <v/>
+      </c>
+      <c r="J12" s="32" t="str">
         <f aca="false">IF(A12="","",SUM($E$5:E12))</f>
         <v/>
       </c>
-      <c r="J12" s="32" t="str">
+      <c r="K12" s="32" t="str">
         <f aca="false">IF(A12="","",SUM($F$5:F12))</f>
         <v/>
       </c>
-      <c r="K12" s="32" t="str">
+      <c r="L12" s="32" t="str">
         <f aca="false">IF(A12="","",SUM($G$5:G12))</f>
         <v/>
       </c>
-      <c r="L12" s="33" t="str">
-        <f aca="false">IF(A12="","",I12+J12+K12)</f>
+      <c r="M12" s="32" t="str">
+        <f aca="false">IF(A12="","",SUM($H$5:H12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="33" t="str">
+        <f aca="false">IF(A12="","",J12+K12+L12+M12)</f>
         <v/>
       </c>
     </row>
@@ -2952,24 +3908,29 @@
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="23"/>
-      <c r="H13" s="24" t="str">
-        <f aca="false">IF(A13="","",SUM(E13:G13))</f>
-        <v/>
-      </c>
-      <c r="I13" s="25" t="str">
+      <c r="H13" s="23"/>
+      <c r="I13" s="24" t="str">
+        <f aca="false">IF(A13="","",SUM(E13:H13))</f>
+        <v/>
+      </c>
+      <c r="J13" s="25" t="str">
         <f aca="false">IF(A13="","",SUM($E$5:E13))</f>
         <v/>
       </c>
-      <c r="J13" s="25" t="str">
+      <c r="K13" s="25" t="str">
         <f aca="false">IF(A13="","",SUM($F$5:F13))</f>
         <v/>
       </c>
-      <c r="K13" s="25" t="str">
+      <c r="L13" s="25" t="str">
         <f aca="false">IF(A13="","",SUM($G$5:G13))</f>
         <v/>
       </c>
-      <c r="L13" s="26" t="str">
-        <f aca="false">IF(A13="","",I13+J13+K13)</f>
+      <c r="M13" s="25" t="str">
+        <f aca="false">IF(A13="","",SUM($H$5:H13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="26" t="str">
+        <f aca="false">IF(A13="","",J13+K13+L13+M13)</f>
         <v/>
       </c>
     </row>
@@ -2981,56 +3942,61 @@
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
-      <c r="H14" s="31" t="str">
-        <f aca="false">IF(A14="","",SUM(E14:G14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="32" t="str">
+      <c r="H14" s="30"/>
+      <c r="I14" s="31" t="str">
+        <f aca="false">IF(A14="","",SUM(E14:H14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="32" t="str">
         <f aca="false">IF(A14="","",SUM($E$5:E14))</f>
         <v/>
       </c>
-      <c r="J14" s="32" t="str">
+      <c r="K14" s="32" t="str">
         <f aca="false">IF(A14="","",SUM($F$5:F14))</f>
         <v/>
       </c>
-      <c r="K14" s="32" t="str">
+      <c r="L14" s="32" t="str">
         <f aca="false">IF(A14="","",SUM($G$5:G14))</f>
         <v/>
       </c>
-      <c r="L14" s="33" t="str">
-        <f aca="false">IF(A14="","",I14+J14+K14)</f>
+      <c r="M14" s="32" t="str">
+        <f aca="false">IF(A14="","",SUM($H$5:H14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="33" t="str">
+        <f aca="false">IF(A14="","",J14+K14+L14+M14)</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B19" s="25" t="n">
-        <f aca="false">IFERROR(INDEX($I$5:$I$14,COUNTA($A$5:$A$14)),0)</f>
-        <v>1700000</v>
+        <f aca="false">IFERROR(INDEX($J$5:$J$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>1550000</v>
       </c>
       <c r="C19" s="35" t="n">
         <f aca="false">SUM(Dashboard!$D$21:$D$32)</f>
@@ -3038,23 +4004,23 @@
       </c>
       <c r="D19" s="25" t="n">
         <f aca="false">B19-C19</f>
-        <v>1602972.52307692</v>
+        <v>1452972.52307692</v>
       </c>
       <c r="E19" s="36" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0.0570749864253394</v>
+        <v>0.0625983722084367</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B20" s="32" t="n">
-        <f aca="false">IFERROR(INDEX($J$5:$J$14,COUNTA($A$5:$A$14)),0)</f>
+        <f aca="false">IFERROR(INDEX($K$5:$K$14,COUNTA($A$5:$A$14)),0)</f>
         <v>350000</v>
       </c>
       <c r="C20" s="38" t="n">
-        <f aca="false">SUM(Dashboard!$F$21:$F$32)</f>
+        <f aca="false">SUM(Dashboard!$G$21:$G$32)</f>
         <v>2240</v>
       </c>
       <c r="D20" s="32" t="n">
@@ -3068,54 +4034,75 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="B21" s="25" t="n">
-        <f aca="false">IFERROR(INDEX($K$5:$K$14,COUNTA($A$5:$A$14)),0)</f>
-        <v>350000</v>
+        <f aca="false">IFERROR(INDEX($L$5:$L$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>280000</v>
       </c>
       <c r="C21" s="35" t="n">
         <f aca="false">SUM(Dashboard!$E$21:$E$32)</f>
-        <v>25900</v>
+        <v>5370</v>
       </c>
       <c r="D21" s="25" t="n">
         <f aca="false">B21-C21</f>
-        <v>324100</v>
+        <v>274630</v>
       </c>
       <c r="E21" s="36" t="n">
         <f aca="false">IFERROR(C21/B21,0)</f>
-        <v>0.074</v>
+        <v>0.0191785714285714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="41" t="n">
-        <f aca="false">SUM(B19:B21)</f>
-        <v>2400000</v>
-      </c>
-      <c r="C22" s="41" t="n">
-        <f aca="false">SUM(C19:C21)</f>
-        <v>125167.476923077</v>
-      </c>
-      <c r="D22" s="41" t="n">
-        <f aca="false">SUM(D19:D21)</f>
-        <v>2274832.52307692</v>
-      </c>
-      <c r="E22" s="42" t="n">
+      <c r="A22" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="32" t="n">
+        <f aca="false">IFERROR(INDEX($M$5:$M$14,COUNTA($A$5:$A$14)),0)</f>
+        <v>170000</v>
+      </c>
+      <c r="C22" s="38" t="n">
+        <f aca="false">SUM(Dashboard!$F$21:$F$32)</f>
+        <v>25900</v>
+      </c>
+      <c r="D22" s="32" t="n">
+        <f aca="false">B22-C22</f>
+        <v>144100</v>
+      </c>
+      <c r="E22" s="39" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
-        <v>0.0521531153846154</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>0.152352941176471</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="41" t="n">
+        <f aca="false">SUM(B19:B22)</f>
+        <v>2350000</v>
+      </c>
+      <c r="C23" s="41" t="n">
+        <f aca="false">SUM(C19:C22)</f>
+        <v>130537.476923077</v>
+      </c>
+      <c r="D23" s="41" t="n">
+        <f aca="false">SUM(D19:D22)</f>
+        <v>2219462.52307692</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <f aca="false">IFERROR(C23/B23,0)</f>
+        <v>0.0555478625204583</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A3:N3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3134,53 +4121,53 @@
     <tabColor rgb="FF01696F"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="43" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B3" s="43"/>
       <c r="C3" s="44" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="43" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="44" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B5" s="43"/>
       <c r="C5" s="45" t="n">
@@ -3189,7 +4176,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="43" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="45" t="n">
@@ -3198,7 +4185,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="43" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B7" s="43"/>
       <c r="C7" s="46" t="n">
@@ -3208,32 +4195,32 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B8" s="43"/>
       <c r="C8" s="47" t="n">
-        <f aca="false">FundingMods!$B$22</f>
-        <v>2400000</v>
+        <f aca="false">FundingMods!$B$23</f>
+        <v>2350000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="48" t="n">
         <f aca="false">C8/C7</f>
-        <v>200000</v>
+        <v>195833.333333333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="34" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B12" s="43"/>
       <c r="C12" s="46" t="n">
@@ -3243,47 +4230,47 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B13" s="43"/>
       <c r="C13" s="48" t="n">
-        <f aca="false">IF(C12=0,0,INDEX(L21:L32,C12))</f>
-        <v>150000.704344615</v>
+        <f aca="false">IF(C12=0,0,INDEX(M21:M32,C12))</f>
+        <v>156436.112344615</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B14" s="43"/>
       <c r="C14" s="48" t="n">
         <f aca="false">C8-C13</f>
-        <v>2249999.29565538</v>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="43" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B15" s="43"/>
       <c r="C15" s="49" t="n">
         <f aca="false">IFERROR(C13/C8,0)</f>
-        <v>0.0625002934769231</v>
+        <v>0.0665685584445172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="43" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B16" s="43"/>
       <c r="C16" s="48" t="n">
-        <f aca="true">IFERROR(AVERAGE(OFFSET(K21,MAX(C12-3,0),0,MIN(C12,3),1)),0)</f>
+        <f aca="true">IFERROR(AVERAGE(OFFSET(L21,MAX(C12-3,0),0,MIN(C12,3),1)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="43" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="str">
@@ -3293,7 +4280,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="43" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B18" s="43"/>
       <c r="C18" s="50" t="str">
@@ -3307,49 +4294,52 @@
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>144</v>
+        <v>157</v>
+      </c>
+      <c r="P20" s="17" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3362,7 +4352,7 @@
       </c>
       <c r="C21" s="25" t="n">
         <f aca="false">$C$9*A21</f>
-        <v>200000</v>
+        <v>195833.333333333</v>
       </c>
       <c r="D21" s="35" t="n">
         <f aca="false">Labor!H25</f>
@@ -3370,47 +4360,51 @@
       </c>
       <c r="E21" s="35" t="n">
         <f aca="false">IF(D21="","",ODCs!C27)</f>
+        <v>4200</v>
+      </c>
+      <c r="F21" s="35" t="n">
+        <f aca="false">IF(D21="","",'M&amp;E'!C27)</f>
         <v>14200</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="G21" s="35" t="n">
         <f aca="false">IF(D21="","",Travel!C27)</f>
         <v>1090</v>
       </c>
-      <c r="G21" s="25" t="n">
-        <f aca="false">IF(D21="","",D21+E21+F21)</f>
-        <v>48336.3216947115</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <f aca="false">IF(G21="","",G21*Rates!$B$8)</f>
-        <v>5800.35860336539</v>
-      </c>
-      <c r="I21" s="25" t="n">
-        <f aca="false">IF(G21="","",G21+H21)</f>
-        <v>54136.6802980769</v>
-      </c>
-      <c r="J21" s="35" t="n">
-        <f aca="false">IF(I21="","",I21*Rates!$C$17)</f>
-        <v>3789.56762086539</v>
-      </c>
-      <c r="K21" s="25" t="n">
-        <f aca="false">IF(I21="","",I21+J21)</f>
-        <v>57926.2479189423</v>
+      <c r="H21" s="25" t="n">
+        <f aca="false">IF(D21="","",D21+E21+F21+G21)</f>
+        <v>52536.3216947115</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <f aca="false">IF(H21="","",H21*Rates!$B$8)</f>
+        <v>6304.35860336539</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <f aca="false">IF(H21="","",H21+I21)</f>
+        <v>58840.6802980769</v>
+      </c>
+      <c r="K21" s="35" t="n">
+        <f aca="false">IF(J21="","",J21*Rates!$C$17)</f>
+        <v>4118.84762086539</v>
       </c>
       <c r="L21" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K21)=0,"",SUM($K$21:K21))</f>
-        <v>57926.2479189423</v>
-      </c>
-      <c r="M21" s="53" t="n">
-        <f aca="false">IF(OR(L21="",C21=""),"",L21-C21)</f>
-        <v>-142073.752081058</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <f aca="false">IF(OR(L21="",C21="",C21=0),"",M21/C21)</f>
-        <v>-0.710368760405289</v>
-      </c>
-      <c r="O21" s="25" t="n">
-        <f aca="false">IF(L21="","",$C$8-L21)</f>
-        <v>2342073.75208106</v>
+        <f aca="false">IF(J21="","",J21+K21)</f>
+        <v>62959.5279189423</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L21)=0,"",SUM($L$21:L21))</f>
+        <v>62959.5279189423</v>
+      </c>
+      <c r="N21" s="53" t="n">
+        <f aca="false">IF(OR(M21="",C21=""),"",M21-C21)</f>
+        <v>-132873.805414391</v>
+      </c>
+      <c r="O21" s="36" t="n">
+        <f aca="false">IF(OR(M21="",C21="",C21=0),"",N21/C21)</f>
+        <v>-0.678504538286252</v>
+      </c>
+      <c r="P21" s="25" t="n">
+        <f aca="false">IF(M21="","",$C$8-M21)</f>
+        <v>2287040.47208106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3423,7 +4417,7 @@
       </c>
       <c r="C22" s="32" t="n">
         <f aca="false">$C$9*A22</f>
-        <v>400000</v>
+        <v>391666.666666667</v>
       </c>
       <c r="D22" s="38" t="n">
         <f aca="false">Labor!H26</f>
@@ -3431,47 +4425,51 @@
       </c>
       <c r="E22" s="38" t="n">
         <f aca="false">IF(D22="","",ODCs!C28)</f>
+        <v>310</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <f aca="false">IF(D22="","",'M&amp;E'!C28)</f>
         <v>3100</v>
       </c>
-      <c r="F22" s="38" t="n">
+      <c r="G22" s="38" t="n">
         <f aca="false">IF(D22="","",Travel!C28)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="32" t="n">
-        <f aca="false">IF(D22="","",D22+E22+F22)</f>
-        <v>31871.3216947115</v>
-      </c>
-      <c r="H22" s="38" t="n">
-        <f aca="false">IF(G22="","",G22*Rates!$B$8)</f>
-        <v>3824.55860336539</v>
-      </c>
-      <c r="I22" s="32" t="n">
-        <f aca="false">IF(G22="","",G22+H22)</f>
-        <v>35695.8802980769</v>
-      </c>
-      <c r="J22" s="38" t="n">
-        <f aca="false">IF(I22="","",I22*Rates!$C$17)</f>
-        <v>2498.71162086539</v>
-      </c>
-      <c r="K22" s="32" t="n">
-        <f aca="false">IF(I22="","",I22+J22)</f>
-        <v>38194.5919189423</v>
+      <c r="H22" s="32" t="n">
+        <f aca="false">IF(D22="","",D22+E22+F22+G22)</f>
+        <v>32181.3216947115</v>
+      </c>
+      <c r="I22" s="38" t="n">
+        <f aca="false">IF(H22="","",H22*Rates!$B$8)</f>
+        <v>3861.75860336539</v>
+      </c>
+      <c r="J22" s="32" t="n">
+        <f aca="false">IF(H22="","",H22+I22)</f>
+        <v>36043.0802980769</v>
+      </c>
+      <c r="K22" s="38" t="n">
+        <f aca="false">IF(J22="","",J22*Rates!$C$17)</f>
+        <v>2523.01562086539</v>
       </c>
       <c r="L22" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K22)=0,"",SUM($K$21:K22))</f>
-        <v>96120.8398378846</v>
-      </c>
-      <c r="M22" s="56" t="n">
-        <f aca="false">IF(OR(L22="",C22=""),"",L22-C22)</f>
-        <v>-303879.160162115</v>
-      </c>
-      <c r="N22" s="39" t="n">
-        <f aca="false">IF(OR(L22="",C22="",C22=0),"",M22/C22)</f>
-        <v>-0.759697900405288</v>
-      </c>
-      <c r="O22" s="32" t="n">
-        <f aca="false">IF(L22="","",$C$8-L22)</f>
-        <v>2303879.16016212</v>
+        <f aca="false">IF(J22="","",J22+K22)</f>
+        <v>38566.0959189423</v>
+      </c>
+      <c r="M22" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L22)=0,"",SUM($L$21:L22))</f>
+        <v>101525.623837885</v>
+      </c>
+      <c r="N22" s="56" t="n">
+        <f aca="false">IF(OR(M22="",C22=""),"",M22-C22)</f>
+        <v>-290141.042828782</v>
+      </c>
+      <c r="O22" s="39" t="n">
+        <f aca="false">IF(OR(M22="",C22="",C22=0),"",N22/C22)</f>
+        <v>-0.740785641264975</v>
+      </c>
+      <c r="P22" s="32" t="n">
+        <f aca="false">IF(M22="","",$C$8-M22)</f>
+        <v>2248474.37616212</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3484,7 +4482,7 @@
       </c>
       <c r="C23" s="25" t="n">
         <f aca="false">$C$9*A23</f>
-        <v>600000</v>
+        <v>587500</v>
       </c>
       <c r="D23" s="35" t="n">
         <f aca="false">Labor!H27</f>
@@ -3495,44 +4493,48 @@
         <v>0</v>
       </c>
       <c r="F23" s="35" t="n">
+        <f aca="false">IF(D23="","",'M&amp;E'!C29)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="35" t="n">
         <f aca="false">IF(D23="","",Travel!C29)</f>
         <v>1150</v>
       </c>
-      <c r="G23" s="25" t="n">
-        <f aca="false">IF(D23="","",D23+E23+F23)</f>
+      <c r="H23" s="25" t="n">
+        <f aca="false">IF(D23="","",D23+E23+F23+G23)</f>
         <v>1150</v>
       </c>
-      <c r="H23" s="35" t="n">
-        <f aca="false">IF(G23="","",G23*Rates!$B$8)</f>
+      <c r="I23" s="35" t="n">
+        <f aca="false">IF(H23="","",H23*Rates!$B$8)</f>
         <v>138</v>
       </c>
-      <c r="I23" s="25" t="n">
-        <f aca="false">IF(G23="","",G23+H23)</f>
+      <c r="J23" s="25" t="n">
+        <f aca="false">IF(H23="","",H23+I23)</f>
         <v>1288</v>
       </c>
-      <c r="J23" s="35" t="n">
-        <f aca="false">IF(I23="","",I23*Rates!$C$17)</f>
+      <c r="K23" s="35" t="n">
+        <f aca="false">IF(J23="","",J23*Rates!$C$17)</f>
         <v>90.16</v>
       </c>
-      <c r="K23" s="25" t="n">
-        <f aca="false">IF(I23="","",I23+J23)</f>
+      <c r="L23" s="25" t="n">
+        <f aca="false">IF(J23="","",J23+K23)</f>
         <v>1378.16</v>
       </c>
-      <c r="L23" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K23)=0,"",SUM($K$21:K23))</f>
-        <v>97498.9998378846</v>
-      </c>
-      <c r="M23" s="53" t="n">
-        <f aca="false">IF(OR(L23="",C23=""),"",L23-C23)</f>
-        <v>-502501.000162115</v>
-      </c>
-      <c r="N23" s="36" t="n">
-        <f aca="false">IF(OR(L23="",C23="",C23=0),"",M23/C23)</f>
-        <v>-0.837501666936859</v>
-      </c>
-      <c r="O23" s="25" t="n">
-        <f aca="false">IF(L23="","",$C$8-L23)</f>
-        <v>2302501.00016212</v>
+      <c r="M23" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L23)=0,"",SUM($L$21:L23))</f>
+        <v>102903.783837885</v>
+      </c>
+      <c r="N23" s="53" t="n">
+        <f aca="false">IF(OR(M23="",C23=""),"",M23-C23)</f>
+        <v>-484596.216162115</v>
+      </c>
+      <c r="O23" s="36" t="n">
+        <f aca="false">IF(OR(M23="",C23="",C23=0),"",N23/C23)</f>
+        <v>-0.824844623254665</v>
+      </c>
+      <c r="P23" s="25" t="n">
+        <f aca="false">IF(M23="","",$C$8-M23)</f>
+        <v>2247096.21616212</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3545,7 +4547,7 @@
       </c>
       <c r="C24" s="32" t="n">
         <f aca="false">$C$9*A24</f>
-        <v>800000</v>
+        <v>783333.333333333</v>
       </c>
       <c r="D24" s="38" t="n">
         <f aca="false">Labor!H28</f>
@@ -3553,47 +4555,51 @@
       </c>
       <c r="E24" s="38" t="n">
         <f aca="false">IF(D24="","",ODCs!C30)</f>
+        <v>860</v>
+      </c>
+      <c r="F24" s="38" t="n">
+        <f aca="false">IF(D24="","",'M&amp;E'!C30)</f>
         <v>8600</v>
       </c>
-      <c r="F24" s="38" t="n">
+      <c r="G24" s="38" t="n">
         <f aca="false">IF(D24="","",Travel!C30)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="32" t="n">
-        <f aca="false">IF(D24="","",D24+E24+F24)</f>
-        <v>8600</v>
-      </c>
-      <c r="H24" s="38" t="n">
-        <f aca="false">IF(G24="","",G24*Rates!$B$8)</f>
-        <v>1032</v>
-      </c>
-      <c r="I24" s="32" t="n">
-        <f aca="false">IF(G24="","",G24+H24)</f>
-        <v>9632</v>
-      </c>
-      <c r="J24" s="38" t="n">
-        <f aca="false">IF(I24="","",I24*Rates!$C$17)</f>
-        <v>674.24</v>
-      </c>
-      <c r="K24" s="32" t="n">
-        <f aca="false">IF(I24="","",I24+J24)</f>
-        <v>10306.24</v>
+      <c r="H24" s="32" t="n">
+        <f aca="false">IF(D24="","",D24+E24+F24+G24)</f>
+        <v>9460</v>
+      </c>
+      <c r="I24" s="38" t="n">
+        <f aca="false">IF(H24="","",H24*Rates!$B$8)</f>
+        <v>1135.2</v>
+      </c>
+      <c r="J24" s="32" t="n">
+        <f aca="false">IF(H24="","",H24+I24)</f>
+        <v>10595.2</v>
+      </c>
+      <c r="K24" s="38" t="n">
+        <f aca="false">IF(J24="","",J24*Rates!$C$17)</f>
+        <v>741.664</v>
       </c>
       <c r="L24" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K24)=0,"",SUM($K$21:K24))</f>
-        <v>107805.239837885</v>
-      </c>
-      <c r="M24" s="56" t="n">
-        <f aca="false">IF(OR(L24="",C24=""),"",L24-C24)</f>
-        <v>-692194.760162115</v>
-      </c>
-      <c r="N24" s="39" t="n">
-        <f aca="false">IF(OR(L24="",C24="",C24=0),"",M24/C24)</f>
-        <v>-0.865243450202644</v>
-      </c>
-      <c r="O24" s="32" t="n">
-        <f aca="false">IF(L24="","",$C$8-L24)</f>
-        <v>2292194.76016212</v>
+        <f aca="false">IF(J24="","",J24+K24)</f>
+        <v>11336.864</v>
+      </c>
+      <c r="M24" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L24)=0,"",SUM($L$21:L24))</f>
+        <v>114240.647837885</v>
+      </c>
+      <c r="N24" s="56" t="n">
+        <f aca="false">IF(OR(M24="",C24=""),"",M24-C24)</f>
+        <v>-669092.685495449</v>
+      </c>
+      <c r="O24" s="39" t="n">
+        <f aca="false">IF(OR(M24="",C24="",C24=0),"",N24/C24)</f>
+        <v>-0.854160875100573</v>
+      </c>
+      <c r="P24" s="32" t="n">
+        <f aca="false">IF(M24="","",$C$8-M24)</f>
+        <v>2235759.35216212</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3606,7 +4612,7 @@
       </c>
       <c r="C25" s="25" t="n">
         <f aca="false">$C$9*A25</f>
-        <v>1000000</v>
+        <v>979166.666666667</v>
       </c>
       <c r="D25" s="35" t="n">
         <f aca="false">Labor!H29</f>
@@ -3617,44 +4623,48 @@
         <v>0</v>
       </c>
       <c r="F25" s="35" t="n">
+        <f aca="false">IF(D25="","",'M&amp;E'!C31)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="35" t="n">
         <f aca="false">IF(D25="","",Travel!C31)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="25" t="n">
-        <f aca="false">IF(D25="","",D25+E25+F25)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <f aca="false">IF(G25="","",G25*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="25" t="n">
-        <f aca="false">IF(G25="","",G25+H25)</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="35" t="n">
-        <f aca="false">IF(I25="","",I25*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="25" t="n">
-        <f aca="false">IF(I25="","",I25+J25)</f>
+      <c r="H25" s="25" t="n">
+        <f aca="false">IF(D25="","",D25+E25+F25+G25)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="35" t="n">
+        <f aca="false">IF(H25="","",H25*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="25" t="n">
+        <f aca="false">IF(H25="","",H25+I25)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="35" t="n">
+        <f aca="false">IF(J25="","",J25*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L25" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K25)=0,"",SUM($K$21:K25))</f>
-        <v>107805.239837885</v>
-      </c>
-      <c r="M25" s="53" t="n">
-        <f aca="false">IF(OR(L25="",C25=""),"",L25-C25)</f>
-        <v>-892194.760162115</v>
-      </c>
-      <c r="N25" s="36" t="n">
-        <f aca="false">IF(OR(L25="",C25="",C25=0),"",M25/C25)</f>
-        <v>-0.892194760162115</v>
-      </c>
-      <c r="O25" s="25" t="n">
-        <f aca="false">IF(L25="","",$C$8-L25)</f>
-        <v>2292194.76016212</v>
+        <f aca="false">IF(J25="","",J25+K25)</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L25)=0,"",SUM($L$21:L25))</f>
+        <v>114240.647837885</v>
+      </c>
+      <c r="N25" s="53" t="n">
+        <f aca="false">IF(OR(M25="",C25=""),"",M25-C25)</f>
+        <v>-864926.018828782</v>
+      </c>
+      <c r="O25" s="36" t="n">
+        <f aca="false">IF(OR(M25="",C25="",C25=0),"",N25/C25)</f>
+        <v>-0.883328700080458</v>
+      </c>
+      <c r="P25" s="25" t="n">
+        <f aca="false">IF(M25="","",$C$8-M25)</f>
+        <v>2235759.35216212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3667,7 +4677,7 @@
       </c>
       <c r="C26" s="32" t="n">
         <f aca="false">$C$9*A26</f>
-        <v>1200000</v>
+        <v>1175000</v>
       </c>
       <c r="D26" s="38" t="n">
         <f aca="false">Labor!H30</f>
@@ -3678,44 +4688,48 @@
         <v>0</v>
       </c>
       <c r="F26" s="38" t="n">
+        <f aca="false">IF(D26="","",'M&amp;E'!C32)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="38" t="n">
         <f aca="false">IF(D26="","",Travel!C32)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="32" t="n">
-        <f aca="false">IF(D26="","",D26+E26+F26)</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <f aca="false">IF(G26="","",G26*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="32" t="n">
-        <f aca="false">IF(G26="","",G26+H26)</f>
-        <v>0</v>
-      </c>
-      <c r="J26" s="38" t="n">
-        <f aca="false">IF(I26="","",I26*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="32" t="n">
-        <f aca="false">IF(I26="","",I26+J26)</f>
+      <c r="H26" s="32" t="n">
+        <f aca="false">IF(D26="","",D26+E26+F26+G26)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="38" t="n">
+        <f aca="false">IF(H26="","",H26*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="32" t="n">
+        <f aca="false">IF(H26="","",H26+I26)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="38" t="n">
+        <f aca="false">IF(J26="","",J26*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L26" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K26)=0,"",SUM($K$21:K26))</f>
-        <v>107805.239837885</v>
-      </c>
-      <c r="M26" s="56" t="n">
-        <f aca="false">IF(OR(L26="",C26=""),"",L26-C26)</f>
-        <v>-1092194.76016212</v>
-      </c>
-      <c r="N26" s="39" t="n">
-        <f aca="false">IF(OR(L26="",C26="",C26=0),"",M26/C26)</f>
-        <v>-0.910162300135096</v>
-      </c>
-      <c r="O26" s="32" t="n">
-        <f aca="false">IF(L26="","",$C$8-L26)</f>
-        <v>2292194.76016212</v>
+        <f aca="false">IF(J26="","",J26+K26)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L26)=0,"",SUM($L$21:L26))</f>
+        <v>114240.647837885</v>
+      </c>
+      <c r="N26" s="56" t="n">
+        <f aca="false">IF(OR(M26="",C26=""),"",M26-C26)</f>
+        <v>-1060759.35216212</v>
+      </c>
+      <c r="O26" s="39" t="n">
+        <f aca="false">IF(OR(M26="",C26="",C26=0),"",N26/C26)</f>
+        <v>-0.902773916733715</v>
+      </c>
+      <c r="P26" s="32" t="n">
+        <f aca="false">IF(M26="","",$C$8-M26)</f>
+        <v>2235759.35216212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3728,7 +4742,7 @@
       </c>
       <c r="C27" s="25" t="n">
         <f aca="false">$C$9*A27</f>
-        <v>1400000</v>
+        <v>1370833.33333333</v>
       </c>
       <c r="D27" s="35" t="n">
         <f aca="false">Labor!H31</f>
@@ -3739,44 +4753,48 @@
         <v>0</v>
       </c>
       <c r="F27" s="35" t="n">
+        <f aca="false">IF(D27="","",'M&amp;E'!C33)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="35" t="n">
         <f aca="false">IF(D27="","",Travel!C33)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="25" t="n">
-        <f aca="false">IF(D27="","",D27+E27+F27)</f>
+      <c r="H27" s="25" t="n">
+        <f aca="false">IF(D27="","",D27+E27+F27+G27)</f>
         <v>9054.08653846154</v>
       </c>
-      <c r="H27" s="35" t="n">
-        <f aca="false">IF(G27="","",G27*Rates!$B$8)</f>
+      <c r="I27" s="35" t="n">
+        <f aca="false">IF(H27="","",H27*Rates!$B$8)</f>
         <v>1086.49038461538</v>
       </c>
-      <c r="I27" s="25" t="n">
-        <f aca="false">IF(G27="","",G27+H27)</f>
+      <c r="J27" s="25" t="n">
+        <f aca="false">IF(H27="","",H27+I27)</f>
         <v>10140.5769230769</v>
       </c>
-      <c r="J27" s="35" t="n">
-        <f aca="false">IF(I27="","",I27*Rates!$C$17)</f>
+      <c r="K27" s="35" t="n">
+        <f aca="false">IF(J27="","",J27*Rates!$C$17)</f>
         <v>709.840384615385</v>
       </c>
-      <c r="K27" s="25" t="n">
-        <f aca="false">IF(I27="","",I27+J27)</f>
+      <c r="L27" s="25" t="n">
+        <f aca="false">IF(J27="","",J27+K27)</f>
         <v>10850.4173076923</v>
       </c>
-      <c r="L27" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K27)=0,"",SUM($K$21:K27))</f>
-        <v>118655.657145577</v>
-      </c>
-      <c r="M27" s="53" t="n">
-        <f aca="false">IF(OR(L27="",C27=""),"",L27-C27)</f>
-        <v>-1281344.34285442</v>
-      </c>
-      <c r="N27" s="36" t="n">
-        <f aca="false">IF(OR(L27="",C27="",C27=0),"",M27/C27)</f>
-        <v>-0.915245959181731</v>
-      </c>
-      <c r="O27" s="25" t="n">
-        <f aca="false">IF(L27="","",$C$8-L27)</f>
-        <v>2281344.34285442</v>
+      <c r="M27" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L27)=0,"",SUM($L$21:L27))</f>
+        <v>125091.065145577</v>
+      </c>
+      <c r="N27" s="53" t="n">
+        <f aca="false">IF(OR(M27="",C27=""),"",M27-C27)</f>
+        <v>-1245742.26818776</v>
+      </c>
+      <c r="O27" s="36" t="n">
+        <f aca="false">IF(OR(M27="",C27="",C27=0),"",N27/C27)</f>
+        <v>-0.908748159164321</v>
+      </c>
+      <c r="P27" s="25" t="n">
+        <f aca="false">IF(M27="","",$C$8-M27)</f>
+        <v>2224908.93485442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3789,7 +4807,7 @@
       </c>
       <c r="C28" s="32" t="n">
         <f aca="false">$C$9*A28</f>
-        <v>1600000</v>
+        <v>1566666.66666667</v>
       </c>
       <c r="D28" s="38" t="n">
         <f aca="false">Labor!H32</f>
@@ -3800,44 +4818,48 @@
         <v>0</v>
       </c>
       <c r="F28" s="38" t="n">
+        <f aca="false">IF(D28="","",'M&amp;E'!C34)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="38" t="n">
         <f aca="false">IF(D28="","",Travel!C34)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="32" t="n">
-        <f aca="false">IF(D28="","",D28+E28+F28)</f>
+      <c r="H28" s="32" t="n">
+        <f aca="false">IF(D28="","",D28+E28+F28+G28)</f>
         <v>26155.7469951923</v>
       </c>
-      <c r="H28" s="38" t="n">
-        <f aca="false">IF(G28="","",G28*Rates!$B$8)</f>
+      <c r="I28" s="38" t="n">
+        <f aca="false">IF(H28="","",H28*Rates!$B$8)</f>
         <v>3138.68963942308</v>
       </c>
-      <c r="I28" s="32" t="n">
-        <f aca="false">IF(G28="","",G28+H28)</f>
+      <c r="J28" s="32" t="n">
+        <f aca="false">IF(H28="","",H28+I28)</f>
         <v>29294.4366346154</v>
       </c>
-      <c r="J28" s="38" t="n">
-        <f aca="false">IF(I28="","",I28*Rates!$C$17)</f>
+      <c r="K28" s="38" t="n">
+        <f aca="false">IF(J28="","",J28*Rates!$C$17)</f>
         <v>2050.61056442308</v>
       </c>
-      <c r="K28" s="32" t="n">
-        <f aca="false">IF(I28="","",I28+J28)</f>
+      <c r="L28" s="32" t="n">
+        <f aca="false">IF(J28="","",J28+K28)</f>
         <v>31345.0471990385</v>
       </c>
-      <c r="L28" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K28)=0,"",SUM($K$21:K28))</f>
-        <v>150000.704344615</v>
-      </c>
-      <c r="M28" s="56" t="n">
-        <f aca="false">IF(OR(L28="",C28=""),"",L28-C28)</f>
-        <v>-1449999.29565538</v>
-      </c>
-      <c r="N28" s="39" t="n">
-        <f aca="false">IF(OR(L28="",C28="",C28=0),"",M28/C28)</f>
-        <v>-0.906249559784615</v>
-      </c>
-      <c r="O28" s="32" t="n">
-        <f aca="false">IF(L28="","",$C$8-L28)</f>
-        <v>2249999.29565538</v>
+      <c r="M28" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L28)=0,"",SUM($L$21:L28))</f>
+        <v>156436.112344615</v>
+      </c>
+      <c r="N28" s="56" t="n">
+        <f aca="false">IF(OR(M28="",C28=""),"",M28-C28)</f>
+        <v>-1410230.55432205</v>
+      </c>
+      <c r="O28" s="39" t="n">
+        <f aca="false">IF(OR(M28="",C28="",C28=0),"",N28/C28)</f>
+        <v>-0.900147162333224</v>
+      </c>
+      <c r="P28" s="32" t="n">
+        <f aca="false">IF(M28="","",$C$8-M28)</f>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3850,7 +4872,7 @@
       </c>
       <c r="C29" s="25" t="n">
         <f aca="false">$C$9*A29</f>
-        <v>1800000</v>
+        <v>1762500</v>
       </c>
       <c r="D29" s="35" t="n">
         <f aca="false">Labor!H33</f>
@@ -3861,44 +4883,48 @@
         <v>0</v>
       </c>
       <c r="F29" s="35" t="n">
+        <f aca="false">IF(D29="","",'M&amp;E'!C35)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="35" t="n">
         <f aca="false">IF(D29="","",Travel!C35)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="25" t="n">
-        <f aca="false">IF(D29="","",D29+E29+F29)</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <f aca="false">IF(G29="","",G29*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="25" t="n">
-        <f aca="false">IF(G29="","",G29+H29)</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="35" t="n">
-        <f aca="false">IF(I29="","",I29*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="25" t="n">
-        <f aca="false">IF(I29="","",I29+J29)</f>
+      <c r="H29" s="25" t="n">
+        <f aca="false">IF(D29="","",D29+E29+F29+G29)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="35" t="n">
+        <f aca="false">IF(H29="","",H29*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <f aca="false">IF(H29="","",H29+I29)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="35" t="n">
+        <f aca="false">IF(J29="","",J29*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L29" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K29)=0,"",SUM($K$21:K29))</f>
-        <v>150000.704344615</v>
-      </c>
-      <c r="M29" s="53" t="n">
-        <f aca="false">IF(OR(L29="",C29=""),"",L29-C29)</f>
-        <v>-1649999.29565538</v>
-      </c>
-      <c r="N29" s="36" t="n">
-        <f aca="false">IF(OR(L29="",C29="",C29=0),"",M29/C29)</f>
-        <v>-0.916666275364103</v>
-      </c>
-      <c r="O29" s="25" t="n">
-        <f aca="false">IF(L29="","",$C$8-L29)</f>
-        <v>2249999.29565538</v>
+        <f aca="false">IF(J29="","",J29+K29)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L29)=0,"",SUM($L$21:L29))</f>
+        <v>156436.112344615</v>
+      </c>
+      <c r="N29" s="53" t="n">
+        <f aca="false">IF(OR(M29="",C29=""),"",M29-C29)</f>
+        <v>-1606063.88765538</v>
+      </c>
+      <c r="O29" s="36" t="n">
+        <f aca="false">IF(OR(M29="",C29="",C29=0),"",N29/C29)</f>
+        <v>-0.911241922073977</v>
+      </c>
+      <c r="P29" s="25" t="n">
+        <f aca="false">IF(M29="","",$C$8-M29)</f>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3911,7 +4937,7 @@
       </c>
       <c r="C30" s="32" t="n">
         <f aca="false">$C$9*A30</f>
-        <v>2000000</v>
+        <v>1958333.33333333</v>
       </c>
       <c r="D30" s="38" t="n">
         <f aca="false">Labor!H34</f>
@@ -3922,44 +4948,48 @@
         <v>0</v>
       </c>
       <c r="F30" s="38" t="n">
+        <f aca="false">IF(D30="","",'M&amp;E'!C36)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="38" t="n">
         <f aca="false">IF(D30="","",Travel!C36)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="32" t="n">
-        <f aca="false">IF(D30="","",D30+E30+F30)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="38" t="n">
-        <f aca="false">IF(G30="","",G30*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="32" t="n">
-        <f aca="false">IF(G30="","",G30+H30)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="38" t="n">
-        <f aca="false">IF(I30="","",I30*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="32" t="n">
-        <f aca="false">IF(I30="","",I30+J30)</f>
+      <c r="H30" s="32" t="n">
+        <f aca="false">IF(D30="","",D30+E30+F30+G30)</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="38" t="n">
+        <f aca="false">IF(H30="","",H30*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="32" t="n">
+        <f aca="false">IF(H30="","",H30+I30)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="38" t="n">
+        <f aca="false">IF(J30="","",J30*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L30" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K30)=0,"",SUM($K$21:K30))</f>
-        <v>150000.704344615</v>
-      </c>
-      <c r="M30" s="56" t="n">
-        <f aca="false">IF(OR(L30="",C30=""),"",L30-C30)</f>
-        <v>-1849999.29565538</v>
-      </c>
-      <c r="N30" s="39" t="n">
-        <f aca="false">IF(OR(L30="",C30="",C30=0),"",M30/C30)</f>
-        <v>-0.924999647827692</v>
-      </c>
-      <c r="O30" s="32" t="n">
-        <f aca="false">IF(L30="","",$C$8-L30)</f>
-        <v>2249999.29565538</v>
+        <f aca="false">IF(J30="","",J30+K30)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L30)=0,"",SUM($L$21:L30))</f>
+        <v>156436.112344615</v>
+      </c>
+      <c r="N30" s="56" t="n">
+        <f aca="false">IF(OR(M30="",C30=""),"",M30-C30)</f>
+        <v>-1801897.22098872</v>
+      </c>
+      <c r="O30" s="39" t="n">
+        <f aca="false">IF(OR(M30="",C30="",C30=0),"",N30/C30)</f>
+        <v>-0.920117729866579</v>
+      </c>
+      <c r="P30" s="32" t="n">
+        <f aca="false">IF(M30="","",$C$8-M30)</f>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3972,7 +5002,7 @@
       </c>
       <c r="C31" s="25" t="n">
         <f aca="false">$C$9*A31</f>
-        <v>2200000</v>
+        <v>2154166.66666667</v>
       </c>
       <c r="D31" s="35" t="n">
         <f aca="false">Labor!H35</f>
@@ -3983,44 +5013,48 @@
         <v>0</v>
       </c>
       <c r="F31" s="35" t="n">
+        <f aca="false">IF(D31="","",'M&amp;E'!C37)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="35" t="n">
         <f aca="false">IF(D31="","",Travel!C37)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="25" t="n">
-        <f aca="false">IF(D31="","",D31+E31+F31)</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <f aca="false">IF(G31="","",G31*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="25" t="n">
-        <f aca="false">IF(G31="","",G31+H31)</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="35" t="n">
-        <f aca="false">IF(I31="","",I31*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K31" s="25" t="n">
-        <f aca="false">IF(I31="","",I31+J31)</f>
+      <c r="H31" s="25" t="n">
+        <f aca="false">IF(D31="","",D31+E31+F31+G31)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="35" t="n">
+        <f aca="false">IF(H31="","",H31*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <f aca="false">IF(H31="","",H31+I31)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="35" t="n">
+        <f aca="false">IF(J31="","",J31*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L31" s="25" t="n">
-        <f aca="false">IF(SUM($K$21:K31)=0,"",SUM($K$21:K31))</f>
-        <v>150000.704344615</v>
-      </c>
-      <c r="M31" s="53" t="n">
-        <f aca="false">IF(OR(L31="",C31=""),"",L31-C31)</f>
-        <v>-2049999.29565538</v>
-      </c>
-      <c r="N31" s="36" t="n">
-        <f aca="false">IF(OR(L31="",C31="",C31=0),"",M31/C31)</f>
-        <v>-0.931817861661539</v>
-      </c>
-      <c r="O31" s="25" t="n">
-        <f aca="false">IF(L31="","",$C$8-L31)</f>
-        <v>2249999.29565538</v>
+        <f aca="false">IF(J31="","",J31+K31)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="25" t="n">
+        <f aca="false">IF(SUM($L$21:L31)=0,"",SUM($L$21:L31))</f>
+        <v>156436.112344615</v>
+      </c>
+      <c r="N31" s="53" t="n">
+        <f aca="false">IF(OR(M31="",C31=""),"",M31-C31)</f>
+        <v>-1997730.55432205</v>
+      </c>
+      <c r="O31" s="36" t="n">
+        <f aca="false">IF(OR(M31="",C31="",C31=0),"",N31/C31)</f>
+        <v>-0.927379754424163</v>
+      </c>
+      <c r="P31" s="25" t="n">
+        <f aca="false">IF(M31="","",$C$8-M31)</f>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4033,7 +5067,7 @@
       </c>
       <c r="C32" s="32" t="n">
         <f aca="false">$C$9*A32</f>
-        <v>2400000</v>
+        <v>2350000</v>
       </c>
       <c r="D32" s="38" t="n">
         <f aca="false">Labor!H36</f>
@@ -4044,49 +5078,53 @@
         <v>0</v>
       </c>
       <c r="F32" s="38" t="n">
+        <f aca="false">IF(D32="","",'M&amp;E'!C38)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="38" t="n">
         <f aca="false">IF(D32="","",Travel!C38)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="32" t="n">
-        <f aca="false">IF(D32="","",D32+E32+F32)</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="38" t="n">
-        <f aca="false">IF(G32="","",G32*Rates!$B$8)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="32" t="n">
-        <f aca="false">IF(G32="","",G32+H32)</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="38" t="n">
-        <f aca="false">IF(I32="","",I32*Rates!$C$17)</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="32" t="n">
-        <f aca="false">IF(I32="","",I32+J32)</f>
+      <c r="H32" s="32" t="n">
+        <f aca="false">IF(D32="","",D32+E32+F32+G32)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="38" t="n">
+        <f aca="false">IF(H32="","",H32*Rates!$B$8)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="32" t="n">
+        <f aca="false">IF(H32="","",H32+I32)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="38" t="n">
+        <f aca="false">IF(J32="","",J32*Rates!$C$17)</f>
         <v>0</v>
       </c>
       <c r="L32" s="32" t="n">
-        <f aca="false">IF(SUM($K$21:K32)=0,"",SUM($K$21:K32))</f>
-        <v>150000.704344615</v>
-      </c>
-      <c r="M32" s="56" t="n">
-        <f aca="false">IF(OR(L32="",C32=""),"",L32-C32)</f>
-        <v>-2249999.29565538</v>
-      </c>
-      <c r="N32" s="39" t="n">
-        <f aca="false">IF(OR(L32="",C32="",C32=0),"",M32/C32)</f>
-        <v>-0.937499706523077</v>
-      </c>
-      <c r="O32" s="32" t="n">
-        <f aca="false">IF(L32="","",$C$8-L32)</f>
-        <v>2249999.29565538</v>
+        <f aca="false">IF(J32="","",J32+K32)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="32" t="n">
+        <f aca="false">IF(SUM($L$21:L32)=0,"",SUM($L$21:L32))</f>
+        <v>156436.112344615</v>
+      </c>
+      <c r="N32" s="56" t="n">
+        <f aca="false">IF(OR(M32="",C32=""),"",M32-C32)</f>
+        <v>-2193563.88765539</v>
+      </c>
+      <c r="O32" s="39" t="n">
+        <f aca="false">IF(OR(M32="",C32="",C32=0),"",N32/C32)</f>
+        <v>-0.933431441555483</v>
+      </c>
+      <c r="P32" s="32" t="n">
+        <f aca="false">IF(M32="","",$C$8-M32)</f>
+        <v>2193563.88765539</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4151,65 +5189,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4217,13 +5255,13 @@
         <v>123456</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E5" s="23" t="n">
         <v>150000</v>
@@ -4265,13 +5303,13 @@
         <v>123457</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>165000</v>
@@ -4313,13 +5351,13 @@
         <v>123458</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E7" s="23"/>
       <c r="F7" s="57" t="n">
@@ -4742,7 +5780,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -4819,119 +5857,119 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="BF1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="H4" s="66"/>
       <c r="I4" s="66"/>
       <c r="J4" s="66"/>
       <c r="K4" s="66" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="L4" s="66"/>
       <c r="M4" s="66"/>
       <c r="N4" s="66"/>
       <c r="O4" s="66" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="P4" s="66"/>
       <c r="Q4" s="66"/>
       <c r="R4" s="66"/>
       <c r="S4" s="66" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="T4" s="66"/>
       <c r="U4" s="66"/>
       <c r="V4" s="66"/>
       <c r="W4" s="66" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="X4" s="66"/>
       <c r="Y4" s="66"/>
       <c r="Z4" s="66"/>
       <c r="AA4" s="66" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="AB4" s="66"/>
       <c r="AC4" s="66"/>
       <c r="AD4" s="66"/>
       <c r="AE4" s="66" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AF4" s="66"/>
       <c r="AG4" s="66"/>
       <c r="AH4" s="66"/>
       <c r="AI4" s="66" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="AJ4" s="66"/>
       <c r="AK4" s="66"/>
       <c r="AL4" s="66"/>
       <c r="AM4" s="66" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="AN4" s="66"/>
       <c r="AO4" s="66"/>
       <c r="AP4" s="66"/>
       <c r="AQ4" s="66" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="AR4" s="66"/>
       <c r="AS4" s="66"/>
       <c r="AT4" s="66"/>
       <c r="AU4" s="66" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="AV4" s="66"/>
       <c r="AW4" s="66"/>
       <c r="AX4" s="66"/>
       <c r="AY4" s="66" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="AZ4" s="66"/>
       <c r="BA4" s="66"/>
       <c r="BB4" s="66"/>
       <c r="BC4" s="19" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="BD4" s="19" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="BE4" s="19" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="BF4" s="19" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4942,148 +5980,148 @@
       <c r="E5" s="19"/>
       <c r="F5" s="65"/>
       <c r="G5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="N5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="O5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="R5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="S5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="V5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="W5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="X5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="Y5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="Z5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AA5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AB5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AC5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AD5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AE5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AF5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AG5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AH5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AI5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AJ5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AK5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AL5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AM5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AN5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AO5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AP5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AQ5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AR5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AS5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AT5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AU5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AV5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="AW5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="AX5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="AY5" s="17" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="AZ5" s="17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="BA5" s="17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="BB5" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="BC5" s="19"/>
       <c r="BD5" s="19"/>
@@ -5107,7 +6145,7 @@
         <v>72.1153846153846</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="F6" s="69" t="str">
         <f aca="false">IF(A6="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A6,Personnel!$A$5:$A$19,0)),""))</f>
@@ -5271,7 +6309,7 @@
         <v>79.3269230769231</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="F7" s="86" t="str">
         <f aca="false">IF(A7="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A7,Personnel!$A$5:$A$19,0)),""))</f>
@@ -5435,7 +6473,7 @@
         <v>28.5</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F8" s="69" t="str">
         <f aca="false">IF(A8="","",IFERROR(INDEX(Personnel!$D$5:$D$19,MATCH($A8,Personnel!$A$5:$A$19,0)),""))</f>
@@ -7456,39 +8494,39 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="34" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7985,12 +9023,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8134,32 +9172,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="89" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B4" s="89" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8167,16 +9205,16 @@
         <v>46036</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>14200</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8184,16 +9222,16 @@
         <v>46056</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>3100</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8201,16 +9239,16 @@
         <v>46132</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>8600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8321,29 +9359,29 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="90"/>
       <c r="B23" s="91" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C23" s="90"/>
       <c r="D23" s="90"/>
       <c r="E23" s="92" t="n">
         <f aca="false">SUM(E5:E22)</f>
-        <v>25900</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="89" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B26" s="89" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C26" s="89" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8356,7 +9394,7 @@
       </c>
       <c r="C27" s="25" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A27)</f>
-        <v>14200</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8369,7 +9407,7 @@
       </c>
       <c r="C28" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A28)</f>
-        <v>3100</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8395,7 +9433,7 @@
       </c>
       <c r="C30" s="32" t="n">
         <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A30)</f>
-        <v>8600</v>
+        <v>860</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8504,7 +9542,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8537,32 +9575,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="3" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="34" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="89" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B4" s="89" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E4" s="89" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8570,10 +9608,10 @@
         <v>46042</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="D5" s="20" t="n">
         <v>1</v>
@@ -8587,10 +9625,10 @@
         <v>46042</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D6" s="27" t="n">
         <v>1</v>
@@ -8604,10 +9642,10 @@
         <v>46091</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>3</v>
@@ -8724,7 +9762,7 @@
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="90"/>
       <c r="B23" s="91" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C23" s="90"/>
       <c r="D23" s="90"/>
@@ -8735,18 +9773,18 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="89" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B26" s="89" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C26" s="89" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,7 +9945,410 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF0F6E56"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="34" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="89" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="23"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="30"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="23"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="30"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="30"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="23"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="30"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="30"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="23"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="30"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="90"/>
+      <c r="B23" s="91" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="92" t="n">
+        <f aca="false">SUM(E5:E22)</f>
+        <v>25900</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="34" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="89" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="89" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A27-1)</f>
+        <v>46023</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A27)</f>
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A28-1)</f>
+        <v>46054</v>
+      </c>
+      <c r="C28" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A28)</f>
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A29-1)</f>
+        <v>46082</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A30-1)</f>
+        <v>46113</v>
+      </c>
+      <c r="C30" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A30)</f>
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A31-1)</f>
+        <v>46143</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A32-1)</f>
+        <v>46174</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A33-1)</f>
+        <v>46204</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A34-1)</f>
+        <v>46235</v>
+      </c>
+      <c r="C34" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A35-1)</f>
+        <v>46266</v>
+      </c>
+      <c r="C35" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A36-1)</f>
+        <v>46296</v>
+      </c>
+      <c r="C36" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" s="52" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A37-1)</f>
+        <v>46327</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="55" t="n">
+        <f aca="false">EDATE(Dashboard!$C$5,A38-1)</f>
+        <v>46357</v>
+      </c>
+      <c r="C38" s="32" t="n">
+        <f aca="false">SUMIFS($E$5:$E$22,$D$5:$D$22,A38)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -6823,8 +6823,8 @@
       </c>
       <c r="G14" s="137" t="inlineStr">
         <is>
-          <t>70%
-Line</t>
+          <t>Chart Ref
+Only: 70%</t>
         </is>
       </c>
       <c r="I14" s="117" t="inlineStr">
@@ -7784,6 +7784,50 @@
     </cfRule>
     <cfRule type="expression" priority="12" dxfId="13">
       <formula>B10&lt;0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:C38">
+    <cfRule type="expression" priority="13" dxfId="11">
+      <formula>C15&gt;=0.7</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="12">
+      <formula>AND(C15&gt;=0.5,C15&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="13">
+      <formula>C15&lt;0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15:D38">
+    <cfRule type="expression" priority="16" dxfId="11">
+      <formula>D15&gt;=0.7</formula>
+    </cfRule>
+    <cfRule type="expression" priority="17" dxfId="12">
+      <formula>AND(D15&gt;=0.5,D15&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="13">
+      <formula>D15&lt;0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15:E38">
+    <cfRule type="expression" priority="19" dxfId="11">
+      <formula>E15&gt;=0.7</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="12">
+      <formula>AND(E15&gt;=0.5,E15&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="21" dxfId="13">
+      <formula>E15&lt;0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F38">
+    <cfRule type="expression" priority="22" dxfId="11">
+      <formula>F15&gt;=0.7</formula>
+    </cfRule>
+    <cfRule type="expression" priority="23" dxfId="12">
+      <formula>AND(F15&gt;=0.5,F15&lt;0.7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="13">
+      <formula>F15&lt;0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -28,6 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ODCs'!$A$4:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Travel'!$A$4:$F$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'M&amp;E'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'FundingMods'!$A$4:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -563,7 +564,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1100,49 +1101,13 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="28" fillId="19" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1183,6 +1148,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1201,7 +1172,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill>
@@ -1322,6 +1293,29 @@
           <fgColor rgb="FFDCEEDC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF3B6D11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCEEDC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF3B6D11"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C1C1C"/>
+      </font>
     </dxf>
   </dxfs>
   <colors>
@@ -1912,47 +1906,31 @@
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
+  <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>0</col>
-      <colOff>247320</colOff>
-      <row>0</row>
-      <rowOff>247320</rowOff>
-    </to>
+    <ext cx="266700" cy="266700"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 1" descr="Picture"/>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="247320" cy="247320"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -7837,666 +7815,825 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <tabColor rgb="FFEF9F27"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" style="108" min="1" max="1"/>
-    <col width="12" customWidth="1" style="108" min="2" max="2"/>
-    <col width="34" customWidth="1" style="108" min="3" max="3"/>
-    <col width="14" customWidth="1" style="108" min="4" max="4"/>
-    <col width="13" customWidth="1" style="108" min="5" max="9"/>
-    <col width="14" customWidth="1" style="108" min="10" max="14"/>
+    <col width="17" customWidth="1" style="109" min="1" max="1"/>
+    <col width="13" customWidth="1" style="109" min="2" max="2"/>
+    <col width="13" customWidth="1" style="109" min="3" max="3"/>
+    <col width="16" customWidth="1" style="109" min="4" max="4"/>
+    <col width="34" customWidth="1" style="109" min="5" max="5"/>
+    <col width="14" customWidth="1" style="109" min="6" max="6"/>
+    <col width="13" customWidth="1" style="109" min="7" max="7"/>
+    <col width="13" customWidth="1" style="109" min="8" max="8"/>
+    <col width="13" customWidth="1" style="109" min="9" max="9"/>
+    <col width="13" customWidth="1" style="109" min="10" max="10"/>
+    <col width="13" customWidth="1" style="109" min="11" max="11"/>
+    <col width="13" customWidth="1" style="109" min="12" max="12"/>
+    <col width="13" customWidth="1" style="109" min="13" max="13"/>
+    <col width="13" customWidth="1" style="109" min="14" max="14"/>
+    <col width="13" customWidth="1" style="109" min="15" max="15"/>
+    <col width="13" customWidth="1" style="109" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" s="109">
-      <c r="B1" s="141" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Funding Modification Log</t>
         </is>
       </c>
-      <c r="N1" s="142" t="inlineStr">
+      <c r="P1" s="122" t="inlineStr">
         <is>
           <t>Acqlerate  ·  acqlerate.com</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" s="109">
-      <c r="A3" s="164" t="inlineStr">
-        <is>
-          <t>HISTORICAL AUDIT LOG — for reference only. This no longer feeds the Dashboard or the CLIN Funding Status table below; those now read live TOA from the Projects tab. Keep logging mods here anyway — it's the paper trail a real contract needs, split across CLIN and (optionally) Project the same way as before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" s="109">
-      <c r="A4" s="151" t="inlineStr">
+    <row r="3" ht="48" customHeight="1" s="109">
+      <c r="A3" s="114" t="inlineStr">
+        <is>
+          <t>HISTORICAL AUDIT LOG — for reference only. This no longer feeds the Dashboard or the CLIN Funding Status table below; those now read live TOA from the Projects tab. Keep logging mods here anyway — it's the paper trail a real contract needs. ACRN and SLIN let you track each mod down to its actual funding line, not just its CLIN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" s="109">
+      <c r="A4" s="126" t="inlineStr">
         <is>
           <t>Mod #</t>
         </is>
       </c>
-      <c r="B4" s="151" t="inlineStr">
+      <c r="B4" s="126" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="151" t="inlineStr">
+      <c r="C4" s="126" t="inlineStr">
+        <is>
+          <t>ACRN</t>
+        </is>
+      </c>
+      <c r="D4" s="126" t="inlineStr">
+        <is>
+          <t>SLIN</t>
+        </is>
+      </c>
+      <c r="E4" s="126" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D4" s="210" t="inlineStr">
+      <c r="F4" s="126" t="inlineStr">
         <is>
           <t>Project
 (optional)</t>
         </is>
       </c>
-      <c r="E4" s="151" t="inlineStr">
+      <c r="G4" s="126" t="inlineStr">
         <is>
           <t>Labor CLIN
 $</t>
         </is>
       </c>
-      <c r="F4" s="151" t="inlineStr">
+      <c r="H4" s="126" t="inlineStr">
         <is>
           <t>Travel CLIN
 $</t>
         </is>
       </c>
-      <c r="G4" s="151" t="inlineStr">
+      <c r="I4" s="126" t="inlineStr">
         <is>
           <t>ODC CLIN
 $</t>
         </is>
       </c>
-      <c r="H4" s="151" t="inlineStr">
+      <c r="J4" s="126" t="inlineStr">
         <is>
           <t>M&amp;E CLIN
 $</t>
         </is>
       </c>
-      <c r="I4" s="210" t="inlineStr">
+      <c r="K4" s="126" t="inlineStr">
         <is>
           <t>Mod Total
 $</t>
         </is>
       </c>
-      <c r="J4" s="211" t="inlineStr">
+      <c r="L4" s="126" t="inlineStr">
         <is>
           <t>Cum. Labor
 TOA $</t>
         </is>
       </c>
-      <c r="K4" s="211" t="inlineStr">
+      <c r="M4" s="126" t="inlineStr">
         <is>
           <t>Cum. Travel
 TOA $</t>
         </is>
       </c>
-      <c r="L4" s="211" t="inlineStr">
+      <c r="N4" s="126" t="inlineStr">
         <is>
           <t>Cum. ODC
 TOA $</t>
         </is>
       </c>
-      <c r="M4" s="211" t="inlineStr">
+      <c r="O4" s="126" t="inlineStr">
         <is>
           <t>Cum. M&amp;E
 TOA $</t>
         </is>
       </c>
-      <c r="N4" s="211" t="inlineStr">
+      <c r="P4" s="126" t="inlineStr">
         <is>
           <t>Cum. Total
 TOA $</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="109">
-      <c r="A5" s="165" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="128" t="inlineStr">
         <is>
           <t>P00000 (Award)</t>
         </is>
       </c>
-      <c r="B5" s="169" t="n">
+      <c r="B5" s="202" t="n">
         <v>46023</v>
       </c>
-      <c r="C5" s="165" t="inlineStr">
+      <c r="C5" s="128" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="D5" s="128" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E5" s="128" t="inlineStr">
         <is>
           <t>Original award — base period</t>
         </is>
       </c>
-      <c r="D5" s="212" t="n"/>
-      <c r="E5" s="166" t="n">
+      <c r="F5" s="128" t="n"/>
+      <c r="G5" s="131" t="n">
         <v>1300000</v>
       </c>
-      <c r="F5" s="166" t="n">
+      <c r="H5" s="131" t="n">
         <v>300000</v>
       </c>
-      <c r="G5" s="166" t="n">
+      <c r="I5" s="131" t="n">
         <v>250000</v>
       </c>
-      <c r="H5" s="166" t="n">
+      <c r="J5" s="131" t="n">
         <v>150000</v>
       </c>
-      <c r="I5" s="213">
-        <f>IF(A5="","",SUM(E5:H5))</f>
-        <v/>
-      </c>
-      <c r="J5" s="154">
-        <f>IF(A5="","",SUM($E$5:E5))</f>
-        <v/>
-      </c>
-      <c r="K5" s="154">
-        <f>IF(A5="","",SUM($F$5:F5))</f>
-        <v/>
-      </c>
-      <c r="L5" s="154">
+      <c r="K5" s="132">
+        <f>IF(A5="","",SUM(G5:J5))</f>
+        <v/>
+      </c>
+      <c r="L5" s="132">
         <f>IF(A5="","",SUM($G$5:G5))</f>
         <v/>
       </c>
-      <c r="M5" s="154">
+      <c r="M5" s="132">
         <f>IF(A5="","",SUM($H$5:H5))</f>
         <v/>
       </c>
-      <c r="N5" s="214">
-        <f>IF(A5="","",J5+K5+L5+M5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="109">
-      <c r="A6" s="172" t="inlineStr">
+      <c r="N5" s="132">
+        <f>IF(A5="","",SUM($I$5:I5))</f>
+        <v/>
+      </c>
+      <c r="O5" s="132">
+        <f>IF(A5="","",SUM($J$5:J5))</f>
+        <v/>
+      </c>
+      <c r="P5" s="132">
+        <f>IF(A5="","",L5+M5+N5+O5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="128" t="inlineStr">
         <is>
           <t>P00001</t>
         </is>
       </c>
-      <c r="B6" s="176" t="n">
+      <c r="B6" s="202" t="n">
         <v>46143</v>
       </c>
-      <c r="C6" s="172" t="inlineStr">
+      <c r="C6" s="128" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D6" s="128" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="E6" s="128" t="inlineStr">
         <is>
           <t>Incremental funding — added scope</t>
         </is>
       </c>
-      <c r="D6" s="215" t="n"/>
-      <c r="E6" s="173" t="n">
+      <c r="F6" s="128" t="n"/>
+      <c r="G6" s="131" t="n">
         <v>250000</v>
       </c>
-      <c r="F6" s="173" t="n">
+      <c r="H6" s="131" t="n">
         <v>50000</v>
       </c>
-      <c r="G6" s="173" t="n">
+      <c r="I6" s="131" t="n">
         <v>30000</v>
       </c>
-      <c r="H6" s="173" t="n">
+      <c r="J6" s="131" t="n">
         <v>20000</v>
       </c>
-      <c r="I6" s="216">
-        <f>IF(A6="","",SUM(E6:H6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="160">
-        <f>IF(A6="","",SUM($E$5:E6))</f>
-        <v/>
-      </c>
-      <c r="K6" s="160">
-        <f>IF(A6="","",SUM($F$5:F6))</f>
-        <v/>
-      </c>
-      <c r="L6" s="160">
+      <c r="K6" s="132">
+        <f>IF(A6="","",SUM(G6:J6))</f>
+        <v/>
+      </c>
+      <c r="L6" s="132">
         <f>IF(A6="","",SUM($G$5:G6))</f>
         <v/>
       </c>
-      <c r="M6" s="160">
+      <c r="M6" s="132">
         <f>IF(A6="","",SUM($H$5:H6))</f>
         <v/>
       </c>
-      <c r="N6" s="217">
-        <f>IF(A6="","",J6+K6+L6+M6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="109">
-      <c r="A7" s="165" t="n"/>
-      <c r="B7" s="169" t="n"/>
-      <c r="C7" s="165" t="n"/>
-      <c r="D7" s="212" t="n"/>
-      <c r="E7" s="166" t="n"/>
-      <c r="F7" s="166" t="n"/>
-      <c r="G7" s="166" t="n"/>
-      <c r="H7" s="166" t="n"/>
-      <c r="I7" s="213">
-        <f>IF(A7="","",SUM(E7:H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="154">
-        <f>IF(A7="","",SUM($E$5:E7))</f>
-        <v/>
-      </c>
-      <c r="K7" s="154">
-        <f>IF(A7="","",SUM($F$5:F7))</f>
-        <v/>
-      </c>
-      <c r="L7" s="154">
+      <c r="N6" s="132">
+        <f>IF(A6="","",SUM($I$5:I6))</f>
+        <v/>
+      </c>
+      <c r="O6" s="132">
+        <f>IF(A6="","",SUM($J$5:J6))</f>
+        <v/>
+      </c>
+      <c r="P6" s="132">
+        <f>IF(A6="","",L6+M6+N6+O6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="128" t="n"/>
+      <c r="B7" s="202" t="n"/>
+      <c r="C7" s="128" t="n"/>
+      <c r="D7" s="128" t="n"/>
+      <c r="E7" s="128" t="n"/>
+      <c r="F7" s="128" t="n"/>
+      <c r="G7" s="131" t="n"/>
+      <c r="H7" s="131" t="n"/>
+      <c r="I7" s="131" t="n"/>
+      <c r="J7" s="131" t="n"/>
+      <c r="K7" s="132">
+        <f>IF(A7="","",SUM(G7:J7))</f>
+        <v/>
+      </c>
+      <c r="L7" s="132">
         <f>IF(A7="","",SUM($G$5:G7))</f>
         <v/>
       </c>
-      <c r="M7" s="154">
+      <c r="M7" s="132">
         <f>IF(A7="","",SUM($H$5:H7))</f>
         <v/>
       </c>
-      <c r="N7" s="214">
-        <f>IF(A7="","",J7+K7+L7+M7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="109">
-      <c r="A8" s="172" t="n"/>
-      <c r="B8" s="176" t="n"/>
-      <c r="C8" s="172" t="n"/>
-      <c r="D8" s="215" t="n"/>
-      <c r="E8" s="173" t="n"/>
-      <c r="F8" s="173" t="n"/>
-      <c r="G8" s="173" t="n"/>
-      <c r="H8" s="173" t="n"/>
-      <c r="I8" s="216">
-        <f>IF(A8="","",SUM(E8:H8))</f>
-        <v/>
-      </c>
-      <c r="J8" s="160">
-        <f>IF(A8="","",SUM($E$5:E8))</f>
-        <v/>
-      </c>
-      <c r="K8" s="160">
-        <f>IF(A8="","",SUM($F$5:F8))</f>
-        <v/>
-      </c>
-      <c r="L8" s="160">
+      <c r="N7" s="132">
+        <f>IF(A7="","",SUM($I$5:I7))</f>
+        <v/>
+      </c>
+      <c r="O7" s="132">
+        <f>IF(A7="","",SUM($J$5:J7))</f>
+        <v/>
+      </c>
+      <c r="P7" s="132">
+        <f>IF(A7="","",L7+M7+N7+O7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="128" t="n"/>
+      <c r="B8" s="202" t="n"/>
+      <c r="C8" s="128" t="n"/>
+      <c r="D8" s="128" t="n"/>
+      <c r="E8" s="128" t="n"/>
+      <c r="F8" s="128" t="n"/>
+      <c r="G8" s="131" t="n"/>
+      <c r="H8" s="131" t="n"/>
+      <c r="I8" s="131" t="n"/>
+      <c r="J8" s="131" t="n"/>
+      <c r="K8" s="132">
+        <f>IF(A8="","",SUM(G8:J8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="132">
         <f>IF(A8="","",SUM($G$5:G8))</f>
         <v/>
       </c>
-      <c r="M8" s="160">
+      <c r="M8" s="132">
         <f>IF(A8="","",SUM($H$5:H8))</f>
         <v/>
       </c>
-      <c r="N8" s="217">
-        <f>IF(A8="","",J8+K8+L8+M8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="109">
-      <c r="A9" s="165" t="n"/>
-      <c r="B9" s="169" t="n"/>
-      <c r="C9" s="165" t="n"/>
-      <c r="D9" s="212" t="n"/>
-      <c r="E9" s="166" t="n"/>
-      <c r="F9" s="166" t="n"/>
-      <c r="G9" s="166" t="n"/>
-      <c r="H9" s="166" t="n"/>
-      <c r="I9" s="213">
-        <f>IF(A9="","",SUM(E9:H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="154">
-        <f>IF(A9="","",SUM($E$5:E9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="154">
-        <f>IF(A9="","",SUM($F$5:F9))</f>
-        <v/>
-      </c>
-      <c r="L9" s="154">
+      <c r="N8" s="132">
+        <f>IF(A8="","",SUM($I$5:I8))</f>
+        <v/>
+      </c>
+      <c r="O8" s="132">
+        <f>IF(A8="","",SUM($J$5:J8))</f>
+        <v/>
+      </c>
+      <c r="P8" s="132">
+        <f>IF(A8="","",L8+M8+N8+O8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="128" t="n"/>
+      <c r="B9" s="202" t="n"/>
+      <c r="C9" s="128" t="n"/>
+      <c r="D9" s="128" t="n"/>
+      <c r="E9" s="128" t="n"/>
+      <c r="F9" s="128" t="n"/>
+      <c r="G9" s="131" t="n"/>
+      <c r="H9" s="131" t="n"/>
+      <c r="I9" s="131" t="n"/>
+      <c r="J9" s="131" t="n"/>
+      <c r="K9" s="132">
+        <f>IF(A9="","",SUM(G9:J9))</f>
+        <v/>
+      </c>
+      <c r="L9" s="132">
         <f>IF(A9="","",SUM($G$5:G9))</f>
         <v/>
       </c>
-      <c r="M9" s="154">
+      <c r="M9" s="132">
         <f>IF(A9="","",SUM($H$5:H9))</f>
         <v/>
       </c>
-      <c r="N9" s="214">
-        <f>IF(A9="","",J9+K9+L9+M9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="109">
-      <c r="A10" s="172" t="n"/>
-      <c r="B10" s="176" t="n"/>
-      <c r="C10" s="172" t="n"/>
-      <c r="D10" s="215" t="n"/>
-      <c r="E10" s="173" t="n"/>
-      <c r="F10" s="173" t="n"/>
-      <c r="G10" s="173" t="n"/>
-      <c r="H10" s="173" t="n"/>
-      <c r="I10" s="216">
-        <f>IF(A10="","",SUM(E10:H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="160">
-        <f>IF(A10="","",SUM($E$5:E10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="160">
-        <f>IF(A10="","",SUM($F$5:F10))</f>
-        <v/>
-      </c>
-      <c r="L10" s="160">
+      <c r="N9" s="132">
+        <f>IF(A9="","",SUM($I$5:I9))</f>
+        <v/>
+      </c>
+      <c r="O9" s="132">
+        <f>IF(A9="","",SUM($J$5:J9))</f>
+        <v/>
+      </c>
+      <c r="P9" s="132">
+        <f>IF(A9="","",L9+M9+N9+O9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="128" t="n"/>
+      <c r="B10" s="202" t="n"/>
+      <c r="C10" s="128" t="n"/>
+      <c r="D10" s="128" t="n"/>
+      <c r="E10" s="128" t="n"/>
+      <c r="F10" s="128" t="n"/>
+      <c r="G10" s="131" t="n"/>
+      <c r="H10" s="131" t="n"/>
+      <c r="I10" s="131" t="n"/>
+      <c r="J10" s="131" t="n"/>
+      <c r="K10" s="132">
+        <f>IF(A10="","",SUM(G10:J10))</f>
+        <v/>
+      </c>
+      <c r="L10" s="132">
         <f>IF(A10="","",SUM($G$5:G10))</f>
         <v/>
       </c>
-      <c r="M10" s="160">
+      <c r="M10" s="132">
         <f>IF(A10="","",SUM($H$5:H10))</f>
         <v/>
       </c>
-      <c r="N10" s="217">
-        <f>IF(A10="","",J10+K10+L10+M10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="109">
-      <c r="A11" s="165" t="n"/>
-      <c r="B11" s="169" t="n"/>
-      <c r="C11" s="165" t="n"/>
-      <c r="D11" s="212" t="n"/>
-      <c r="E11" s="166" t="n"/>
-      <c r="F11" s="166" t="n"/>
-      <c r="G11" s="166" t="n"/>
-      <c r="H11" s="166" t="n"/>
-      <c r="I11" s="213">
-        <f>IF(A11="","",SUM(E11:H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="154">
-        <f>IF(A11="","",SUM($E$5:E11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="154">
-        <f>IF(A11="","",SUM($F$5:F11))</f>
-        <v/>
-      </c>
-      <c r="L11" s="154">
+      <c r="N10" s="132">
+        <f>IF(A10="","",SUM($I$5:I10))</f>
+        <v/>
+      </c>
+      <c r="O10" s="132">
+        <f>IF(A10="","",SUM($J$5:J10))</f>
+        <v/>
+      </c>
+      <c r="P10" s="132">
+        <f>IF(A10="","",L10+M10+N10+O10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="128" t="n"/>
+      <c r="B11" s="202" t="n"/>
+      <c r="C11" s="128" t="n"/>
+      <c r="D11" s="128" t="n"/>
+      <c r="E11" s="128" t="n"/>
+      <c r="F11" s="128" t="n"/>
+      <c r="G11" s="131" t="n"/>
+      <c r="H11" s="131" t="n"/>
+      <c r="I11" s="131" t="n"/>
+      <c r="J11" s="131" t="n"/>
+      <c r="K11" s="132">
+        <f>IF(A11="","",SUM(G11:J11))</f>
+        <v/>
+      </c>
+      <c r="L11" s="132">
         <f>IF(A11="","",SUM($G$5:G11))</f>
         <v/>
       </c>
-      <c r="M11" s="154">
+      <c r="M11" s="132">
         <f>IF(A11="","",SUM($H$5:H11))</f>
         <v/>
       </c>
-      <c r="N11" s="214">
-        <f>IF(A11="","",J11+K11+L11+M11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="109">
-      <c r="A12" s="172" t="n"/>
-      <c r="B12" s="176" t="n"/>
-      <c r="C12" s="172" t="n"/>
-      <c r="D12" s="215" t="n"/>
-      <c r="E12" s="173" t="n"/>
-      <c r="F12" s="173" t="n"/>
-      <c r="G12" s="173" t="n"/>
-      <c r="H12" s="173" t="n"/>
-      <c r="I12" s="216">
-        <f>IF(A12="","",SUM(E12:H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="160">
-        <f>IF(A12="","",SUM($E$5:E12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="160">
-        <f>IF(A12="","",SUM($F$5:F12))</f>
-        <v/>
-      </c>
-      <c r="L12" s="160">
+      <c r="N11" s="132">
+        <f>IF(A11="","",SUM($I$5:I11))</f>
+        <v/>
+      </c>
+      <c r="O11" s="132">
+        <f>IF(A11="","",SUM($J$5:J11))</f>
+        <v/>
+      </c>
+      <c r="P11" s="132">
+        <f>IF(A11="","",L11+M11+N11+O11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="128" t="n"/>
+      <c r="B12" s="202" t="n"/>
+      <c r="C12" s="128" t="n"/>
+      <c r="D12" s="128" t="n"/>
+      <c r="E12" s="128" t="n"/>
+      <c r="F12" s="128" t="n"/>
+      <c r="G12" s="131" t="n"/>
+      <c r="H12" s="131" t="n"/>
+      <c r="I12" s="131" t="n"/>
+      <c r="J12" s="131" t="n"/>
+      <c r="K12" s="132">
+        <f>IF(A12="","",SUM(G12:J12))</f>
+        <v/>
+      </c>
+      <c r="L12" s="132">
         <f>IF(A12="","",SUM($G$5:G12))</f>
         <v/>
       </c>
-      <c r="M12" s="160">
+      <c r="M12" s="132">
         <f>IF(A12="","",SUM($H$5:H12))</f>
         <v/>
       </c>
-      <c r="N12" s="217">
-        <f>IF(A12="","",J12+K12+L12+M12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="109">
-      <c r="A13" s="165" t="n"/>
-      <c r="B13" s="169" t="n"/>
-      <c r="C13" s="165" t="n"/>
-      <c r="D13" s="212" t="n"/>
-      <c r="E13" s="166" t="n"/>
-      <c r="F13" s="166" t="n"/>
-      <c r="G13" s="166" t="n"/>
-      <c r="H13" s="166" t="n"/>
-      <c r="I13" s="213">
-        <f>IF(A13="","",SUM(E13:H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="154">
-        <f>IF(A13="","",SUM($E$5:E13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="154">
-        <f>IF(A13="","",SUM($F$5:F13))</f>
-        <v/>
-      </c>
-      <c r="L13" s="154">
+      <c r="N12" s="132">
+        <f>IF(A12="","",SUM($I$5:I12))</f>
+        <v/>
+      </c>
+      <c r="O12" s="132">
+        <f>IF(A12="","",SUM($J$5:J12))</f>
+        <v/>
+      </c>
+      <c r="P12" s="132">
+        <f>IF(A12="","",L12+M12+N12+O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="128" t="n"/>
+      <c r="B13" s="202" t="n"/>
+      <c r="C13" s="128" t="n"/>
+      <c r="D13" s="128" t="n"/>
+      <c r="E13" s="128" t="n"/>
+      <c r="F13" s="128" t="n"/>
+      <c r="G13" s="131" t="n"/>
+      <c r="H13" s="131" t="n"/>
+      <c r="I13" s="131" t="n"/>
+      <c r="J13" s="131" t="n"/>
+      <c r="K13" s="132">
+        <f>IF(A13="","",SUM(G13:J13))</f>
+        <v/>
+      </c>
+      <c r="L13" s="132">
         <f>IF(A13="","",SUM($G$5:G13))</f>
         <v/>
       </c>
-      <c r="M13" s="154">
+      <c r="M13" s="132">
         <f>IF(A13="","",SUM($H$5:H13))</f>
         <v/>
       </c>
-      <c r="N13" s="214">
-        <f>IF(A13="","",J13+K13+L13+M13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="109">
-      <c r="A14" s="172" t="n"/>
-      <c r="B14" s="176" t="n"/>
-      <c r="C14" s="172" t="n"/>
-      <c r="D14" s="215" t="n"/>
-      <c r="E14" s="173" t="n"/>
-      <c r="F14" s="173" t="n"/>
-      <c r="G14" s="173" t="n"/>
-      <c r="H14" s="173" t="n"/>
-      <c r="I14" s="216">
-        <f>IF(A14="","",SUM(E14:H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="160">
-        <f>IF(A14="","",SUM($E$5:E14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="160">
-        <f>IF(A14="","",SUM($F$5:F14))</f>
-        <v/>
-      </c>
-      <c r="L14" s="160">
+      <c r="N13" s="132">
+        <f>IF(A13="","",SUM($I$5:I13))</f>
+        <v/>
+      </c>
+      <c r="O13" s="132">
+        <f>IF(A13="","",SUM($J$5:J13))</f>
+        <v/>
+      </c>
+      <c r="P13" s="132">
+        <f>IF(A13="","",L13+M13+N13+O13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="128" t="n"/>
+      <c r="B14" s="202" t="n"/>
+      <c r="C14" s="128" t="n"/>
+      <c r="D14" s="128" t="n"/>
+      <c r="E14" s="128" t="n"/>
+      <c r="F14" s="128" t="n"/>
+      <c r="G14" s="131" t="n"/>
+      <c r="H14" s="131" t="n"/>
+      <c r="I14" s="131" t="n"/>
+      <c r="J14" s="131" t="n"/>
+      <c r="K14" s="132">
+        <f>IF(A14="","",SUM(G14:J14))</f>
+        <v/>
+      </c>
+      <c r="L14" s="132">
         <f>IF(A14="","",SUM($G$5:G14))</f>
         <v/>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="132">
         <f>IF(A14="","",SUM($H$5:H14))</f>
         <v/>
       </c>
-      <c r="N14" s="217">
-        <f>IF(A14="","",J14+K14+L14+M14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="109">
-      <c r="A17" s="115" t="inlineStr">
+      <c r="N14" s="132">
+        <f>IF(A14="","",SUM($I$5:I14))</f>
+        <v/>
+      </c>
+      <c r="O14" s="132">
+        <f>IF(A14="","",SUM($J$5:J14))</f>
+        <v/>
+      </c>
+      <c r="P14" s="132">
+        <f>IF(A14="","",L14+M14+N14+O14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="123" t="inlineStr">
         <is>
           <t>CLIN Funding Status (auto — reads Projects tab, not this log)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="27.75" customHeight="1" s="109">
-      <c r="A18" s="151" t="inlineStr">
+    <row r="17" ht="28" customHeight="1" s="109">
+      <c r="A17" s="137" t="inlineStr">
         <is>
           <t>CLIN</t>
         </is>
       </c>
-      <c r="B18" s="151" t="inlineStr">
-        <is>
-          <t>Cumulative
-TOA $</t>
-        </is>
-      </c>
-      <c r="C18" s="151" t="inlineStr">
+      <c r="B17" s="137" t="inlineStr">
+        <is>
+          <t>Funded $
+(from Projects)</t>
+        </is>
+      </c>
+      <c r="C17" s="137" t="inlineStr">
+        <is>
+          <t>Mod Log
+Total $</t>
+        </is>
+      </c>
+      <c r="D17" s="137" t="inlineStr">
+        <is>
+          <t>Reconciled?</t>
+        </is>
+      </c>
+      <c r="E17" s="137" t="inlineStr">
         <is>
           <t>Spent to
 Date $</t>
         </is>
       </c>
-      <c r="D18" s="151" t="inlineStr">
+      <c r="F17" s="137" t="inlineStr">
         <is>
           <t>Remaining
 $</t>
         </is>
       </c>
-      <c r="E18" s="151" t="inlineStr">
+      <c r="G17" s="137" t="inlineStr">
         <is>
           <t>% Used</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="109">
-      <c r="A19" s="218" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="127" t="inlineStr">
         <is>
           <t>Labor</t>
         </is>
       </c>
-      <c r="B19" s="154">
+      <c r="B18" s="132">
         <f>SUM(Projects!$C$6:$C$13)</f>
         <v/>
       </c>
-      <c r="C19" s="155">
+      <c r="C18" s="132">
+        <f>SUM(G$5:G$14)</f>
+        <v/>
+      </c>
+      <c r="D18" s="138">
+        <f>IF(ROUND(B18-C18,2)=0,"Match","MISMATCH: "&amp;TEXT(C18-B18,"+$#,##0;-$#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="132">
         <f>SUM(Dashboard!$D$21:$D$32)</f>
         <v/>
       </c>
-      <c r="D19" s="154">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="157">
-        <f>IFERROR(C19/B19,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="109">
-      <c r="A20" s="219" t="inlineStr">
+      <c r="F18" s="132">
+        <f>B18-E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="129">
+        <f>IFERROR(E18/B18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="127" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="B20" s="160">
+      <c r="B19" s="132">
         <f>SUM(Projects!$D$6:$D$13)</f>
         <v/>
       </c>
-      <c r="C20" s="161">
+      <c r="C19" s="132">
+        <f>SUM(H$5:H$14)</f>
+        <v/>
+      </c>
+      <c r="D19" s="138">
+        <f>IF(ROUND(B19-C19,2)=0,"Match","MISMATCH: "&amp;TEXT(C19-B19,"+$#,##0;-$#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="132">
         <f>SUM(Dashboard!$G$21:$G$32)</f>
         <v/>
       </c>
-      <c r="D20" s="160">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="163">
-        <f>IFERROR(C20/B20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="109">
-      <c r="A21" s="218" t="inlineStr">
+      <c r="F19" s="132">
+        <f>B19-E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="129">
+        <f>IFERROR(E19/B19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="127" t="inlineStr">
         <is>
           <t>ODC</t>
         </is>
       </c>
-      <c r="B21" s="154">
+      <c r="B20" s="132">
         <f>SUM(Projects!$E$6:$E$13)</f>
         <v/>
       </c>
-      <c r="C21" s="155">
+      <c r="C20" s="132">
+        <f>SUM(I$5:I$14)</f>
+        <v/>
+      </c>
+      <c r="D20" s="138">
+        <f>IF(ROUND(B20-C20,2)=0,"Match","MISMATCH: "&amp;TEXT(C20-B20,"+$#,##0;-$#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="132">
         <f>SUM(Dashboard!$E$21:$E$32)</f>
         <v/>
       </c>
-      <c r="D21" s="154">
-        <f>B21-C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="157">
-        <f>IFERROR(C21/B21,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="109">
-      <c r="A22" s="219" t="inlineStr">
+      <c r="F20" s="132">
+        <f>B20-E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="129">
+        <f>IFERROR(E20/B20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="127" t="inlineStr">
         <is>
           <t>M&amp;E</t>
         </is>
       </c>
-      <c r="B22" s="160">
+      <c r="B21" s="132">
         <f>SUM(Projects!$F$6:$F$13)</f>
         <v/>
       </c>
-      <c r="C22" s="161">
+      <c r="C21" s="132">
+        <f>SUM(J$5:J$14)</f>
+        <v/>
+      </c>
+      <c r="D21" s="138">
+        <f>IF(ROUND(B21-C21,2)=0,"Match","MISMATCH: "&amp;TEXT(C21-B21,"+$#,##0;-$#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E21" s="132">
         <f>SUM(Dashboard!$F$21:$F$32)</f>
         <v/>
       </c>
-      <c r="D22" s="160">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="163">
-        <f>IFERROR(C22/B22,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="109">
-      <c r="A23" s="220" t="inlineStr">
+      <c r="F21" s="132">
+        <f>B21-E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="129">
+        <f>IFERROR(E21/B21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="124" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="221">
-        <f>SUM(B19:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="221">
-        <f>SUM(C19:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="221">
-        <f>SUM(D19:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="222">
-        <f>IFERROR(C23/B23,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="109">
-      <c r="A26" s="111" t="inlineStr">
+      <c r="B22" s="135">
+        <f>SUM(B18:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="135">
+        <f>SUM(C18:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="139">
+        <f>IF(ROUND(B22-C22,2)=0,"Match","MISMATCH: "&amp;TEXT(C22-B22,"+$#,##0;-$#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E22" s="135">
+        <f>SUM(E18:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="135">
+        <f>SUM(F18:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="140">
+        <f>IFERROR(E22/B22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" s="109">
+      <c r="A24" s="114" t="inlineStr">
+        <is>
+          <t>Reconciled = this log's CLIN totals match what's actually funded on the Projects tab. If it says MISMATCH, someone updated one tab without the other — fix Projects (the source of truth) or log the missing mod here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="117" t="inlineStr">
         <is>
           <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:N3"/>
+  <autoFilter ref="A4:P14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A24:P24"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="expression" priority="1" dxfId="14">
+      <formula>D18="Match"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="11">
+      <formula>D18&lt;&gt;"Match"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="expression" priority="3" dxfId="14">
+      <formula>D19="Match"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="11">
+      <formula>D19&lt;&gt;"Match"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="expression" priority="5" dxfId="14">
+      <formula>D20="Match"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="11">
+      <formula>D20&lt;&gt;"Match"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="expression" priority="7" dxfId="14">
+      <formula>D21="Match"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="11">
+      <formula>D21&lt;&gt;"Match"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22">
+    <cfRule type="expression" priority="9" dxfId="15">
+      <formula>D22="Match"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="16">
+      <formula>D22&lt;&gt;"Match"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=Projects!$A$6:$A$13</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -8531,14 +8668,14 @@
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1" s="109">
-      <c r="A3" s="223" t="inlineStr">
+      <c r="A3" s="210" t="inlineStr">
         <is>
           <t>Quick answer for "what would it cost to add or change this person?" — a standalone what-if, separate from your actual Labor log. Doesn't affect Dashboard totals or Labor actuals.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="109">
-      <c r="A5" s="224" t="inlineStr">
+      <c r="A5" s="211" t="inlineStr">
         <is>
           <t>SCENARIO INPUTS</t>
         </is>
@@ -8552,105 +8689,105 @@
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1" s="109">
-      <c r="A8" s="218" t="inlineStr">
+      <c r="A8" s="212" t="inlineStr">
         <is>
           <t>Role / LCAT</t>
         </is>
       </c>
-      <c r="B8" s="225" t="inlineStr">
+      <c r="B8" s="213" t="inlineStr">
         <is>
           <t>Engineer 4</t>
         </is>
       </c>
-      <c r="C8" s="226" t="n"/>
-      <c r="D8" s="226" t="n"/>
-      <c r="E8" s="226" t="n"/>
+      <c r="C8" s="214" t="n"/>
+      <c r="D8" s="214" t="n"/>
+      <c r="E8" s="214" t="n"/>
     </row>
     <row r="9" ht="19.5" customHeight="1" s="109">
-      <c r="A9" s="218" t="inlineStr">
+      <c r="A9" s="212" t="inlineStr">
         <is>
           <t>Employee Type</t>
         </is>
       </c>
-      <c r="B9" s="225" t="inlineStr">
+      <c r="B9" s="213" t="inlineStr">
         <is>
           <t>Exempt</t>
         </is>
       </c>
-      <c r="C9" s="226" t="n"/>
-      <c r="D9" s="226" t="n"/>
-      <c r="E9" s="226" t="n"/>
+      <c r="C9" s="214" t="n"/>
+      <c r="D9" s="214" t="n"/>
+      <c r="E9" s="214" t="n"/>
     </row>
     <row r="10" ht="19.5" customHeight="1" s="109">
-      <c r="A10" s="218" t="inlineStr">
+      <c r="A10" s="212" t="inlineStr">
         <is>
           <t>Annual Salary (Exempt only)</t>
         </is>
       </c>
-      <c r="B10" s="227" t="n">
+      <c r="B10" s="215" t="n">
         <v>150000</v>
       </c>
-      <c r="C10" s="226" t="n"/>
-      <c r="D10" s="226" t="n"/>
-      <c r="E10" s="226" t="n"/>
+      <c r="C10" s="214" t="n"/>
+      <c r="D10" s="214" t="n"/>
+      <c r="E10" s="214" t="n"/>
     </row>
     <row r="11" ht="19.5" customHeight="1" s="109">
-      <c r="A11" s="218" t="inlineStr">
+      <c r="A11" s="212" t="inlineStr">
         <is>
           <t>Direct Hourly Rate (Non-Exempt only)</t>
         </is>
       </c>
-      <c r="B11" s="228" t="n"/>
-      <c r="C11" s="226" t="n"/>
-      <c r="D11" s="226" t="n"/>
-      <c r="E11" s="226" t="n"/>
+      <c r="B11" s="216" t="n"/>
+      <c r="C11" s="214" t="n"/>
+      <c r="D11" s="214" t="n"/>
+      <c r="E11" s="214" t="n"/>
     </row>
     <row r="12" ht="19.5" customHeight="1" s="109">
-      <c r="A12" s="218" t="inlineStr">
+      <c r="A12" s="212" t="inlineStr">
         <is>
           <t>Standard Annual Hours</t>
         </is>
       </c>
-      <c r="B12" s="225" t="n">
+      <c r="B12" s="213" t="n">
         <v>2080</v>
       </c>
-      <c r="C12" s="226" t="n"/>
-      <c r="D12" s="226" t="n"/>
-      <c r="E12" s="226" t="n"/>
+      <c r="C12" s="214" t="n"/>
+      <c r="D12" s="214" t="n"/>
+      <c r="E12" s="214" t="n"/>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="109">
-      <c r="A13" s="218" t="inlineStr">
+      <c r="A13" s="212" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="B13" s="229" t="n">
+      <c r="B13" s="217" t="n">
         <v>46266</v>
       </c>
-      <c r="C13" s="226" t="n"/>
-      <c r="D13" s="226" t="n"/>
-      <c r="E13" s="226" t="n"/>
+      <c r="C13" s="214" t="n"/>
+      <c r="D13" s="214" t="n"/>
+      <c r="E13" s="214" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="109">
-      <c r="A14" s="218" t="inlineStr">
+      <c r="A14" s="212" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
       </c>
-      <c r="B14" s="230">
+      <c r="B14" s="218">
         <f>Dashboard!$C$6</f>
         <v/>
       </c>
-      <c r="C14" s="231" t="inlineStr">
+      <c r="C14" s="219" t="inlineStr">
         <is>
           <t>Defaults to your PoP End on Dashboard — type over it for a custom end date.</t>
         </is>
       </c>
-      <c r="D14" s="232" t="n"/>
-      <c r="E14" s="233" t="n"/>
+      <c r="D14" s="220" t="n"/>
+      <c r="E14" s="221" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="109">
-      <c r="A16" s="224" t="inlineStr">
+      <c r="A16" s="211" t="inlineStr">
         <is>
           <t>BASE LABOR COST (auto)</t>
         </is>
@@ -8664,7 +8801,7 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="109">
-      <c r="A19" s="234" t="inlineStr">
+      <c r="A19" s="222" t="inlineStr">
         <is>
           <t>Straight-Time Rate $/hr</t>
         </is>
@@ -8673,26 +8810,26 @@
         <f>IF(B9="Exempt",IF(B12=0,"",B10/B12),B11)</f>
         <v/>
       </c>
-      <c r="C19" s="226" t="n"/>
-      <c r="D19" s="226" t="n"/>
-      <c r="E19" s="226" t="n"/>
+      <c r="C19" s="214" t="n"/>
+      <c r="D19" s="214" t="n"/>
+      <c r="E19" s="214" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="109">
-      <c r="A20" s="234" t="inlineStr">
+      <c r="A20" s="222" t="inlineStr">
         <is>
           <t>Days in Period</t>
         </is>
       </c>
-      <c r="B20" s="235">
+      <c r="B20" s="223">
         <f>IF(OR(B13="",B14=""),"",B14-B13+1)</f>
         <v/>
       </c>
-      <c r="C20" s="226" t="n"/>
-      <c r="D20" s="226" t="n"/>
-      <c r="E20" s="226" t="n"/>
+      <c r="C20" s="214" t="n"/>
+      <c r="D20" s="214" t="n"/>
+      <c r="E20" s="214" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="109">
-      <c r="A21" s="234" t="inlineStr">
+      <c r="A21" s="222" t="inlineStr">
         <is>
           <t>Estimated Hours in Period</t>
         </is>
@@ -8701,12 +8838,12 @@
         <f>IF(B20="","",B12*B20/365)</f>
         <v/>
       </c>
-      <c r="C21" s="226" t="n"/>
-      <c r="D21" s="226" t="n"/>
-      <c r="E21" s="226" t="n"/>
+      <c r="C21" s="214" t="n"/>
+      <c r="D21" s="214" t="n"/>
+      <c r="E21" s="214" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="109">
-      <c r="A22" s="234" t="inlineStr">
+      <c r="A22" s="222" t="inlineStr">
         <is>
           <t>Direct Labor $</t>
         </is>
@@ -8715,12 +8852,12 @@
         <f>IF(OR(B21="",B19=""),"",B21*B19)</f>
         <v/>
       </c>
-      <c r="C22" s="226" t="n"/>
-      <c r="D22" s="226" t="n"/>
-      <c r="E22" s="226" t="n"/>
+      <c r="C22" s="214" t="n"/>
+      <c r="D22" s="214" t="n"/>
+      <c r="E22" s="214" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="109">
-      <c r="A23" s="234" t="inlineStr">
+      <c r="A23" s="222" t="inlineStr">
         <is>
           <t>Fringe $</t>
         </is>
@@ -8729,12 +8866,12 @@
         <f>IF(B22="","",B22*Rates!$B$6)</f>
         <v/>
       </c>
-      <c r="C23" s="226" t="n"/>
-      <c r="D23" s="226" t="n"/>
-      <c r="E23" s="226" t="n"/>
+      <c r="C23" s="214" t="n"/>
+      <c r="D23" s="214" t="n"/>
+      <c r="E23" s="214" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="109">
-      <c r="A24" s="234" t="inlineStr">
+      <c r="A24" s="222" t="inlineStr">
         <is>
           <t>OH $</t>
         </is>
@@ -8743,26 +8880,26 @@
         <f>IF(B22="","",(B22+B23)*Rates!$B$7)</f>
         <v/>
       </c>
-      <c r="C24" s="226" t="n"/>
-      <c r="D24" s="226" t="n"/>
-      <c r="E24" s="226" t="n"/>
+      <c r="C24" s="214" t="n"/>
+      <c r="D24" s="214" t="n"/>
+      <c r="E24" s="214" t="n"/>
     </row>
     <row r="25" ht="25.5" customHeight="1" s="109">
-      <c r="A25" s="236" t="inlineStr">
+      <c r="A25" s="224" t="inlineStr">
         <is>
           <t>Base Fully Burdened Labor $</t>
         </is>
       </c>
-      <c r="B25" s="237">
+      <c r="B25" s="225">
         <f>IF(B22="","",B22+B23+B24)</f>
         <v/>
       </c>
-      <c r="C25" s="238" t="n"/>
-      <c r="D25" s="238" t="n"/>
-      <c r="E25" s="238" t="n"/>
+      <c r="C25" s="226" t="n"/>
+      <c r="D25" s="226" t="n"/>
+      <c r="E25" s="226" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="109">
-      <c r="A27" s="224" t="inlineStr">
+      <c r="A27" s="211" t="inlineStr">
         <is>
           <t>LOCATION / ALLOWANCE ADDERS</t>
         </is>
@@ -8872,20 +9009,20 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="109">
-      <c r="A35" s="220" t="inlineStr">
+      <c r="A35" s="227" t="inlineStr">
         <is>
           <t>Total Adders</t>
         </is>
       </c>
-      <c r="B35" s="238" t="n"/>
-      <c r="C35" s="238" t="n"/>
-      <c r="D35" s="221">
+      <c r="B35" s="226" t="n"/>
+      <c r="C35" s="226" t="n"/>
+      <c r="D35" s="228">
         <f>SUM(D31:D34)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="109">
-      <c r="A37" s="224" t="inlineStr">
+      <c r="A37" s="211" t="inlineStr">
         <is>
           <t>ROM ESTIMATE</t>
         </is>
@@ -8899,7 +9036,7 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="109">
-      <c r="A40" s="234" t="inlineStr">
+      <c r="A40" s="222" t="inlineStr">
         <is>
           <t>Subtotal (Labor + Adders) $</t>
         </is>
@@ -8908,12 +9045,12 @@
         <f>IF(B25="","",B25+D35)</f>
         <v/>
       </c>
-      <c r="C40" s="226" t="n"/>
-      <c r="D40" s="226" t="n"/>
-      <c r="E40" s="226" t="n"/>
+      <c r="C40" s="214" t="n"/>
+      <c r="D40" s="214" t="n"/>
+      <c r="E40" s="214" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="109">
-      <c r="A41" s="234" t="inlineStr">
+      <c r="A41" s="222" t="inlineStr">
         <is>
           <t>G&amp;A $</t>
         </is>
@@ -8922,12 +9059,12 @@
         <f>IF(B40="","",B40*Rates!$B$8)</f>
         <v/>
       </c>
-      <c r="C41" s="226" t="n"/>
-      <c r="D41" s="226" t="n"/>
-      <c r="E41" s="226" t="n"/>
+      <c r="C41" s="214" t="n"/>
+      <c r="D41" s="214" t="n"/>
+      <c r="E41" s="214" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="109">
-      <c r="A42" s="234" t="inlineStr">
+      <c r="A42" s="222" t="inlineStr">
         <is>
           <t>Total Cost $</t>
         </is>
@@ -8936,12 +9073,12 @@
         <f>IF(B40="","",B40+B41)</f>
         <v/>
       </c>
-      <c r="C42" s="226" t="n"/>
-      <c r="D42" s="226" t="n"/>
-      <c r="E42" s="226" t="n"/>
+      <c r="C42" s="214" t="n"/>
+      <c r="D42" s="214" t="n"/>
+      <c r="E42" s="214" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="109">
-      <c r="A43" s="234" t="inlineStr">
+      <c r="A43" s="222" t="inlineStr">
         <is>
           <t>Fee $</t>
         </is>
@@ -8950,26 +9087,26 @@
         <f>IF(B42="","",B42*Rates!$C$18)</f>
         <v/>
       </c>
-      <c r="C43" s="226" t="n"/>
-      <c r="D43" s="226" t="n"/>
-      <c r="E43" s="226" t="n"/>
+      <c r="C43" s="214" t="n"/>
+      <c r="D43" s="214" t="n"/>
+      <c r="E43" s="214" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1" s="109">
-      <c r="A44" s="239" t="inlineStr">
+      <c r="A44" s="229" t="inlineStr">
         <is>
           <t>TOTAL ROM ESTIMATE (fully burdened)</t>
         </is>
       </c>
-      <c r="B44" s="240">
+      <c r="B44" s="230">
         <f>IF(B42="","",B42+B43)</f>
         <v/>
       </c>
-      <c r="C44" s="238" t="n"/>
-      <c r="D44" s="238" t="n"/>
-      <c r="E44" s="238" t="n"/>
+      <c r="C44" s="226" t="n"/>
+      <c r="D44" s="226" t="n"/>
+      <c r="E44" s="226" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1" s="109">
-      <c r="A46" s="241">
+      <c r="A46" s="231">
         <f>"For "&amp;B8&amp;" from "&amp;TEXT(B13,"mm/dd/yyyy")&amp;" to "&amp;TEXT(B14,"mm/dd/yyyy")&amp;" ("&amp;B20&amp;" days): "&amp;TEXT(B44,"$#,##0")&amp;" fully burdened, ROM estimate."</f>
         <v/>
       </c>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -9268,7 +9268,7 @@
     <row r="11" ht="28" customHeight="1" s="109">
       <c r="A11" s="117" t="inlineStr">
         <is>
-          <t>Fixed = flat % of Total Cost (CPFF). Award = pool rate, actual earned fee depends on your award fee score. A contract can run BOTH — pick which CLINs draw from which pool in the table below.</t>
+          <t>Fixed = flat % of Total Cost (CPFF). Award = pool rate, actual earned fee depends on your award fee score. CR = Cost Reimbursable — no fee at all (0%), common for cost-only CLINs like travel. A contract can run all three — pick which CLINs draw from which pool in the table below.</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="C18" s="129">
-        <f>IF(B18="Fixed",$B$13,IF(B18="Award",$B$14,NA()))</f>
+        <f>IF(B18="Fixed",$B$13,IF(B18="Award",$B$14,IF(B18="CR",0,NA())))</f>
         <v/>
       </c>
     </row>
@@ -9347,11 +9347,11 @@
       </c>
       <c r="B19" s="128" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C19" s="129">
-        <f>IF(B19="Fixed",$B$13,IF(B19="Award",$B$14,NA()))</f>
+        <f>IF(B19="Fixed",$B$13,IF(B19="Award",$B$14,IF(B19="CR",0,NA())))</f>
         <v/>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="C20" s="129">
-        <f>IF(B20="Fixed",$B$13,IF(B20="Award",$B$14,NA()))</f>
+        <f>IF(B20="Fixed",$B$13,IF(B20="Award",$B$14,IF(B20="CR",0,NA())))</f>
         <v/>
       </c>
     </row>
@@ -9383,14 +9383,14 @@
         </is>
       </c>
       <c r="C21" s="129">
-        <f>IF(B21="Fixed",$B$13,IF(B21="Award",$B$14,NA()))</f>
+        <f>IF(B21="Fixed",$B$13,IF(B21="Award",$B$14,IF(B21="CR",0,NA())))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" s="109">
       <c r="A23" s="117" t="inlineStr">
         <is>
-          <t>This is what Dashboard, Revenue Forecast, and the ROM Calculator (Labor row) use — Total Cost per CLIN times that CLIN's Applicable Fee Rate.</t>
+          <t>This is what Dashboard, Revenue Forecast, and the ROM Calculator (Labor row) use — Total Cost per CLIN times that CLIN's Applicable Fee Rate. CR CLINs always resolve to 0%.</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B18 B19 B20 B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Fixed,Award"</formula1>
+      <formula1>"Fixed,Award,CR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection workbookPassword="B0B1" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Burn Rate Forecast" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FundingMods" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROM Calculator" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_License" sheetId="15" state="veryHidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Projects'!$A$4:$G$13</definedName>
@@ -48,7 +49,7 @@
     <numFmt numFmtId="172" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="173" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -209,6 +210,11 @@
       <i val="1"/>
       <color rgb="FF0F172A"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -575,7 +581,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -910,70 +916,78 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="26" fillId="11" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="11" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="25" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="26" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="25" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="26" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -1014,7 +1028,7 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1036,112 +1050,148 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="29" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="173" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="170" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="169" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="29" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="173" fontId="28" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="170" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="28" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="28" fillId="15" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="15" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="15" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="28" fillId="16" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="16" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="16" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="28" fillId="17" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="17" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="17" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="28" fillId="18" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="18" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="18" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="28" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="17" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="26" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="25" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="29" fillId="15" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="15" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="15" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="29" fillId="16" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="16" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="16" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="29" fillId="17" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="17" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="17" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="29" fillId="18" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="27" fillId="18" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="18" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="29" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="27" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="28" fillId="19" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="26" fillId="11" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="28" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="30" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="31" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="29" fillId="19" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="11" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="29" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="32" fillId="13" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2418,6 +2468,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18.55" customHeight="1" s="109">
       <c r="A4" s="112" t="inlineStr">
         <is>
@@ -2808,6 +2859,7 @@
       <c r="A81" s="113" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="7">
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A28:B28"/>
@@ -2855,6 +2907,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -3206,6 +3259,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -3499,14 +3553,15 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A41" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:G22"/>
   <mergeCells count="1">
     <mergeCell ref="A39:E39"/>
@@ -3566,6 +3621,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -3573,6 +3629,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -3972,6 +4029,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="123" t="inlineStr">
         <is>
@@ -4071,6 +4129,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="136">
         <f>IF(Projects!$A$6="","",Projects!$A$6&amp;" — "&amp;Projects!$B$6)</f>
@@ -4365,6 +4424,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="136">
         <f>IF(Projects!$A$7="","",Projects!$A$7&amp;" — "&amp;Projects!$B$7)</f>
@@ -4659,6 +4719,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="136">
         <f>IF(Projects!$A$8="","",Projects!$A$8&amp;" — "&amp;Projects!$B$8)</f>
@@ -4953,6 +5014,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="136">
         <f>IF(Projects!$A$9="","",Projects!$A$9&amp;" — "&amp;Projects!$B$9)</f>
@@ -5247,6 +5309,7 @@
         <v/>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="136">
         <f>IF(Projects!$A$10="","",Projects!$A$10&amp;" — "&amp;Projects!$B$10)</f>
@@ -5541,6 +5604,7 @@
         <v/>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="136">
         <f>IF(Projects!$A$11="","",Projects!$A$11&amp;" — "&amp;Projects!$B$11)</f>
@@ -5835,6 +5899,7 @@
         <v/>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="136">
         <f>IF(Projects!$A$12="","",Projects!$A$12&amp;" — "&amp;Projects!$B$12)</f>
@@ -6129,6 +6194,7 @@
         <v/>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="136">
         <f>IF(Projects!$A$13="","",Projects!$A$13&amp;" — "&amp;Projects!$B$13)</f>
@@ -6423,6 +6489,8 @@
         <v/>
       </c>
     </row>
+    <row r="62"/>
+    <row r="63"/>
     <row r="64" ht="15" customHeight="1" s="109">
       <c r="A64" s="123" t="inlineStr">
         <is>
@@ -6692,14 +6760,15 @@
       <c r="G80" s="128" t="n"/>
       <c r="H80" s="128" t="n"/>
     </row>
+    <row r="81"/>
     <row r="82">
-      <c r="A82" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A82" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="9">
     <mergeCell ref="A3:R3"/>
     <mergeCell ref="A21:R21"/>
@@ -6755,6 +6824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -6762,6 +6832,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -6892,6 +6963,8 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="123" t="inlineStr">
         <is>
@@ -7844,14 +7917,15 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
-      <c r="A40" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A40" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
   </mergeCells>
@@ -7988,6 +8062,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="48" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -8500,6 +8575,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="123" t="inlineStr">
         <is>
@@ -8703,6 +8779,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="28" customHeight="1" s="109">
       <c r="A24" s="114" t="inlineStr">
         <is>
@@ -8710,14 +8787,15 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A26" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:P14"/>
   <mergeCells count="2">
     <mergeCell ref="A24:P24"/>
@@ -8802,6 +8880,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -8809,6 +8888,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -8823,6 +8903,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1" s="109">
       <c r="A8" s="137" t="inlineStr">
         <is>
@@ -8983,6 +9064,8 @@
       <c r="D23" s="217" t="n"/>
       <c r="E23" s="131" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="123" t="inlineStr">
         <is>
@@ -8997,6 +9080,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -9088,6 +9172,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="123" t="inlineStr">
         <is>
@@ -9102,6 +9187,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -9179,6 +9265,7 @@
         <v/>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="123" t="inlineStr">
         <is>
@@ -9193,6 +9280,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="24" customHeight="1" s="109">
       <c r="A52" s="137" t="inlineStr">
         <is>
@@ -9325,6 +9413,7 @@
         <v/>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="123" t="inlineStr">
         <is>
@@ -9339,6 +9428,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -9394,6 +9484,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="136">
         <f>"For "&amp;B30&amp;" from "&amp;TEXT(B35,"mm/dd/yyyy")&amp;" to "&amp;TEXT(B36,"mm/dd/yyyy")&amp;" ("&amp;B42&amp;" days): "&amp;TEXT(B66,"$#,##0")&amp;" fully burdened, ROM estimate."</f>
@@ -9407,14 +9498,15 @@
         </is>
       </c>
     </row>
+    <row r="70"/>
     <row r="71">
-      <c r="A71" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A71" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="6">
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A50:E50"/>
@@ -9442,6 +9534,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" style="109" min="1" max="1"/>
+    <col width="34" customWidth="1" style="109" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="228" t="inlineStr">
+        <is>
+          <t>Acqlerate — License Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Licensed To (name or org):</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Email:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>License Date:</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="229" t="inlineStr">
+        <is>
+          <t>This workbook is licensed for use by the individual or organization named above. Copyright Acqlerate. Redistribution, resale, or sharing outside that license without Acqlerate's written permission is prohibited.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9472,6 +9620,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -9486,6 +9635,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="124" t="inlineStr">
         <is>
@@ -9546,6 +9696,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="123" t="inlineStr">
         <is>
@@ -9560,6 +9711,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="28" customHeight="1" s="109">
       <c r="A14" s="124" t="inlineStr">
         <is>
@@ -9590,6 +9742,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="117" t="inlineStr"/>
     </row>
@@ -9675,6 +9828,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="28" customHeight="1" s="109">
       <c r="A24" s="117" t="inlineStr">
         <is>
@@ -9682,6 +9836,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="42" customHeight="1" s="109">
       <c r="A26" s="114" t="inlineStr">
         <is>
@@ -9690,6 +9845,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="10">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="C9:F9"/>
@@ -9744,6 +9900,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="30" customFormat="1" customHeight="1" s="130">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -9793,6 +9950,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="128" t="inlineStr">
         <is>
@@ -9937,6 +10095,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="133" t="n"/>
       <c r="B15" s="134" t="inlineStr">
@@ -9965,6 +10124,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="123" t="inlineStr">
         <is>
@@ -9979,6 +10139,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="136">
         <f>IF($A$6="","",$A$6&amp;" — "&amp;$B$6)</f>
@@ -10127,6 +10288,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="136">
         <f>IF($A$7="","",$A$7&amp;" — "&amp;$B$7)</f>
@@ -10275,6 +10437,7 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="136">
         <f>IF($A$8="","",$A$8&amp;" — "&amp;$B$8)</f>
@@ -10423,6 +10586,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="136">
         <f>IF($A$9="","",$A$9&amp;" — "&amp;$B$9)</f>
@@ -10571,6 +10735,7 @@
         <v/>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="136">
         <f>IF($A$10="","",$A$10&amp;" — "&amp;$B$10)</f>
@@ -10719,6 +10884,7 @@
         <v/>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="136">
         <f>IF($A$11="","",$A$11&amp;" — "&amp;$B$11)</f>
@@ -10867,6 +11033,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="136">
         <f>IF($A$12="","",$A$12&amp;" — "&amp;$B$12)</f>
@@ -11015,6 +11182,7 @@
         <v/>
       </c>
     </row>
+    <row r="75"/>
     <row r="76">
       <c r="A76" s="136">
         <f>IF($A$13="","",$A$13&amp;" — "&amp;$B$13)</f>
@@ -11163,14 +11331,16 @@
         <v/>
       </c>
     </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="85">
-      <c r="A85" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A85" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:G13"/>
   <mergeCells count="9">
     <mergeCell ref="A36:G36"/>
@@ -11228,6 +11398,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="118" t="inlineStr">
         <is>
@@ -11305,6 +11476,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="109">
       <c r="A11" s="148" t="inlineStr">
         <is>
@@ -11389,6 +11561,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="33.75" customHeight="1" s="109">
       <c r="A20" s="151" t="inlineStr">
         <is>
@@ -12418,14 +12591,15 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="109">
-      <c r="A34" s="111" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A34" s="120">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A3:B3"/>
@@ -13138,13 +13312,13 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="109">
-      <c r="A21" s="111" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A21" s="120">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="1">
     <mergeCell ref="A20:N20"/>
   </mergeCells>
@@ -13217,6 +13391,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -14060,14 +14235,15 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A22" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="18">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="P4:Q4"/>
@@ -14176,6 +14352,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="117" t="inlineStr">
         <is>
@@ -17652,6 +17829,7 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="123" t="inlineStr">
         <is>
@@ -18211,6 +18389,7 @@
         <v/>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="117" t="inlineStr">
         <is>
@@ -18218,14 +18397,15 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A44" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:G25"/>
   <mergeCells count="23">
     <mergeCell ref="C4:C5"/>
@@ -18377,6 +18557,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -18728,6 +18909,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -19021,14 +19203,15 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A41" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:G22"/>
   <mergeCells count="1">
     <mergeCell ref="A39:E39"/>
@@ -19077,6 +19260,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -19428,6 +19612,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -19721,14 +19906,15 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="117" t="inlineStr">
-        <is>
-          <t>Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com</t>
-        </is>
+      <c r="A41" s="117">
+        <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <autoFilter ref="A4:G22"/>
   <mergeCells count="1">
     <mergeCell ref="A39:E39"/>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -37,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
@@ -45,9 +45,8 @@
     <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="172" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="173" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -395,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -570,6 +569,55 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -581,7 +629,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1076,7 +1124,7 @@
     <xf numFmtId="169" fontId="31" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="173" fontId="29" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="29" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1112,7 +1160,7 @@
     <xf numFmtId="169" fontId="31" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="173" fontId="29" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="29" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1192,6 +1240,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="171" fontId="29" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="171" fontId="29" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1741,26 +1798,9 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.2"/>
-          <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% of CLIN Funding Used</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1844,6 +1884,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1874,6 +1917,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1926,6 +1972,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1956,6 +2005,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1986,6 +2038,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2016,6 +2071,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2046,6 +2104,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2168,6 +2229,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2198,6 +2262,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2228,6 +2295,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2258,6 +2328,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2468,7 +2541,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="18.55" customHeight="1" s="109">
       <c r="A4" s="112" t="inlineStr">
         <is>
@@ -2907,7 +2979,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -3259,7 +3330,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -3553,7 +3623,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -3621,7 +3690,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -3629,7 +3697,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -4029,7 +4096,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="123" t="inlineStr">
         <is>
@@ -4129,7 +4195,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="136">
         <f>IF(Projects!$A$6="","",Projects!$A$6&amp;" — "&amp;Projects!$B$6)</f>
@@ -4424,7 +4489,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="136">
         <f>IF(Projects!$A$7="","",Projects!$A$7&amp;" — "&amp;Projects!$B$7)</f>
@@ -4719,7 +4783,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="136">
         <f>IF(Projects!$A$8="","",Projects!$A$8&amp;" — "&amp;Projects!$B$8)</f>
@@ -5014,7 +5077,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="136">
         <f>IF(Projects!$A$9="","",Projects!$A$9&amp;" — "&amp;Projects!$B$9)</f>
@@ -5309,7 +5371,6 @@
         <v/>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="136">
         <f>IF(Projects!$A$10="","",Projects!$A$10&amp;" — "&amp;Projects!$B$10)</f>
@@ -5604,7 +5665,6 @@
         <v/>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="136">
         <f>IF(Projects!$A$11="","",Projects!$A$11&amp;" — "&amp;Projects!$B$11)</f>
@@ -5899,7 +5959,6 @@
         <v/>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="136">
         <f>IF(Projects!$A$12="","",Projects!$A$12&amp;" — "&amp;Projects!$B$12)</f>
@@ -6194,7 +6253,6 @@
         <v/>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="136">
         <f>IF(Projects!$A$13="","",Projects!$A$13&amp;" — "&amp;Projects!$B$13)</f>
@@ -6489,8 +6547,6 @@
         <v/>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63"/>
     <row r="64" ht="15" customHeight="1" s="109">
       <c r="A64" s="123" t="inlineStr">
         <is>
@@ -6760,7 +6816,6 @@
       <c r="G80" s="128" t="n"/>
       <c r="H80" s="128" t="n"/>
     </row>
-    <row r="81"/>
     <row r="82">
       <c r="A82" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -6824,7 +6879,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -6832,7 +6886,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -6963,8 +7016,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="123" t="inlineStr">
         <is>
@@ -7917,7 +7968,6 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -8062,7 +8112,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="48" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -8575,7 +8624,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="123" t="inlineStr">
         <is>
@@ -8779,7 +8827,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="28" customHeight="1" s="109">
       <c r="A24" s="114" t="inlineStr">
         <is>
@@ -8787,7 +8834,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -8880,7 +8926,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -8888,7 +8933,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="123" t="inlineStr">
         <is>
@@ -8903,7 +8947,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="24" customHeight="1" s="109">
       <c r="A8" s="137" t="inlineStr">
         <is>
@@ -9064,8 +9107,6 @@
       <c r="D23" s="217" t="n"/>
       <c r="E23" s="131" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="123" t="inlineStr">
         <is>
@@ -9080,9 +9121,8 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="108" t="inlineStr">
         <is>
           <t>Duty Location</t>
         </is>
@@ -9095,7 +9135,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="108" t="inlineStr">
         <is>
           <t>Role / LCAT</t>
         </is>
@@ -9107,7 +9147,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="108" t="inlineStr">
         <is>
           <t>Employee Type</t>
         </is>
@@ -9119,7 +9159,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="108" t="inlineStr">
         <is>
           <t>Annual Salary (Exempt only)</t>
         </is>
@@ -9129,7 +9169,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="108" t="inlineStr">
         <is>
           <t>Direct Hourly Rate (Non-Exempt only)</t>
         </is>
@@ -9137,7 +9177,7 @@
       <c r="B33" s="218" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="108" t="inlineStr">
         <is>
           <t>Standard Annual Hours</t>
         </is>
@@ -9147,7 +9187,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="108" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
@@ -9157,7 +9197,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="108" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
@@ -9172,7 +9212,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="123" t="inlineStr">
         <is>
@@ -9187,9 +9226,8 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="108" t="inlineStr">
         <is>
           <t>Straight-Time Rate $/hr</t>
         </is>
@@ -9200,7 +9238,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="108" t="inlineStr">
         <is>
           <t>Days in Period</t>
         </is>
@@ -9211,7 +9249,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="108" t="inlineStr">
         <is>
           <t>Estimated Hours in Period</t>
         </is>
@@ -9222,7 +9260,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="108" t="inlineStr">
         <is>
           <t>Direct Labor $</t>
         </is>
@@ -9233,7 +9271,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="108" t="inlineStr">
         <is>
           <t>Fringe $</t>
         </is>
@@ -9244,7 +9282,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="108" t="inlineStr">
         <is>
           <t>OH $</t>
         </is>
@@ -9265,7 +9303,6 @@
         <v/>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="123" t="inlineStr">
         <is>
@@ -9280,7 +9317,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52" ht="24" customHeight="1" s="109">
       <c r="A52" s="137" t="inlineStr">
         <is>
@@ -9413,7 +9449,6 @@
         <v/>
       </c>
     </row>
-    <row r="58"/>
     <row r="59">
       <c r="A59" s="123" t="inlineStr">
         <is>
@@ -9428,9 +9463,8 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="108" t="inlineStr">
         <is>
           <t>Subtotal (Labor + Adders) $</t>
         </is>
@@ -9441,7 +9475,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="108" t="inlineStr">
         <is>
           <t>G&amp;A $</t>
         </is>
@@ -9452,7 +9486,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="108" t="inlineStr">
         <is>
           <t>Total Cost $</t>
         </is>
@@ -9463,7 +9497,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="108" t="inlineStr">
         <is>
           <t>Fee $</t>
         </is>
@@ -9484,7 +9518,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="136">
         <f>"For "&amp;B30&amp;" from "&amp;TEXT(B35,"mm/dd/yyyy")&amp;" to "&amp;TEXT(B36,"mm/dd/yyyy")&amp;" ("&amp;B42&amp;" days): "&amp;TEXT(B66,"$#,##0")&amp;" fully burdened, ROM estimate."</f>
@@ -9498,7 +9531,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -9555,28 +9587,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="108" t="inlineStr">
         <is>
           <t>Licensed To (name or org):</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="108" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Email:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" s="108" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>License Date:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" s="108" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="229" t="inlineStr">
@@ -9620,7 +9652,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -9635,7 +9666,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="124" t="inlineStr">
         <is>
@@ -9677,7 +9707,7 @@
       </c>
       <c r="C8" s="114" t="inlineStr">
         <is>
-          <t>Applied to PRIME-sourced cost only: Prime fully burdened labor + Prime-bought Travel/ODC/M&amp;E. Covers company-wide G&amp;A: executive, finance, HR, business development.</t>
+          <t>Applied to Prime-sourced cost (fully burdened labor + Prime-bought Travel/ODC/M&amp;E) AND to Sub-sourced Travel/ODC/M&amp;E after the M&amp;S markup (below) is added to it. Covers company-wide G&amp;A: executive, finance, HR, business development.</t>
         </is>
       </c>
     </row>
@@ -9692,11 +9722,10 @@
       </c>
       <c r="C9" s="114" t="inlineStr">
         <is>
-          <t>Applied to SUB-sourced Travel/ODC/M&amp;E only — not Sub labor, which passes through at raw cost. Your Sub already carries their own G&amp;A in what they bill you, so this is a smaller subcontract administration/handling markup, not a second G&amp;A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Applied to SUB-sourced Travel/ODC/M&amp;E only — not Sub labor, which passes through at raw cost. This is a subcontract administration/handling markup. G&amp;A (above) is then charged on top of Sub cost plus this M&amp;S markup, the same way it's charged on Prime cost.</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="123" t="inlineStr">
         <is>
@@ -9711,7 +9740,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="28" customHeight="1" s="109">
       <c r="A14" s="124" t="inlineStr">
         <is>
@@ -9742,7 +9770,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="117" t="inlineStr"/>
     </row>
@@ -9828,7 +9855,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="28" customHeight="1" s="109">
       <c r="A24" s="117" t="inlineStr">
         <is>
@@ -9836,7 +9862,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="42" customHeight="1" s="109">
       <c r="A26" s="114" t="inlineStr">
         <is>
@@ -9900,7 +9925,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customFormat="1" customHeight="1" s="130">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -9950,7 +9974,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="128" t="inlineStr">
         <is>
@@ -10095,7 +10118,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="133" t="n"/>
       <c r="B15" s="134" t="inlineStr">
@@ -10124,7 +10146,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="123" t="inlineStr">
         <is>
@@ -10139,7 +10160,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="136">
         <f>IF($A$6="","",$A$6&amp;" — "&amp;$B$6)</f>
@@ -10288,7 +10308,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="136">
         <f>IF($A$7="","",$A$7&amp;" — "&amp;$B$7)</f>
@@ -10437,7 +10456,6 @@
         <v/>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="136">
         <f>IF($A$8="","",$A$8&amp;" — "&amp;$B$8)</f>
@@ -10586,7 +10604,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="136">
         <f>IF($A$9="","",$A$9&amp;" — "&amp;$B$9)</f>
@@ -10735,7 +10752,6 @@
         <v/>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="136">
         <f>IF($A$10="","",$A$10&amp;" — "&amp;$B$10)</f>
@@ -10884,7 +10900,6 @@
         <v/>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="136">
         <f>IF($A$11="","",$A$11&amp;" — "&amp;$B$11)</f>
@@ -11033,7 +11048,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="136">
         <f>IF($A$12="","",$A$12&amp;" — "&amp;$B$12)</f>
@@ -11182,7 +11196,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="136">
         <f>IF($A$13="","",$A$13&amp;" — "&amp;$B$13)</f>
@@ -11331,8 +11344,6 @@
         <v/>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -11398,7 +11409,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="118" t="inlineStr">
         <is>
@@ -11476,7 +11486,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="109">
       <c r="A11" s="148" t="inlineStr">
         <is>
@@ -11561,7 +11570,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20" ht="33.75" customHeight="1" s="109">
       <c r="A20" s="151" t="inlineStr">
         <is>
@@ -11700,7 +11708,7 @@
         <v/>
       </c>
       <c r="I21" s="155">
-        <f>IF(H21="","",Q21*Rates!$B$8)</f>
+        <f>IF(H21="","",(Q21+R21+S21)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J21" s="154">
@@ -11708,7 +11716,7 @@
         <v/>
       </c>
       <c r="K21" s="155">
-        <f>IF(H21="","",(Labor!F29+IFERROR(Labor!F29/Q21*I21,0)+Labor!G29)*Rates!$C$19+(Travel!D27+IFERROR(Travel!D27/Q21*I21,0)+Travel!E27+IFERROR(Travel!E27/R21*S21,0))*Rates!$C$20+(ODCs!D27+IFERROR(ODCs!D27/Q21*I21,0)+ODCs!E27+IFERROR(ODCs!E27/R21*S21,0))*Rates!$C$21+('M&amp;E'!D27+IFERROR('M&amp;E'!D27/Q21*I21,0)+'M&amp;E'!E27+IFERROR('M&amp;E'!E27/R21*S21,0))*Rates!$C$22)</f>
+        <f>IF(H21="","",(Labor!F29+IFERROR(Labor!F29/(Q21+R21+S21)*I21,0)+Labor!G29)*Rates!$C$19+(Travel!D27+IFERROR(Travel!D27/(Q21+R21+S21)*I21,0)+Travel!E27+IFERROR(Travel!E27/R21*S21,0)+IFERROR((Travel!E27+Travel!E27/R21*S21)/(Q21+R21+S21)*I21,0))*Rates!$C$20+(ODCs!D27+IFERROR(ODCs!D27/(Q21+R21+S21)*I21,0)+ODCs!E27+IFERROR(ODCs!E27/R21*S21,0)+IFERROR((ODCs!E27+ODCs!E27/R21*S21)/(Q21+R21+S21)*I21,0))*Rates!$C$21+('M&amp;E'!D27+IFERROR('M&amp;E'!D27/(Q21+R21+S21)*I21,0)+'M&amp;E'!E27+IFERROR('M&amp;E'!E27/R21*S21,0)+IFERROR(('M&amp;E'!E27+'M&amp;E'!E27/R21*S21)/(Q21+R21+S21)*I21,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L21" s="154">
@@ -11777,7 +11785,7 @@
         <v/>
       </c>
       <c r="I22" s="162">
-        <f>IF(H22="","",Q22*Rates!$B$8)</f>
+        <f>IF(H22="","",(Q22+R22+S22)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J22" s="161">
@@ -11785,7 +11793,7 @@
         <v/>
       </c>
       <c r="K22" s="162">
-        <f>IF(H22="","",(Labor!F30+IFERROR(Labor!F30/Q22*I22,0)+Labor!G30)*Rates!$C$19+(Travel!D28+IFERROR(Travel!D28/Q22*I22,0)+Travel!E28+IFERROR(Travel!E28/R22*S22,0))*Rates!$C$20+(ODCs!D28+IFERROR(ODCs!D28/Q22*I22,0)+ODCs!E28+IFERROR(ODCs!E28/R22*S22,0))*Rates!$C$21+('M&amp;E'!D28+IFERROR('M&amp;E'!D28/Q22*I22,0)+'M&amp;E'!E28+IFERROR('M&amp;E'!E28/R22*S22,0))*Rates!$C$22)</f>
+        <f>IF(H22="","",(Labor!F30+IFERROR(Labor!F30/(Q22+R22+S22)*I22,0)+Labor!G30)*Rates!$C$19+(Travel!D28+IFERROR(Travel!D28/(Q22+R22+S22)*I22,0)+Travel!E28+IFERROR(Travel!E28/R22*S22,0)+IFERROR((Travel!E28+Travel!E28/R22*S22)/(Q22+R22+S22)*I22,0))*Rates!$C$20+(ODCs!D28+IFERROR(ODCs!D28/(Q22+R22+S22)*I22,0)+ODCs!E28+IFERROR(ODCs!E28/R22*S22,0)+IFERROR((ODCs!E28+ODCs!E28/R22*S22)/(Q22+R22+S22)*I22,0))*Rates!$C$21+('M&amp;E'!D28+IFERROR('M&amp;E'!D28/(Q22+R22+S22)*I22,0)+'M&amp;E'!E28+IFERROR('M&amp;E'!E28/R22*S22,0)+IFERROR(('M&amp;E'!E28+'M&amp;E'!E28/R22*S22)/(Q22+R22+S22)*I22,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L22" s="161">
@@ -11854,7 +11862,7 @@
         <v/>
       </c>
       <c r="I23" s="155">
-        <f>IF(H23="","",Q23*Rates!$B$8)</f>
+        <f>IF(H23="","",(Q23+R23+S23)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J23" s="154">
@@ -11862,7 +11870,7 @@
         <v/>
       </c>
       <c r="K23" s="155">
-        <f>IF(H23="","",(Labor!F31+IFERROR(Labor!F31/Q23*I23,0)+Labor!G31)*Rates!$C$19+(Travel!D29+IFERROR(Travel!D29/Q23*I23,0)+Travel!E29+IFERROR(Travel!E29/R23*S23,0))*Rates!$C$20+(ODCs!D29+IFERROR(ODCs!D29/Q23*I23,0)+ODCs!E29+IFERROR(ODCs!E29/R23*S23,0))*Rates!$C$21+('M&amp;E'!D29+IFERROR('M&amp;E'!D29/Q23*I23,0)+'M&amp;E'!E29+IFERROR('M&amp;E'!E29/R23*S23,0))*Rates!$C$22)</f>
+        <f>IF(H23="","",(Labor!F31+IFERROR(Labor!F31/(Q23+R23+S23)*I23,0)+Labor!G31)*Rates!$C$19+(Travel!D29+IFERROR(Travel!D29/(Q23+R23+S23)*I23,0)+Travel!E29+IFERROR(Travel!E29/R23*S23,0)+IFERROR((Travel!E29+Travel!E29/R23*S23)/(Q23+R23+S23)*I23,0))*Rates!$C$20+(ODCs!D29+IFERROR(ODCs!D29/(Q23+R23+S23)*I23,0)+ODCs!E29+IFERROR(ODCs!E29/R23*S23,0)+IFERROR((ODCs!E29+ODCs!E29/R23*S23)/(Q23+R23+S23)*I23,0))*Rates!$C$21+('M&amp;E'!D29+IFERROR('M&amp;E'!D29/(Q23+R23+S23)*I23,0)+'M&amp;E'!E29+IFERROR('M&amp;E'!E29/R23*S23,0)+IFERROR(('M&amp;E'!E29+'M&amp;E'!E29/R23*S23)/(Q23+R23+S23)*I23,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L23" s="154">
@@ -11931,7 +11939,7 @@
         <v/>
       </c>
       <c r="I24" s="162">
-        <f>IF(H24="","",Q24*Rates!$B$8)</f>
+        <f>IF(H24="","",(Q24+R24+S24)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J24" s="161">
@@ -11939,7 +11947,7 @@
         <v/>
       </c>
       <c r="K24" s="162">
-        <f>IF(H24="","",(Labor!F32+IFERROR(Labor!F32/Q24*I24,0)+Labor!G32)*Rates!$C$19+(Travel!D30+IFERROR(Travel!D30/Q24*I24,0)+Travel!E30+IFERROR(Travel!E30/R24*S24,0))*Rates!$C$20+(ODCs!D30+IFERROR(ODCs!D30/Q24*I24,0)+ODCs!E30+IFERROR(ODCs!E30/R24*S24,0))*Rates!$C$21+('M&amp;E'!D30+IFERROR('M&amp;E'!D30/Q24*I24,0)+'M&amp;E'!E30+IFERROR('M&amp;E'!E30/R24*S24,0))*Rates!$C$22)</f>
+        <f>IF(H24="","",(Labor!F32+IFERROR(Labor!F32/(Q24+R24+S24)*I24,0)+Labor!G32)*Rates!$C$19+(Travel!D30+IFERROR(Travel!D30/(Q24+R24+S24)*I24,0)+Travel!E30+IFERROR(Travel!E30/R24*S24,0)+IFERROR((Travel!E30+Travel!E30/R24*S24)/(Q24+R24+S24)*I24,0))*Rates!$C$20+(ODCs!D30+IFERROR(ODCs!D30/(Q24+R24+S24)*I24,0)+ODCs!E30+IFERROR(ODCs!E30/R24*S24,0)+IFERROR((ODCs!E30+ODCs!E30/R24*S24)/(Q24+R24+S24)*I24,0))*Rates!$C$21+('M&amp;E'!D30+IFERROR('M&amp;E'!D30/(Q24+R24+S24)*I24,0)+'M&amp;E'!E30+IFERROR('M&amp;E'!E30/R24*S24,0)+IFERROR(('M&amp;E'!E30+'M&amp;E'!E30/R24*S24)/(Q24+R24+S24)*I24,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L24" s="161">
@@ -12008,7 +12016,7 @@
         <v/>
       </c>
       <c r="I25" s="155">
-        <f>IF(H25="","",Q25*Rates!$B$8)</f>
+        <f>IF(H25="","",(Q25+R25+S25)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J25" s="154">
@@ -12016,7 +12024,7 @@
         <v/>
       </c>
       <c r="K25" s="155">
-        <f>IF(H25="","",(Labor!F33+IFERROR(Labor!F33/Q25*I25,0)+Labor!G33)*Rates!$C$19+(Travel!D31+IFERROR(Travel!D31/Q25*I25,0)+Travel!E31+IFERROR(Travel!E31/R25*S25,0))*Rates!$C$20+(ODCs!D31+IFERROR(ODCs!D31/Q25*I25,0)+ODCs!E31+IFERROR(ODCs!E31/R25*S25,0))*Rates!$C$21+('M&amp;E'!D31+IFERROR('M&amp;E'!D31/Q25*I25,0)+'M&amp;E'!E31+IFERROR('M&amp;E'!E31/R25*S25,0))*Rates!$C$22)</f>
+        <f>IF(H25="","",(Labor!F33+IFERROR(Labor!F33/(Q25+R25+S25)*I25,0)+Labor!G33)*Rates!$C$19+(Travel!D31+IFERROR(Travel!D31/(Q25+R25+S25)*I25,0)+Travel!E31+IFERROR(Travel!E31/R25*S25,0)+IFERROR((Travel!E31+Travel!E31/R25*S25)/(Q25+R25+S25)*I25,0))*Rates!$C$20+(ODCs!D31+IFERROR(ODCs!D31/(Q25+R25+S25)*I25,0)+ODCs!E31+IFERROR(ODCs!E31/R25*S25,0)+IFERROR((ODCs!E31+ODCs!E31/R25*S25)/(Q25+R25+S25)*I25,0))*Rates!$C$21+('M&amp;E'!D31+IFERROR('M&amp;E'!D31/(Q25+R25+S25)*I25,0)+'M&amp;E'!E31+IFERROR('M&amp;E'!E31/R25*S25,0)+IFERROR(('M&amp;E'!E31+'M&amp;E'!E31/R25*S25)/(Q25+R25+S25)*I25,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L25" s="154">
@@ -12085,7 +12093,7 @@
         <v/>
       </c>
       <c r="I26" s="162">
-        <f>IF(H26="","",Q26*Rates!$B$8)</f>
+        <f>IF(H26="","",(Q26+R26+S26)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J26" s="161">
@@ -12093,7 +12101,7 @@
         <v/>
       </c>
       <c r="K26" s="162">
-        <f>IF(H26="","",(Labor!F34+IFERROR(Labor!F34/Q26*I26,0)+Labor!G34)*Rates!$C$19+(Travel!D32+IFERROR(Travel!D32/Q26*I26,0)+Travel!E32+IFERROR(Travel!E32/R26*S26,0))*Rates!$C$20+(ODCs!D32+IFERROR(ODCs!D32/Q26*I26,0)+ODCs!E32+IFERROR(ODCs!E32/R26*S26,0))*Rates!$C$21+('M&amp;E'!D32+IFERROR('M&amp;E'!D32/Q26*I26,0)+'M&amp;E'!E32+IFERROR('M&amp;E'!E32/R26*S26,0))*Rates!$C$22)</f>
+        <f>IF(H26="","",(Labor!F34+IFERROR(Labor!F34/(Q26+R26+S26)*I26,0)+Labor!G34)*Rates!$C$19+(Travel!D32+IFERROR(Travel!D32/(Q26+R26+S26)*I26,0)+Travel!E32+IFERROR(Travel!E32/R26*S26,0)+IFERROR((Travel!E32+Travel!E32/R26*S26)/(Q26+R26+S26)*I26,0))*Rates!$C$20+(ODCs!D32+IFERROR(ODCs!D32/(Q26+R26+S26)*I26,0)+ODCs!E32+IFERROR(ODCs!E32/R26*S26,0)+IFERROR((ODCs!E32+ODCs!E32/R26*S26)/(Q26+R26+S26)*I26,0))*Rates!$C$21+('M&amp;E'!D32+IFERROR('M&amp;E'!D32/(Q26+R26+S26)*I26,0)+'M&amp;E'!E32+IFERROR('M&amp;E'!E32/R26*S26,0)+IFERROR(('M&amp;E'!E32+'M&amp;E'!E32/R26*S26)/(Q26+R26+S26)*I26,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L26" s="161">
@@ -12162,7 +12170,7 @@
         <v/>
       </c>
       <c r="I27" s="155">
-        <f>IF(H27="","",Q27*Rates!$B$8)</f>
+        <f>IF(H27="","",(Q27+R27+S27)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J27" s="154">
@@ -12170,7 +12178,7 @@
         <v/>
       </c>
       <c r="K27" s="155">
-        <f>IF(H27="","",(Labor!F35+IFERROR(Labor!F35/Q27*I27,0)+Labor!G35)*Rates!$C$19+(Travel!D33+IFERROR(Travel!D33/Q27*I27,0)+Travel!E33+IFERROR(Travel!E33/R27*S27,0))*Rates!$C$20+(ODCs!D33+IFERROR(ODCs!D33/Q27*I27,0)+ODCs!E33+IFERROR(ODCs!E33/R27*S27,0))*Rates!$C$21+('M&amp;E'!D33+IFERROR('M&amp;E'!D33/Q27*I27,0)+'M&amp;E'!E33+IFERROR('M&amp;E'!E33/R27*S27,0))*Rates!$C$22)</f>
+        <f>IF(H27="","",(Labor!F35+IFERROR(Labor!F35/(Q27+R27+S27)*I27,0)+Labor!G35)*Rates!$C$19+(Travel!D33+IFERROR(Travel!D33/(Q27+R27+S27)*I27,0)+Travel!E33+IFERROR(Travel!E33/R27*S27,0)+IFERROR((Travel!E33+Travel!E33/R27*S27)/(Q27+R27+S27)*I27,0))*Rates!$C$20+(ODCs!D33+IFERROR(ODCs!D33/(Q27+R27+S27)*I27,0)+ODCs!E33+IFERROR(ODCs!E33/R27*S27,0)+IFERROR((ODCs!E33+ODCs!E33/R27*S27)/(Q27+R27+S27)*I27,0))*Rates!$C$21+('M&amp;E'!D33+IFERROR('M&amp;E'!D33/(Q27+R27+S27)*I27,0)+'M&amp;E'!E33+IFERROR('M&amp;E'!E33/R27*S27,0)+IFERROR(('M&amp;E'!E33+'M&amp;E'!E33/R27*S27)/(Q27+R27+S27)*I27,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L27" s="154">
@@ -12239,7 +12247,7 @@
         <v/>
       </c>
       <c r="I28" s="162">
-        <f>IF(H28="","",Q28*Rates!$B$8)</f>
+        <f>IF(H28="","",(Q28+R28+S28)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J28" s="161">
@@ -12247,7 +12255,7 @@
         <v/>
       </c>
       <c r="K28" s="162">
-        <f>IF(H28="","",(Labor!F36+IFERROR(Labor!F36/Q28*I28,0)+Labor!G36)*Rates!$C$19+(Travel!D34+IFERROR(Travel!D34/Q28*I28,0)+Travel!E34+IFERROR(Travel!E34/R28*S28,0))*Rates!$C$20+(ODCs!D34+IFERROR(ODCs!D34/Q28*I28,0)+ODCs!E34+IFERROR(ODCs!E34/R28*S28,0))*Rates!$C$21+('M&amp;E'!D34+IFERROR('M&amp;E'!D34/Q28*I28,0)+'M&amp;E'!E34+IFERROR('M&amp;E'!E34/R28*S28,0))*Rates!$C$22)</f>
+        <f>IF(H28="","",(Labor!F36+IFERROR(Labor!F36/(Q28+R28+S28)*I28,0)+Labor!G36)*Rates!$C$19+(Travel!D34+IFERROR(Travel!D34/(Q28+R28+S28)*I28,0)+Travel!E34+IFERROR(Travel!E34/R28*S28,0)+IFERROR((Travel!E34+Travel!E34/R28*S28)/(Q28+R28+S28)*I28,0))*Rates!$C$20+(ODCs!D34+IFERROR(ODCs!D34/(Q28+R28+S28)*I28,0)+ODCs!E34+IFERROR(ODCs!E34/R28*S28,0)+IFERROR((ODCs!E34+ODCs!E34/R28*S28)/(Q28+R28+S28)*I28,0))*Rates!$C$21+('M&amp;E'!D34+IFERROR('M&amp;E'!D34/(Q28+R28+S28)*I28,0)+'M&amp;E'!E34+IFERROR('M&amp;E'!E34/R28*S28,0)+IFERROR(('M&amp;E'!E34+'M&amp;E'!E34/R28*S28)/(Q28+R28+S28)*I28,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L28" s="161">
@@ -12316,7 +12324,7 @@
         <v/>
       </c>
       <c r="I29" s="155">
-        <f>IF(H29="","",Q29*Rates!$B$8)</f>
+        <f>IF(H29="","",(Q29+R29+S29)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J29" s="154">
@@ -12324,7 +12332,7 @@
         <v/>
       </c>
       <c r="K29" s="155">
-        <f>IF(H29="","",(Labor!F37+IFERROR(Labor!F37/Q29*I29,0)+Labor!G37)*Rates!$C$19+(Travel!D35+IFERROR(Travel!D35/Q29*I29,0)+Travel!E35+IFERROR(Travel!E35/R29*S29,0))*Rates!$C$20+(ODCs!D35+IFERROR(ODCs!D35/Q29*I29,0)+ODCs!E35+IFERROR(ODCs!E35/R29*S29,0))*Rates!$C$21+('M&amp;E'!D35+IFERROR('M&amp;E'!D35/Q29*I29,0)+'M&amp;E'!E35+IFERROR('M&amp;E'!E35/R29*S29,0))*Rates!$C$22)</f>
+        <f>IF(H29="","",(Labor!F37+IFERROR(Labor!F37/(Q29+R29+S29)*I29,0)+Labor!G37)*Rates!$C$19+(Travel!D35+IFERROR(Travel!D35/(Q29+R29+S29)*I29,0)+Travel!E35+IFERROR(Travel!E35/R29*S29,0)+IFERROR((Travel!E35+Travel!E35/R29*S29)/(Q29+R29+S29)*I29,0))*Rates!$C$20+(ODCs!D35+IFERROR(ODCs!D35/(Q29+R29+S29)*I29,0)+ODCs!E35+IFERROR(ODCs!E35/R29*S29,0)+IFERROR((ODCs!E35+ODCs!E35/R29*S29)/(Q29+R29+S29)*I29,0))*Rates!$C$21+('M&amp;E'!D35+IFERROR('M&amp;E'!D35/(Q29+R29+S29)*I29,0)+'M&amp;E'!E35+IFERROR('M&amp;E'!E35/R29*S29,0)+IFERROR(('M&amp;E'!E35+'M&amp;E'!E35/R29*S29)/(Q29+R29+S29)*I29,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L29" s="154">
@@ -12393,7 +12401,7 @@
         <v/>
       </c>
       <c r="I30" s="162">
-        <f>IF(H30="","",Q30*Rates!$B$8)</f>
+        <f>IF(H30="","",(Q30+R30+S30)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J30" s="161">
@@ -12401,7 +12409,7 @@
         <v/>
       </c>
       <c r="K30" s="162">
-        <f>IF(H30="","",(Labor!F38+IFERROR(Labor!F38/Q30*I30,0)+Labor!G38)*Rates!$C$19+(Travel!D36+IFERROR(Travel!D36/Q30*I30,0)+Travel!E36+IFERROR(Travel!E36/R30*S30,0))*Rates!$C$20+(ODCs!D36+IFERROR(ODCs!D36/Q30*I30,0)+ODCs!E36+IFERROR(ODCs!E36/R30*S30,0))*Rates!$C$21+('M&amp;E'!D36+IFERROR('M&amp;E'!D36/Q30*I30,0)+'M&amp;E'!E36+IFERROR('M&amp;E'!E36/R30*S30,0))*Rates!$C$22)</f>
+        <f>IF(H30="","",(Labor!F38+IFERROR(Labor!F38/(Q30+R30+S30)*I30,0)+Labor!G38)*Rates!$C$19+(Travel!D36+IFERROR(Travel!D36/(Q30+R30+S30)*I30,0)+Travel!E36+IFERROR(Travel!E36/R30*S30,0)+IFERROR((Travel!E36+Travel!E36/R30*S30)/(Q30+R30+S30)*I30,0))*Rates!$C$20+(ODCs!D36+IFERROR(ODCs!D36/(Q30+R30+S30)*I30,0)+ODCs!E36+IFERROR(ODCs!E36/R30*S30,0)+IFERROR((ODCs!E36+ODCs!E36/R30*S30)/(Q30+R30+S30)*I30,0))*Rates!$C$21+('M&amp;E'!D36+IFERROR('M&amp;E'!D36/(Q30+R30+S30)*I30,0)+'M&amp;E'!E36+IFERROR('M&amp;E'!E36/R30*S30,0)+IFERROR(('M&amp;E'!E36+'M&amp;E'!E36/R30*S30)/(Q30+R30+S30)*I30,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L30" s="161">
@@ -12470,7 +12478,7 @@
         <v/>
       </c>
       <c r="I31" s="155">
-        <f>IF(H31="","",Q31*Rates!$B$8)</f>
+        <f>IF(H31="","",(Q31+R31+S31)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J31" s="154">
@@ -12478,7 +12486,7 @@
         <v/>
       </c>
       <c r="K31" s="155">
-        <f>IF(H31="","",(Labor!F39+IFERROR(Labor!F39/Q31*I31,0)+Labor!G39)*Rates!$C$19+(Travel!D37+IFERROR(Travel!D37/Q31*I31,0)+Travel!E37+IFERROR(Travel!E37/R31*S31,0))*Rates!$C$20+(ODCs!D37+IFERROR(ODCs!D37/Q31*I31,0)+ODCs!E37+IFERROR(ODCs!E37/R31*S31,0))*Rates!$C$21+('M&amp;E'!D37+IFERROR('M&amp;E'!D37/Q31*I31,0)+'M&amp;E'!E37+IFERROR('M&amp;E'!E37/R31*S31,0))*Rates!$C$22)</f>
+        <f>IF(H31="","",(Labor!F39+IFERROR(Labor!F39/(Q31+R31+S31)*I31,0)+Labor!G39)*Rates!$C$19+(Travel!D37+IFERROR(Travel!D37/(Q31+R31+S31)*I31,0)+Travel!E37+IFERROR(Travel!E37/R31*S31,0)+IFERROR((Travel!E37+Travel!E37/R31*S31)/(Q31+R31+S31)*I31,0))*Rates!$C$20+(ODCs!D37+IFERROR(ODCs!D37/(Q31+R31+S31)*I31,0)+ODCs!E37+IFERROR(ODCs!E37/R31*S31,0)+IFERROR((ODCs!E37+ODCs!E37/R31*S31)/(Q31+R31+S31)*I31,0))*Rates!$C$21+('M&amp;E'!D37+IFERROR('M&amp;E'!D37/(Q31+R31+S31)*I31,0)+'M&amp;E'!E37+IFERROR('M&amp;E'!E37/R31*S31,0)+IFERROR(('M&amp;E'!E37+'M&amp;E'!E37/R31*S31)/(Q31+R31+S31)*I31,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L31" s="154">
@@ -12547,7 +12555,7 @@
         <v/>
       </c>
       <c r="I32" s="162">
-        <f>IF(H32="","",Q32*Rates!$B$8)</f>
+        <f>IF(H32="","",(Q32+R32+S32)*Rates!$B$8)</f>
         <v/>
       </c>
       <c r="J32" s="161">
@@ -12555,7 +12563,7 @@
         <v/>
       </c>
       <c r="K32" s="162">
-        <f>IF(H32="","",(Labor!F40+IFERROR(Labor!F40/Q32*I32,0)+Labor!G40)*Rates!$C$19+(Travel!D38+IFERROR(Travel!D38/Q32*I32,0)+Travel!E38+IFERROR(Travel!E38/R32*S32,0))*Rates!$C$20+(ODCs!D38+IFERROR(ODCs!D38/Q32*I32,0)+ODCs!E38+IFERROR(ODCs!E38/R32*S32,0))*Rates!$C$21+('M&amp;E'!D38+IFERROR('M&amp;E'!D38/Q32*I32,0)+'M&amp;E'!E38+IFERROR('M&amp;E'!E38/R32*S32,0))*Rates!$C$22)</f>
+        <f>IF(H32="","",(Labor!F40+IFERROR(Labor!F40/(Q32+R32+S32)*I32,0)+Labor!G40)*Rates!$C$19+(Travel!D38+IFERROR(Travel!D38/(Q32+R32+S32)*I32,0)+Travel!E38+IFERROR(Travel!E38/R32*S32,0)+IFERROR((Travel!E38+Travel!E38/R32*S32)/(Q32+R32+S32)*I32,0))*Rates!$C$20+(ODCs!D38+IFERROR(ODCs!D38/(Q32+R32+S32)*I32,0)+ODCs!E38+IFERROR(ODCs!E38/R32*S32,0)+IFERROR((ODCs!E38+ODCs!E38/R32*S32)/(Q32+R32+S32)*I32,0))*Rates!$C$21+('M&amp;E'!D38+IFERROR('M&amp;E'!D38/(Q32+R32+S32)*I32,0)+'M&amp;E'!E38+IFERROR('M&amp;E'!E38/R32*S32,0)+IFERROR(('M&amp;E'!E38+'M&amp;E'!E38/R32*S32)/(Q32+R32+S32)*I32,0))*Rates!$C$22)</f>
         <v/>
       </c>
       <c r="L32" s="161">
@@ -12591,7 +12599,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="109">
       <c r="A34" s="120">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -12667,7 +12674,6 @@
       </c>
       <c r="P1" s="142" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="165" t="inlineStr">
         <is>
@@ -12805,7 +12811,7 @@
         <f>IF(A5="","",IF(L5="Prime",H5*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H5))</f>
         <v/>
       </c>
-      <c r="N5" s="173">
+      <c r="N5" s="230">
         <f>IF(A5="","",IF(H5="","",IFERROR(M5/H5,"")))</f>
         <v/>
       </c>
@@ -12859,7 +12865,7 @@
         <f>IF(A6="","",IF(L6="Prime",H6*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H6))</f>
         <v/>
       </c>
-      <c r="N6" s="183">
+      <c r="N6" s="231">
         <f>IF(A6="","",IF(H6="","",IFERROR(M6/H6,"")))</f>
         <v/>
       </c>
@@ -12913,7 +12919,7 @@
         <f>IF(A7="","",IF(L7="Prime",H7*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H7))</f>
         <v/>
       </c>
-      <c r="N7" s="173">
+      <c r="N7" s="230">
         <f>IF(A7="","",IF(H7="","",IFERROR(M7/H7,"")))</f>
         <v/>
       </c>
@@ -12945,7 +12951,7 @@
         <f>IF(A8="","",IF(L8="Prime",H8*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H8))</f>
         <v/>
       </c>
-      <c r="N8" s="183">
+      <c r="N8" s="231">
         <f>IF(A8="","",IF(H8="","",IFERROR(M8/H8,"")))</f>
         <v/>
       </c>
@@ -12977,7 +12983,7 @@
         <f>IF(A9="","",IF(L9="Prime",H9*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H9))</f>
         <v/>
       </c>
-      <c r="N9" s="173">
+      <c r="N9" s="230">
         <f>IF(A9="","",IF(H9="","",IFERROR(M9/H9,"")))</f>
         <v/>
       </c>
@@ -13009,7 +13015,7 @@
         <f>IF(A10="","",IF(L10="Prime",H10*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H10))</f>
         <v/>
       </c>
-      <c r="N10" s="183">
+      <c r="N10" s="231">
         <f>IF(A10="","",IF(H10="","",IFERROR(M10/H10,"")))</f>
         <v/>
       </c>
@@ -13041,7 +13047,7 @@
         <f>IF(A11="","",IF(L11="Prime",H11*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H11))</f>
         <v/>
       </c>
-      <c r="N11" s="173">
+      <c r="N11" s="230">
         <f>IF(A11="","",IF(H11="","",IFERROR(M11/H11,"")))</f>
         <v/>
       </c>
@@ -13073,7 +13079,7 @@
         <f>IF(A12="","",IF(L12="Prime",H12*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H12))</f>
         <v/>
       </c>
-      <c r="N12" s="183">
+      <c r="N12" s="231">
         <f>IF(A12="","",IF(H12="","",IFERROR(M12/H12,"")))</f>
         <v/>
       </c>
@@ -13105,7 +13111,7 @@
         <f>IF(A13="","",IF(L13="Prime",H13*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H13))</f>
         <v/>
       </c>
-      <c r="N13" s="173">
+      <c r="N13" s="230">
         <f>IF(A13="","",IF(H13="","",IFERROR(M13/H13,"")))</f>
         <v/>
       </c>
@@ -13137,7 +13143,7 @@
         <f>IF(A14="","",IF(L14="Prime",H14*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H14))</f>
         <v/>
       </c>
-      <c r="N14" s="183">
+      <c r="N14" s="231">
         <f>IF(A14="","",IF(H14="","",IFERROR(M14/H14,"")))</f>
         <v/>
       </c>
@@ -13169,7 +13175,7 @@
         <f>IF(A15="","",IF(L15="Prime",H15*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H15))</f>
         <v/>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="230">
         <f>IF(A15="","",IF(H15="","",IFERROR(M15/H15,"")))</f>
         <v/>
       </c>
@@ -13201,7 +13207,7 @@
         <f>IF(A16="","",IF(L16="Prime",H16*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H16))</f>
         <v/>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="231">
         <f>IF(A16="","",IF(H16="","",IFERROR(M16/H16,"")))</f>
         <v/>
       </c>
@@ -13233,7 +13239,7 @@
         <f>IF(A17="","",IF(L17="Prime",H17*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H17))</f>
         <v/>
       </c>
-      <c r="N17" s="173">
+      <c r="N17" s="230">
         <f>IF(A17="","",IF(H17="","",IFERROR(M17/H17,"")))</f>
         <v/>
       </c>
@@ -13265,7 +13271,7 @@
         <f>IF(A18="","",IF(L18="Prime",H18*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H18))</f>
         <v/>
       </c>
-      <c r="N18" s="183">
+      <c r="N18" s="231">
         <f>IF(A18="","",IF(H18="","",IFERROR(M18/H18,"")))</f>
         <v/>
       </c>
@@ -13297,7 +13303,7 @@
         <f>IF(A19="","",IF(L19="Prime",H19*(1+Rates!$B$6)*(1+Rates!$B$7)*(1+Rates!$B$8),H19))</f>
         <v/>
       </c>
-      <c r="N19" s="173">
+      <c r="N19" s="230">
         <f>IF(A19="","",IF(H19="","",IFERROR(M19/H19,"")))</f>
         <v/>
       </c>
@@ -13391,7 +13397,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1" s="109">
       <c r="A3" s="114" t="inlineStr">
         <is>
@@ -13421,73 +13426,73 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="E4" s="187" t="n"/>
+      <c r="E4" s="232" t="n"/>
       <c r="F4" s="186" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="G4" s="187" t="n"/>
+      <c r="G4" s="232" t="n"/>
       <c r="H4" s="186" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="I4" s="187" t="n"/>
+      <c r="I4" s="232" t="n"/>
       <c r="J4" s="186" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="K4" s="187" t="n"/>
+      <c r="K4" s="232" t="n"/>
       <c r="L4" s="186" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="M4" s="187" t="n"/>
+      <c r="M4" s="232" t="n"/>
       <c r="N4" s="186" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="O4" s="187" t="n"/>
+      <c r="O4" s="232" t="n"/>
       <c r="P4" s="186" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="Q4" s="187" t="n"/>
+      <c r="Q4" s="232" t="n"/>
       <c r="R4" s="186" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="S4" s="187" t="n"/>
+      <c r="S4" s="232" t="n"/>
       <c r="T4" s="186" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="U4" s="187" t="n"/>
+      <c r="U4" s="232" t="n"/>
       <c r="V4" s="186" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="W4" s="187" t="n"/>
+      <c r="W4" s="232" t="n"/>
       <c r="X4" s="186" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="Y4" s="187" t="n"/>
+      <c r="Y4" s="232" t="n"/>
       <c r="Z4" s="186" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="AA4" s="187" t="n"/>
+      <c r="AA4" s="232" t="n"/>
       <c r="AB4" s="126" t="inlineStr">
         <is>
           <t>Yearly
@@ -13502,9 +13507,9 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" s="109">
-      <c r="A5" s="188" t="n"/>
-      <c r="B5" s="188" t="n"/>
-      <c r="C5" s="188" t="n"/>
+      <c r="A5" s="233" t="n"/>
+      <c r="B5" s="233" t="n"/>
+      <c r="C5" s="233" t="n"/>
       <c r="D5" s="137" t="inlineStr">
         <is>
           <t>Planned
@@ -13649,8 +13654,8 @@
 Hrs</t>
         </is>
       </c>
-      <c r="AB5" s="188" t="n"/>
-      <c r="AC5" s="188" t="n"/>
+      <c r="AB5" s="233" t="n"/>
+      <c r="AC5" s="233" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="109">
       <c r="A6" s="128" t="n">
@@ -14235,7 +14240,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -14246,10 +14250,10 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0" password="B0B1"/>
   <mergeCells count="18">
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A3:AA3"/>
     <mergeCell ref="L4:M4"/>
@@ -14352,7 +14356,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="117" t="inlineStr">
         <is>
@@ -14406,97 +14409,97 @@
           <t>Jan</t>
         </is>
       </c>
-      <c r="I4" s="194" t="n"/>
-      <c r="J4" s="194" t="n"/>
-      <c r="K4" s="187" t="n"/>
+      <c r="I4" s="234" t="n"/>
+      <c r="J4" s="234" t="n"/>
+      <c r="K4" s="232" t="n"/>
       <c r="L4" s="186" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="M4" s="194" t="n"/>
-      <c r="N4" s="194" t="n"/>
-      <c r="O4" s="187" t="n"/>
+      <c r="M4" s="234" t="n"/>
+      <c r="N4" s="234" t="n"/>
+      <c r="O4" s="232" t="n"/>
       <c r="P4" s="186" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="Q4" s="194" t="n"/>
-      <c r="R4" s="194" t="n"/>
-      <c r="S4" s="187" t="n"/>
+      <c r="Q4" s="234" t="n"/>
+      <c r="R4" s="234" t="n"/>
+      <c r="S4" s="232" t="n"/>
       <c r="T4" s="186" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="U4" s="194" t="n"/>
-      <c r="V4" s="194" t="n"/>
-      <c r="W4" s="187" t="n"/>
+      <c r="U4" s="234" t="n"/>
+      <c r="V4" s="234" t="n"/>
+      <c r="W4" s="232" t="n"/>
       <c r="X4" s="186" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="Y4" s="194" t="n"/>
-      <c r="Z4" s="194" t="n"/>
-      <c r="AA4" s="187" t="n"/>
+      <c r="Y4" s="234" t="n"/>
+      <c r="Z4" s="234" t="n"/>
+      <c r="AA4" s="232" t="n"/>
       <c r="AB4" s="186" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="AC4" s="194" t="n"/>
-      <c r="AD4" s="194" t="n"/>
-      <c r="AE4" s="187" t="n"/>
+      <c r="AC4" s="234" t="n"/>
+      <c r="AD4" s="234" t="n"/>
+      <c r="AE4" s="232" t="n"/>
       <c r="AF4" s="186" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="AG4" s="194" t="n"/>
-      <c r="AH4" s="194" t="n"/>
-      <c r="AI4" s="187" t="n"/>
+      <c r="AG4" s="234" t="n"/>
+      <c r="AH4" s="234" t="n"/>
+      <c r="AI4" s="232" t="n"/>
       <c r="AJ4" s="186" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="AK4" s="194" t="n"/>
-      <c r="AL4" s="194" t="n"/>
-      <c r="AM4" s="187" t="n"/>
+      <c r="AK4" s="234" t="n"/>
+      <c r="AL4" s="234" t="n"/>
+      <c r="AM4" s="232" t="n"/>
       <c r="AN4" s="186" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="AO4" s="194" t="n"/>
-      <c r="AP4" s="194" t="n"/>
-      <c r="AQ4" s="187" t="n"/>
+      <c r="AO4" s="234" t="n"/>
+      <c r="AP4" s="234" t="n"/>
+      <c r="AQ4" s="232" t="n"/>
       <c r="AR4" s="186" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="AS4" s="194" t="n"/>
-      <c r="AT4" s="194" t="n"/>
-      <c r="AU4" s="187" t="n"/>
+      <c r="AS4" s="234" t="n"/>
+      <c r="AT4" s="234" t="n"/>
+      <c r="AU4" s="232" t="n"/>
       <c r="AV4" s="186" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="AW4" s="194" t="n"/>
-      <c r="AX4" s="194" t="n"/>
-      <c r="AY4" s="187" t="n"/>
+      <c r="AW4" s="234" t="n"/>
+      <c r="AX4" s="234" t="n"/>
+      <c r="AY4" s="232" t="n"/>
       <c r="AZ4" s="186" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="BA4" s="194" t="n"/>
-      <c r="BB4" s="194" t="n"/>
-      <c r="BC4" s="187" t="n"/>
+      <c r="BA4" s="234" t="n"/>
+      <c r="BB4" s="234" t="n"/>
+      <c r="BC4" s="232" t="n"/>
       <c r="BD4" s="126" t="inlineStr">
         <is>
           <t>Yearly Max
@@ -14523,13 +14526,13 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" s="109">
-      <c r="A5" s="188" t="n"/>
-      <c r="B5" s="188" t="n"/>
-      <c r="C5" s="188" t="n"/>
-      <c r="D5" s="188" t="n"/>
-      <c r="E5" s="188" t="n"/>
-      <c r="F5" s="188" t="n"/>
-      <c r="G5" s="188" t="n"/>
+      <c r="A5" s="233" t="n"/>
+      <c r="B5" s="233" t="n"/>
+      <c r="C5" s="233" t="n"/>
+      <c r="D5" s="233" t="n"/>
+      <c r="E5" s="233" t="n"/>
+      <c r="F5" s="233" t="n"/>
+      <c r="G5" s="233" t="n"/>
       <c r="H5" s="137" t="inlineStr">
         <is>
           <t>Max
@@ -14818,10 +14821,10 @@
 $</t>
         </is>
       </c>
-      <c r="BD5" s="188" t="n"/>
-      <c r="BE5" s="188" t="n"/>
-      <c r="BF5" s="188" t="n"/>
-      <c r="BG5" s="188" t="n"/>
+      <c r="BD5" s="233" t="n"/>
+      <c r="BE5" s="233" t="n"/>
+      <c r="BF5" s="233" t="n"/>
+      <c r="BG5" s="233" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="109">
       <c r="A6" s="128" t="n">
@@ -17829,7 +17832,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="123" t="inlineStr">
         <is>
@@ -18389,7 +18391,6 @@
         <v/>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="117" t="inlineStr">
         <is>
@@ -18397,7 +18398,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -18420,9 +18420,9 @@
     <mergeCell ref="P4:S4"/>
     <mergeCell ref="H4:K4"/>
     <mergeCell ref="BD4:BD5"/>
+    <mergeCell ref="T4:W4"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="T4:W4"/>
     <mergeCell ref="AB4:AE4"/>
     <mergeCell ref="AN4:AQ4"/>
     <mergeCell ref="AF4:AI4"/>
@@ -18557,7 +18557,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -18909,7 +18908,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -19203,7 +19201,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>
@@ -19260,7 +19257,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="109">
       <c r="A3" s="123" t="inlineStr">
         <is>
@@ -19612,7 +19608,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="123" t="inlineStr">
         <is>
@@ -19906,7 +19901,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="117">
         <f>"Acqlerate  ·  DoD Acquisition Training  ·  acqlerate.com"&amp;IF(_License!$B$2="","","  ·  Licensed to: "&amp;_License!$B$2)</f>

--- a/client/public/examples/cost-and-burn-rate-tracker.xlsx
+++ b/client/public/examples/cost-and-burn-rate-tracker.xlsx
@@ -2799,10 +2799,23 @@
       <c r="A37" s="113" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="109">
-      <c r="A38" s="113" t="n"/>
+      <c r="A38" s="115" t="inlineStr">
+        <is>
+          <t>Key terms</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="109">
-      <c r="A39" s="113" t="n"/>
+      <c r="A39" s="116" t="inlineStr">
+        <is>
+          <t>TOA</t>
+        </is>
+      </c>
+      <c r="B39" s="114" t="inlineStr">
+        <is>
+          <t>Total Obligated Amount (Current Funding). The total dollar amount funded on this contract or task order right now. It comes from the CONTRACT TOTAL row on the Projects tab, and the whole Dashboard (burn rate, % spent, months to exhaustion) is calculated against it.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="109">
       <c r="A40" s="113" t="n"/>
@@ -11467,7 +11480,7 @@
     <row r="8" ht="15" customHeight="1" s="109">
       <c r="A8" s="118" t="inlineStr">
         <is>
-          <t>Current TOA (from Projects tab)</t>
+          <t>Current TOA (Current Funding)</t>
         </is>
       </c>
       <c r="C8" s="146">
